--- a/词汇表.xlsx
+++ b/词汇表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="367">
   <si>
     <t>玩家词汇 · 大白话对照表（v2.8.14 界面口径）</t>
   </si>
@@ -48,7 +48,7 @@
     <t>一 棋盘与数字：30 条</t>
   </si>
   <si>
-    <t>二 行动按钮与提示：37 条</t>
+    <t>二 行动按钮与提示：38 条</t>
   </si>
   <si>
     <t>三 抽卡与开局：21 条</t>
@@ -60,7 +60,7 @@
     <t>五 结算录像日志：9 条</t>
   </si>
   <si>
-    <t>六 图鉴设置开发者：17 条</t>
+    <t>六 图鉴设置开发者：18 条</t>
   </si>
   <si>
     <t>七 界面里没有的词：8 条</t>
@@ -393,19 +393,19 @@
     <t>⏭️结束回合</t>
   </si>
   <si>
-    <t>我这回合到此为止。</t>
+    <t>我这回合到此为止。问话窗正开着时再点它＝等于「都不发动」，不会绕过窗。</t>
   </si>
   <si>
     <t>🌙 回合结束询问 · 是否发动将领技能？</t>
   </si>
   <si>
-    <t>回合收尾时问你一句：这些"回合结束时"技能要不要现在用。</t>
-  </si>
-  <si>
-    <t>⏭️ 跳过并结束回合</t>
-  </si>
-  <si>
-    <t>一个都不发动，直接收。</t>
+    <t>回合收尾时问你一句：这些"回合结束时"技能要不要现在用。问不问、列不列不能发动的，由对局设置里的「技能提示」两档决定（见 §六）。</t>
+  </si>
+  <si>
+    <t>🚫 都不发动</t>
+  </si>
+  <si>
+    <t>一个也不发动，直接结束本回合——这扇问话窗里唯一的出口（原先那个「⏭️ 跳过并结束回合（旧说法，已作废）」按钮已按 2.8.17 的裁决合并进来，只剩这一句）。</t>
   </si>
   <si>
     <t>⏳ 反应窗口开启 · 等待通过</t>
@@ -444,6 +444,12 @@
     <t>这个分支此刻不能选，原因写在冒号后面。</t>
   </si>
   <si>
+    <t>✕ {将名}【{技能名}】（本回合已发动过 / 不满足发动门槛：…）</t>
+  </si>
+  <si>
+    <t>「完整」档才出现的灰条：它只是告诉你为什么现在不能用，点它没有任何反应，也不算技能被拒绝——能不能发动从来由战场决定，不由这扇窗决定。</t>
+  </si>
+  <si>
     <t>⚡ {将名}【{技能名}】</t>
   </si>
   <si>
@@ -916,6 +922,12 @@
   </si>
   <si>
     <t>开着＝每次回合结束自动存一遍当前对局。</t>
+  </si>
+  <si>
+    <t>技能提示＝智能 / 完整（对局设置，2.8.17 起）</t>
+  </si>
+  <si>
+    <t>回合收尾时要不要停下来问你的档位。智能（默认）＝确实有能发动的才问，不能发动的不列；完整＝只要场上有"回合结束时"技能就问，暂时不能发动的也列出来并写明原因。两档都不改变技能本身能不能发动，也不影响录像。</t>
   </si>
   <si>
     <t>你以为有的词</t>
@@ -1981,7 +1993,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -2404,6 +2416,17 @@
         <v>152</v>
       </c>
       <c r="C38" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2436,10 +2459,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -2447,10 +2470,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -2458,21 +2481,21 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -2480,10 +2503,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -2491,10 +2514,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -2502,10 +2525,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -2513,10 +2536,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -2524,10 +2547,10 @@
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -2535,10 +2558,10 @@
     </row>
     <row r="11" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>1</v>
@@ -2546,10 +2569,10 @@
     </row>
     <row r="12" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>1</v>
@@ -2557,10 +2580,10 @@
     </row>
     <row r="13" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>1</v>
@@ -2568,10 +2591,10 @@
     </row>
     <row r="14" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>1</v>
@@ -2579,10 +2602,10 @@
     </row>
     <row r="15" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>1</v>
@@ -2590,10 +2613,10 @@
     </row>
     <row r="16" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>1</v>
@@ -2601,10 +2624,10 @@
     </row>
     <row r="17" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>1</v>
@@ -2612,10 +2635,10 @@
     </row>
     <row r="18" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>1</v>
@@ -2623,10 +2646,10 @@
     </row>
     <row r="19" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>1</v>
@@ -2634,10 +2657,10 @@
     </row>
     <row r="20" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>1</v>
@@ -2645,10 +2668,10 @@
     </row>
     <row r="21" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>1</v>
@@ -2656,10 +2679,10 @@
     </row>
     <row r="22" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>1</v>
@@ -2694,10 +2717,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -2705,10 +2728,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -2716,10 +2739,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -2727,10 +2750,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -2738,10 +2761,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -2749,10 +2772,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -2760,10 +2783,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -2771,10 +2794,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -2782,10 +2805,10 @@
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -2793,10 +2816,10 @@
     </row>
     <row r="11" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>1</v>
@@ -2804,10 +2827,10 @@
     </row>
     <row r="12" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>1</v>
@@ -2815,10 +2838,10 @@
     </row>
     <row r="13" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>1</v>
@@ -2826,10 +2849,10 @@
     </row>
     <row r="14" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>1</v>
@@ -2837,10 +2860,10 @@
     </row>
     <row r="15" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>1</v>
@@ -2848,10 +2871,10 @@
     </row>
     <row r="16" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>1</v>
@@ -2859,10 +2882,10 @@
     </row>
     <row r="17" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>1</v>
@@ -2870,10 +2893,10 @@
     </row>
     <row r="18" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>1</v>
@@ -2881,10 +2904,10 @@
     </row>
     <row r="19" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>1</v>
@@ -2892,10 +2915,10 @@
     </row>
     <row r="20" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>1</v>
@@ -2903,10 +2926,10 @@
     </row>
     <row r="21" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>1</v>
@@ -2914,10 +2937,10 @@
     </row>
     <row r="22" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>1</v>
@@ -2925,10 +2948,10 @@
     </row>
     <row r="23" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>1</v>
@@ -2936,10 +2959,10 @@
     </row>
     <row r="24" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>1</v>
@@ -2947,10 +2970,10 @@
     </row>
     <row r="25" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>1</v>
@@ -2958,10 +2981,10 @@
     </row>
     <row r="26" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>1</v>
@@ -2969,7 +2992,7 @@
     </row>
     <row r="28" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -3006,10 +3029,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3017,10 +3040,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3028,10 +3051,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3039,10 +3062,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3050,10 +3073,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3061,10 +3084,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3072,10 +3095,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3083,10 +3106,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3094,10 +3117,10 @@
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -3111,7 +3134,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -3132,10 +3155,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3143,10 +3166,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3154,10 +3177,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3165,10 +3188,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3176,10 +3199,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3187,10 +3210,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3198,10 +3221,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3209,10 +3232,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3220,10 +3243,10 @@
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -3231,10 +3254,10 @@
     </row>
     <row r="11" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>1</v>
@@ -3242,10 +3265,10 @@
     </row>
     <row r="12" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>1</v>
@@ -3253,10 +3276,10 @@
     </row>
     <row r="13" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>1</v>
@@ -3264,10 +3287,10 @@
     </row>
     <row r="14" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>1</v>
@@ -3275,10 +3298,10 @@
     </row>
     <row r="15" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>1</v>
@@ -3286,10 +3309,10 @@
     </row>
     <row r="16" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>1</v>
@@ -3297,10 +3320,10 @@
     </row>
     <row r="17" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>1</v>
@@ -3308,12 +3331,23 @@
     </row>
     <row r="18" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3335,10 +3369,10 @@
   <sheetData>
     <row r="1" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>18</v>
@@ -3346,10 +3380,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3357,10 +3391,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3368,10 +3402,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3379,10 +3413,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3390,10 +3424,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3401,10 +3435,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3412,10 +3446,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3423,10 +3457,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3451,50 +3485,50 @@
   <sheetData>
     <row r="1" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>1</v>
@@ -3502,16 +3536,16 @@
     </row>
     <row r="4" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>1</v>
@@ -3519,16 +3553,16 @@
     </row>
     <row r="5" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>1</v>
@@ -3536,16 +3570,16 @@
     </row>
     <row r="6" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>1</v>
@@ -3553,16 +3587,16 @@
     </row>
     <row r="7" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>1</v>
@@ -3570,16 +3604,16 @@
     </row>
     <row r="8" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>1</v>
@@ -3587,16 +3621,16 @@
     </row>
     <row r="9" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>1</v>
@@ -3604,16 +3638,16 @@
     </row>
     <row r="10" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>1</v>
@@ -3621,16 +3655,16 @@
     </row>
     <row r="11" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>1</v>

--- a/词汇表.xlsx
+++ b/词汇表.xlsx
@@ -19,9 +19,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="367">
-  <si>
-    <t>玩家词汇 · 大白话对照表（v2.8.14 界面口径）</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="376">
+  <si>
+    <t>玩家词汇 · 大白话对照表（v2.8.18 界面口径）</t>
   </si>
   <si>
     <t/>
@@ -36,7 +36,7 @@
     <t>· 出处：所有词条都对应到 文件:行号（仓库根＝Qoder/2.0）。规则类翻译另标了"定规则的代码在哪"，方便日后核对。</t>
   </si>
   <si>
-    <t>· 已知坑：界面有几处措辞跟真实规则对不上（护甲、营地/本营、装备卡、补给），我在翻译里写明"界面这么说、实际这么算"。</t>
+    <t>· 已知坑：第八节那十条"界面这么说、代码这么算"的冲突，第 1～8 条与第 10 条已经对齐（v2.8.14／v2.8.18），只有第 9 条（卡面徽章与"强制发动"到底管不管事）还等一份提案；已作废的旧写法在表里用 ~~删除线~~ 标出，投影进 Excel 时会渲染成"（旧说法，已作废）"。</t>
   </si>
   <si>
     <t>· 本轮之后如果界面改词，这张表要跟着改；它随 Git 走，别在别处另抄一份。</t>
@@ -117,19 +117,19 @@
     <t>抽牌堆</t>
   </si>
   <si>
-    <t>还没被抽走的牌摞。抽干了会把弃牌堆洗一洗接着用。定规则：core/eventProcessors/drawEvents.ts:144</t>
-  </si>
-  <si>
-    <t>卡牌池</t>
-  </si>
-  <si>
-    <t>抽卡窗口里对"抽牌堆"的另一个叫法。同一个东西两个名字。</t>
-  </si>
-  <si>
-    <t>牌堆</t>
-  </si>
-  <si>
-    <t>门槛短句、编辑器里对同一个牌摞的第三个叫法。抽牌堆／卡牌池／牌堆＝一样东西，别当成三个区域。</t>
+    <t>还没被抽走的牌摞。抽干了会把弃牌堆洗一洗接着用。全游戏只有这一个名字（顶栏、抽卡窗、门槛短句、编辑器都说它）。定规则：core/eventProcessors/drawEvents.ts:144</t>
+  </si>
+  <si>
+    <t>卡牌池（旧说法，已作废）</t>
+  </si>
+  <si>
+    <t>（旧说法，已作废）v2.8.18 前抽卡窗里对"抽牌堆"的另一个叫法。现在那里也写"抽牌堆"。</t>
+  </si>
+  <si>
+    <t>牌堆（旧说法，已作废）</t>
+  </si>
+  <si>
+    <t>（旧说法，已作废）v2.8.18 前门槛短句与编辑器里的第三个叫法，同一个 cardDeck。现在统一写"抽牌堆"；你手上的旧 Excel 里那句"牌堆≥5"照样读得懂，只是再导出时会写成"抽牌堆≥5"。只有"看牌堆顶""放回牌堆"这类复合词照旧——那里说的是牌摞的顶或底，不是第二个牌摞。</t>
   </si>
   <si>
     <t>弃牌堆</t>
@@ -153,7 +153,7 @@
     <t>营地</t>
   </si>
   <si>
-    <t>你自家那一格一格放将领的地盘（棋盘区域之一，将领先站在这儿）。注意：抽卡窗里写的"营地将失去1点体力"其实扣的是"本营"的血，这两个词在那句话里被混用了。定规则：action/resolvers/ResolveBaseLossResolver.ts:24</t>
+    <t>你自家那一格一格放将领的地盘（棋盘区域之一，将领先站在这儿）。它不流血：抽卡窗那句"本营将失去1点体力"扣的是上面那个"本营"，v2.8.18 已把这两个词分开写死了。定规则：action/resolvers/ResolveBaseLossResolver.ts:24</t>
   </si>
   <si>
     <t>前线</t>
@@ -183,7 +183,7 @@
     <t>护甲 🛡️</t>
   </si>
   <si>
-    <t>将领外面的缓冲层。关键：攒够 2 点护甲才抵消 1 点伤害，只有 1 点时它不挡刀、原样留着。定规则：core/armorDamage.ts:15</t>
+    <t>将领外面的缓冲层。关键：攒够 2 点护甲才抵消 1 点伤害，只有 1 点时它不挡刀、原样留着。定规则：core/armorDamage.ts:15。v2.8.18 起这句话也印在卡面那一格上（图鉴与操作条的"🛡️护甲"悬停提示），规则页也写明了。</t>
   </si>
   <si>
     <t>🛡️基础</t>
@@ -333,13 +333,13 @@
     <t>补给 💊</t>
   </si>
   <si>
-    <t>喂粮草回血：交几张牌＝回几点体力，但在敌方地盘要多烧 1 张且不回数（交 3 张回 2 点）。封顶不能补过体力上限。定规则：action/resolvers/SupplyResolver.ts:65</t>
-  </si>
-  <si>
-    <t>敌方区域：补给额外消耗1张手牌</t>
-  </si>
-  <si>
-    <t>你站在抢来的地盘上，做什么都多花一张。</t>
+    <t>喂粮草回血：交几张牌＝回几点体力，但在敌方地盘要多烧 1 张且不回数（交 3 张回 2 点）。封顶补到体力上限为止、多交的牌也不退；每个回合各将领可补一次（不是全局一局一次）。定规则：action/resolvers/SupplyResolver.ts:65、清零见 core/eventProcessors/turnEvents.ts:32</t>
+  </si>
+  <si>
+    <t>⚠️ 敌方区域：补给多烧 1 张手牌，这张只算代价、不算回复（交 3 张只回 2 点）</t>
+  </si>
+  <si>
+    <t>你站在抢来的地盘上，做什么都多花一张。（v2.8.18 把这行的算术写明了；以前只写"额外消耗1张手牌"，没说那张算不算回数。）</t>
   </si>
   <si>
     <t>体力已满，无需补给</t>
@@ -435,7 +435,7 @@
     <t>🚪 发动门槛 / 不满足：手牌≤2</t>
   </si>
   <si>
-    <t>技能的"条件"。界面直接把条件原话印出来（例：手牌≤2，牌堆≥5），意思是"此刻手牌不到 2 张才让发动"。</t>
+    <t>技能的"条件"。界面直接把条件原话印出来（例：手牌≤2，抽牌堆≥5），意思是"此刻手牌不到 2 张才让发动"。</t>
   </si>
   <si>
     <t>不满足发动门槛</t>
@@ -516,31 +516,31 @@
     <t>自由分配抽取来源</t>
   </si>
   <si>
-    <t>你可以指定这次摸的几张里，几张从"将领池"来、几张从"卡牌池"来。</t>
-  </si>
-  <si>
-    <t>当前玩家将领池剩余 / ← 全部卡牌池 / 全部将领池 →</t>
+    <t>你可以指定这次摸的几张里，几张从"将领池"来、几张从"抽牌堆"来。</t>
+  </si>
+  <si>
+    <t>当前玩家将领池剩余 / ← 全部抽牌堆 / 全部将领池 →</t>
   </si>
   <si>
     <t>上面那件事的快捷滑条：两头分别一键全给牌摞或全给将池。</t>
   </si>
   <si>
-    <t>将领池已空，全部从卡牌池抽取</t>
+    <t>将领池已空，全部从抽牌堆抽取</t>
   </si>
   <si>
     <t>没将可摸了，只能摸牌摞。</t>
   </si>
   <si>
-    <t>本次抽卡后将领池将被抽空；将领池为空时，回合开始时营地将失去1点体力</t>
+    <t>本次抽卡后将领池将被抽空；将领池为空时，回合开始时本营将失去1点体力</t>
   </si>
   <si>
     <t>提醒：把将池抽光之后，以后每回合开头本营先掉 1 点血，再摸牌。</t>
   </si>
   <si>
-    <t>🏯💥 营地受到伤害 / 结算失去体力 / 先结算营地失去体力，若存活再进行抽卡</t>
-  </si>
-  <si>
-    <t>就是上面那条扣血，要你按一下才落地（扣的是本营的血，不是营地格）。</t>
+    <t>🏯💥 本营受到伤害 / 结算失去体力 / 先结算本营失去体力，若存活再进行抽卡</t>
+  </si>
+  <si>
+    <t>就是上面那条扣血，要你按一下才落地。v2.8.18 前这几行写的是"营地"，其实扣的一直是本营的血——两个词现在分开了。</t>
   </si>
   <si>
     <t>🏯 创建房间 / 房间名称 / 游戏人数</t>
@@ -714,13 +714,13 @@
     <t>拆掉装备</t>
   </si>
   <si>
-    <t>把目标身上的军备扒下来扔进弃牌堆，护甲跟着少；不减体力。</t>
-  </si>
-  <si>
-    <t>装备卡</t>
-  </si>
-  <si>
-    <t>技能描述里的老说法，界面牌种其实叫 军备。游戏里没有独立的"装备区"，军备是叠甲用的消耗牌。</t>
+    <t>把目标身上的军备扒下来扔进弃牌堆，护甲跟着少；不减体力。编辑器效果栏里这个词的"装备"是动词，所以照旧（v2.8.18 只统一了"装备卡／装备牌"这个并不存在的牌种名）。</t>
+  </si>
+  <si>
+    <t>装备卡 / 装备牌（旧说法，已作废）</t>
+  </si>
+  <si>
+    <t>（旧说法，已作废）v2.8.18 起三条官方技能描述（强袭、枭姬、崩坏）与触发细分词统一写成 军备卡／军备牌。游戏里没有独立的"装备区"，军备是叠甲用的消耗牌。你手上的旧 Excel 里那格"失去手牌时→失去装备牌"照样读得懂，只是再导出会写成"失去军备牌"。</t>
   </si>
   <si>
     <t>看牌堆顶</t>
@@ -756,13 +756,13 @@
     <t>击破 / 出局 / 阵亡 / 获得胜利</t>
   </si>
   <si>
-    <t>同一件事的不同说法：将领或本营被打到底＝那家出局；横幅写"X势力击破"，日志写"阵亡"，结算写"获得胜利"。游戏里没有"淘汰"这个词。</t>
-  </si>
-  <si>
-    <t>BASE DESTROYED</t>
-  </si>
-  <si>
-    <t>中文横幅上方残留的一行英文小字，意思是"本营被打掉了"。属于该翻没翻的漏网词。</t>
+    <t>同一件事的不同说法：将领或本营被打到底＝那家出局；横幅写"X势力击破"（上方那行小字「本营击破」），日志写"阵亡"，结算写"获得胜利"。游戏里没有"淘汰"这个词。</t>
+  </si>
+  <si>
+    <t>BASE DESTROYED（旧说法，已作废）</t>
+  </si>
+  <si>
+    <t>（旧说法，已作废）击破横幅上方那行残留的英文小字，v2.8.18 已翻成「本营击破」。</t>
   </si>
   <si>
     <t>本节末尾必须说清的一件事：五个"××技"徽章和"强制发动"这一列，在当前版本里都还没接进对局结算。证据：编译环节 skills/skillCompiler.ts 与触发桥 skills/SkillTriggerBridge.ts 里没有任何一处读 tag 或 forced（这两个字段只在编辑器与存档里来回搬：store/gameStoreEditorActions.ts:307）。所以现在决定一条技能"什么时候响、响不响、响几次"的，只有：触发时机（含细分）＋ 发动门槛 ＋ 那条"每回合限一次"的账。徽章是给玩家看的分类，不是开关。</t>
@@ -888,10 +888,10 @@
     <t>跑几局、随机种子（同种子必复现）、单局最多走多少步（防僵持）。</t>
   </si>
   <si>
-    <t>高级设置（将池 / 牌堆 / 技能注入）</t>
-  </si>
-  <si>
-    <t>每人发几个将、牌摞多厚、多大比例把技能塞进对局。</t>
+    <t>高级设置（将池 / 抽牌堆 / 技能注入）</t>
+  </si>
+  <si>
+    <t>每人发几个将、牌摞多厚、技能注入比例。技能注入默认 0＝不给将池塞那种"演練・"开头的演练技能（v2.8.16 起按您的裁决关掉的），想要场景才调高；命令行同理（--skill 0.35）。</t>
   </si>
   <si>
     <t>身份锁旁路开关 / 身份白名单</t>
@@ -1020,34 +1020,43 @@
     <t>扣的是谁的血</t>
   </si>
   <si>
-    <t>抽卡窗："营地将失去1点体力"（UnifiedDraw.tsx:220）</t>
+    <t>抽卡窗："营地将失去1点体力"（UnifiedDraw.tsx:220）（旧说法，已作废） 已改为"本营"（v2.8.18）</t>
   </si>
   <si>
     <t>扣的是本营血量（ResolveBaseLossResolver.ts:24 发 BASE_DAMAGE）；"营地"在棋盘上另有所指（放将领的区域）</t>
   </si>
   <si>
+    <t>✅ 您 2026-09-29 说"这些能开工就开"，按代码为准改了界面措辞：抽卡窗四行（标题、两行说明、滑条下的提醒）现在都写"本营"</t>
+  </si>
+  <si>
     <t>3</t>
   </si>
   <si>
     <t>护甲挡刀比例</t>
   </si>
   <si>
-    <t>只写"护甲"数值，玩家自然以为是 1 挡 1</t>
+    <t>只写"护甲"数值，玩家自然以为是 1 挡 1（旧说法，已作废） 规则页与两处卡面提示已写明（v2.8.18）</t>
   </si>
   <si>
     <t>2 点护甲才抵消 1 点伤害，单数护甲不挡刀（core/armorDamage.ts:15）</t>
   </si>
   <si>
+    <t>✅ 您的原话：「护甲：现在是 2 点护甲才挡 1 点伤害（单数不挡），是这样」——按这句把规则页"补给与军备"改写明白，操作条「🛡️护甲」那一格与图鉴同一格加了悬停提示</t>
+  </si>
+  <si>
     <t>4</t>
   </si>
   <si>
     <t>补给回几点</t>
   </si>
   <si>
-    <t>按钮只写"补给"</t>
-  </si>
-  <si>
-    <t>敌方地盘多烧 1 张且不回数：交 3 张只回 2 点（SupplyResolver.ts:65）</t>
+    <t>按钮只写"补给"（旧说法，已作废） 规则页、敌方区域提醒条、选牌条三处已写清算术（v2.8.18）</t>
+  </si>
+  <si>
+    <t>敌方地盘多烧 1 张且不回数：交 3 张只回 2 点（SupplyResolver.ts:65），且封顶不超过体力上限、每回合每将领各可补给一次（不是全局一局一次）</t>
+  </si>
+  <si>
+    <t>✅ 与第 3 条同批改文案：规则页与场上那行黄字现在直接写「交 3 张只回 2 点」</t>
   </si>
   <si>
     <t>5</t>
@@ -1056,22 +1065,28 @@
     <t>装备 / 军备</t>
   </si>
   <si>
-    <t>技能描述写"拆掉目标的一张装备卡""失去装备牌"（generals.ts:322、generals.ts:124）</t>
+    <t>技能描述写"拆掉目标的一张装备卡""失去装备牌"（generals.ts:322、generals.ts:124）（旧说法，已作废） 已改（v2.8.18）</t>
   </si>
   <si>
     <t>牌种只有 粮草／材料／军备，没有"装备"这个牌种、也没有装备区（data/cards.ts:4）</t>
   </si>
   <si>
+    <t>✅ 您的原话：「"装备"这个词：把技能描述改成"军备"」。落地＝强袭／枭姬／崩坏三条描述＋触发细分词"失去军备牌"＋编辑器效果预览＋AI 操作日志那行（装备护甲（旧说法，已作废）→叠甲 …，军备N张，与"补给 …，用卡N张"同一个句式）；旧 Excel 里那格"失去装备牌"仍读得懂，只是再导出会写新词。没改的三处，理由：①编辑器效果类型名"拆掉装备"是类型名不是技能描述，您的裁决只圈了描述；②"剥离装备"是读入侧旧别名，只进不出；③源码注释里的"装备"不上界面</t>
+  </si>
+  <si>
     <t>6</t>
   </si>
   <si>
     <t>一个牌摞三个名字</t>
   </si>
   <si>
-    <t>顶栏"抽牌堆"／抽卡窗"卡牌池"／门槛与编辑器"牌堆"</t>
-  </si>
-  <si>
-    <t>同一个 cardDeck（GameBoard.tsx:475、UnifiedDraw.tsx:199、skillGateText.ts:28）</t>
+    <t>顶栏"抽牌堆"／抽卡窗"卡牌池"／门槛与编辑器"牌堆"（旧说法，已作废） 已统一为一个名字（v2.8.18）</t>
+  </si>
+  <si>
+    <t>同一个 cardDeck（GameBoard.tsx:475、UnifiedDraw.tsx:196、skillGateText.ts:26）</t>
+  </si>
+  <si>
+    <t>✅ 统一到抽牌堆：抽卡窗三处、门槛量名与其提示语、门槛录入框示例与帮助行、演练窗高级设置那三处现在都写"抽牌堆"。旧写法"牌堆≥5"照样读得懂（只进不出）。没改的两处，理由：①"看牌堆顶""放回牌堆"是复合词，说的是牌摞的顶／底，不是第二个牌摞；②"公共牌堆"改成了"公共抽牌堆"（演练窗搭池子时那个数字）</t>
   </si>
   <si>
     <t>7</t>
@@ -1080,24 +1095,30 @@
     <t>生命 vs 体力</t>
   </si>
   <si>
-    <t>规则页写"6 点生命""恢复将领生命"（Rules.tsx:41,44）</t>
+    <t>规则页写"6 点生命""恢复将领生命"（Rules.tsx:41,44）（旧说法，已作废） 已改（v2.8.18）</t>
   </si>
   <si>
     <t>界面与代码全用体力（currentHp/maxHp）</t>
   </si>
   <si>
+    <t>✅ 规则页两处"生命"已换成"体力"；全库源码里"生命"这个词现在 0 处</t>
+  </si>
+  <si>
     <t>8</t>
   </si>
   <si>
     <t>英文残留</t>
   </si>
   <si>
-    <t>击破横幅上方还挂着一行 BASE DESTROYED（GameBoard.tsx:566）</t>
+    <t>击破横幅上方还挂着一行 BASE DESTROYED（GameBoard.tsx:566）（旧说法，已作废） 已翻（v2.8.18）</t>
   </si>
   <si>
     <t>无</t>
   </si>
   <si>
+    <t>✅ 那行小字改成「本营击破」。没删掉它：横幅的版式靠这一行起头，删了会塌一行空白</t>
+  </si>
+  <si>
     <t>9</t>
   </si>
   <si>
@@ -1110,6 +1131,9 @@
     <t>编译器与触发桥一处都不读 tag/forced；只有触发时机＋门槛＋"每回合限一次"的账在起作用</t>
   </si>
   <si>
+    <t>⏳ 您 2026-09-29 说"开始真管事"——这一条要动结算，按老规矩我先交一份"每个徽章到底管什么"的短提案给您裁，提案点头前不动代码</t>
+  </si>
+  <si>
     <t>10</t>
   </si>
   <si>
@@ -1120,6 +1144,9 @@
   </si>
   <si>
     <t>其它类型填 0 会被按没填处理并在导入总结里点名（摸牌/伤害那几类引擎会当 1；看牌堆顶的 0 会真的看 0 张）。v2.8.13 已按此收口：skills/skillExcelFormat.ts</t>
+  </si>
+  <si>
+    <t>✅ 已按您给的口径落地（v2.8.13 录入面按类型表达"全部"＋v2.8.14 导入总结点名），本轮无改动</t>
   </si>
 </sst>
 </file>
@@ -3531,143 +3558,143 @@
         <v>334</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1</v>
+        <v>335</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>1</v>
+        <v>340</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>1</v>
+        <v>345</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>1</v>
+        <v>350</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>1</v>
+        <v>355</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>1</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>1</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>1</v>
+        <v>370</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>1</v>
+        <v>375</v>
       </c>
     </row>
   </sheetData>

--- a/词汇表.xlsx
+++ b/词汇表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="378">
   <si>
     <t>玩家词汇 · 大白话对照表（v2.8.18 界面口径）</t>
   </si>
@@ -54,7 +54,7 @@
     <t>三 抽卡与开局：21 条</t>
   </si>
   <si>
-    <t>四 技能相关词：25 条</t>
+    <t>四 技能相关词：26 条</t>
   </si>
   <si>
     <t>五 结算录像日志：9 条</t>
@@ -618,25 +618,31 @@
     <t>锁定技</t>
   </si>
   <si>
-    <t>给人看的分类徽章（"这技能不用你选，到点就响"）。当前运行时不看这个徽章——见本节末尾的说明。</t>
+    <t>这枚技能不能被无效、也不能被改变。它不是"到点就自动响"——自动不自动是下面「强制发动」那一格管的事，两者互不相关。</t>
   </si>
   <si>
     <t>限定技</t>
   </si>
   <si>
-    <t>分类徽章（"这技能有次数额度，用完就没了"）。运行时不看它；引擎现在只有一本"每回合限一次"的账（core/GameState.ts:66＋action/resolvers/TurnEndSkillResolver.ts），"一局一次"这类更狠的额度还没有实现。</t>
+    <t>分类徽章（"一局之内的次数额度，用完就没了"）。运行时不看它；引擎现在只有一本"每回合限一次"的账（core/GameState.ts:66＋action/resolvers/TurnEndSkillResolver.ts），"一局一次"这类更狠的额度还没有实现。</t>
   </si>
   <si>
     <t>登场技</t>
   </si>
   <si>
-    <t>分类徽章（"上场那一刻响"）。真正决定响不响的是触发时机选了"将领登场时"，不是这个徽章。</t>
+    <t>分类徽章（"上场那一刻响"）。真正决定响不响的是触发时机选了"将领登场时"，不是这个徽章。导入时会核对这两处说的是不是同一件事，对不上就在导入总结里点名。</t>
   </si>
   <si>
     <t>遗计技</t>
   </si>
   <si>
-    <t>分类徽章（"临死/离场时留给你的东西"）。同上，实际靠触发时机"自身被击杀时"。</t>
+    <t>分类徽章（"被击杀那一刻留给你的东西"）。同上，实际靠触发时机"自身被击杀时"。</t>
+  </si>
+  <si>
+    <t>徽章可以同时挂几枚</t>
+  </si>
+  <si>
+    <t>一枚技能不必只戴一枚：闭月＝锁定技＋遗计技（既不能被无效、又响在被击杀那一刻）。编辑器里是一排可点亮的徽章，Excel 的「技能标签」格里用顿号分开写；图鉴、卡面、对局里几枚都会显示出来。不认识的徽章名会被点名退回，不会静悄悄丢掉。</t>
   </si>
   <si>
     <t>觉醒技</t>
@@ -648,7 +654,7 @@
     <t>强制发动</t>
   </si>
   <si>
-    <t>编辑器里的开关（ Excel 也有这一列）。目前只被存下来，运行时没有任何地方读它（编译器和触发桥都不看这个字段）——开或关，对局里的表现一模一样。要不要让它真的起作用，得先定语义。</t>
+    <t>编辑器里的开关（Excel 也有这一列）：满足触发条件与代价后直接响／直接适用效果，不用玩家点头。它跟锁定技不是一件事，跟"数值变化／持续生效"也不绑定，三者可以任意组合。目前只被存下来，运行时没有任何地方读它（编译器和触发桥都不看这个字段）——开或关，对局里的表现一模一样。</t>
   </si>
   <si>
     <t>触发时机</t>
@@ -765,7 +771,7 @@
     <t>（旧说法，已作废）击破横幅上方那行残留的英文小字，v2.8.18 已翻成「本营击破」。</t>
   </si>
   <si>
-    <t>本节末尾必须说清的一件事：五个"××技"徽章和"强制发动"这一列，在当前版本里都还没接进对局结算。证据：编译环节 skills/skillCompiler.ts 与触发桥 skills/SkillTriggerBridge.ts 里没有任何一处读 tag 或 forced（这两个字段只在编辑器与存档里来回搬：store/gameStoreEditorActions.ts:307）。所以现在决定一条技能"什么时候响、响不响、响几次"的，只有：触发时机（含细分）＋ 发动门槛 ＋ 那条"每回合限一次"的账。徽章是给玩家看的分类，不是开关。</t>
+    <t>本节末尾必须说清的一件事：五个"××技"徽章和"强制发动"这一列，v2.8.19 起读得到、写得出、显示得出、还能核对（一枚技能可挂几枚；徽章与触发时机对不上会在编辑器与导入总结里点名），但都还没接进对局结算。证据：编译环节 skills/skillCompiler.ts 与触发桥 skills/SkillTriggerBridge.ts 里没有任何一处读 tags/tag 或 forced（这些字段只在编辑器与存档里来回搬：store/gameStoreEditorActions.ts:307）。所以现在决定一条技能"什么时候响、响不响、响几次"的，仍然只有：触发时机（含细分）＋ 发动门槛 ＋ 那条"每回合限一次"的账。徽章是给玩家看的分类，不是开关；读写口径全库只有一份，在 domain/skillTags.ts。</t>
   </si>
   <si>
     <t>游戏结束 / 对局结束</t>
@@ -1125,13 +1131,13 @@
     <t>徽章与开关不落地</t>
   </si>
   <si>
-    <t>卡面印着 锁定技／限定技／登场技／遗计技／觉醒技，编辑器有"强制发动"列</t>
-  </si>
-  <si>
-    <t>编译器与触发桥一处都不读 tag/forced；只有触发时机＋门槛＋"每回合限一次"的账在起作用</t>
-  </si>
-  <si>
-    <t>⏳ 您 2026-09-29 说"开始真管事"——这一条要动结算，按老规矩我先交一份"每个徽章到底管什么"的短提案给您裁，提案点头前不动代码</t>
+    <t>编辑器只有单枚标签下拉、卡面只印一枚（旧说法，已作废） 已多枚化（v2.8.19：编辑器一排徽章可同时点亮几枚，Excel「技能标签」格用顿号分开写，图鉴／卡面／对局几枚都显示）</t>
+  </si>
+  <si>
+    <t>半落地：词汇、录入、显示、核对四处已按您 2026-09-30 的更正对齐，读写口径全库只有一份（domain/skillTags.ts）；结算那半处都不读 tags/forced——锁定技的"不能被无效、不能被改变"、限定技的"一局一次"、强制发动的"不用玩家点头"都还没进引擎</t>
+  </si>
+  <si>
+    <t>⏳ 您的更正口径已逐字落进第四节：「锁定技实际上是指无法被无效和改变的技能，而强制发动则是指某些技能在满足触发条件和代价后会强制发动/直接适用其效果，两者和数值变化+永续生效的组合一样，不是强关联」；样本＝闭月同时挂 锁定技＋遗计技。结算那一刀要改引擎、会换锚（B12/B11），等您口令再开</t>
   </si>
   <si>
     <t>10</t>
@@ -2723,7 +2729,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -3017,16 +3023,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
+    <row r="27" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
+      <c r="B27" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A29:C29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3056,10 +3073,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3067,10 +3084,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3078,10 +3095,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3089,10 +3106,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3100,10 +3117,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3111,10 +3128,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3122,10 +3139,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3133,10 +3150,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3144,10 +3161,10 @@
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -3182,10 +3199,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3193,10 +3210,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3204,10 +3221,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3215,10 +3232,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3226,10 +3243,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3237,10 +3254,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3248,10 +3265,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3259,10 +3276,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3270,10 +3287,10 @@
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -3281,10 +3298,10 @@
     </row>
     <row r="11" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>1</v>
@@ -3292,10 +3309,10 @@
     </row>
     <row r="12" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>1</v>
@@ -3303,10 +3320,10 @@
     </row>
     <row r="13" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>1</v>
@@ -3314,10 +3331,10 @@
     </row>
     <row r="14" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>1</v>
@@ -3325,10 +3342,10 @@
     </row>
     <row r="15" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>1</v>
@@ -3336,10 +3353,10 @@
     </row>
     <row r="16" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>1</v>
@@ -3347,10 +3364,10 @@
     </row>
     <row r="17" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>1</v>
@@ -3358,10 +3375,10 @@
     </row>
     <row r="18" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>1</v>
@@ -3369,10 +3386,10 @@
     </row>
     <row r="19" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>1</v>
@@ -3396,10 +3413,10 @@
   <sheetData>
     <row r="1" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>18</v>
@@ -3407,10 +3424,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3418,10 +3435,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3429,10 +3446,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3440,10 +3457,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3451,10 +3468,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3462,10 +3479,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3473,10 +3490,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3484,10 +3501,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3512,189 +3529,189 @@
   <sheetData>
     <row r="1" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>

--- a/词汇表.xlsx
+++ b/词汇表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="380">
   <si>
     <t>玩家词汇 · 大白话对照表（v2.8.18 界面口径）</t>
   </si>
@@ -54,7 +54,7 @@
     <t>三 抽卡与开局：21 条</t>
   </si>
   <si>
-    <t>四 技能相关词：26 条</t>
+    <t>四 技能相关词：27 条</t>
   </si>
   <si>
     <t>五 结算录像日志：9 条</t>
@@ -714,7 +714,7 @@
     <t>整只手（全部）／数值 0</t>
   </si>
   <si>
-    <t>"全都要"的写法：只有 弃牌／发放／放回牌堆 这三类效果认它。其它类型写 0 会被当作没填（摸牌／伤害那几类引擎会当成 1；看牌堆顶更特殊，它的 0 会真的"一张也不看"）。</t>
+    <t>"全都要"的写法：只有 弃牌／发放／放回牌堆 这三类效果认它。其它类型写 0 会被当作没填（摸牌／伤害那几类引擎会当成 1；看牌堆顶更特殊，它的 0 会真的"一张也不看"）。决斗是另一类：它根本没有数量可填（轮数由规则定死＝双方各三轮、最多六次），那一格填了也会被点名退回、按没填处理。</t>
   </si>
   <si>
     <t>拆掉装备</t>
@@ -747,6 +747,12 @@
     <t>把你的牌交给别人（给别人手牌）。</t>
   </si>
   <si>
+    <t>决斗（技能效果，2.8.20 起）</t>
+  </si>
+  <si>
+    <t>自己的将领和目标的将领轮流各出手三次（最多六次）互砍：每一轮用当下出手那一方的攻击力，护甲照旧"2 点挡 1 点"；伤害算技能伤害、不消耗手牌；谁先体力归零就当场停，剩下的轮次不补。决斗中阵亡同样算"被击破"，由失去这名将领的一方补抽 1 张。只能由技能发起——棋盘上没有"决斗"按钮。决斗进行中不会再唤起"受到伤害后／成为目标时"那一类被动技能（唤起它们的只有发起决斗的那次攻击）。</t>
+  </si>
+  <si>
     <t>效果模式：全部生效 / 选择其一</t>
   </si>
   <si>
@@ -951,7 +957,7 @@
     <t>决斗</t>
   </si>
   <si>
-    <t>界面上没有决斗这张牌、也还没有这个流程。规则您早就给全了（PROJECT_ARCH_MAP.md §H5 第 6 条七条口径 ＋ 2026-09-29 四句补充：只能由技能发起、不消耗手牌、死了也算击破、伤害算技能伤害）⇒ 等实装，任务 #30。</t>
+    <t>牌还是没有（本作只有 粮草／材料／军备 三种牌），流程已经有了：2.8.20 起技能效果类型里多了「决斗」，见上面 §四 那一行。仍然没有"玩家自己发起决斗"的按钮——它只能由技能带来。</t>
   </si>
   <si>
     <t>顺手牵羊 / 过河拆桥 / 借刀杀人 / 无中生有</t>
@@ -2729,7 +2735,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -3034,16 +3040,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
+    <row r="28" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
+      <c r="B28" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3073,10 +3090,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3084,10 +3101,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3095,10 +3112,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3106,10 +3123,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3117,10 +3134,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3128,10 +3145,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3139,10 +3156,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3150,10 +3167,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3161,10 +3178,10 @@
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -3199,10 +3216,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3210,10 +3227,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3221,10 +3238,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3232,10 +3249,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3243,10 +3260,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3254,10 +3271,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3265,10 +3282,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3276,10 +3293,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3287,10 +3304,10 @@
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -3298,10 +3315,10 @@
     </row>
     <row r="11" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>1</v>
@@ -3309,10 +3326,10 @@
     </row>
     <row r="12" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>1</v>
@@ -3320,10 +3337,10 @@
     </row>
     <row r="13" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>1</v>
@@ -3331,10 +3348,10 @@
     </row>
     <row r="14" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>1</v>
@@ -3342,10 +3359,10 @@
     </row>
     <row r="15" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>1</v>
@@ -3353,10 +3370,10 @@
     </row>
     <row r="16" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>1</v>
@@ -3364,10 +3381,10 @@
     </row>
     <row r="17" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>1</v>
@@ -3375,10 +3392,10 @@
     </row>
     <row r="18" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>1</v>
@@ -3386,10 +3403,10 @@
     </row>
     <row r="19" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>1</v>
@@ -3413,10 +3430,10 @@
   <sheetData>
     <row r="1" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>18</v>
@@ -3424,10 +3441,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3435,10 +3452,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3446,10 +3463,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3457,10 +3474,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3468,10 +3485,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3479,10 +3496,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3490,10 +3507,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3501,10 +3518,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3529,189 +3546,189 @@
   <sheetData>
     <row r="1" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
   </sheetData>

--- a/词汇表.xlsx
+++ b/词汇表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="384">
   <si>
     <t>玩家词汇 · 大白话对照表（v2.8.18 界面口径）</t>
   </si>
@@ -54,7 +54,7 @@
     <t>三 抽卡与开局：21 条</t>
   </si>
   <si>
-    <t>四 技能相关词：27 条</t>
+    <t>四 技能相关词：29 条</t>
   </si>
   <si>
     <t>五 结算录像日志：9 条</t>
@@ -663,10 +663,10 @@
     <t>"这技能在哪一刻响"的下拉。玩家在对局里只会看到结果，看不到这个词本身。</t>
   </si>
   <si>
-    <t>回合开始时 / 回合结束时 / 将领登场时 / 受到伤害后 / 造成伤害后 / 成为攻击目标时 / 击杀将领时 / 自身被击杀时 / 失去手牌时 / 获得手牌时</t>
-  </si>
-  <si>
-    <t>十种"哪一刻响"的说法，字面就是那件事发生的时刻。</t>
+    <t>回合开始时 / 回合结束时 / 将领登场时 / 受到伤害后 / 造成伤害后 / 成为目标时 / 击杀将领时 / 自身被击杀时 / 失去手牌时 / 获得手牌时</t>
+  </si>
+  <si>
+    <t>十种"哪一刻响"的说法，字面就是那件事发生的时刻。（"成为攻击目标时"这个旧名字 v2.8.21 起改成了泛指的"成为目标时"，具体被谁指名交给下面那一格说。）</t>
   </si>
   <si>
     <t>攻击伤害 / 技能伤害</t>
@@ -675,7 +675,19 @@
     <t>两种来路不同的伤害。"受到攻击伤害后"那类技能对技能伤害不响，反之亦然。定规则：core/eventProcessors/chainedConsequences.ts:42</t>
   </si>
   <si>
-    <t>细分（伤害类型／击杀对象／卡牌时机／失效条件）</t>
+    <t>成为目标时→被谁指名（成为攻击目标／成为技能目标／成为目标（两种都算））</t>
+  </si>
+  <si>
+    <t>"被点名"这一刻分三种来路：成为攻击目标＝被人拿兵刃指上；成为技能目标＝被一条技能点上火；成为目标（两种都算）＝两条来路都算。不选＝只算攻击，与今天对局一致。你手上的旧 Excel 里那格"成为攻击目标时"照样读得懂，只是再导出会写成"成为目标时→成为攻击目标"。要紧的实话：对局里今天只有"攻击"会发出这一声，"技能指名目标"那一路还没接上——所以选「成为技能目标」或「两种都算」时，这条限制会被如实记下、存进档案，但要等技能会点名的那一路接上才真的响（选「成为攻击目标」或留空则当场就与今天一样）。</t>
+  </si>
+  <si>
+    <t>我听谁（只听自己／听己方（同一席位）／听场上（所有玩家））</t>
+  </si>
+  <si>
+    <t>与"哪一刻响"无关的第二把尺子：那一声响起时，这条技能听多宽。只听自己＝只算这名将自己身上发生的事；听己方（同一席位）＝同一个玩家席位下的全部将领都算己方（跟"座位"走，不跟"势力"走）；听场上（所有玩家）＝谁的席位出事都算听到。Excel 里它是自己的一列（技能级「我听谁」＋每个效果的「效果N我听谁」），不写在触发时机那句话里，跟"技能门槛／效果N门槛"那两列一个摆法。不填＝只听自己，与今天对局逐字一致。两个实话：①手牌、回合这类事本来就记在玩家身上，所以这类时机里"只听自己"与"听己方（同一席位）"是同一回事；②"回合结束时、其他玩家登场时、技能失效时"这几类不认这一栏——填了会按没填处理并在导入总结里点名，不会静悄悄收下。</t>
+  </si>
+  <si>
+    <t>细分（伤害类型／被谁指名／击杀对象／卡牌时机／失效条件）</t>
   </si>
   <si>
     <t>触发时机的下一级筛选：例如"受到伤害后"还能再限定成只挡攻击伤害／只挡技能伤害。</t>
@@ -777,7 +789,7 @@
     <t>（旧说法，已作废）击破横幅上方那行残留的英文小字，v2.8.18 已翻成「本营击破」。</t>
   </si>
   <si>
-    <t>本节末尾必须说清的一件事：五个"××技"徽章和"强制发动"这一列，v2.8.19 起读得到、写得出、显示得出、还能核对（一枚技能可挂几枚；徽章与触发时机对不上会在编辑器与导入总结里点名），但都还没接进对局结算。证据：编译环节 skills/skillCompiler.ts 与触发桥 skills/SkillTriggerBridge.ts 里没有任何一处读 tags/tag 或 forced（这些字段只在编辑器与存档里来回搬：store/gameStoreEditorActions.ts:307）。所以现在决定一条技能"什么时候响、响不响、响几次"的，仍然只有：触发时机（含细分）＋ 发动门槛 ＋ 那条"每回合限一次"的账。徽章是给玩家看的分类，不是开关；读写口径全库只有一份，在 domain/skillTags.ts。</t>
+    <t>本节末尾必须说清的一件事：五个"××技"徽章和"强制发动"这一列，v2.8.19 起读得到、写得出、显示得出、还能核对（一枚技能可挂几枚；徽章与触发时机对不上会在编辑器与导入总结里点名），但都还没接进对局结算。证据：编译环节 skills/skillCompiler.ts 与触发桥 skills/SkillTriggerBridge.ts 里没有任何一处读 tags/tag 或 forced（这些字段只在编辑器与存档里来回搬：store/gameStoreEditorActions.ts:307）。所以现在决定一条技能"什么时候响、响不响、响几次"的是：触发时机（含细分）＋「我听谁」与「被谁指名」这两档监听范围（v2.8.21 起触发桥逐条读；两档的缺省＝只听自己／只算攻击，⇒ 与今天对局逐字一致。唯一的空档＝"成为技能目标"这一声今日没有发射器，记下了要等技能会指名目标那一路接上才真响）＋ 发动门槛 ＋ 那条"每回合限一次"的账。徽章是给玩家看的分类，不是开关；读写口径全库只有一份，在 domain/skillTags.ts。</t>
   </si>
   <si>
     <t>游戏结束 / 对局结束</t>
@@ -2735,7 +2747,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -3051,16 +3063,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
+    <row r="29" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
+      <c r="B29" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A32:C32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3090,10 +3124,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3101,10 +3135,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3112,10 +3146,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3123,10 +3157,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3134,10 +3168,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3145,10 +3179,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3156,10 +3190,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3167,10 +3201,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3178,10 +3212,10 @@
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -3216,10 +3250,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3227,10 +3261,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3238,10 +3272,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3249,10 +3283,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3260,10 +3294,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3271,10 +3305,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3282,10 +3316,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3293,10 +3327,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3304,10 +3338,10 @@
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -3315,10 +3349,10 @@
     </row>
     <row r="11" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>1</v>
@@ -3326,10 +3360,10 @@
     </row>
     <row r="12" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>1</v>
@@ -3337,10 +3371,10 @@
     </row>
     <row r="13" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>1</v>
@@ -3348,10 +3382,10 @@
     </row>
     <row r="14" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>1</v>
@@ -3359,10 +3393,10 @@
     </row>
     <row r="15" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>1</v>
@@ -3370,10 +3404,10 @@
     </row>
     <row r="16" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>1</v>
@@ -3381,10 +3415,10 @@
     </row>
     <row r="17" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>1</v>
@@ -3392,10 +3426,10 @@
     </row>
     <row r="18" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>1</v>
@@ -3403,10 +3437,10 @@
     </row>
     <row r="19" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>1</v>
@@ -3430,10 +3464,10 @@
   <sheetData>
     <row r="1" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>18</v>
@@ -3441,10 +3475,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3452,10 +3486,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3463,10 +3497,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3474,10 +3508,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3485,10 +3519,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3496,10 +3530,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3507,10 +3541,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3518,10 +3552,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3546,189 +3580,189 @@
   <sheetData>
     <row r="1" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>

--- a/词汇表.xlsx
+++ b/词汇表.xlsx
@@ -678,7 +678,7 @@
     <t>成为目标时→被谁指名（成为攻击目标／成为技能目标／成为目标（两种都算））</t>
   </si>
   <si>
-    <t>"被点名"这一刻分三种来路：成为攻击目标＝被人拿兵刃指上；成为技能目标＝被一条技能点上火；成为目标（两种都算）＝两条来路都算。不选＝只算攻击，与今天对局一致。你手上的旧 Excel 里那格"成为攻击目标时"照样读得懂，只是再导出会写成"成为目标时→成为攻击目标"。要紧的实话：对局里今天只有"攻击"会发出这一声，"技能指名目标"那一路还没接上——所以选「成为技能目标」或「两种都算」时，这条限制会被如实记下、存进档案，但要等技能会点名的那一路接上才真的响（选「成为攻击目标」或留空则当场就与今天一样）。</t>
+    <t>"被点名"这一刻分三种来路：成为攻击目标＝被人拿兵刃指上；成为技能目标＝被一条技能点上火；成为目标（两种都算）＝两条来路都算。不选＝只算攻击，与今天对局一致。你手上的旧 Excel 里那格"成为攻击目标时"照样读得懂，只是再导出会写成"成为目标时→成为攻击目标"。要紧的实话（2.8.24 更新）："成为技能目标"这一声如今有一个发射器＝决斗开局（哪个技能拿「决斗」点了敌将的名，决斗开打前必发这一声）；其余"技能指名目标"的路还没接上（仍要等内容刀）。"成为攻击目标"那一声照常由每次普攻发出。</t>
   </si>
   <si>
     <t>我听谁（只听自己／听己方（同一席位）／听场上（所有玩家））</t>
@@ -759,10 +759,10 @@
     <t>把你的牌交给别人（给别人手牌）。</t>
   </si>
   <si>
-    <t>决斗（技能效果，2.8.20 起）</t>
-  </si>
-  <si>
-    <t>自己的将领和目标的将领轮流各出手三次（最多六次）互砍：每一轮用当下出手那一方的攻击力，护甲照旧"2 点挡 1 点"；伤害算技能伤害、不消耗手牌；谁先体力归零就当场停，剩下的轮次不补。决斗中阵亡同样算"被击破"，由失去这名将领的一方补抽 1 张。只能由技能发起——棋盘上没有"决斗"按钮。决斗进行中不会再唤起"受到伤害后／成为目标时"那一类被动技能（唤起它们的只有发起决斗的那次攻击）。</t>
+    <t>决斗（技能效果，2.8.20 起；2.8.24 起两端问答落地）</t>
+  </si>
+  <si>
+    <t>自己的将领和目标的将领轮流各出手三次（最多六次）互砍：每一轮用当下出手那一方的攻击力，护甲照旧"2 点挡 1 点"；伤害算技能伤害、不消耗手牌；谁先体力归零就当场停，剩下的轮次不补。决斗中阵亡同样算"被击破"，由失去这名将领的一方补抽 1 张。只能由技能发起——棋盘上没有"决斗"按钮。问答节奏（2.8.24 起）：开场先停下来问一遍"成为技能目标"（被决斗点名的那一方、以及监听范围填了"己方／场上"的这一类被动都有表态权；答复里回复的体力算进决斗起点）；这一层全部问完才开始互砍，互砍的每一"打"中间不唤任何监听；全部打完再按"受到伤害后"问一遍——判定值＝该将领这一场实际掉掉的体力总额（军备减免不算），只算一笔、只问一次、绝不再扣第二次血；问的次序＝受邀者那笔先问完（本人先答→旁人按座次绕圈），发起者那笔后问。决斗中阵亡的那一位那一笔整笔跳过（本人和旁人均不问），但他的遗言技（自身被击杀时）与击破补偿抽照旧。</t>
   </si>
   <si>
     <t>效果模式：全部生效 / 选择其一</t>
@@ -789,7 +789,7 @@
     <t>（旧说法，已作废）击破横幅上方那行残留的英文小字，v2.8.18 已翻成「本营击破」。</t>
   </si>
   <si>
-    <t>本节末尾必须说清的一件事：五个"××技"徽章和"强制发动"这一列，v2.8.19 起读得到、写得出、显示得出、还能核对（一枚技能可挂几枚；徽章与触发时机对不上会在编辑器与导入总结里点名），但都还没接进对局结算。证据：编译环节 skills/skillCompiler.ts 与触发桥 skills/SkillTriggerBridge.ts 里没有任何一处读 tags/tag 或 forced（这些字段只在编辑器与存档里来回搬：store/gameStoreEditorActions.ts:307）。所以现在决定一条技能"什么时候响、响不响、响几次"的是：触发时机（含细分）＋「我听谁」与「被谁指名」这两档监听范围（v2.8.21 起触发桥逐条读；两档的缺省＝只听自己／只算攻击，⇒ 与今天对局逐字一致。唯一的空档＝"成为技能目标"这一声今日没有发射器，记下了要等技能会指名目标那一路接上才真响）＋ 发动门槛 ＋ 那条"每回合限一次"的账。徽章是给玩家看的分类，不是开关；读写口径全库只有一份，在 domain/skillTags.ts。</t>
+    <t>本节末尾必须说清的一件事：五个"××技"徽章和"强制发动"这一列，v2.8.19 起读得到、写得出、显示得出、还能核对（一枚技能可挂几枚；徽章与触发时机对不上会在编辑器与导入总结里点名），但都还没接进对局结算。证据：编译环节 skills/skillCompiler.ts 与触发桥 skills/SkillTriggerBridge.ts 里没有任何一处读 tags/tag 或 forced（这些字段只在编辑器与存档里来回搬：store/gameStoreEditorActions.ts:307）。所以现在决定一条技能"什么时候响、响不响、响几次"的是：触发时机（含细分）＋「我听谁」与「被谁指名」这两档监听范围（v2.8.21 起触发桥逐条读；两档的缺省＝只听自己／只算攻击，⇒ 与今天对局逐字一致。"成为技能目标"这一声 v2.8.24 起已有发射器＝决斗开局（其余技能指名目标的路仍未发这一声，等内容刀））＋ 发动门槛 ＋ 那条"每回合限一次"的账。徽章是给玩家看的分类，不是开关；读写口径全库只有一份，在 domain/skillTags.ts。</t>
   </si>
   <si>
     <t>游戏结束 / 对局结束</t>

--- a/词汇表.xlsx
+++ b/词汇表.xlsx
@@ -36,7 +36,7 @@
     <t>· 出处：所有词条都对应到 文件:行号（仓库根＝Qoder/2.0）。规则类翻译另标了"定规则的代码在哪"，方便日后核对。</t>
   </si>
   <si>
-    <t>· 已知坑：第八节那十条"界面这么说、代码这么算"的冲突，第 1～8 条与第 10 条已经对齐（v2.8.14／v2.8.18），只有第 9 条（卡面徽章与"强制发动"到底管不管事）还等一份提案；已作废的旧写法在表里用 ~~删除线~~ 标出，投影进 Excel 时会渲染成"（旧说法，已作废）"。</t>
+    <t>· 已知坑：第八节那十条"界面这么说、代码这么算"的冲突，第 1～8 条与第 10 条已经对齐（v2.8.14／v2.8.18）；第 9 条自 v2.8.25 起拆成两半——「强制发动」那一半已经进引擎（勾了就不问玩家、到点自己响），徽章那一半仍只是分类（锁定技的"不能被无效"、限定技的"一局一次"还没进引擎，等您口令）；已作废的旧写法在表里用 ~~删除线~~ 标出，投影进 Excel 时会渲染成"（旧说法，已作废）"。</t>
   </si>
   <si>
     <t>· 本轮之后如果界面改词，这张表要跟着改；它随 Git 走，别在别处另抄一份。</t>
@@ -654,7 +654,7 @@
     <t>强制发动</t>
   </si>
   <si>
-    <t>编辑器里的开关（Excel 也有这一列）：满足触发条件与代价后直接响／直接适用效果，不用玩家点头。它跟锁定技不是一件事，跟"数值变化／持续生效"也不绑定，三者可以任意组合。目前只被存下来，运行时没有任何地方读它（编译器和触发桥都不看这个字段）——开或关，对局里的表现一模一样。</t>
+    <t>编辑器里的开关（Excel 也有这一列）：满足触发条件与代价后直接响／直接适用效果，不用玩家点头。它跟锁定技不是一件事，跟"数值变化／持续生效"也不绑定，三者可以任意组合。v2.8.25 起这一格真的管事了：勾上之后，凡是本来会停下来问您"要不要发动"的那一刻（＝成为目标时／受到伤害后这两型），这条技能不再问、自己就响了；不勾就照旧问。四句实话边界：①它只决定"问不问人"，不会让一条技能多响一次，也不绕过发动门槛与代价；②本来就到点自动响的时机（登场／回合开始／击杀／失去手牌……）勾不勾都一样；③「回合结束时」那一型永远要您点头（一条技能不许响两次的常设规矩），勾了也不自响；④决斗那一套的"开局被点名"与"收官掉血"两刻同样吃这一格——勾了就自己响、没勾就问。今天的官方 95 将与您手上的样本卡还没有一条勾了这个开关，所以对局里的表现与上一版逐字相同。</t>
   </si>
   <si>
     <t>触发时机</t>
@@ -762,7 +762,7 @@
     <t>决斗（技能效果，2.8.20 起；2.8.24 起两端问答落地）</t>
   </si>
   <si>
-    <t>自己的将领和目标的将领轮流各出手三次（最多六次）互砍：每一轮用当下出手那一方的攻击力，护甲照旧"2 点挡 1 点"；伤害算技能伤害、不消耗手牌；谁先体力归零就当场停，剩下的轮次不补。决斗中阵亡同样算"被击破"，由失去这名将领的一方补抽 1 张。只能由技能发起——棋盘上没有"决斗"按钮。问答节奏（2.8.24 起）：开场先停下来问一遍"成为技能目标"（被决斗点名的那一方、以及监听范围填了"己方／场上"的这一类被动都有表态权；答复里回复的体力算进决斗起点）；这一层全部问完才开始互砍，互砍的每一"打"中间不唤任何监听；全部打完再按"受到伤害后"问一遍——判定值＝该将领这一场实际掉掉的体力总额（军备减免不算），只算一笔、只问一次、绝不再扣第二次血；问的次序＝受邀者那笔先问完（本人先答→旁人按座次绕圈），发起者那笔后问。决斗中阵亡的那一位那一笔整笔跳过（本人和旁人均不问），但他的遗言技（自身被击杀时）与击破补偿抽照旧。</t>
+    <t>自己的将领和目标的将领轮流各出手三次（最多六次）互砍：每一轮用当下出手那一方的攻击力，护甲照旧"2 点挡 1 点"；伤害算技能伤害、不消耗手牌；谁先体力归零就当场停，剩下的轮次不补。决斗中阵亡同样算"被击破"，由失去这名将领的一方补抽 1 张。只能由技能发起——棋盘上没有"决斗"按钮。问答节奏（2.8.24 起）：开场先停下来问一遍"成为技能目标"（被决斗点名的那一方、以及监听范围填了"己方／场上"的这一类被动都有表态权；答复里回复的体力算进决斗起点；2.8.25 起这一层还吃「强制发动」那一格——打了勾的技能不问、自己响完，且这一层全部响完才开始互砍）；这一层全部问完才开始互砍，互砍的每一"打"中间不唤任何监听；全部打完再按"受到伤害后"问一遍——判定值＝该将领这一场实际掉掉的体力总额（军备减免不算），只算一笔、只问一次、绝不再扣第二次血；问的次序＝受邀者那笔先问完（本人先答→旁人按座次绕圈），发起者那笔后问。决斗中阵亡的那一位那一笔整笔跳过（本人和旁人均不问），但他的遗言技（自身被击杀时）与击破补偿抽照旧。</t>
   </si>
   <si>
     <t>效果模式：全部生效 / 选择其一</t>
@@ -789,7 +789,7 @@
     <t>（旧说法，已作废）击破横幅上方那行残留的英文小字，v2.8.18 已翻成「本营击破」。</t>
   </si>
   <si>
-    <t>本节末尾必须说清的一件事：五个"××技"徽章和"强制发动"这一列，v2.8.19 起读得到、写得出、显示得出、还能核对（一枚技能可挂几枚；徽章与触发时机对不上会在编辑器与导入总结里点名），但都还没接进对局结算。证据：编译环节 skills/skillCompiler.ts 与触发桥 skills/SkillTriggerBridge.ts 里没有任何一处读 tags/tag 或 forced（这些字段只在编辑器与存档里来回搬：store/gameStoreEditorActions.ts:307）。所以现在决定一条技能"什么时候响、响不响、响几次"的是：触发时机（含细分）＋「我听谁」与「被谁指名」这两档监听范围（v2.8.21 起触发桥逐条读；两档的缺省＝只听自己／只算攻击，⇒ 与今天对局逐字一致。"成为技能目标"这一声 v2.8.24 起已有发射器＝决斗开局（其余技能指名目标的路仍未发这一声，等内容刀））＋ 发动门槛 ＋ 那条"每回合限一次"的账。徽章是给玩家看的分类，不是开关；读写口径全库只有一份，在 domain/skillTags.ts。</t>
+    <t>本节末尾必须说清的一件事：五个"××技"徽章和"强制发动"这一列，v2.8.19 起读得到、写得出、显示得出、还能核对（一枚技能可挂几枚；徽章与触发时机对不上会在编辑器与导入总结里点名）。这两样如今落地程度不同：「强制发动」v2.8.25 起接进对局了——全库只有一个地方读它（skills/SkillTriggerBridge.ts 的 defersToReactionQueue：受击／受伤这两型里没打勾的定义才交给问答队列问人，打了勾的直接走自动发动那条路），所以它管的事恰恰只有一件＝"这一刻问不问您"；五个徽章仍然只是分类，结算里没有任何一处读 tags/tag（它们只在编辑器与存档里来回搬：store/gameStoreEditorActions.ts:314），锁定技的"不能被无效／改变"与限定技的"一局一次"额度都还没进引擎。所以现在决定一条技能"什么时候响、响不响、响几次"的是：触发时机（含细分）＋「我听谁」与「被谁指名」这两档监听范围（v2.8.21 起触发桥逐条读；两档的缺省＝只听自己／只算攻击，⇒ 与今天对局逐字一致。"成为技能目标"这一声 v2.8.24 起已有发射器＝决斗开局（其余技能指名目标的路仍未发这一声，等内容刀））＋ 发动门槛 ＋ 那条"每回合限一次"的账 ＋「强制发动」这一格（v2.8.25 起，只管问不问人）。徽章是给玩家看的分类，不是开关；读写口径全库只有一份，在 domain/skillTags.ts。</t>
   </si>
   <si>
     <t>游戏结束 / 对局结束</t>
@@ -1146,16 +1146,16 @@
     <t>9</t>
   </si>
   <si>
-    <t>徽章与开关不落地</t>
+    <t>徽章与开关落不落地</t>
   </si>
   <si>
     <t>编辑器只有单枚标签下拉、卡面只印一枚（旧说法，已作废） 已多枚化（v2.8.19：编辑器一排徽章可同时点亮几枚，Excel「技能标签」格用顿号分开写，图鉴／卡面／对局几枚都显示）</t>
   </si>
   <si>
-    <t>半落地：词汇、录入、显示、核对四处已按您 2026-09-30 的更正对齐，读写口径全库只有一份（domain/skillTags.ts）；结算那半处都不读 tags/forced——锁定技的"不能被无效、不能被改变"、限定技的"一局一次"、强制发动的"不用玩家点头"都还没进引擎</t>
-  </si>
-  <si>
-    <t>⏳ 您的更正口径已逐字落进第四节：「锁定技实际上是指无法被无效和改变的技能，而强制发动则是指某些技能在满足触发条件和代价后会强制发动/直接适用其效果，两者和数值变化+永续生效的组合一样，不是强关联」；样本＝闭月同时挂 锁定技＋遗计技。结算那一刀要改引擎、会换锚（B12/B11），等您口令再开</t>
+    <t>两半现在分开了：「强制发动」那半 v2.8.25 已进引擎（SkillTriggerBridge.defersToReactionQueue 读它⇒勾了就不问人、直接走自动发动路；全库只有这一处读，所以它只管"问不问"这一件事）；五个徽章那半结算里仍一处都不读 tags/tag——锁定技的"不能被无效、不能被改变"、限定技的"一局一次"还没进引擎。读写口径全库只有一份（domain/skillTags.ts）</t>
+  </si>
+  <si>
+    <t>✅ 您的更正口径已逐字落进第四节：「锁定技实际上是指无法被无效和改变的技能，而强制发动则是指某些技能在满足触发条件和代价后会强制发动/直接适用其效果，两者和数值变化+永续生效的组合一样，不是强关联」；样本＝闭月同时挂 锁定技＋遗计技。强制发动那一刀已开完（v2.8.25，两锚逐字未动＝今天还没有一条数据勾着它）；剩下的锁定技／限定技执法仍要改引擎、会换锚，等您口令再开</t>
   </si>
   <si>
     <t>10</t>

--- a/词汇表.xlsx
+++ b/词汇表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="394">
   <si>
     <t>玩家词汇 · 大白话对照表（v2.8.18 界面口径）</t>
   </si>
@@ -54,7 +54,7 @@
     <t>三 抽卡与开局：21 条</t>
   </si>
   <si>
-    <t>四 技能相关词：29 条</t>
+    <t>四 技能相关词：34 条</t>
   </si>
   <si>
     <t>五 结算录像日志：9 条</t>
@@ -669,6 +669,12 @@
     <t>十种"哪一刻响"的说法，字面就是那件事发生的时刻。（"成为攻击目标时"这个旧名字 v2.8.21 起改成了泛指的"成为目标时"，具体被谁指名交给下面那一格说。）</t>
   </si>
   <si>
+    <t>在场即生效（不用发动，人在就算）（v2.8 刀4 起可结算）</t>
+  </si>
+  <si>
+    <t>第十一种选择，但它根本不是"哪一刻响"——它是"没有哪一刻需要它响"。这一型编译出来不监听任何事件、不进问答窗、不吃「强制发动」那一格：将领登场那一刻落一笔账（配合下面的「修改数值」用），离场当场销账，人在的整段时间都算数。三句实话：①旧名字「全局生效（在场时持续）」容易读成"影响全场所有人"，v2.8 刀4 起改叫这个名，旧 Excel 里那一格照样读得懂、再导出会写新名；②这一型不许配门槛、不许配有效周期、不许配「选择其一」（门槛要"情况一变就改口"、周期要"发动笔"那一档、择一要有人点头——三样都没有落点），填了会在编译时逐条点名跳过，不会悄悄变成"全都要"；③官方 95 将与您手上的样本卡今天还没有一条用这一型，所以对局里的表现与上一版逐字相同。</t>
+  </si>
+  <si>
     <t>攻击伤害 / 技能伤害</t>
   </si>
   <si>
@@ -777,6 +783,30 @@
     <t>两级条件：整组门槛（技能级，不满足这一刻整条技能不响）→ 逐项门槛（每条效果自己的条件）。先判整组，再判逐项。</t>
   </si>
   <si>
+    <t>修改数值（效果类型，v2.8 刀4 起可结算）</t>
+  </si>
+  <si>
+    <t>第十一条效果类型。它不改卡面上的印刷数字，而是给这名将领记一笔"账"（引擎里那本账叫 state.statModifiers，随存档走、录像能重放）。所以同一张卡在棋盘上会同时存在两个数：卡上印的（永远不变，图鉴与手抄核对用它）和当下算数的（对局里真正用来砍人的）。今天只有三个数能被这样改：近战攻击力／远程攻击力／体力上限。四句实话：①当前体力不走这本账（它本来就是"损失记录"那一本，回血、扣血照旧直接动它）；②护甲、手牌上限这一版还没接（写了会被点名跳过）；③只能改自己的账面数字——"让别人的攻击＋1"那种跨将改数还没有目标选择器，编译时逐条点名跳过；④官方 95 将与您手上的样本卡今天还没有一条用它，所以对局表现与上一版逐字相同。</t>
+  </si>
+  <si>
+    <t>改哪个数 / 怎么改 / 有效周期（Excel 里效果组第 9–11 列）</t>
+  </si>
+  <si>
+    <t>「修改数值」的三格配套，各占一列（与「我听谁」「门槛」同一族做法，不挤进触发时机那句话）。改哪个数＝上面那三个数之一；怎么改＝两档：「增加或减少（可填负数）」＝往上添/往下减，「固定为（覆盖卡面值）」＝不管卡上印几，一律摁成这个数；有效周期＝这笔账管到什么时候（见下一行）。只有「效果类型＝修改数值」读这三格，别的类型填了会在导入总结里逐条点名，不会静悄悄收下。数值格是全库唯一允许 0 与负数的地方（往下调就填 −1）。</t>
+  </si>
+  <si>
+    <t>有效周期（这笔账什么时候结束）</t>
+  </si>
+  <si>
+    <t>四种写法：到下个己方回合开始前／到下个己方回合结束前／到下个其他玩家回合开始前／到下个其他玩家回合结束前。留空＝在场上就一直有效、离场当场结束（表头批注里写了这一句，免得空着被读成"没生效"）。词表里故意没有"直到将领被击杀前"这一档——离场打断一切，它与"直到离开场上前"同义，旧文件真写了这两个词也照样读成留空。周期只跟"发动那一笔"配对：在场即生效的那笔账不许填周期（它本来就没有"开始"以外的时刻，填了编译时点名跳过）。</t>
+  </si>
+  <si>
+    <t>几笔账同时算一个数时谁说了算</t>
+  </si>
+  <si>
+    <t>规矩是「固定」压过「增减」：只要有一笔"固定为"在场，同一种伤害上所有"增减"都不参与（先按您定的规则走完"固定"这一段，增减没有可作用的中间值）；同一形态有多笔，按发动的先后排，后落的那笔接着前一笔的结果算。当事人自己那笔排在最后（这条是我的建议、还在等您裁）。账本上标了「锁定技」的那一笔，别的技能移不走——这是"锁定技不能被改变"这枚徽章第一次真的由结算来管；但请注意它的边界：它管的是"这笔账不许被撤销"，不管"这条技能不许被无效"（后一半今天仍然没有任何结算代码读它）。</t>
+  </si>
+  <si>
     <t>击破 / 出局 / 阵亡 / 获得胜利</t>
   </si>
   <si>
@@ -789,7 +819,7 @@
     <t>（旧说法，已作废）击破横幅上方那行残留的英文小字，v2.8.18 已翻成「本营击破」。</t>
   </si>
   <si>
-    <t>本节末尾必须说清的一件事：五个"××技"徽章和"强制发动"这一列，v2.8.19 起读得到、写得出、显示得出、还能核对（一枚技能可挂几枚；徽章与触发时机对不上会在编辑器与导入总结里点名）。这两样如今落地程度不同：「强制发动」v2.8.25 起接进对局了——全库只有一个地方读它（skills/SkillTriggerBridge.ts 的 defersToReactionQueue：受击／受伤这两型里没打勾的定义才交给问答队列问人，打了勾的直接走自动发动那条路），所以它管的事恰恰只有一件＝"这一刻问不问您"；五个徽章仍然只是分类，结算里没有任何一处读 tags/tag（它们只在编辑器与存档里来回搬：store/gameStoreEditorActions.ts:314），锁定技的"不能被无效／改变"与限定技的"一局一次"额度都还没进引擎。所以现在决定一条技能"什么时候响、响不响、响几次"的是：触发时机（含细分）＋「我听谁」与「被谁指名」这两档监听范围（v2.8.21 起触发桥逐条读；两档的缺省＝只听自己／只算攻击，⇒ 与今天对局逐字一致。"成为技能目标"这一声 v2.8.24 起已有发射器＝决斗开局（其余技能指名目标的路仍未发这一声，等内容刀））＋ 发动门槛 ＋ 那条"每回合限一次"的账 ＋「强制发动」这一格（v2.8.25 起，只管问不问人）。徽章是给玩家看的分类，不是开关；读写口径全库只有一份，在 domain/skillTags.ts。</t>
+    <t>本节末尾必须说清的一件事：五个"××技"徽章和"强制发动"这一列，v2.8.19 起读得到、写得出、显示得出、还能核对（一枚技能可挂几枚；徽章与触发时机对不上会在编辑器与导入总结里点名）。这两样如今落地程度不同：「强制发动」v2.8.25 起接进对局了——全库只有一个地方读它（skills/SkillTriggerBridge.ts 的 defersToReactionQueue：受击／受伤这两型里没打勾的定义才交给问答队列问人，打了勾的直接走自动发动那条路），所以它管的事恰恰只有一件＝"这一刻问不问您"；徽章里「锁定技」v2.8 刀4 起有了第一个结算侧的消费者，但只管一寸地方：编译器认出这枚徽章 → 这条技能往数值账本落的那笔账打上"移不走"的记号（statModifiers.revokeModifier 是全库唯一"移走别人那笔账"的入口，它见到这个记号就拒绝）。徽章的其余部分（"不能被无效""不能被改变"在伤害、护甲、被弃牌这些环节到底管不管）今天仍然没有任何结算代码读它；另外四枚徽章（限定／登场／遗计／觉醒）还是纯分类，限定技的"一局一次"额度依然没进引擎。所以现在决定一条技能"什么时候响、响不响、响几次"的是：触发时机（含细分）＋「我听谁」与「被谁指名」这两档监听范围（v2.8.21 起触发桥逐条读；两档的缺省＝只听自己／只算攻击，⇒ 与今天对局逐字一致。"成为技能目标"这一声 v2.8.24 起已有发射器＝决斗开局（其余技能指名目标的路仍未发这一声，等内容刀））＋ 发动门槛 ＋ 那条"每回合限一次"的账 ＋「强制发动」这一格（v2.8.25 起，只管问不问人）。「在场即生效」那一型不看上面这些，它只在登场／离场两刻动账本。徽章的读写口径全库只有一份，在 domain/skillTags.ts。</t>
   </si>
   <si>
     <t>游戏结束 / 对局结束</t>
@@ -2747,7 +2777,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -3085,16 +3115,71 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
+    <row r="31" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
+      <c r="B31" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A37:C37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3124,10 +3209,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3135,10 +3220,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3146,10 +3231,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3157,10 +3242,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3168,10 +3253,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3179,10 +3264,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3190,10 +3275,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3201,10 +3286,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3212,10 +3297,10 @@
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -3250,10 +3335,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3261,10 +3346,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3272,10 +3357,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3283,10 +3368,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3294,10 +3379,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3305,10 +3390,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3316,10 +3401,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3327,10 +3412,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3338,10 +3423,10 @@
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -3349,10 +3434,10 @@
     </row>
     <row r="11" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>1</v>
@@ -3360,10 +3445,10 @@
     </row>
     <row r="12" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>1</v>
@@ -3371,10 +3456,10 @@
     </row>
     <row r="13" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>1</v>
@@ -3382,10 +3467,10 @@
     </row>
     <row r="14" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>1</v>
@@ -3393,10 +3478,10 @@
     </row>
     <row r="15" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>1</v>
@@ -3404,10 +3489,10 @@
     </row>
     <row r="16" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>1</v>
@@ -3415,10 +3500,10 @@
     </row>
     <row r="17" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>1</v>
@@ -3426,10 +3511,10 @@
     </row>
     <row r="18" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>1</v>
@@ -3437,10 +3522,10 @@
     </row>
     <row r="19" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>1</v>
@@ -3464,10 +3549,10 @@
   <sheetData>
     <row r="1" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>18</v>
@@ -3475,10 +3560,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3486,10 +3571,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3497,10 +3582,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3508,10 +3593,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3519,10 +3604,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3530,10 +3615,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3541,10 +3626,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3552,10 +3637,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3580,189 +3665,189 @@
   <sheetData>
     <row r="1" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
     </row>
   </sheetData>

--- a/词汇表.xlsx
+++ b/词汇表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="394">
   <si>
     <t>玩家词汇 · 大白话对照表（v2.8.18 界面口径）</t>
   </si>
@@ -666,7 +666,7 @@
     <t>回合开始时 / 回合结束时 / 将领登场时 / 受到伤害后 / 造成伤害后 / 成为目标时 / 击杀将领时 / 自身被击杀时 / 失去手牌时 / 获得手牌时</t>
   </si>
   <si>
-    <t>十种"哪一刻响"的说法，字面就是那件事发生的时刻。（"成为攻击目标时"这个旧名字 v2.8.21 起改成了泛指的"成为目标时"，具体被谁指名交给下面那一格说。）</t>
+    <t>十种"哪一刻响"的说法，字面就是那件事发生的时刻。（"成为攻击目标时"这个旧名字 v2.8.21 起改成了泛指的"成为目标时"，具体被谁指名交给下面那一格说。）「受到伤害后」的判据（v2.8 刀5 起，您 2026-10-03 重新裁定）＝只有真的掉了体力才算受到了伤害：这一刀被护甲全挡住、一点血没掉 ⇒ 不算受到，技能不问也不响；伤害算出来是 0 或负数 ⇒ 也不算。掉多少算多少：普攻／技能伤害每一刀各算一声；决斗那一整场只在打完时按"这个将一共掉了多少体力"算一笔（见上面「决斗」那一格）。</t>
   </si>
   <si>
     <t>在场即生效（不用发动，人在就算）（v2.8 刀4 起可结算）</t>
@@ -786,25 +786,25 @@
     <t>修改数值（效果类型，v2.8 刀4 起可结算）</t>
   </si>
   <si>
-    <t>第十一条效果类型。它不改卡面上的印刷数字，而是给这名将领记一笔"账"（引擎里那本账叫 state.statModifiers，随存档走、录像能重放）。所以同一张卡在棋盘上会同时存在两个数：卡上印的（永远不变，图鉴与手抄核对用它）和当下算数的（对局里真正用来砍人的）。今天只有三个数能被这样改：近战攻击力／远程攻击力／体力上限。四句实话：①当前体力不走这本账（它本来就是"损失记录"那一本，回血、扣血照旧直接动它）；②护甲、手牌上限这一版还没接（写了会被点名跳过）；③只能改自己的账面数字——"让别人的攻击＋1"那种跨将改数还没有目标选择器，编译时逐条点名跳过；④官方 95 将与您手上的样本卡今天还没有一条用它，所以对局表现与上一版逐字相同。</t>
+    <t>第十一条效果类型。它不改卡面上的印刷数字，而是给这名将领记一笔"账"（引擎里那本账叫 state.statModifiers，随存档走、录像能重放）。所以同一张卡在棋盘上会同时存在两个数：卡上印的（永远不变，图鉴与手抄核对用它）和当下算数的（对局里真正用来砍人的）。今天有四个数能被这样改：近战攻击力／远程攻击力／体力上限（v2.8 刀4）＋受到的伤害（v2.8 刀5）。五句实话：①当前体力不走这本账（它本来就是"损失记录"那一本，回血、扣血照旧直接动它）；②护甲、手牌上限这一版还没接（写了会被点名跳过）；③只能改自己的账面数字——"让别人的攻击＋1"那种跨将改数还没有目标选择器，编译时逐条点名跳过；④「受到的伤害」这一格作用在护甲之前：先把伤害这个数摁好，再交给"2 点护甲挡 1 点"那套算术，所以它是"看不见的减伤"，不是第二层护甲，也不改变身上有没有护甲这件事；本营（老家）不吃这一格——规则上本营单次受到的伤害最多 1 点，那一条由攻击那一步钉死，不是账本管的事；⑤官方 95 将与您手上的样本卡今天还没有一条用它（仓库那叠试作样本除外），所以对局表现与上一版逐字相同。</t>
   </si>
   <si>
     <t>改哪个数 / 怎么改 / 有效周期（Excel 里效果组第 9–11 列）</t>
   </si>
   <si>
-    <t>「修改数值」的三格配套，各占一列（与「我听谁」「门槛」同一族做法，不挤进触发时机那句话）。改哪个数＝上面那三个数之一；怎么改＝两档：「增加或减少（可填负数）」＝往上添/往下减，「固定为（覆盖卡面值）」＝不管卡上印几，一律摁成这个数；有效周期＝这笔账管到什么时候（见下一行）。只有「效果类型＝修改数值」读这三格，别的类型填了会在导入总结里逐条点名，不会静悄悄收下。数值格是全库唯一允许 0 与负数的地方（往下调就填 −1）。</t>
+    <t>「修改数值」的三格配套，各占一列（与「我听谁」「门槛」同一族做法，不挤进触发时机那句话）。改哪个数＝上面那四个数之一；怎么改＝两档：「增加或减少（可填负数）」＝往上添/往下减，「固定为（覆盖卡面值）」＝不管卡上印几，一律摁成这个数；有效周期＝这笔账管到什么时候（见下一行）。只有「效果类型＝修改数值」读这三格，别的类型填了会在导入总结里逐条点名，不会静悄悄收下。数值格是全库唯一允许 0 与负数的地方（往下调就填 −1）。</t>
   </si>
   <si>
     <t>有效周期（这笔账什么时候结束）</t>
   </si>
   <si>
-    <t>四种写法：到下个己方回合开始前／到下个己方回合结束前／到下个其他玩家回合开始前／到下个其他玩家回合结束前。留空＝在场上就一直有效、离场当场结束（表头批注里写了这一句，免得空着被读成"没生效"）。词表里故意没有"直到将领被击杀前"这一档——离场打断一切，它与"直到离开场上前"同义，旧文件真写了这两个词也照样读成留空。周期只跟"发动那一笔"配对：在场即生效的那笔账不许填周期（它本来就没有"开始"以外的时刻，填了编译时点名跳过）。</t>
+    <t>五种写法：到下个己方回合开始前／到下个己方回合结束前／到下个其他玩家回合开始前／到下个其他玩家回合结束前／一次性（用掉就销）（v2.8 刀5 新增，只对「受到的伤害」这把钥匙有意义＝"下一次受到伤害时算，算完当场销掉"；挂到攻击力或体力上限上，因为那两样没有"被用掉一次"的那一刻，会被导入报告与编译器逐条点名跳过）。留空＝在场上就一直有效、离场当场结束（表头批注里写了这一句，免得空着被读成"没生效"）。词表里故意没有"直到将领被击杀前"这一档——离场打断一切，它与"直到离开场上前"同义，旧文件真写了这两个词也照样读成留空。周期只跟"发动那一笔"配对：在场即生效的那笔账不许填周期（它本来就没有"开始"以外的时刻，填了编译时点名跳过）。一次性那笔在决斗里只挡一轮（您 2026-10-03 裁："下 1 次受到伤害−1"算一轮、"2 次"算两轮，以此类推），同一次读数里也只销掉最早的那一笔。</t>
   </si>
   <si>
     <t>几笔账同时算一个数时谁说了算</t>
   </si>
   <si>
-    <t>规矩是「固定」压过「增减」：只要有一笔"固定为"在场，同一种伤害上所有"增减"都不参与（先按您定的规则走完"固定"这一段，增减没有可作用的中间值）；同一形态有多笔，按发动的先后排，后落的那笔接着前一笔的结果算。当事人自己那笔排在最后（这条是我的建议、还在等您裁）。账本上标了「锁定技」的那一笔，别的技能移不走——这是"锁定技不能被改变"这枚徽章第一次真的由结算来管；但请注意它的边界：它管的是"这笔账不许被撤销"，不管"这条技能不许被无效"（后一半今天仍然没有任何结算代码读它）。</t>
+    <t>规矩是「固定」压过「增减」：只要有一笔"固定为"在场，同一种伤害上所有"增减"都不参与（先按您定的规则走完"固定"这一段，增减没有可作用的中间值）；同一形态有多笔，按发动的先后排，后落的那笔接着前一笔的结果算——同格两笔"固定"⇒后发的那笔盖掉先发的那笔（v2.8 刀5 钉死）。"固定"那笔一旦失效（用掉、离场、周期到点），此前被压住的增减立刻恢复参与，不用重新发动（被压住的那笔一次性增减不算被用掉，它还留着等下一刀）。跨侧（一个技能改自己受到的伤害、另一个改自己造成的伤害）谁赢＝已裁＝受方那一格恒盖过造方那一格，实现方式不是弹窗口问先后，而是入算次序：造方先入算、受方后入算，后读的覆写先读的（v2.8 刀5 只接了受方这一把钥匙，造方那一把您裁了本轮不接，规矩先立着等接线那把刀）。账本上标了「锁定技」的那一笔，别的技能移不走——这是"锁定技不能被改变"这枚徽章第一次真的由结算来管；但请注意它的边界：它管的是"这笔账不许被撤销"，不管"这条技能不许被无效"（后一半今天仍然没有任何结算代码读它）。</t>
   </si>
   <si>
     <t>击破 / 出局 / 阵亡 / 获得胜利</t>
@@ -2777,7 +2777,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -2884,7 +2884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>214</v>
       </c>
@@ -2892,6 +2892,9 @@
         <v>215</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>1</v>
       </c>
     </row>

--- a/词汇表.xlsx
+++ b/词汇表.xlsx
@@ -147,7 +147,7 @@
     <t>本营</t>
   </si>
   <si>
-    <t>每家的大本营，有独立血量（初始 6）。归零这家就打完了。定规则：action/resolvers/AttackResolver.ts:116（每次挨打最多掉 1 点）</t>
+    <t>每家的大本营，有独立血量（初始 6）。归零这家就打完了。定规则：不管是普通攻击还是技能打来的，本营每次挨打最多掉 1 点（v2.8.29 起技能伤害也走这一条；那个"1"只写在一个地方＝core/baseDamage.ts）。</t>
   </si>
   <si>
     <t>营地</t>

--- a/词汇表.xlsx
+++ b/词汇表.xlsx
@@ -666,7 +666,7 @@
     <t>回合开始时 / 回合结束时 / 将领登场时 / 受到伤害后 / 造成伤害后 / 成为目标时 / 击杀将领时 / 自身被击杀时 / 失去手牌时 / 获得手牌时</t>
   </si>
   <si>
-    <t>十种"哪一刻响"的说法，字面就是那件事发生的时刻。（"成为攻击目标时"这个旧名字 v2.8.21 起改成了泛指的"成为目标时"，具体被谁指名交给下面那一格说。）「受到伤害后」的判据（v2.8 刀5 起，您 2026-10-03 重新裁定）＝只有真的掉了体力才算受到了伤害：这一刀被护甲全挡住、一点血没掉 ⇒ 不算受到，技能不问也不响；伤害算出来是 0 或负数 ⇒ 也不算。掉多少算多少：普攻／技能伤害每一刀各算一声；决斗那一整场只在打完时按"这个将一共掉了多少体力"算一笔（见上面「决斗」那一格）。</t>
+    <t>十种"哪一刻响"的说法，字面就是那件事发生的时刻。（"成为攻击目标时"这个旧名字 v2.8.21 起改成了泛指的"成为目标时"，具体被谁指名交给下面那一格说。）「受到伤害后」的判据（v2.8 刀5 起，您 2026-10-03 重新裁定）＝只有真的掉了体力才算受到了伤害：这一刀被护甲全挡住、一点血没掉 ⇒ 不算受到，技能不问也不响；伤害算出来是 0 或负数 ⇒ 也不算。掉多少算多少：普攻／技能伤害每一刀各算一声；决斗那一整场只在打完时按"这个将一共掉了多少体力"算一笔（见上面「决斗」那一格）。如果被这一下打死，它这两类技能都赶不上响应这一次——「受到伤害后」和「成为目标时」一起不算（2026-10-03 定案＝规则、不是毛病：游戏里这两问都是在"这一刀的全部后果算完"之后才开口问的，那时候人已经离场，没处可问；于是那一格本该产生的效果也不会发生，比如反伤的那 1 点、摸的那一张牌。它上一刀挨的、上一刀答过的都照常有效。一条边界（这一条只管到这儿，别读宽）：这一条只管"会停下来问您要不要发动"的那一类；如果这条技能勾了「强制发动」，它根本不等问、在算这一刀的过程中就已经响完了，所以打死也拦不住它（实测＝反伤那 1 点照样落、牌照样摸进手）。⇒ 要不要把同一把闸也加到"不用问就响"那一类，还没有裁定，今天就按上面这样算。判据与取证＝PROJECT_HANDOFF.md §12-100）。</t>
   </si>
   <si>
     <t>在场即生效（不用发动，人在就算）（v2.8 刀4 起可结算）</t>

--- a/词汇表.xlsx
+++ b/词汇表.xlsx
@@ -654,7 +654,7 @@
     <t>强制发动</t>
   </si>
   <si>
-    <t>编辑器里的开关（Excel 也有这一列）：满足触发条件与代价后直接响／直接适用效果，不用玩家点头。它跟锁定技不是一件事，跟"数值变化／持续生效"也不绑定，三者可以任意组合。v2.8.25 起这一格真的管事了：勾上之后，凡是本来会停下来问您"要不要发动"的那一刻（＝成为目标时／受到伤害后这两型），这条技能不再问、自己就响了；不勾就照旧问。四句实话边界：①它只决定"问不问人"，不会让一条技能多响一次，也不绕过发动门槛与代价；②本来就到点自动响的时机（登场／回合开始／击杀／失去手牌……）勾不勾都一样；③「回合结束时」那一型永远要您点头（一条技能不许响两次的常设规矩），勾了也不自响；④决斗那一套的"开局被点名"与"收官掉血"两刻同样吃这一格——勾了就自己响、没勾就问。今天的官方 95 将与您手上的样本卡还没有一条勾了这个开关，所以对局里的表现与上一版逐字相同。</t>
+    <t>编辑器里的开关（Excel 也有这一列）：满足触发条件与代价后直接响／直接适用效果，不用玩家点头。它跟锁定技不是一件事，跟"数值变化／持续生效"也不绑定，三者可以任意组合。v2.8.25 起这一格真的管事了：勾上之后，凡是本来会停下来问您"要不要发动"的那一刻（＝成为目标时／受到伤害后这两型），这条技能不再问、自己就响了；不勾就照旧问。四句实话边界：①它只决定"问不问人"，不会让一条技能多响一次，也不绕过发动门槛与代价；②本来就到点自动响的时机（登场／回合开始／击杀／失去手牌……）勾不勾都一样；③「回合结束时」那一型永远要您点头（一条技能不许响两次的常设规矩），勾了也不自响；④决斗那一套的"开局被点名"与"收官掉血"两刻同样吃这一格——勾了就自己响、没勾就问；⑤v2.8.30 起它也不绕过"人在场上"这一条：把主人打死的那一刀，它那份效果同样不落账（与不勾时问人的那一型同一判据、同一形状），只有「自身被击杀时」那一型放行。今天的官方 95 将与您手上的样本卡还没有一条勾了这个开关，所以对局里的表现与上一版逐字相同。</t>
   </si>
   <si>
     <t>触发时机</t>
@@ -666,7 +666,7 @@
     <t>回合开始时 / 回合结束时 / 将领登场时 / 受到伤害后 / 造成伤害后 / 成为目标时 / 击杀将领时 / 自身被击杀时 / 失去手牌时 / 获得手牌时</t>
   </si>
   <si>
-    <t>十种"哪一刻响"的说法，字面就是那件事发生的时刻。（"成为攻击目标时"这个旧名字 v2.8.21 起改成了泛指的"成为目标时"，具体被谁指名交给下面那一格说。）「受到伤害后」的判据（v2.8 刀5 起，您 2026-10-03 重新裁定）＝只有真的掉了体力才算受到了伤害：这一刀被护甲全挡住、一点血没掉 ⇒ 不算受到，技能不问也不响；伤害算出来是 0 或负数 ⇒ 也不算。掉多少算多少：普攻／技能伤害每一刀各算一声；决斗那一整场只在打完时按"这个将一共掉了多少体力"算一笔（见上面「决斗」那一格）。如果被这一下打死，它这两类技能都赶不上响应这一次——「受到伤害后」和「成为目标时」一起不算（2026-10-03 定案＝规则、不是毛病：游戏里这两问都是在"这一刀的全部后果算完"之后才开口问的，那时候人已经离场，没处可问；于是那一格本该产生的效果也不会发生，比如反伤的那 1 点、摸的那一张牌。它上一刀挨的、上一刀答过的都照常有效。一条边界（这一条只管到这儿，别读宽）：这一条只管"会停下来问您要不要发动"的那一类；如果这条技能勾了「强制发动」，它根本不等问、在算这一刀的过程中就已经响完了，所以打死也拦不住它（实测＝反伤那 1 点照样落、牌照样摸进手）。⇒ 要不要把同一把闸也加到"不用问就响"那一类，还没有裁定，今天就按上面这样算。判据与取证＝PROJECT_HANDOFF.md §12-100）。</t>
+    <t>十种"哪一刻响"的说法，字面就是那件事发生的时刻。（"成为攻击目标时"这个旧名字 v2.8.21 起改成了泛指的"成为目标时"，具体被谁指名交给下面那一格说。）「受到伤害后」的判据（v2.8 刀5 起，您 2026-10-03 重新裁定）＝只有真的掉了体力才算受到了伤害：这一刀被护甲全挡住、一点血没掉 ⇒ 不算受到，技能不问也不响；伤害算出来是 0 或负数 ⇒ 也不算。掉多少算多少：普攻／技能伤害每一刀各算一声；决斗那一整场只在打完时按"这个将一共掉了多少体力"算一笔（见上面「决斗」那一格）。如果被这一下打死，它这两类技能都赶不上响应这一次——「受到伤害后」和「成为目标时」一起不算（2026-10-03 定案＝规则、不是毛病：游戏里这两问都是在"这一刀的全部后果算完"之后才开口问的，那时候人已经离场，没处可问；于是那一格本该产生的效果也不会发生，比如反伤的那 1 点、摸的那一张牌。它上一刀挨的、上一刀答过的都照常有效。v2.8.30 起这一条不再分"问不问人"（您 2026-10-03 追加裁定，原文＝「将领不在场上不能发动技能，被砍死了不算在场上，能发动就是空发，就算是『强制发动』不能发动」；判断时刻与上面同一把尺＝这一刀的全部后果算完之后人还在不在场）：勾了「强制发动」的这两型现在也一样——这一刀打死它，反伤那 1 点不落到来时、牌也不摸进手，与问人那一型逐字同形（界面上就是"压根没发生"）。没打死则照旧当场自己响完，时机一点没挪。唯一的豁口＝「自身被击杀时」那一型（遗言／遗计）：它按定义就是在主人离场这一声上发动，所以两边都放行，牌照旧摸进手。判据与取证＝PROJECT_HANDOFF.md §12-100 与 §12-101）。</t>
   </si>
   <si>
     <t>在场即生效（不用发动，人在就算）（v2.8 刀4 起可结算）</t>

--- a/词汇表.xlsx
+++ b/词汇表.xlsx
@@ -654,7 +654,7 @@
     <t>强制发动</t>
   </si>
   <si>
-    <t>编辑器里的开关（Excel 也有这一列）：满足触发条件与代价后直接响／直接适用效果，不用玩家点头。它跟锁定技不是一件事，跟"数值变化／持续生效"也不绑定，三者可以任意组合。v2.8.25 起这一格真的管事了：勾上之后，凡是本来会停下来问您"要不要发动"的那一刻（＝成为目标时／受到伤害后这两型），这条技能不再问、自己就响了；不勾就照旧问。四句实话边界：①它只决定"问不问人"，不会让一条技能多响一次，也不绕过发动门槛与代价；②本来就到点自动响的时机（登场／回合开始／击杀／失去手牌……）勾不勾都一样；③「回合结束时」那一型永远要您点头（一条技能不许响两次的常设规矩），勾了也不自响；④决斗那一套的"开局被点名"与"收官掉血"两刻同样吃这一格——勾了就自己响、没勾就问；⑤v2.8.30 起它也不绕过"人在场上"这一条：把主人打死的那一刀，它那份效果同样不落账（与不勾时问人的那一型同一判据、同一形状），只有「自身被击杀时」那一型放行。今天的官方 95 将与您手上的样本卡还没有一条勾了这个开关，所以对局里的表现与上一版逐字相同。</t>
+    <t>编辑器里的开关（Excel 也有这一列）：满足触发条件与代价后直接响／直接适用效果，不用玩家点头。它跟锁定技不是一件事，跟"数值变化／持续生效"也不绑定，三者可以任意组合。v2.8.25 起这一格真的管事了：勾上之后，凡是本来会停下来问您"要不要发动"的那一刻（＝成为目标时／受到伤害后这两型），这条技能不再问、自己就响了；不勾就照旧问。四句实话边界：①它只决定"问不问人"，不会让一条技能多响一次，也不绕过发动门槛与代价；②本来就到点自动响的时机（登场／回合开始／击杀／失去手牌……）勾不勾都一样；③「回合结束时」那一型永远要您点头（一条技能不许响两次的常设规矩），勾了也不自响；④决斗那一套的"开局被点名"与"收官掉血"两刻同样吃这一格——勾了就自己响、没勾就问；⑤v2.8.31 起它与"不勾"完全同一条时机判据（您 2026-10-04 定稿：强制发动和手动发动的处理必须一致，区别只在"需不需要玩家自行响应"）——被这一刀砍死时，勾了的「成为目标时」照样响、勾了的「受到伤害后」照样不响，与没勾时问您那一型逐字同形（只有「自身被击杀时」那一型放行）。今天的官方 95 将与您手上的样本卡还没有一条勾了这个开关，所以对局里的表现与上一版逐字相同。</t>
   </si>
   <si>
     <t>触发时机</t>
@@ -666,7 +666,7 @@
     <t>回合开始时 / 回合结束时 / 将领登场时 / 受到伤害后 / 造成伤害后 / 成为目标时 / 击杀将领时 / 自身被击杀时 / 失去手牌时 / 获得手牌时</t>
   </si>
   <si>
-    <t>十种"哪一刻响"的说法，字面就是那件事发生的时刻。（"成为攻击目标时"这个旧名字 v2.8.21 起改成了泛指的"成为目标时"，具体被谁指名交给下面那一格说。）「受到伤害后」的判据（v2.8 刀5 起，您 2026-10-03 重新裁定）＝只有真的掉了体力才算受到了伤害：这一刀被护甲全挡住、一点血没掉 ⇒ 不算受到，技能不问也不响；伤害算出来是 0 或负数 ⇒ 也不算。掉多少算多少：普攻／技能伤害每一刀各算一声；决斗那一整场只在打完时按"这个将一共掉了多少体力"算一笔（见上面「决斗」那一格）。如果被这一下打死，它这两类技能都赶不上响应这一次——「受到伤害后」和「成为目标时」一起不算（2026-10-03 定案＝规则、不是毛病：游戏里这两问都是在"这一刀的全部后果算完"之后才开口问的，那时候人已经离场，没处可问；于是那一格本该产生的效果也不会发生，比如反伤的那 1 点、摸的那一张牌。它上一刀挨的、上一刀答过的都照常有效。v2.8.30 起这一条不再分"问不问人"（您 2026-10-03 追加裁定，原文＝「将领不在场上不能发动技能，被砍死了不算在场上，能发动就是空发，就算是『强制发动』不能发动」；判断时刻与上面同一把尺＝这一刀的全部后果算完之后人还在不在场）：勾了「强制发动」的这两型现在也一样——这一刀打死它，反伤那 1 点不落到来时、牌也不摸进手，与问人那一型逐字同形（界面上就是"压根没发生"）。没打死则照旧当场自己响完，时机一点没挪。唯一的豁口＝「自身被击杀时」那一型（遗言／遗计）：它按定义就是在主人离场这一声上发动，所以两边都放行，牌照旧摸进手。判据与取证＝PROJECT_HANDOFF.md §12-100 与 §12-101）。</t>
+    <t>十种"哪一刻响"的说法，字面就是那件事发生的时刻。（"成为攻击目标时"这个旧名字 v2.8.21 起改成了泛指的"成为目标时"，具体被谁指名交给下面那一格说。）「受到伤害后」的判据（v2.8 刀5 起，您 2026-10-03 重新裁定）＝只有真的掉了体力才算受到了伤害：这一刀被护甲全挡住、一点血没掉 ⇒ 不算受到，技能不问也不响；伤害算出来是 0 或负数 ⇒ 也不算。掉多少算多少：普攻／技能伤害每一刀各算一声；决斗那一整场只在打完时按"这个将一共掉了多少体力"算一笔（见上面「决斗」那一格）。被这一刀打死的那一位，两类里只有「受到伤害后」不算（v2.8.31 定稿＝您 2026-10-04 把两类的定义封死：「成为目标时」＝受击，它在伤害算出来之前就发动完了，所以和这一刀实际打多少、主人会不会被这一刀砍死无关——被砍死的那一刀里它照样问、照样响；「受到伤害后」＝受伤，必须真的掉了血才成立，所以它在伤害之后才问，主人死在这一刀里就不问也不响）。两条路的判据一模一样，区别只在"需不需要您自己点头"。追加的那一条（甲）也在这里生效：反伤先把出手的那位扎死了⇒那一刀跟着取消，挨打的那位自救成功，粮草也没被吃掉。唯一的豁口＝「自身被击杀时」那一型（遗言／遗计）：它按定义就是在主人离场这一声上发动，所以两边都放行，牌照旧摸进手。判据与取证＝PROJECT_HANDOFF.md §12-100／§12-101／§12-102。</t>
   </si>
   <si>
     <t>在场即生效（不用发动，人在就算）（v2.8 刀4 起可结算）</t>

--- a/词汇表.xlsx
+++ b/词汇表.xlsx
@@ -36,7 +36,7 @@
     <t>· 出处：所有词条都对应到 文件:行号（仓库根＝Qoder/2.0）。规则类翻译另标了"定规则的代码在哪"，方便日后核对。</t>
   </si>
   <si>
-    <t>· 已知坑：第八节那十条"界面这么说、代码这么算"的冲突，第 1～8 条与第 10 条已经对齐（v2.8.14／v2.8.18）；第 9 条自 v2.8.25 起拆成两半——「强制发动」那一半已经进引擎（勾了就不问玩家、到点自己响），徽章那一半仍只是分类（锁定技的"不能被无效"、限定技的"一局一次"还没进引擎，等您口令）；已作废的旧写法在表里用 ~~删除线~~ 标出，投影进 Excel 时会渲染成"（旧说法，已作废）"。</t>
+    <t>· 已知坑：第八节那十条"界面这么说、代码这么算"的冲突，第 1～8 条与第 10 条已经对齐（v2.8.14／v2.8.18）；第 9 条自 v2.8.25 起拆成两半——「强制发动」那一半已经进引擎（勾了就不问玩家、到点自己响），徽章那一半：限定技的"一局一次"自 v2.8.32 起已经进引擎（见第四节「限定技」那一格），锁定技的"不能被无效"仍只是分类（引擎里压根没有"无效技能"这套机制，没有可以 enforcement 的对象）；已作废的旧写法在表里用 ~~删除线~~ 标出，投影进 Excel 时会渲染成"（旧说法，已作废）"。</t>
   </si>
   <si>
     <t>· 本轮之后如果界面改词，这张表要跟着改；它随 Git 走，别在别处另抄一份。</t>
@@ -624,7 +624,7 @@
     <t>限定技</t>
   </si>
   <si>
-    <t>分类徽章（"一局之内的次数额度，用完就没了"）。运行时不看它；引擎现在只有一本"每回合限一次"的账（core/GameState.ts:66＋action/resolvers/TurnEndSkillResolver.ts），"一局一次"这类更狠的额度还没有实现。</t>
+    <t>一局只许发动一次，用完就没了（src/skills/skillQuota.ts）。四条细则：① 额度记在每枚技能头上——一个将带两枚限定技就能各用一次；② 用完之后这枚技能在候选里照常列出、但灰掉，写明「本局已用尽」；③ 被人挡掉、无效掉不退额度（用过了就是用过了）；④ 想发动但没当成（代价付不出、被规则拒绝）不消耗额度。</t>
   </si>
   <si>
     <t>登场技</t>
@@ -648,7 +648,7 @@
     <t>觉醒技</t>
   </si>
   <si>
-    <t>分类徽章（"满足大条件后变强"）。本作目前没有任何觉醒机制：它现在纯粹是个标签。</t>
+    <t>分类徽章（您 2026-10-04 给的口径原文存档："一般是满足一定条件后可以自选发动，从而获得新技能或者改变已有技能的效果，非强制发动"）。翻译成对局里该发生的事＝条件满足了问您一次，您点头才生效，生效后这枚将拿到新技能或让老技能改效果；它不是到点自己响、也不是被动一直算数。本作目前还没有任何觉醒机制：徽章照常读写显示，引擎里没有人读它，所以今天挂不挂都不改变对局。单独一刀再做（裁决原文与判据＝PROJECT_HANDOFF.md §12-104⑥）。</t>
   </si>
   <si>
     <t>强制发动</t>
@@ -819,7 +819,7 @@
     <t>（旧说法，已作废）击破横幅上方那行残留的英文小字，v2.8.18 已翻成「本营击破」。</t>
   </si>
   <si>
-    <t>本节末尾必须说清的一件事：五个"××技"徽章和"强制发动"这一列，v2.8.19 起读得到、写得出、显示得出、还能核对（一枚技能可挂几枚；徽章与触发时机对不上会在编辑器与导入总结里点名）。这两样如今落地程度不同：「强制发动」v2.8.25 起接进对局了——全库只有一个地方读它（skills/SkillTriggerBridge.ts 的 defersToReactionQueue：受击／受伤这两型里没打勾的定义才交给问答队列问人，打了勾的直接走自动发动那条路），所以它管的事恰恰只有一件＝"这一刻问不问您"；徽章里「锁定技」v2.8 刀4 起有了第一个结算侧的消费者，但只管一寸地方：编译器认出这枚徽章 → 这条技能往数值账本落的那笔账打上"移不走"的记号（statModifiers.revokeModifier 是全库唯一"移走别人那笔账"的入口，它见到这个记号就拒绝）。徽章的其余部分（"不能被无效""不能被改变"在伤害、护甲、被弃牌这些环节到底管不管）今天仍然没有任何结算代码读它；另外四枚徽章（限定／登场／遗计／觉醒）还是纯分类，限定技的"一局一次"额度依然没进引擎。所以现在决定一条技能"什么时候响、响不响、响几次"的是：触发时机（含细分）＋「我听谁」与「被谁指名」这两档监听范围（v2.8.21 起触发桥逐条读；两档的缺省＝只听自己／只算攻击，⇒ 与今天对局逐字一致。"成为技能目标"这一声 v2.8.24 起已有发射器＝决斗开局（其余技能指名目标的路仍未发这一声，等内容刀））＋ 发动门槛 ＋ 那条"每回合限一次"的账 ＋「强制发动」这一格（v2.8.25 起，只管问不问人）。「在场即生效」那一型不看上面这些，它只在登场／离场两刻动账本。徽章的读写口径全库只有一份，在 domain/skillTags.ts。</t>
+    <t>本节末尾必须说清的一件事：五个"××技"徽章和"强制发动"这一列，v2.8.19 起读得到、写得出、显示得出、还能核对（一枚技能可挂几枚；徽章与触发时机对不上会在编辑器与导入总结里点名）。这两样如今落地程度不同：「强制发动」v2.8.25 起接进对局了——全库只有一个地方读它（skills/SkillTriggerBridge.ts 的 defersToReactionQueue：受击／受伤这两型里没打勾的定义才交给问答队列问人，打了勾的直接走自动发动那条路），所以它管的事恰恰只有一件＝"这一刻问不问您"；徽章里「锁定技」v2.8 刀4 起有了第一个结算侧的消费者，但只管一寸地方：编译器认出这枚徽章 → 这条技能往数值账本落的那笔账打上"移不走"的记号（statModifiers.revokeModifier 是全库唯一"移走别人那笔账"的入口，它见到这个记号就拒绝）。徽章的其余部分（"不能被无效""不能被改变"在伤害、护甲、被弃牌这些环节到底管不管）今天仍然没有任何结算代码读它；四枚徽章里限定技自 v2.8.32 起有了第二个结算侧消费者（编译器认出它 ⇒ 这枚技能每发动一次就在同一本账上落一笔，账上有这一笔就不再让它发动；"一局一次"的判据与记账形状全库只有一份＝skills/skillQuota.ts，三条发动路——回合结束、停下问您、到点自己响——都从这里过），登场／遗计／觉醒还是纯分类。所以现在决定一条技能"什么时候响、响不响、响几次"的是：触发时机（含细分）＋「我听谁」与「被谁指名」这两档监听范围（v2.8.21 起触发桥逐条读；两档的缺省＝只听自己／只算攻击，⇒ 与今天对局逐字一致。"成为技能目标"这一声 v2.8.24 起已有发射器＝决斗开局（其余技能指名目标的路仍未发这一声，等内容刀））＋ 发动门槛 ＋ 那条"每回合限一次"的账 ＋ 限定技"一局一次"的账（v2.8.32 起）＋「强制发动」这一格（v2.8.25 起，只管问不问人）。「在场即生效」那一型不看上面这些，它只在登场／离场两刻动账本。徽章的读写口径全库只有一份，在 domain/skillTags.ts。</t>
   </si>
   <si>
     <t>游戏结束 / 对局结束</t>
@@ -1182,10 +1182,10 @@
     <t>编辑器只有单枚标签下拉、卡面只印一枚（旧说法，已作废） 已多枚化（v2.8.19：编辑器一排徽章可同时点亮几枚，Excel「技能标签」格用顿号分开写，图鉴／卡面／对局几枚都显示）</t>
   </si>
   <si>
-    <t>两半现在分开了：「强制发动」那半 v2.8.25 已进引擎（SkillTriggerBridge.defersToReactionQueue 读它⇒勾了就不问人、直接走自动发动路；全库只有这一处读，所以它只管"问不问"这一件事）；五个徽章那半结算里仍一处都不读 tags/tag——锁定技的"不能被无效、不能被改变"、限定技的"一局一次"还没进引擎。读写口径全库只有一份（domain/skillTags.ts）</t>
-  </si>
-  <si>
-    <t>✅ 您的更正口径已逐字落进第四节：「锁定技实际上是指无法被无效和改变的技能，而强制发动则是指某些技能在满足触发条件和代价后会强制发动/直接适用其效果，两者和数值变化+永续生效的组合一样，不是强关联」；样本＝闭月同时挂 锁定技＋遗计技。强制发动那一刀已开完（v2.8.25，两锚逐字未动＝今天还没有一条数据勾着它）；剩下的锁定技／限定技执法仍要改引擎、会换锚，等您口令再开</t>
+    <t>三半现在分开了：「强制发动」那半 v2.8.25 已进引擎（SkillTriggerBridge.defersToReactionQueue 读它⇒勾了就不问人、直接走自动发动路；全库只有这一处读，所以它只管"问不问"这一件事）；限定技那半 v2.8.32 已进引擎（编译器读这枚徽章 ⇒ 落额度键；三条发动路的"还能不能发动"与"记这一笔账"全库只有一份＝skills/skillQuota.ts）；剩下锁定技的"不能被无效、不能被改变"结算里仍一处不读——引擎压根没有"无效一枚技能"这套机制，没有可执法的对象（唯一消费者是 v2.8 刀4 那寸"账本移不走"记号）。读写口径全库只有一份（domain/skillTags.ts）</t>
+  </si>
+  <si>
+    <t>✅ 您的更正口径已逐字落进第四节：「锁定技实际上是指无法被无效和改变的技能，而强制发动则是指某些技能在满足触发条件和代价后会强制发动/直接适用其效果，两者和数值变化+永续生效的组合一样，不是强关联」；样本＝闭月同时挂 锁定技＋遗计技。强制发动那一刀已开完（v2.8.25，两锚逐字未动＝今天还没有一条数据勾着它）；限定技那一刀已开完（v2.8.32，同样本池还没有一条数据挂着它⇒两锚读数见 §H10）；锁定技"被无效"那一半不做（没有机制可执法，等引擎长出一套"无效技能"再议）</t>
   </si>
   <si>
     <t>10</t>

--- a/词汇表.xlsx
+++ b/词汇表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="405">
   <si>
     <t>玩家词汇 · 大白话对照表（v2.8.18 界面口径）</t>
   </si>
@@ -27,7 +27,8 @@
     <t/>
   </si>
   <si>
-    <t>本文件是唯一事实源：Excel 版 词汇表.xlsx（与本文件同目录）由 npm run glossary-xlsx 从本文件生成，不要手抄、不要在 Excel 里改内容列；要改词就改这里再重跑那一条命令（测试里有一条守卫专门盯着这件事：改了本文件却没重跑，npm test 就会红）。Excel 里第三列「你的理解」才是给您填的；您填的答案请同时抄回本文件的第三列（或直接写在 md 里）——重跑生成命令会把 Excel 整个覆盖掉，只留在 Excel 里的字会丢。</t>
+    <t xml:space="preserve">本文件是唯一事实源：Excel 版 词汇表.xlsx（与本文件同目录）由 npm run glossary-xlsx 从本文件生成，不要手抄、不要在 Excel 里改内容列；要改词就改这里再重跑那一条命令（测试里有一条守卫专门盯着这件事：改了本文件却没重跑，npm test 就会红）。Excel 里第三列「你的理解」才是给您填的；您填的答案请同时抄回本文件的第三列（或直接写在 md 里）——重跑生成命令会把 Excel 整个覆盖掉，只留在 Excel 里的字会丢。一格要写好几行时，在 md 里用 
+ 分开（Excel 里就显示成换行），别直接在表格里敲回车，那会把这一行劈断。本轮您的 13 条答复已逐字抄进第三列（2026-10-06）。</t>
   </si>
   <si>
     <t>这张表怎么用：第一列是玩家在游戏里真的会看到的词（逐处从界面代码里捞出来的，不是设想出来的）；第二列是我给的大白话翻译；第三列留给你填——填你心里认为这个词实际是什么效果。两列不一致的地方，就是下一步要定的规则。</t>
@@ -84,18 +85,27 @@
     <t>轮到某一家行动的完整一圈：先抽卡，再让将领动，最后收个尾。</t>
   </si>
   <si>
+    <t>一个回合分为回合开始阶段、行动阶段、回合结束阶段三部分。</t>
+  </si>
+  <si>
     <t>第N轮</t>
   </si>
   <si>
     <t>每家都回合过一次＝一轮走完。第 1 轮的抽卡数和后面不一样（见"抽卡阶段"）。</t>
   </si>
   <si>
+    <t>补充：除了规则上不存在“抽卡阶段”这一点，基本无异议。</t>
+  </si>
+  <si>
     <t>你的回合</t>
   </si>
   <si>
     <t>现在轮到你了，可以操作。</t>
   </si>
   <si>
+    <t>无异议</t>
+  </si>
+  <si>
     <t>AI 出手中…</t>
   </si>
   <si>
@@ -114,6 +124,11 @@
     <t>你征召来、还没登场（没派上场）的将领，堆在这儿候着。抽卡时它能当抽卡来源之一。</t>
   </si>
   <si>
+    <t xml:space="preserve">将领池：将领池由主要势力X个+群雄势力Y个=30/15个组成，其中群雄势力占比不能超过1/3（向下取整，允许为0），如晋国为主要势力则不限制群雄势力占比
+【游戏开始抽25张主势力，15张群雄来组成30张卡。或者是主15，群10组成15张】
+同一卡组只能存在一个同名武将</t>
+  </si>
+  <si>
     <t>抽牌堆</t>
   </si>
   <si>
@@ -150,6 +165,9 @@
     <t>每家的大本营，有独立血量（初始 6）。归零这家就打完了。定规则：不管是普通攻击还是技能打来的，本营每次挨打最多掉 1 点（v2.8.29 起技能伤害也走这一条；那个"1"只写在一个地方＝core/baseDamage.ts）。</t>
   </si>
   <si>
+    <t>营地：也作为一个目标存在于场地上，每次受到伤害时最多减少1点体力，初始体力6点，没有体力上限，营地所在的区域统称营地区域，营地为营地区域内的一个目标。</t>
+  </si>
+  <si>
     <t>营地</t>
   </si>
   <si>
@@ -192,18 +210,27 @@
     <t>卡上自带的那点护甲底数（不叠甲也有）。</t>
   </si>
   <si>
+    <t>这个是护甲上限的意思吗？</t>
+  </si>
+  <si>
     <t>整备</t>
   </si>
   <si>
     <t>叠完甲之后的"定住"状态：本回合不能移动、不能攻击、也不能再叠甲。到下个回合开始或被别人打中才解除。定规则：action/resolvers/ArmorResolver.ts:30、core/eventProcessors/turnEvents.ts:34、core/eventProcessors/damageEvents.ts:134</t>
   </si>
   <si>
+    <t>纠正：整备状态在下个回合开始自动解除，所有行动均不会解除整备状态，除非是某些特殊的技能效果</t>
+  </si>
+  <si>
     <t>近战</t>
   </si>
   <si>
     <t>两义：①卡上的属性数字（⚔️近战 2＝近战能打多狠）；②行动按钮（⚔️近战(-1牌)＝打一次烧 1 张手牌）。</t>
   </si>
   <si>
+    <t>补充：某些将领的技能可以改变自身的远程攻击范围</t>
+  </si>
+  <si>
     <t>远程</t>
   </si>
   <si>
@@ -240,6 +267,9 @@
     <t>"散人群"标签。可以选进队伍当将领来源，但不能当你家主势力，且征召时限 1～3 名。</t>
   </si>
   <si>
+    <t>纠正：征召数量限制参考将领池部分，与现有规则略有不同</t>
+  </si>
+  <si>
     <t>身份</t>
   </si>
   <si>
@@ -336,6 +366,9 @@
     <t>喂粮草回血：交几张牌＝回几点体力，但在敌方地盘要多烧 1 张且不回数（交 3 张回 2 点）。封顶补到体力上限为止、多交的牌也不退；每个回合各将领可补一次（不是全局一局一次）。定规则：action/resolvers/SupplyResolver.ts:65、清零见 core/eventProcessors/turnEvents.ts:32</t>
   </si>
   <si>
+    <t>补充：补给消耗的牌数遵循1牌＝1体力，消耗数必须≤已损失体力值（因技能效果或规则要求的额外不算在内）</t>
+  </si>
+  <si>
     <t>⚠️ 敌方区域：补给多烧 1 张手牌，这张只算代价、不算回复（交 3 张只回 2 点）</t>
   </si>
   <si>
@@ -541,6 +574,9 @@
   </si>
   <si>
     <t>就是上面那条扣血，要你按一下才落地。v2.8.18 前这几行写的是"营地"，其实扣的一直是本营的血——两个词现在分开了。</t>
+  </si>
+  <si>
+    <t>两个词现在改回去了，叫营地和营地区域</t>
   </si>
   <si>
     <t>🏯 创建房间 / 房间名称 / 游戏人数</t>
@@ -1744,48 +1780,48 @@
         <v>20</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -1793,32 +1829,32 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -1826,10 +1862,10 @@
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -1837,10 +1873,10 @@
     </row>
     <row r="11" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>1</v>
@@ -1848,10 +1884,10 @@
     </row>
     <row r="12" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>1</v>
@@ -1859,21 +1895,21 @@
     </row>
     <row r="13" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>1</v>
@@ -1881,10 +1917,10 @@
     </row>
     <row r="15" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>1</v>
@@ -1892,10 +1928,10 @@
     </row>
     <row r="16" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>1</v>
@@ -1903,10 +1939,10 @@
     </row>
     <row r="17" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>1</v>
@@ -1914,10 +1950,10 @@
     </row>
     <row r="18" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>1</v>
@@ -1925,10 +1961,10 @@
     </row>
     <row r="19" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>1</v>
@@ -1936,43 +1972,43 @@
     </row>
     <row r="20" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>1</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>1</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>1</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>1</v>
@@ -1980,10 +2016,10 @@
     </row>
     <row r="24" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>1</v>
@@ -1991,10 +2027,10 @@
     </row>
     <row r="25" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>1</v>
@@ -2002,10 +2038,10 @@
     </row>
     <row r="26" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>1</v>
@@ -2013,10 +2049,10 @@
     </row>
     <row r="27" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>1</v>
@@ -2024,21 +2060,21 @@
     </row>
     <row r="28" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>1</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>1</v>
@@ -2046,10 +2082,10 @@
     </row>
     <row r="30" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>1</v>
@@ -2057,10 +2093,10 @@
     </row>
     <row r="31" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>1</v>
@@ -2095,10 +2131,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -2106,10 +2142,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -2117,10 +2153,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -2128,10 +2164,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -2139,10 +2175,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -2150,10 +2186,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -2161,10 +2197,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -2172,10 +2208,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -2183,10 +2219,10 @@
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -2194,10 +2230,10 @@
     </row>
     <row r="11" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>1</v>
@@ -2205,10 +2241,10 @@
     </row>
     <row r="12" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>1</v>
@@ -2216,10 +2252,10 @@
     </row>
     <row r="13" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>1</v>
@@ -2227,21 +2263,21 @@
     </row>
     <row r="14" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>1</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>1</v>
@@ -2249,10 +2285,10 @@
     </row>
     <row r="16" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>1</v>
@@ -2260,10 +2296,10 @@
     </row>
     <row r="17" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>1</v>
@@ -2271,10 +2307,10 @@
     </row>
     <row r="18" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>1</v>
@@ -2282,10 +2318,10 @@
     </row>
     <row r="19" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>1</v>
@@ -2293,10 +2329,10 @@
     </row>
     <row r="20" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>1</v>
@@ -2304,10 +2340,10 @@
     </row>
     <row r="21" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>1</v>
@@ -2315,10 +2351,10 @@
     </row>
     <row r="22" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>1</v>
@@ -2326,10 +2362,10 @@
     </row>
     <row r="23" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>1</v>
@@ -2337,10 +2373,10 @@
     </row>
     <row r="24" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>1</v>
@@ -2348,10 +2384,10 @@
     </row>
     <row r="25" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>1</v>
@@ -2359,10 +2395,10 @@
     </row>
     <row r="26" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>1</v>
@@ -2370,10 +2406,10 @@
     </row>
     <row r="27" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>1</v>
@@ -2381,10 +2417,10 @@
     </row>
     <row r="28" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>1</v>
@@ -2392,10 +2428,10 @@
     </row>
     <row r="29" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>1</v>
@@ -2403,10 +2439,10 @@
     </row>
     <row r="30" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>1</v>
@@ -2414,10 +2450,10 @@
     </row>
     <row r="31" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>1</v>
@@ -2425,10 +2461,10 @@
     </row>
     <row r="32" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>1</v>
@@ -2436,10 +2472,10 @@
     </row>
     <row r="33" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>1</v>
@@ -2447,10 +2483,10 @@
     </row>
     <row r="34" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>1</v>
@@ -2458,10 +2494,10 @@
     </row>
     <row r="35" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>1</v>
@@ -2469,10 +2505,10 @@
     </row>
     <row r="36" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>1</v>
@@ -2480,10 +2516,10 @@
     </row>
     <row r="37" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>1</v>
@@ -2491,10 +2527,10 @@
     </row>
     <row r="38" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>1</v>
@@ -2502,10 +2538,10 @@
     </row>
     <row r="39" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>1</v>
@@ -2540,10 +2576,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -2551,10 +2587,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -2562,21 +2598,21 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -2584,10 +2620,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -2595,10 +2631,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -2606,10 +2642,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -2617,10 +2653,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -2628,21 +2664,21 @@
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>1</v>
@@ -2650,10 +2686,10 @@
     </row>
     <row r="12" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>1</v>
@@ -2661,10 +2697,10 @@
     </row>
     <row r="13" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>1</v>
@@ -2672,10 +2708,10 @@
     </row>
     <row r="14" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>1</v>
@@ -2683,10 +2719,10 @@
     </row>
     <row r="15" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>1</v>
@@ -2694,10 +2730,10 @@
     </row>
     <row r="16" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>1</v>
@@ -2705,10 +2741,10 @@
     </row>
     <row r="17" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>1</v>
@@ -2716,10 +2752,10 @@
     </row>
     <row r="18" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>1</v>
@@ -2727,10 +2763,10 @@
     </row>
     <row r="19" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>1</v>
@@ -2738,10 +2774,10 @@
     </row>
     <row r="20" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>1</v>
@@ -2749,10 +2785,10 @@
     </row>
     <row r="21" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>1</v>
@@ -2760,10 +2796,10 @@
     </row>
     <row r="22" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>1</v>
@@ -2798,10 +2834,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -2809,10 +2845,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -2820,10 +2856,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -2831,10 +2867,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -2842,10 +2878,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -2853,10 +2889,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -2864,10 +2900,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -2875,10 +2911,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -2886,10 +2922,10 @@
     </row>
     <row r="10" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -2900,10 +2936,10 @@
     </row>
     <row r="11" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>1</v>
@@ -2911,10 +2947,10 @@
     </row>
     <row r="12" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>1</v>
@@ -2922,10 +2958,10 @@
     </row>
     <row r="13" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>1</v>
@@ -2933,10 +2969,10 @@
     </row>
     <row r="14" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>1</v>
@@ -2944,10 +2980,10 @@
     </row>
     <row r="15" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>1</v>
@@ -2955,10 +2991,10 @@
     </row>
     <row r="16" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>1</v>
@@ -2966,10 +3002,10 @@
     </row>
     <row r="17" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>1</v>
@@ -2977,10 +3013,10 @@
     </row>
     <row r="18" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>1</v>
@@ -2988,10 +3024,10 @@
     </row>
     <row r="19" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>1</v>
@@ -2999,10 +3035,10 @@
     </row>
     <row r="20" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>1</v>
@@ -3010,10 +3046,10 @@
     </row>
     <row r="21" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>1</v>
@@ -3021,10 +3057,10 @@
     </row>
     <row r="22" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>1</v>
@@ -3032,10 +3068,10 @@
     </row>
     <row r="23" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>1</v>
@@ -3043,10 +3079,10 @@
     </row>
     <row r="24" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>1</v>
@@ -3054,10 +3090,10 @@
     </row>
     <row r="25" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>1</v>
@@ -3065,10 +3101,10 @@
     </row>
     <row r="26" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>1</v>
@@ -3076,10 +3112,10 @@
     </row>
     <row r="27" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>1</v>
@@ -3087,10 +3123,10 @@
     </row>
     <row r="28" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>1</v>
@@ -3098,10 +3134,10 @@
     </row>
     <row r="29" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>1</v>
@@ -3109,10 +3145,10 @@
     </row>
     <row r="30" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>1</v>
@@ -3120,10 +3156,10 @@
     </row>
     <row r="31" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>1</v>
@@ -3131,10 +3167,10 @@
     </row>
     <row r="32" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>1</v>
@@ -3142,10 +3178,10 @@
     </row>
     <row r="33" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>1</v>
@@ -3153,10 +3189,10 @@
     </row>
     <row r="34" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>1</v>
@@ -3164,10 +3200,10 @@
     </row>
     <row r="35" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>1</v>
@@ -3175,7 +3211,7 @@
     </row>
     <row r="37" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -3212,10 +3248,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3223,10 +3259,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3234,10 +3270,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3245,10 +3281,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3256,10 +3292,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3267,10 +3303,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3278,10 +3314,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3289,10 +3325,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3300,10 +3336,10 @@
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -3338,10 +3374,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3349,10 +3385,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3360,10 +3396,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3371,10 +3407,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3382,10 +3418,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3393,10 +3429,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3404,10 +3440,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3415,10 +3451,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3426,10 +3462,10 @@
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -3437,10 +3473,10 @@
     </row>
     <row r="11" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>1</v>
@@ -3448,10 +3484,10 @@
     </row>
     <row r="12" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>1</v>
@@ -3459,10 +3495,10 @@
     </row>
     <row r="13" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>1</v>
@@ -3470,10 +3506,10 @@
     </row>
     <row r="14" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>1</v>
@@ -3481,10 +3517,10 @@
     </row>
     <row r="15" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>1</v>
@@ -3492,10 +3528,10 @@
     </row>
     <row r="16" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>1</v>
@@ -3503,10 +3539,10 @@
     </row>
     <row r="17" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>1</v>
@@ -3514,10 +3550,10 @@
     </row>
     <row r="18" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>1</v>
@@ -3525,10 +3561,10 @@
     </row>
     <row r="19" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>1</v>
@@ -3552,10 +3588,10 @@
   <sheetData>
     <row r="1" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>18</v>
@@ -3563,10 +3599,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3574,10 +3610,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3585,10 +3621,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3596,10 +3632,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3607,10 +3643,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3618,10 +3654,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3629,10 +3665,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3640,10 +3676,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3668,189 +3704,189 @@
   <sheetData>
     <row r="1" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
     </row>
   </sheetData>

--- a/词汇表.xlsx
+++ b/词汇表.xlsx
@@ -159,25 +159,25 @@
     <t>只放将领卡的坟场（被打死的将领进这儿）。它只是给你看的账本，里面的将领会不会回到你手里？当前规则：不会。</t>
   </si>
   <si>
-    <t>本营</t>
-  </si>
-  <si>
-    <t>每家的大本营，有独立血量（初始 6）。归零这家就打完了。定规则：不管是普通攻击还是技能打来的，本营每次挨打最多掉 1 点（v2.8.29 起技能伤害也走这一条；那个"1"只写在一个地方＝core/baseDamage.ts）。</t>
+    <t>营地</t>
+  </si>
+  <si>
+    <t>每家的大本营，它自己是场地上中的一个目标（站在自家营地区域正中间那一格）。有独立血量，初始 6 点，没有体力上限（体力允许超过 6 点）。归零这家就打完了。定规则：不管是普通攻击还是技能打来的，营地每次挨打最多掉 1 点（v2.8.29 起技能伤害也走这一条；那个"1"只写在一个地方＝core/baseDamage.ts）。〔v2.8.39 就地更正：本条目旧名"本营"，您 2026-10-06 裁"改回'营地'这个叫法"，界面与写出侧已零残留（Excel 读入侧仍认旧写法那一格，属"旧词只进不出"）；"没有体力上限"同一轮裁为规则——只有测试擂台当年把它当过上限，那两把夹已摘掉。〕</t>
   </si>
   <si>
     <t>营地：也作为一个目标存在于场地上，每次受到伤害时最多减少1点体力，初始体力6点，没有体力上限，营地所在的区域统称营地区域，营地为营地区域内的一个目标。</t>
   </si>
   <si>
-    <t>营地</t>
-  </si>
-  <si>
-    <t>你自家那一格一格放将领的地盘（棋盘区域之一，将领先站在这儿）。它不流血：抽卡窗那句"本营将失去1点体力"扣的是上面那个"本营"，v2.8.18 已把这两个词分开写死了。定规则：action/resolvers/ResolveBaseLossResolver.ts:24</t>
+    <t>营地区域</t>
+  </si>
+  <si>
+    <t>你自家那一格一格放将领的地盘（棋盘区域之一，将领先站在这儿），共 3 格：左右两格站将领、正中间那格就是上面那个"营地"。定规则：rules/battlefieldRules.ts:84（站位＝0 与 2）。〔旧条目名"营地"；v2.8.18 曾把"流血的那个"改叫"本营"以免两词混淆，v2.8.39 按您裁决改回"营地＋营地区域"这一组叫法——扣血的一直是同一格，从未变过。〕</t>
   </si>
   <si>
     <t>前线</t>
   </si>
   <si>
-    <t>营地和战场中间的那条带子，是抢地盘的缓冲带。</t>
+    <t>营地区域和战场中间的那条带子，是抢地盘的缓冲带（同样 3 格）。</t>
   </si>
   <si>
     <t>战场</t>
@@ -216,7 +216,7 @@
     <t>整备</t>
   </si>
   <si>
-    <t>叠完甲之后的"定住"状态：本回合不能移动、不能攻击、也不能再叠甲。到下个回合开始或被别人打中才解除。定规则：action/resolvers/ArmorResolver.ts:30、core/eventProcessors/turnEvents.ts:34、core/eventProcessors/damageEvents.ts:134</t>
+    <t>叠完甲之后的"定住"状态：本回合不能移动、不能攻击、也不能再叠甲。挨打不会把它打掉，主动移动／攻击／补给也不会——只有三条路收得掉它：①下个回合开始自动解除（core/eventProcessors/turnEvents.ts:34）；②这名将领被打死、随离场一起收掉（core/eventProcessors/damageEvents.ts:151，只在那一支里）；③身上军备被拆到一张不剩（core/eventProcessors/generalEvents.ts:349，v2.7.4 已裁：甲没了，"整备"也就没有载体）。今后若有技能明写"解除整备"，那是第四条。定规则：叠甲即进入整备＝action/resolvers/ArmorResolver.ts:68〔v2.8.39 就地更正：本条旧文案写过"到下个回合开始或被别人打中才解除"，那句是我写错了——引擎从来没有"挨打解除"这条路，您 2026-10-06 裁"把'被打也解除'去掉"，文案已按代码改齐〕</t>
   </si>
   <si>
     <t>纠正：整备状态在下个回合开始自动解除，所有行动均不会解除整备状态，除非是某些特殊的技能效果</t>
@@ -564,16 +564,16 @@
     <t>没将可摸了，只能摸牌摞。</t>
   </si>
   <si>
-    <t>本次抽卡后将领池将被抽空；将领池为空时，回合开始时本营将失去1点体力</t>
-  </si>
-  <si>
-    <t>提醒：把将池抽光之后，以后每回合开头本营先掉 1 点血，再摸牌。</t>
-  </si>
-  <si>
-    <t>🏯💥 本营受到伤害 / 结算失去体力 / 先结算本营失去体力，若存活再进行抽卡</t>
-  </si>
-  <si>
-    <t>就是上面那条扣血，要你按一下才落地。v2.8.18 前这几行写的是"营地"，其实扣的一直是本营的血——两个词现在分开了。</t>
+    <t>本次抽卡后将领池将被抽空；将领池为空时，回合开始时营地将失去1点体力</t>
+  </si>
+  <si>
+    <t>提醒：把将池抽光之后，以后每回合开头营地先掉 1 点血，再摸牌。</t>
+  </si>
+  <si>
+    <t>🏯💥 营地受到伤害 / 结算失去体力 / 先结算营地失去体力，若存活再进行抽卡</t>
+  </si>
+  <si>
+    <t>就是上面那条扣血，要你按一下才落地。〔v2.8.39 就地更正：这几行曾写"营地"→v2.8.18 改成"本营"→您 2026-10-06 裁"改回'营地'"，现已回到"营地"，扣的血、掉的体力从头到尾都是同一个东西，只是叫法绕了一圈。〕</t>
   </si>
   <si>
     <t>两个词现在改回去了，叫营地和营地区域</t>
@@ -648,7 +648,7 @@
     <t>AI·随机 / AI·保守 / AI·均衡 / AI·激进</t>
   </si>
   <si>
-    <t>电脑打法的四档性格：闭眼乱抓牌（入门陪练）／重守本营爱惜将领／攻守各半稳扎稳打／猛打猛冲抢占地盘。</t>
+    <t>电脑打法的四档性格：闭眼乱抓牌（入门陪练）／重守营地爱惜将领／攻守各半稳扎稳打／猛打猛冲抢占地盘。</t>
   </si>
   <si>
     <t>锁定技</t>
@@ -822,7 +822,7 @@
     <t>修改数值（效果类型，v2.8 刀4 起可结算）</t>
   </si>
   <si>
-    <t>第十一条效果类型。它不改卡面上的印刷数字，而是给这名将领记一笔"账"（引擎里那本账叫 state.statModifiers，随存档走、录像能重放）。所以同一张卡在棋盘上会同时存在两个数：卡上印的（永远不变，图鉴与手抄核对用它）和当下算数的（对局里真正用来砍人的）。今天有四个数能被这样改：近战攻击力／远程攻击力／体力上限（v2.8 刀4）＋受到的伤害（v2.8 刀5）。五句实话：①当前体力不走这本账（它本来就是"损失记录"那一本，回血、扣血照旧直接动它）；②护甲、手牌上限这一版还没接（写了会被点名跳过）；③只能改自己的账面数字——"让别人的攻击＋1"那种跨将改数还没有目标选择器，编译时逐条点名跳过；④「受到的伤害」这一格作用在护甲之前：先把伤害这个数摁好，再交给"2 点护甲挡 1 点"那套算术，所以它是"看不见的减伤"，不是第二层护甲，也不改变身上有没有护甲这件事；本营（老家）不吃这一格——规则上本营单次受到的伤害最多 1 点，那一条由攻击那一步钉死，不是账本管的事；⑤官方 95 将与您手上的样本卡今天还没有一条用它（仓库那叠试作样本除外），所以对局表现与上一版逐字相同。</t>
+    <t>第十一条效果类型。它不改卡面上的印刷数字，而是给这名将领记一笔"账"（引擎里那本账叫 state.statModifiers，随存档走、录像能重放）。所以同一张卡在棋盘上会同时存在两个数：卡上印的（永远不变，图鉴与手抄核对用它）和当下算数的（对局里真正用来砍人的）。今天有四个数能被这样改：近战攻击力／远程攻击力／体力上限（v2.8 刀4）＋受到的伤害（v2.8 刀5）。五句实话：①当前体力不走这本账（它本来就是"损失记录"那一本，回血、扣血照旧直接动它）；②护甲、手牌上限这一版还没接（写了会被点名跳过）；③只能改自己的账面数字——"让别人的攻击＋1"那种跨将改数还没有目标选择器，编译时逐条点名跳过；④「受到的伤害」这一格作用在护甲之前：先把伤害这个数摁好，再交给"2 点护甲挡 1 点"那套算术，所以它是"看不见的减伤"，不是第二层护甲，也不改变身上有没有护甲这件事；营地（老家）不吃这一格——规则上营地单次受到的伤害最多 1 点，那一条由攻击那一步钉死，不是账本管的事；⑤官方 95 将与您手上的样本卡今天还没有一条用它（仓库那叠试作样本除外），所以对局表现与上一版逐字相同。</t>
   </si>
   <si>
     <t>改哪个数 / 怎么改 / 有效周期（Excel 里效果组第 9–11 列）</t>
@@ -846,13 +846,13 @@
     <t>击破 / 出局 / 阵亡 / 获得胜利</t>
   </si>
   <si>
-    <t>同一件事的不同说法：将领或本营被打到底＝那家出局；横幅写"X势力击破"（上方那行小字「本营击破」），日志写"阵亡"，结算写"获得胜利"。游戏里没有"淘汰"这个词。</t>
+    <t>同一件事的不同说法：将领或营地被打到底＝那家出局；横幅写"X势力击破"（上方那行小字「营地击破」），日志写"阵亡"，结算写"获得胜利"。游戏里没有"淘汰"这个词。</t>
   </si>
   <si>
     <t>BASE DESTROYED（旧说法，已作废）</t>
   </si>
   <si>
-    <t>（旧说法，已作废）击破横幅上方那行残留的英文小字，v2.8.18 已翻成「本营击破」。</t>
+    <t>（旧说法，已作废）击破横幅上方那行残留的英文小字，v2.8.18 已翻成中文，v2.8.39 起那里写的是「营地击破」。</t>
   </si>
   <si>
     <t>本节末尾必须说清的一件事：五个"××技"徽章和"强制发动"这一列，v2.8.19 起读得到、写得出、显示得出、还能核对（一枚技能可挂几枚；徽章与触发时机对不上会在编辑器与导入总结里点名）。这两样如今落地程度不同：「强制发动」v2.8.25 起接进对局了——全库只有一个地方读它（skills/SkillTriggerBridge.ts 的 defersToReactionQueue：受击／受伤这两型里没打勾的定义才交给问答队列问人，打了勾的直接走自动发动那条路），所以它管的事恰恰只有一件＝"这一刻问不问您"；徽章里「锁定技」v2.8 刀4 起有了第一个结算侧的消费者，但只管一寸地方：编译器认出这枚徽章 → 这条技能往数值账本落的那笔账打上"移不走"的记号（statModifiers.revokeModifier 是全库唯一"移走别人那笔账"的入口，它见到这个记号就拒绝）。徽章的其余部分（"不能被无效""不能被改变"在伤害、护甲、被弃牌这些环节到底管不管）今天仍然没有任何结算代码读它；四枚徽章里限定技自 v2.8.32 起有了第二个结算侧消费者（编译器认出它 ⇒ 这枚技能每发动一次就在同一本账上落一笔，账上有这一笔就不再让它发动；"一局一次"的判据与记账形状全库只有一份＝skills/skillQuota.ts，三条发动路——回合结束、停下问您、到点自己响——都从这里过），登场／遗计／觉醒还是纯分类。所以现在决定一条技能"什么时候响、响不响、响几次"的是：触发时机（含细分）＋「我听谁」与「被谁指名」这两档监听范围（v2.8.21 起触发桥逐条读；两档的缺省＝只听自己／只算攻击，⇒ 与今天对局逐字一致。"成为技能目标"这一声 v2.8.24 起已有发射器＝决斗开局（其余技能指名目标的路仍未发这一声，等内容刀））＋ 发动门槛 ＋ 那条"每回合限一次"的账 ＋ 限定技"一局一次"的账（v2.8.32 起）＋「强制发动」这一格（v2.8.25 起，只管问不问人）。「在场即生效」那一型不看上面这些，它只在登场／离场两刻动账本。徽章的读写口径全库只有一份，在 domain/skillTags.ts。</t>
@@ -957,7 +957,7 @@
     <t>技能测试场 / ⚗️ 测试场</t>
   </si>
   <si>
-    <t>手动造局面、验证一条技能的小屋（能直接改体力/上限/伤害/本营/加牌）。</t>
+    <t>手动造局面、验证一条技能的小屋（能直接改体力/上限/伤害/营地血量/加牌）。营地那一格 v2.8.39 起没有上限，"+1""回6"之外还能一路往上加。</t>
   </si>
   <si>
     <t>🤖 AI 对战演练</t>
@@ -1116,7 +1116,7 @@
     <t>扣的是本营血量（ResolveBaseLossResolver.ts:24 发 BASE_DAMAGE）；"营地"在棋盘上另有所指（放将领的区域）</t>
   </si>
   <si>
-    <t>✅ 您 2026-09-29 说"这些能开工就开"，按代码为准改了界面措辞：抽卡窗四行（标题、两行说明、滑条下的提醒）现在都写"本营"</t>
+    <t>✅ 您 2026-09-29 说"这些能开工就开"，按代码为准改了界面措辞：抽卡窗四行（标题、两行说明、滑条下的提醒）当时都写"本营"〔v2.8.39 就地更正：您 2026-10-06 裁"改回'营地'这个叫法"，那四行现在写"营地"；扣的仍是 ResolveBaseLossResolver.ts 发的 BASE_DAMAGE，血量归属从头到尾没变过〕</t>
   </si>
   <si>
     <t>3</t>
@@ -1206,7 +1206,7 @@
     <t>无</t>
   </si>
   <si>
-    <t>✅ 那行小字改成「本营击破」。没删掉它：横幅的版式靠这一行起头，删了会塌一行空白</t>
+    <t>✅ 那行小字改成「本营击破」。没删掉它：横幅的版式靠这一行起头，删了会塌一行空白〔v2.8.39 就地更正：同一轮改名后这行现在写「营地击破」〕</t>
   </si>
   <si>
     <t>9</t>

--- a/词汇表.xlsx
+++ b/词汇表.xlsx
@@ -225,16 +225,16 @@
     <t>近战</t>
   </si>
   <si>
-    <t>两义：①卡上的属性数字（⚔️近战 2＝近战能打多狠）；②行动按钮（⚔️近战(-1牌)＝打一次烧 1 张手牌）。</t>
-  </si>
-  <si>
-    <t>补充：某些将领的技能可以改变自身的远程攻击范围</t>
+    <t>两义：①卡上的属性数字（⚔️近战 2＝近战能打多狠）；②行动按钮（⚔️近战(-1牌)＝打一次烧 1 张手牌）。近战那一档永远吃不到"射程"加成（v2.9.0 起：近战只看"挨不挨着"，不看射程数）。</t>
+  </si>
+  <si>
+    <t>补充：某些将领的技能可以改变自身的远程攻击范围 ⇒ v2.9.0 已照这句做：改的只有远程那一档</t>
   </si>
   <si>
     <t>远程</t>
   </si>
   <si>
-    <t>同上两义的远程版（🏹）。射程不是"隔几格"，而是看双方各站在哪块区域：自家营地打战场、前线打对面前线、战场打对面营地。定规则：rules/battlefieldRules.ts:120、domain/combatRules.ts:12</t>
+    <t>同上两义的远程版（🏹）。射程不是"隔几格"，而是看双方各站在哪块区域：自家营地打战场、前线打对面前线、战场打对面营地。定规则：core/attackReach.ts（v2.9.0 起全库只此一处"够不够得着"的判据，旧的 rules/battlefieldRules.ts:120 那份镜像表与 domain/combatRules.ts:12 那份死码表都已收掉）。「射程」这个数现在能填了（技能编辑器「改哪个数」→射程，Excel 同一格）：+1 只往外推一格，不把近处一并放开（自家营地多够得着敌前线，但不会因此够得着自家前线；近战照旧不吃）。</t>
   </si>
   <si>
     <t>武将</t>
@@ -408,7 +408,7 @@
     <t>近战范围内没有可攻击的敌军 / 远程射程内没有可攻击的敌军</t>
   </si>
   <si>
-    <t>站位不合法（见"远程"的区域克法），不是距离不够。</t>
+    <t>站位不合法（见"远程"的区域克法），不是距离不够。v2.9.0 起这一句和引擎的拒因走同一份"够不够得着"判据，而且自己席位上的队友不再被列进这份名单（它们本来就被引擎拒，界面却把它们亮成可打＝旧缺口，本轮补上，连带的黄色友军高亮一起撤掉）。</t>
   </si>
   <si>
     <t>当前没有可移动的位置</t>
@@ -822,19 +822,19 @@
     <t>修改数值（效果类型，v2.8 刀4 起可结算）</t>
   </si>
   <si>
-    <t>第十一条效果类型。它不改卡面上的印刷数字，而是给这名将领记一笔"账"（引擎里那本账叫 state.statModifiers，随存档走、录像能重放）。所以同一张卡在棋盘上会同时存在两个数：卡上印的（永远不变，图鉴与手抄核对用它）和当下算数的（对局里真正用来砍人的）。今天有四个数能被这样改：近战攻击力／远程攻击力／体力上限（v2.8 刀4）＋受到的伤害（v2.8 刀5）。五句实话：①当前体力不走这本账（它本来就是"损失记录"那一本，回血、扣血照旧直接动它）；②护甲、手牌上限这一版还没接（写了会被点名跳过）；③只能改自己的账面数字——"让别人的攻击＋1"那种跨将改数还没有目标选择器，编译时逐条点名跳过；④「受到的伤害」这一格作用在护甲之前：先把伤害这个数摁好，再交给"2 点护甲挡 1 点"那套算术，所以它是"看不见的减伤"，不是第二层护甲，也不改变身上有没有护甲这件事；营地（老家）不吃这一格——规则上营地单次受到的伤害最多 1 点，那一条由攻击那一步钉死，不是账本管的事；⑤官方 95 将与您手上的样本卡今天还没有一条用它（仓库那叠试作样本除外），所以对局表现与上一版逐字相同。</t>
+    <t>第十一条效果类型。它不改卡面上的印刷数字，而是给这名将领记一笔"账"（引擎里那本账叫 state.statModifiers，随存档走、录像能重放）。所以同一张卡在棋盘上会同时存在两个数：卡上印的（永远不变，图鉴与手抄核对用它）和当下算数的（对局里真正用来砍人的）。今天有五个数能被这样改：近战攻击力／远程攻击力／体力上限（v2.8 刀4）＋受到的伤害（v2.8 刀5）＋射程（v2.9.0）。五句实话：①当前体力不走这本账（它本来就是"损失记录"那一本，回血、扣血照旧直接动它）；②护甲、手牌上限这一版还没接（写了会被点名跳过）；③只能改自己的账面数字——"让别人的攻击＋1"那种跨将改数还没有目标选择器，编译时逐条点名跳过；④「受到的伤害」这一格作用在护甲之前：先把伤害这个数摁好，再交给"2 点护甲挡 1 点"那套算术，所以它是"看不见的减伤"，不是第二层护甲，也不改变身上有没有护甲这件事；营地（老家）不吃这一格——规则上营地单次受到的伤害最多 1 点，那一条由攻击那一步钉死，不是账本管的事；⑤官方 95 将与您手上的样本卡今天还没有一条用它（仓库那叠试作样本除外），所以正式对局表现与上一版逐字相同。⑥「射程」这一把有两条自己的规矩（v2.9.0）：(a) 只往外推，不把近处一并放开——加 1 就是从自家营地多够得着对面前线，不会因此够得着自家前线；(b) 近战那一档永远吃不到它，近战只看"挨不挨着"，所以给一员将加射程，它的近战名单一格都不会变多。另外摁成 1 或 0 是合法的＝远程名单直接空掉（"这员将只能近战"），不是回退到默认值。</t>
   </si>
   <si>
     <t>改哪个数 / 怎么改 / 有效周期（Excel 里效果组第 9–11 列）</t>
   </si>
   <si>
-    <t>「修改数值」的三格配套，各占一列（与「我听谁」「门槛」同一族做法，不挤进触发时机那句话）。改哪个数＝上面那四个数之一；怎么改＝两档：「增加或减少（可填负数）」＝往上添/往下减，「固定为（覆盖卡面值）」＝不管卡上印几，一律摁成这个数；有效周期＝这笔账管到什么时候（见下一行）。只有「效果类型＝修改数值」读这三格，别的类型填了会在导入总结里逐条点名，不会静悄悄收下。数值格是全库唯一允许 0 与负数的地方（往下调就填 −1）。</t>
+    <t>「修改数值」的三格配套，各占一列（与「我听谁」「门槛」同一族做法，不挤进触发时机那句话）。改哪个数＝上面那五个数之一（v2.9.0 起下拉与 Excel 里多了「射程」）；怎么改＝两档：「增加或减少（可填负数）」＝往上添/往下减，「固定为（覆盖卡面值）」＝不管卡上印几，一律摁成这个数；有效周期＝这笔账管到什么时候（见下一行）。只有「效果类型＝修改数值」读这三格，别的类型填了会在导入总结里逐条点名，不会静悄悄收下。数值格是全库唯一允许 0 与负数的地方（往下调就填 −1）。</t>
   </si>
   <si>
     <t>有效周期（这笔账什么时候结束）</t>
   </si>
   <si>
-    <t>五种写法：到下个己方回合开始前／到下个己方回合结束前／到下个其他玩家回合开始前／到下个其他玩家回合结束前／一次性（用掉就销）（v2.8 刀5 新增，只对「受到的伤害」这把钥匙有意义＝"下一次受到伤害时算，算完当场销掉"；挂到攻击力或体力上限上，因为那两样没有"被用掉一次"的那一刻，会被导入报告与编译器逐条点名跳过）。留空＝在场上就一直有效、离场当场结束（表头批注里写了这一句，免得空着被读成"没生效"）。词表里故意没有"直到将领被击杀前"这一档——离场打断一切，它与"直到离开场上前"同义，旧文件真写了这两个词也照样读成留空。周期只跟"发动那一笔"配对：在场即生效的那笔账不许填周期（它本来就没有"开始"以外的时刻，填了编译时点名跳过）。一次性那笔在决斗里只挡一轮（您 2026-10-03 裁："下 1 次受到伤害−1"算一轮、"2 次"算两轮，以此类推），同一次读数里也只销掉最早的那一笔。</t>
+    <t>五种写法：到下个己方回合开始前／到下个己方回合结束前／到下个其他玩家回合开始前／到下个其他玩家回合结束前／一次性（用掉就销）（v2.8 刀5 新增，只对「受到的伤害」这把钥匙有意义＝"下一次受到伤害时算，算完当场销掉"；挂到攻击力、体力上限或射程（v2.9.0）上，因为那几样没有"被用掉一次"的那一刻，会被导入报告与编译器逐条点名跳过）。留空＝在场上就一直有效、离场当场结束（表头批注里写了这一句，免得空着被读成"没生效"）。词表里故意没有"直到将领被击杀前"这一档——离场打断一切，它与"直到离开场上前"同义，旧文件真写了这两个词也照样读成留空。周期只跟"发动那一笔"配对：在场即生效的那笔账不许填周期（它本来就没有"开始"以外的时刻，填了编译时点名跳过）。一次性那笔在决斗里只挡一轮（您 2026-10-03 裁："下 1 次受到伤害−1"算一轮、"2 次"算两轮，以此类推），同一次读数里也只销掉最早的那一笔。</t>
   </si>
   <si>
     <t>几笔账同时算一个数时谁说了算</t>
@@ -1065,7 +1065,7 @@
     <t>距离 -1 马 / 攻击范围</t>
   </si>
   <si>
-    <t>没有马和武器范围概念。能不能打只看区域（营地／前线／战场）怎么互相够得着。</t>
+    <t>没有马和武器范围概念。能不能打只看区域（营地／前线／战场）怎么互相够得着。v2.9.0 起多一样东西：技能可以给远程那一档加"射程"（+1/+2…只往外推），但它不是"攻击范围数字"、也不是距离计量——它只是把够得着的区域往外多推几档，近战不吃。</t>
   </si>
   <si>
     <t>淘汰</t>

--- a/词汇表.xlsx
+++ b/词汇表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="422">
   <si>
     <t>玩家词汇 · 大白话对照表（v2.8.18 界面口径）</t>
   </si>
@@ -52,7 +52,7 @@
     <t>二 行动按钮与提示：38 条</t>
   </si>
   <si>
-    <t>三 抽卡与开局：21 条</t>
+    <t>三 抽卡与开局：27 条</t>
   </si>
   <si>
     <t>四 技能相关词：34 条</t>
@@ -67,7 +67,7 @@
     <t>七 界面里没有的词：8 条</t>
   </si>
   <si>
-    <t>八 措辞与规则冲突：10 条</t>
+    <t>八 措辞与规则冲突：11 条</t>
   </si>
   <si>
     <t>术语</t>
@@ -651,6 +651,42 @@
     <t>电脑打法的四档性格：闭眼乱抓牌（入门陪练）／重守营地爱惜将领／攻守各半稳扎稳打／猛打猛冲抢占地盘。</t>
   </si>
   <si>
+    <t>🌐 联网对战 / 我开房间 / 我去别人房间</t>
+  </si>
+  <si>
+    <t>主菜单进联机大厅。开房间＝这台机器算牌，去别人房间＝连房主那台机器的地址。（与上面热座的「创建房间」不是一回事：那是同一台电脑大家轮流按。）</t>
+  </si>
+  <si>
+    <t>传话程序地址 / 房间码（房主那边显示的那六个字符）</t>
+  </si>
+  <si>
+    <t>先在算牌那台机器上双击 启动传话程序.bat，它会印出可填的地址（自己用 127.0.0.1，别人连你填你那台的 IP）。同一屋里两边填同一个地址＋同一个房间码就能见面；异地经虚拟网或服务器时，只换地址那一行。房间码故意不用 I、O、0、1 这几个容易看混的字符。</t>
+  </si>
+  <si>
+    <t>房主·算牌 / 客人 /（我）</t>
+  </si>
+  <si>
+    <t>在场名单里每人的身份。牌由房主那台机器算，传话程序只转发、不懂玩法、不存局面。</t>
+  </si>
+  <si>
+    <t>还没连 / 正在对上版本 / 已连上 / 被拒（没连上）/ 已离开</t>
+  </si>
+  <si>
+    <t>大厅里的连接状态。连之前两边先对三个数（游戏版本／协议版本／局面快照版本），任何一个对不上就直接拒并写清是哪一项（话术＝「…对不上：对面 X，本机 Y——两边请打开同一份游戏文件」），不会出现"连上了一半、打到一半才发现"。</t>
+  </si>
+  <si>
+    <t>我这边的名字（账户名功能还没做，这里先手填）</t>
+  </si>
+  <si>
+    <t>临时填一个显示名（最多 12 个字）。</t>
+  </si>
+  <si>
+    <t>还没做的：牌桌画面同步（J2）、左上角 ping 表与掉线判定（J3）、客人动手（J4）。现在连上也不会真的开始一局联机对局</t>
+  </si>
+  <si>
+    <t>这句就写在大厅第一屏（还没连的时候就能看到）。联机第一刀只做到"连得上、版本对得上、看得见谁在场"，别以为连上了就在打一局联机牌。</t>
+  </si>
+  <si>
     <t>锁定技</t>
   </si>
   <si>
@@ -1237,6 +1273,21 @@
   </si>
   <si>
     <t>✅ 已按您给的口径落地（v2.8.13 录入面按类型表达"全部"＋v2.8.14 导入总结点名），本轮无改动</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>「联网对战」四个字说大了</t>
+  </si>
+  <si>
+    <t>主菜单按钮与大厅标题写 🌐 联网对战，而这一格（v2.9.1 第一刀）只做到"连得上、版本对得上、看得见谁在场"——牌桌画面同步＝J2、ping 表与掉线判定＝J3、客人能动手＝J4 都还没做。大厅第一屏（还没连的时候）就写着这句边界。</t>
+  </si>
+  <si>
+    <t>传话程序只转发、不算牌；牌由房主那台机器算。所以现在"连上了"确实=两个人能互相看见，不等于开了一局联机牌。</t>
+  </si>
+  <si>
+    <t>⏳ 等您裁：按钮要不要先改叫「联网大厅」，或者保持原名（我这边倾向保持原名＋第一屏那句边界，等 J2 做完它自然名副其实）</t>
   </si>
 </sst>
 </file>
@@ -2555,7 +2606,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -2802,6 +2853,72 @@
         <v>208</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2834,10 +2951,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -2845,10 +2962,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -2856,10 +2973,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -2867,10 +2984,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -2878,10 +2995,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -2889,10 +3006,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -2900,10 +3017,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -2911,10 +3028,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -2922,10 +3039,10 @@
     </row>
     <row r="10" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -2936,10 +3053,10 @@
     </row>
     <row r="11" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>1</v>
@@ -2947,10 +3064,10 @@
     </row>
     <row r="12" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>1</v>
@@ -2958,10 +3075,10 @@
     </row>
     <row r="13" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>1</v>
@@ -2969,10 +3086,10 @@
     </row>
     <row r="14" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>1</v>
@@ -2980,10 +3097,10 @@
     </row>
     <row r="15" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>1</v>
@@ -2991,10 +3108,10 @@
     </row>
     <row r="16" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>1</v>
@@ -3002,10 +3119,10 @@
     </row>
     <row r="17" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>1</v>
@@ -3013,10 +3130,10 @@
     </row>
     <row r="18" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>1</v>
@@ -3024,10 +3141,10 @@
     </row>
     <row r="19" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>1</v>
@@ -3035,10 +3152,10 @@
     </row>
     <row r="20" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>1</v>
@@ -3046,10 +3163,10 @@
     </row>
     <row r="21" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>1</v>
@@ -3057,10 +3174,10 @@
     </row>
     <row r="22" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>1</v>
@@ -3068,10 +3185,10 @@
     </row>
     <row r="23" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>1</v>
@@ -3079,10 +3196,10 @@
     </row>
     <row r="24" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>1</v>
@@ -3090,10 +3207,10 @@
     </row>
     <row r="25" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>1</v>
@@ -3101,10 +3218,10 @@
     </row>
     <row r="26" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>1</v>
@@ -3112,10 +3229,10 @@
     </row>
     <row r="27" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>1</v>
@@ -3123,10 +3240,10 @@
     </row>
     <row r="28" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>1</v>
@@ -3134,10 +3251,10 @@
     </row>
     <row r="29" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>1</v>
@@ -3145,10 +3262,10 @@
     </row>
     <row r="30" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>1</v>
@@ -3156,10 +3273,10 @@
     </row>
     <row r="31" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>1</v>
@@ -3167,10 +3284,10 @@
     </row>
     <row r="32" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>1</v>
@@ -3178,10 +3295,10 @@
     </row>
     <row r="33" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>1</v>
@@ -3189,10 +3306,10 @@
     </row>
     <row r="34" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>1</v>
@@ -3200,10 +3317,10 @@
     </row>
     <row r="35" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>1</v>
@@ -3211,7 +3328,7 @@
     </row>
     <row r="37" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -3248,10 +3365,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3259,10 +3376,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3270,10 +3387,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3281,10 +3398,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3292,10 +3409,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3303,10 +3420,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3314,10 +3431,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3325,10 +3442,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3336,10 +3453,10 @@
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -3374,10 +3491,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3385,10 +3502,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3396,10 +3513,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3407,10 +3524,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3418,10 +3535,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3429,10 +3546,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3440,10 +3557,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3451,10 +3568,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3462,10 +3579,10 @@
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -3473,10 +3590,10 @@
     </row>
     <row r="11" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>1</v>
@@ -3484,10 +3601,10 @@
     </row>
     <row r="12" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>1</v>
@@ -3495,10 +3612,10 @@
     </row>
     <row r="13" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>1</v>
@@ -3506,10 +3623,10 @@
     </row>
     <row r="14" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>1</v>
@@ -3517,10 +3634,10 @@
     </row>
     <row r="15" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>1</v>
@@ -3528,10 +3645,10 @@
     </row>
     <row r="16" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>1</v>
@@ -3539,10 +3656,10 @@
     </row>
     <row r="17" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>1</v>
@@ -3550,10 +3667,10 @@
     </row>
     <row r="18" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>1</v>
@@ -3561,10 +3678,10 @@
     </row>
     <row r="19" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>1</v>
@@ -3588,10 +3705,10 @@
   <sheetData>
     <row r="1" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>18</v>
@@ -3599,10 +3716,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3610,10 +3727,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3621,10 +3738,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3632,10 +3749,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3643,10 +3760,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3654,10 +3771,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3665,10 +3782,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3676,10 +3793,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3693,7 +3810,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -3704,189 +3821,206 @@
   <sheetData>
     <row r="1" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>404</v>
+        <v>416</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>421</v>
       </c>
     </row>
   </sheetData>

--- a/词汇表.xlsx
+++ b/词汇表.xlsx
@@ -1287,7 +1287,7 @@
     <t>传话程序只转发、不算牌；牌由房主那台机器算。所以现在"连上了"确实=两个人能互相看见，不等于开了一局联机牌。</t>
   </si>
   <si>
-    <t>⏳ 等您裁：按钮要不要先改叫「联网大厅」，或者保持原名（我这边倾向保持原名＋第一屏那句边界，等 J2 做完它自然名副其实）</t>
+    <t>✅ 您的原话（2026-10-08）：「1.不用改」⇒ 保持原名 🌐 联网对战＋大厅第一屏那句边界，按钮与标题一字未动；J2 做完它自然名副其实</t>
   </si>
 </sst>
 </file>

--- a/词汇表.xlsx
+++ b/词汇表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="436">
   <si>
     <t>玩家词汇 · 大白话对照表（v2.8.18 界面口径）</t>
   </si>
@@ -52,7 +52,7 @@
     <t>二 行动按钮与提示：38 条</t>
   </si>
   <si>
-    <t>三 抽卡与开局：27 条</t>
+    <t>三 抽卡与开局：34 条</t>
   </si>
   <si>
     <t>四 技能相关词：34 条</t>
@@ -681,10 +681,52 @@
     <t>临时填一个显示名（最多 12 个字）。</t>
   </si>
   <si>
-    <t>还没做的：牌桌画面同步（J2）、左上角 ping 表与掉线判定（J3）、客人动手（J4）。现在连上也不会真的开始一局联机对局</t>
-  </si>
-  <si>
-    <t>这句就写在大厅第一屏（还没连的时候就能看到）。联机第一刀只做到"连得上、版本对得上、看得见谁在场"，别以为连上了就在打一局联机牌。</t>
+    <t>还没做的：左上角 ping 表与掉线判定（J3）、客人动手与座位绑定（J4）。客人这一格仍然只是"看见同一局"，动不了牌</t>
+  </si>
+  <si>
+    <t>这两句写在大厅页脚（还没连的时候就在，连上之后也一直在）。第二刀做到"客人能看见房主那一局的牌桌"，但客人这边一个能按的牌钮都没有——真要让客人动手＝J4。</t>
+  </si>
+  <si>
+    <t>牌由房主那台机器算，传话程序只转发。现在做到"连得上、版本对得上、看得见谁在场，客人还能看见房主那一局的牌桌"</t>
+  </si>
+  <si>
+    <t>大厅第一屏的边界句（还没连的时候就能读到）。它写明这一格做到哪一步，不让人以为连上了就开了联机局。</t>
+  </si>
+  <si>
+    <t>👀 观战 · 这一局由房主算牌，你这边只看不动</t>
+  </si>
+  <si>
+    <t>客人连上后大厅里那块牌桌的名字。观战＝跟着看、动不了：谁在场面上、谁剩多少体力、轮到谁、营地还剩多少，都跟着房主那边变。</t>
+  </si>
+  <si>
+    <t>第 N 轮 · 轮到某某 ／ 行动中 ／ 场上没有将领</t>
+  </si>
+  <si>
+    <t>观战牌桌上的读数，全部来自房主发来的那一份局面，客人自己不算牌。</t>
+  </si>
+  <si>
+    <t>🏯6 · 🃏7 张 · 👤23 员</t>
+  </si>
+  <si>
+    <t>每席三样：营地剩几点体力、手里几张牌、将池还剩几员。后面两样只有张数/人数，没有牌面。</t>
+  </si>
+  <si>
+    <t>牌堆里还剩 N 张 · 弃牌堆 N 张 · 手牌与牌堆顺序不发（那是各家自己的东西），所以你看到的是数量而不是牌面</t>
+  </si>
+  <si>
+    <t>观战牌桌底下的说明，同时也是这一刀的规矩：私有的东西只发数量，线上根本不会出现别人的手牌、将池名单、牌堆顺序。</t>
+  </si>
+  <si>
+    <t>先关掉这个窗不会退房——连线还在，房主那边继续发局面。真要断线请点「离开房间」</t>
+  </si>
+  <si>
+    <t>大厅页脚第一句。关掉弹窗≠退出房间：房主关了大厅去开局，客人照样看得见；想真断开只有「离开房间」那一个钮。</t>
+  </si>
+  <si>
+    <t>现在有 N 位客人正在看这一局</t>
+  </si>
+  <si>
+    <t>房主那侧才会出现这句（有客人才显示），提醒他：现在每次局面变化都会往出发一份遮蔽过的局面。</t>
   </si>
   <si>
     <t>锁定技</t>
@@ -1281,13 +1323,13 @@
     <t>「联网对战」四个字说大了</t>
   </si>
   <si>
-    <t>主菜单按钮与大厅标题写 🌐 联网对战，而这一格（v2.9.1 第一刀）只做到"连得上、版本对得上、看得见谁在场"——牌桌画面同步＝J2、ping 表与掉线判定＝J3、客人能动手＝J4 都还没做。大厅第一屏（还没连的时候）就写着这句边界。</t>
-  </si>
-  <si>
-    <t>传话程序只转发、不算牌；牌由房主那台机器算。所以现在"连上了"确实=两个人能互相看见，不等于开了一局联机牌。</t>
-  </si>
-  <si>
-    <t>✅ 您的原话（2026-10-08）：「1.不用改」⇒ 保持原名 🌐 联网对战＋大厅第一屏那句边界，按钮与标题一字未动；J2 做完它自然名副其实</t>
+    <t>主菜单按钮与大厅标题写 🌐 联网对战，第一刀（v2.9.1）只做到"连得上、版本对得上、看得见谁在场"；第二刀（v2.9.2）客人这一格能看见房主那一局的牌桌（谁在场面、剩多少体力、轮到谁、营地与牌堆剩多少），但动不了牌——ping 表与掉线判定＝J3、客人动手＝J4 还没做。大厅页脚始终写着这两格没做。</t>
+  </si>
+  <si>
+    <t>传话程序只转发、不算牌；牌由房主那台机器算。观战那块牌桌是房主发来的读数，不是客人自己在打。</t>
+  </si>
+  <si>
+    <t>⏳ 待您裁：按钮名与标题仍一字未动（沿用您 2026-10-08 的「1.不用改」）。现在"连上了"多了"看得见同一局牌桌"，仍然不等于开了一局两人联机对局；要不要再改口，等 J4 客人能动手那天您再定</t>
   </si>
 </sst>
 </file>
@@ -2606,7 +2648,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -2919,6 +2961,83 @@
         <v>220</v>
       </c>
       <c r="C28" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2951,10 +3070,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -2962,10 +3081,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -2973,10 +3092,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -2984,10 +3103,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -2995,10 +3114,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3006,10 +3125,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3017,10 +3136,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3028,10 +3147,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3039,10 +3158,10 @@
     </row>
     <row r="10" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -3053,10 +3172,10 @@
     </row>
     <row r="11" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>1</v>
@@ -3064,10 +3183,10 @@
     </row>
     <row r="12" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>1</v>
@@ -3075,10 +3194,10 @@
     </row>
     <row r="13" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>1</v>
@@ -3086,10 +3205,10 @@
     </row>
     <row r="14" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>1</v>
@@ -3097,10 +3216,10 @@
     </row>
     <row r="15" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>1</v>
@@ -3108,10 +3227,10 @@
     </row>
     <row r="16" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>1</v>
@@ -3119,10 +3238,10 @@
     </row>
     <row r="17" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>1</v>
@@ -3130,10 +3249,10 @@
     </row>
     <row r="18" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>1</v>
@@ -3141,10 +3260,10 @@
     </row>
     <row r="19" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>1</v>
@@ -3152,10 +3271,10 @@
     </row>
     <row r="20" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>1</v>
@@ -3163,10 +3282,10 @@
     </row>
     <row r="21" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>260</v>
+        <v>274</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>1</v>
@@ -3174,10 +3293,10 @@
     </row>
     <row r="22" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>1</v>
@@ -3185,10 +3304,10 @@
     </row>
     <row r="23" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>1</v>
@@ -3196,10 +3315,10 @@
     </row>
     <row r="24" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>1</v>
@@ -3207,10 +3326,10 @@
     </row>
     <row r="25" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>1</v>
@@ -3218,10 +3337,10 @@
     </row>
     <row r="26" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>1</v>
@@ -3229,10 +3348,10 @@
     </row>
     <row r="27" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>1</v>
@@ -3240,10 +3359,10 @@
     </row>
     <row r="28" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>1</v>
@@ -3251,10 +3370,10 @@
     </row>
     <row r="29" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>1</v>
@@ -3262,10 +3381,10 @@
     </row>
     <row r="30" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>1</v>
@@ -3273,10 +3392,10 @@
     </row>
     <row r="31" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>1</v>
@@ -3284,10 +3403,10 @@
     </row>
     <row r="32" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>1</v>
@@ -3295,10 +3414,10 @@
     </row>
     <row r="33" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>1</v>
@@ -3306,10 +3425,10 @@
     </row>
     <row r="34" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>1</v>
@@ -3317,10 +3436,10 @@
     </row>
     <row r="35" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>1</v>
@@ -3328,7 +3447,7 @@
     </row>
     <row r="37" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -3365,10 +3484,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3376,10 +3495,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3387,10 +3506,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3398,10 +3517,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3409,10 +3528,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3420,10 +3539,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3431,10 +3550,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3442,10 +3561,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3453,10 +3572,10 @@
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -3491,10 +3610,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>308</v>
+        <v>322</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3502,10 +3621,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3513,10 +3632,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3524,10 +3643,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3535,10 +3654,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3546,10 +3665,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3557,10 +3676,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3568,10 +3687,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3579,10 +3698,10 @@
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -3590,10 +3709,10 @@
     </row>
     <row r="11" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>1</v>
@@ -3601,10 +3720,10 @@
     </row>
     <row r="12" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>1</v>
@@ -3612,10 +3731,10 @@
     </row>
     <row r="13" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>1</v>
@@ -3623,10 +3742,10 @@
     </row>
     <row r="14" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>1</v>
@@ -3634,10 +3753,10 @@
     </row>
     <row r="15" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>1</v>
@@ -3645,10 +3764,10 @@
     </row>
     <row r="16" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>1</v>
@@ -3656,10 +3775,10 @@
     </row>
     <row r="17" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>1</v>
@@ -3667,10 +3786,10 @@
     </row>
     <row r="18" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>340</v>
+        <v>354</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>1</v>
@@ -3678,10 +3797,10 @@
     </row>
     <row r="19" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>1</v>
@@ -3705,10 +3824,10 @@
   <sheetData>
     <row r="1" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>18</v>
@@ -3716,10 +3835,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3727,10 +3846,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3738,10 +3857,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3749,10 +3868,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3760,10 +3879,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>355</v>
+        <v>369</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3771,10 +3890,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3782,10 +3901,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>358</v>
+        <v>372</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3793,10 +3912,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>360</v>
+        <v>374</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3821,206 +3940,206 @@
   <sheetData>
     <row r="1" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>366</v>
+        <v>380</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>369</v>
+        <v>383</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>370</v>
+        <v>384</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>371</v>
+        <v>385</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>372</v>
+        <v>386</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>374</v>
+        <v>388</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>375</v>
+        <v>389</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>382</v>
+        <v>396</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>386</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>397</v>
+        <v>411</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>400</v>
+        <v>414</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>401</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>402</v>
+        <v>416</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>409</v>
+        <v>423</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>411</v>
+        <v>425</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>412</v>
+        <v>426</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>415</v>
+        <v>429</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>416</v>
+        <v>430</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>417</v>
+        <v>431</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>421</v>
+        <v>435</v>
       </c>
     </row>
   </sheetData>

--- a/词汇表.xlsx
+++ b/词汇表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="440">
   <si>
     <t>玩家词汇 · 大白话对照表（v2.8.18 界面口径）</t>
   </si>
@@ -55,7 +55,7 @@
     <t>三 抽卡与开局：34 条</t>
   </si>
   <si>
-    <t>四 技能相关词：34 条</t>
+    <t>四 技能相关词：36 条</t>
   </si>
   <si>
     <t>五 结算录像日志：9 条</t>
@@ -738,7 +738,7 @@
     <t>限定技</t>
   </si>
   <si>
-    <t>一局只许发动一次，用完就没了（src/skills/skillQuota.ts）。四条细则：① 额度记在每枚技能头上——一个将带两枚限定技就能各用一次；② 用完之后这枚技能在候选里照常列出、但灰掉，写明「本局已用尽」；③ 被人挡掉、无效掉不退额度（用过了就是用过了）；④ 想发动但没当成（代价付不出、被规则拒绝）不消耗额度。</t>
+    <t>一局只许发动一次，用完就没了（src/skills/skillQuota.ts）。四条细则：① 额度记在每枚技能头上——一个将带两枚限定技就能各用一次；② 用完之后这枚技能在候选里照常列出、但灰掉，写明「本局已用尽」；③ 被人挡掉、无效掉不退额度（用过了就是用过了）；④ 想发动但没当成（代价付不出、被规则拒绝）不消耗额度。⑤ v2.9.3 起「觉醒技」也记在这同一本账上（您 2026-10-08 裁："觉醒技和限定技同理"）：上面①"每枚技能各记一笔"、③"被挡掉不退额度"、④"没当成不消耗"三条一字照搬。唯一的差别在界面——觉醒技用尽之后那一格压根不再问您，因为停下问人这条路没有"照常列出但灰掉、写着本局已用尽"这个形状（那是回合结束那条路的显示）。</t>
   </si>
   <si>
     <t>登场技</t>
@@ -762,13 +762,13 @@
     <t>觉醒技</t>
   </si>
   <si>
-    <t>分类徽章（您 2026-10-04 给的口径原文存档："一般是满足一定条件后可以自选发动，从而获得新技能或者改变已有技能的效果，非强制发动"）。翻译成对局里该发生的事＝条件满足了问您一次，您点头才生效，生效后这枚将拿到新技能或让老技能改效果；它不是到点自己响、也不是被动一直算数。本作目前还没有任何觉醒机制：徽章照常读写显示，引擎里没有人读它，所以今天挂不挂都不改变对局。单独一刀再做（裁决原文与判据＝PROJECT_HANDOFF.md §12-104⑥）。</t>
+    <t>分类徽章（您 2026-10-04 给的口径原文存档："一般是满足一定条件后可以自选发动，从而获得新技能或者改变已有技能的效果，非强制发动"）。v2.9.3 起这一格真的管事了，翻译成对局里该发生的事＝条件满足了在达成那一刻当场问您一次（您 2026-10-08 裁的：不当场问、拖到回合结束不算），问的是"觉醒／不觉醒"；点头才结算这枚技能写的那一句（拿到新技能，或者让账面数字变），摇头不扣额度、以后还有机会。一局只觉醒一次，这一笔账跟限定技走同一本（您 2026-10-08 裁："觉醒技和限定技同理，在同一局中发动过一次就不能再发动"），用尽后不再问。边界四句实话：①它不是到点自己响、也不是被动一直算数；②勾了「强制发动」的觉醒技例外——到点自己结算、不停下来问，但额度那一半照扣；③觉醒技挂不得"在场即生效"和"多选一"这两种形状，硬挂会在导入总结里点名退回，不会静悄悄当没事；④问句挂着的时候全场冻结，只有被问的那一席能答（答或者跳过），跟响应链那一格同一套规矩。今天的官方 95 将与您手上的样本卡还没有一条挂这一枚（有测试钉着这个数），所以正式对局里的表现与上一版逐字相同。裁决原文与判据＝PROJECT_HANDOFF.md §12。</t>
   </si>
   <si>
     <t>强制发动</t>
   </si>
   <si>
-    <t>编辑器里的开关（Excel 也有这一列）：满足触发条件与代价后直接响／直接适用效果，不用玩家点头。它跟锁定技不是一件事，跟"数值变化／持续生效"也不绑定，三者可以任意组合。v2.8.25 起这一格真的管事了：勾上之后，凡是本来会停下来问您"要不要发动"的那一刻（＝成为目标时／受到伤害后这两型），这条技能不再问、自己就响了；不勾就照旧问。四句实话边界：①它只决定"问不问人"，不会让一条技能多响一次，也不绕过发动门槛与代价；②本来就到点自动响的时机（登场／回合开始／击杀／失去手牌……）勾不勾都一样；③「回合结束时」那一型永远要您点头（一条技能不许响两次的常设规矩），勾了也不自响；④决斗那一套的"开局被点名"与"收官掉血"两刻同样吃这一格——勾了就自己响、没勾就问；⑤v2.8.31 起它与"不勾"完全同一条时机判据（您 2026-10-04 定稿：强制发动和手动发动的处理必须一致，区别只在"需不需要玩家自行响应"）——被这一刀砍死时，勾了的「成为目标时」照样响、勾了的「受到伤害后」照样不响，与没勾时问您那一型逐字同形（只有「自身被击杀时」那一型放行）。今天的官方 95 将与您手上的样本卡还没有一条勾了这个开关，所以对局里的表现与上一版逐字相同。</t>
+    <t>编辑器里的开关（Excel 也有这一列）：满足触发条件与代价后直接响／直接适用效果，不用玩家点头。它跟锁定技不是一件事，跟"数值变化／持续生效"也不绑定，三者可以任意组合。v2.8.25 起这一格真的管事了：勾上之后，凡是本来会停下来问您"要不要发动"的那一刻（＝成为目标时／受到伤害后这两型），这条技能不再问、自己就响了；不勾就照旧问。四句实话边界：①它只决定"问不问人"，不会让一条技能多响一次，也不绕过发动门槛与代价；②本来就到点自动响的时机（登场／回合开始／击杀／失去手牌……）勾不勾都一样（v2.9.3 起唯一一条例外：同一条技能挂了「觉醒技」徽章时，这些时机改成停下来问您一次，勾了才自己响）；③「回合结束时」那一型永远要您点头（一条技能不许响两次的常设规矩），勾了也不自响；④决斗那一套的"开局被点名"与"收官掉血"两刻同样吃这一格——勾了就自己响、没勾就问；⑤v2.8.31 起它与"不勾"完全同一条时机判据（您 2026-10-04 定稿：强制发动和手动发动的处理必须一致，区别只在"需不需要玩家自行响应"）——被这一刀砍死时，勾了的「成为目标时」照样响、勾了的「受到伤害后」照样不响，与没勾时问您那一型逐字同形（只有「自身被击杀时」那一型放行）。今天的官方 95 将与您手上的样本卡还没有一条勾了这个开关，所以对局里的表现与上一版逐字相同。</t>
   </si>
   <si>
     <t>触发时机</t>
@@ -894,7 +894,7 @@
     <t>技能门槛 / 效果N门槛</t>
   </si>
   <si>
-    <t>两级条件：整组门槛（技能级，不满足这一刻整条技能不响）→ 逐项门槛（每条效果自己的条件）。先判整组，再判逐项。</t>
+    <t>两级条件：整组门槛（技能级，不满足这一刻整条技能不响）→ 逐项门槛（每条效果自己的条件）。先判整组，再判逐项。门槛短句里能填的量一共九个（v2.8.3 起可写、可从 Excel 读，全库唯一的一处翻译与求值＝skills/skillGateText.ts＋skills/skillConditions.ts）：手牌 / 体力 / 护甲 / 场上将领 / 抽牌堆 / 本次伤害（前六枚）＋近战击杀 / 被杀者在战场 / 身边与战场己方（后三枚＝v2.9.3 刀C 新增，就是为了把觉醒技「单骑」那句"你近战击杀战场区域的角色后，若所在区域及战场区域内没有其他己方角色"原话录进去）。三句实话：①"是不是"那一类填 1＝是、0＝否（近战击杀、被杀者在战场），而且这一声是谁打死的它自己认得——决斗砍死的、技能打死的、体力上限被压到 0 的，那三种死法上"近战击杀"永远不成立（引擎压根没在那几声响上记这一格），不会误算；②这五个量没有对象之分（抽牌堆／本次伤害／近战击杀／被杀者在战场／身边与战场己方），写"目标抽牌堆≥5"里那个"目标"不生效；③身边与战场己方数的是"除了自己以外"——看这名将自己踩的那片区域加上"战场"那片，只算同一个席位（同一玩家）的将领，刚刚倒下的那一位不算（人已经离场了，账上没他了）。</t>
   </si>
   <si>
     <t>修改数值（效果类型，v2.8 刀4 起可结算）</t>
@@ -906,7 +906,19 @@
     <t>改哪个数 / 怎么改 / 有效周期（Excel 里效果组第 9–11 列）</t>
   </si>
   <si>
-    <t>「修改数值」的三格配套，各占一列（与「我听谁」「门槛」同一族做法，不挤进触发时机那句话）。改哪个数＝上面那五个数之一（v2.9.0 起下拉与 Excel 里多了「射程」）；怎么改＝两档：「增加或减少（可填负数）」＝往上添/往下减，「固定为（覆盖卡面值）」＝不管卡上印几，一律摁成这个数；有效周期＝这笔账管到什么时候（见下一行）。只有「效果类型＝修改数值」读这三格，别的类型填了会在导入总结里逐条点名，不会静悄悄收下。数值格是全库唯一允许 0 与负数的地方（往下调就填 −1）。</t>
+    <t>「修改数值」的三格配套，各占一列（与「我听谁」「门槛」同一族做法，不挤进触发时机那句话）。改哪个数＝上面那五个数之一（v2.9.0 起下拉与 Excel 里多了「射程」）；怎么改＝两档：「增加或减少（可填负数）」＝往上添/往下减，「固定为（覆盖卡面值）」＝不管卡上印几，一律摁成这个数；有效周期＝这笔账管到什么时候（往下数第三行「有效周期（这笔账什么时候结束）」）。只有「效果类型＝修改数值」读这三格，别的类型填了会在导入总结里逐条点名，不会静悄悄收下。数值格是全库唯一允许 0 与负数的地方（往下调就填 −1）。</t>
+  </si>
+  <si>
+    <t>获得技能（效果类型，v2.9.3 刀A 起可结算）</t>
+  </si>
+  <si>
+    <t>第十二条效果类型，和「修改数值」正好是一正一反：那一档只动账本、卡面一字不改；这一档只动卡面——往这一员将的技能表上添一枚技能，不改任何数字、不掉血、不搬牌。四句实话：①认的是名字，您在那一格里写什么，引擎就拿什么去查名册（＝官方将领卡上印着的那些技能名）；查不到、或者同名却有两份不同内容，都会被导入报告与编译器逐条点名跳过，绝不猜一个"最像的"（自己新编的 DIY 技能名这一版还查不到，已另立待办）；②只能添在自己身上——"给别的将领技能"要等目标选择器那把刀；③添进来之后从下一次发动起这一员将就听得见这枚新技能（本项目没有"技能表缓存"，每次发动前都从对局现场重算一遍），同一枚拿第二次也只留一份；④如果拿到的是一枚在场即生效的技能，那笔账在获得这一刻补落进账本（同一枚不落第二笔），不是等下一次登场。另外官方 95 将与您手上的样本卡今天还没有一条用它，所以正式对局表现与上一版逐字相同。</t>
+  </si>
+  <si>
+    <t>获得哪个技能（Excel 里效果组第 12 列）</t>
+  </si>
+  <si>
+    <t>「获得技能」那一枚的名字格，只服务这一个效果类型（与「改哪个数」「我听谁」同一族做法：一个正交维度占一列）。这一格故意不做死下拉：可选的名字是一百多个技能名、而且随内容增长，做成封闭下拉会把"先写技能、那枚技能还没进池"这条路堵死——所以名字是原样收字，认不认由引擎那一处唯一的查名册说了算（界面里给的是可自由输入的候选清单，不是强制选项）。只有「效果类型＝获得技能」读这一格，别的类型填了会在导入总结里点名、按没填处理；这一格留空同样点名（那是一条半截效果，不会被静悄悄收下）。旧的 11 列导出文件照样能导入，只是那种文件里没有这一格——凡是「获得技能」的效果会报"缺名字"。</t>
   </si>
   <si>
     <t>有效周期（这笔账什么时候结束）</t>
@@ -933,7 +945,7 @@
     <t>（旧说法，已作废）击破横幅上方那行残留的英文小字，v2.8.18 已翻成中文，v2.8.39 起那里写的是「营地击破」。</t>
   </si>
   <si>
-    <t>本节末尾必须说清的一件事：五个"××技"徽章和"强制发动"这一列，v2.8.19 起读得到、写得出、显示得出、还能核对（一枚技能可挂几枚；徽章与触发时机对不上会在编辑器与导入总结里点名）。这两样如今落地程度不同：「强制发动」v2.8.25 起接进对局了——全库只有一个地方读它（skills/SkillTriggerBridge.ts 的 defersToReactionQueue：受击／受伤这两型里没打勾的定义才交给问答队列问人，打了勾的直接走自动发动那条路），所以它管的事恰恰只有一件＝"这一刻问不问您"；徽章里「锁定技」v2.8 刀4 起有了第一个结算侧的消费者，但只管一寸地方：编译器认出这枚徽章 → 这条技能往数值账本落的那笔账打上"移不走"的记号（statModifiers.revokeModifier 是全库唯一"移走别人那笔账"的入口，它见到这个记号就拒绝）。徽章的其余部分（"不能被无效""不能被改变"在伤害、护甲、被弃牌这些环节到底管不管）今天仍然没有任何结算代码读它；四枚徽章里限定技自 v2.8.32 起有了第二个结算侧消费者（编译器认出它 ⇒ 这枚技能每发动一次就在同一本账上落一笔，账上有这一笔就不再让它发动；"一局一次"的判据与记账形状全库只有一份＝skills/skillQuota.ts，三条发动路——回合结束、停下问您、到点自己响——都从这里过），登场／遗计／觉醒还是纯分类。所以现在决定一条技能"什么时候响、响不响、响几次"的是：触发时机（含细分）＋「我听谁」与「被谁指名」这两档监听范围（v2.8.21 起触发桥逐条读；两档的缺省＝只听自己／只算攻击，⇒ 与今天对局逐字一致。"成为技能目标"这一声 v2.8.24 起已有发射器＝决斗开局（其余技能指名目标的路仍未发这一声，等内容刀））＋ 发动门槛 ＋ 那条"每回合限一次"的账 ＋ 限定技"一局一次"的账（v2.8.32 起）＋「强制发动」这一格（v2.8.25 起，只管问不问人）。「在场即生效」那一型不看上面这些，它只在登场／离场两刻动账本。徽章的读写口径全库只有一份，在 domain/skillTags.ts。</t>
+    <t>本节末尾必须说清的一件事：五个"××技"徽章和"强制发动"这一列，v2.8.19 起读得到、写得出、显示得出、还能核对（一枚技能可挂几枚；徽章与触发时机对不上会在编辑器与导入总结里点名）。这两样如今落地程度不同：「强制发动」v2.8.25 起接进对局了——全库只有一个地方读它（skills/SkillTriggerBridge.ts 的 defersToReactionQueue：受击／受伤这两型里没打勾的定义才交给问答队列问人，打了勾的直接走自动发动那条路；v2.9.3 起这一处还多认一枚徽章——挂了「觉醒技」的技能没打勾时同样停下来问您，打了勾就照旧自己响），所以它管的事恰恰只有一件＝"这一刻问不问您"；徽章里「锁定技」v2.8 刀4 起有了第一个结算侧的消费者，但只管一寸地方：编译器认出这枚徽章 → 这条技能往数值账本落的那笔账打上"移不走"的记号（statModifiers.revokeModifier 是全库唯一"移走别人那笔账"的入口，它见到这个记号就拒绝）。徽章的其余部分（"不能被无效""不能被改变"在伤害、护甲、被弃牌这些环节到底管不管）今天仍然没有任何结算代码读它；四枚徽章里限定技自 v2.8.32 起有了第二个结算侧消费者（编译器认出它 ⇒ 这枚技能每发动一次就在同一本账上落一笔，账上有这一笔就不再让它发动；"一局一次"的判据与记账形状全库只有一份＝skills/skillQuota.ts，三条发动路——回合结束、停下问您、到点自己响——都从这里过），登场／遗计还是纯分类，而「觉醒技」自 v2.9.3 起也有了结算侧消费者：编译器认出这枚徽章后同时发生两件事——这枚技能听的那一声从"到点自己响"搬进"停下来问您一次"的队列，并且它与限定技共用同一本一局一次的账（摇头不算发动、不扣这笔账）。所以现在决定一条技能"什么时候响、响不响、响几次"的是：触发时机（含细分）＋「我听谁」与「被谁指名」这两档监听范围（v2.8.21 起触发桥逐条读；两档的缺省＝只听自己／只算攻击，⇒ 与今天对局逐字一致。"成为技能目标"这一声 v2.8.24 起已有发射器＝决斗开局（其余技能指名目标的路仍未发这一声，等内容刀））＋ 发动门槛 ＋ 那条"每回合限一次"的账 ＋ 限定技与觉醒技"一局一次"的同一本账（v2.8.32 起／v2.9.3 起）＋「强制发动」这一格（v2.8.25 起，只管问不问人；v2.9.3 起它对觉醒技同样管用——勾了就不问、到点自己结算）。「在场即生效」那一型不看上面这些，它只在登场／离场两刻动账本。徽章的读写口径全库只有一份，在 domain/skillTags.ts。</t>
   </si>
   <si>
     <t>游戏结束 / 对局结束</t>
@@ -3049,7 +3061,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -3445,16 +3457,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="6" t="s">
+    <row r="36" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="B37" s="6"/>
-      <c r="C37" s="6"/>
+      <c r="B36" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A39:C39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3484,10 +3518,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3495,10 +3529,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3506,10 +3540,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3517,10 +3551,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3528,10 +3562,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3539,10 +3573,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3550,10 +3584,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3561,10 +3595,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3572,10 +3606,10 @@
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -3610,10 +3644,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3621,10 +3655,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3632,10 +3666,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3643,10 +3677,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3654,10 +3688,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3665,10 +3699,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3676,10 +3710,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3687,10 +3721,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3698,10 +3732,10 @@
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -3709,10 +3743,10 @@
     </row>
     <row r="11" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>1</v>
@@ -3720,10 +3754,10 @@
     </row>
     <row r="12" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>1</v>
@@ -3731,10 +3765,10 @@
     </row>
     <row r="13" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>1</v>
@@ -3742,10 +3776,10 @@
     </row>
     <row r="14" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>1</v>
@@ -3753,10 +3787,10 @@
     </row>
     <row r="15" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>1</v>
@@ -3764,10 +3798,10 @@
     </row>
     <row r="16" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>1</v>
@@ -3775,10 +3809,10 @@
     </row>
     <row r="17" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>1</v>
@@ -3786,10 +3820,10 @@
     </row>
     <row r="18" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>1</v>
@@ -3797,10 +3831,10 @@
     </row>
     <row r="19" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>1</v>
@@ -3824,10 +3858,10 @@
   <sheetData>
     <row r="1" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>18</v>
@@ -3835,10 +3869,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3846,10 +3880,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3857,10 +3891,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3868,10 +3902,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3879,10 +3913,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3890,10 +3924,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3901,10 +3935,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3912,10 +3946,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3940,206 +3974,206 @@
   <sheetData>
     <row r="1" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>

--- a/词汇表.xlsx
+++ b/词汇表.xlsx
@@ -882,7 +882,7 @@
     <t>决斗（技能效果，2.8.20 起；2.8.24 起两端问答落地）</t>
   </si>
   <si>
-    <t>自己的将领和目标的将领轮流各出手三次（最多六次）互砍：每一轮用当下出手那一方的攻击力，护甲照旧"2 点挡 1 点"；伤害算技能伤害、不消耗手牌；谁先体力归零就当场停，剩下的轮次不补。决斗中阵亡同样算"被击破"，由失去这名将领的一方补抽 1 张。只能由技能发起——棋盘上没有"决斗"按钮。问答节奏（2.8.24 起）：开场先停下来问一遍"成为技能目标"（被决斗点名的那一方、以及监听范围填了"己方／场上"的这一类被动都有表态权；答复里回复的体力算进决斗起点；2.8.25 起这一层还吃「强制发动」那一格——打了勾的技能不问、自己响完，且这一层全部响完才开始互砍）；这一层全部问完才开始互砍，互砍的每一"打"中间不唤任何监听；全部打完再按"受到伤害后"问一遍——判定值＝该将领这一场实际掉掉的体力总额（军备减免不算），只算一笔、只问一次、绝不再扣第二次血；问的次序＝受邀者那笔先问完（本人先答→旁人按座次绕圈），发起者那笔后问。决斗中阵亡的那一位那一笔整笔跳过（本人和旁人均不问），但他的遗言技（自身被击杀时）与击破补偿抽照旧。</t>
+    <t>自己的将领和目标的将领轮流各出手三次（最多六次）互砍：每一轮用当下出手那一方的攻击力，护甲之前那两格（造成伤害 → 受到伤害）也是每一轮各算一次（v2.9.4＝您裁"决斗的每一轮都算"；一次性那笔仍旧一轮只销一次），护甲照旧"2 点挡 1 点"；伤害算技能伤害、不消耗手牌；谁先体力归零就当场停，剩下的轮次不补。决斗中阵亡同样算"被击破"，由失去这名将领的一方补抽 1 张。只能由技能发起——棋盘上没有"决斗"按钮。问答节奏（2.8.24 起）：开场先停下来问一遍"成为技能目标"（被决斗点名的那一方、以及监听范围填了"己方／场上"的这一类被动都有表态权；答复里回复的体力算进决斗起点；2.8.25 起这一层还吃「强制发动」那一格——打了勾的技能不问、自己响完，且这一层全部响完才开始互砍）；这一层全部问完才开始互砍，互砍的每一"打"中间不唤任何监听；全部打完再按"受到伤害后"问一遍——判定值＝该将领这一场实际掉掉的体力总额（军备减免不算），只算一笔、只问一次、绝不再扣第二次血；问的次序＝受邀者那笔先问完（本人先答→旁人按座次绕圈），发起者那笔后问。决斗中阵亡的那一位那一笔整笔跳过（本人和旁人均不问），但他的遗言技（自身被击杀时）与击破补偿抽照旧。</t>
   </si>
   <si>
     <t>效果模式：全部生效 / 选择其一</t>
@@ -900,13 +900,13 @@
     <t>修改数值（效果类型，v2.8 刀4 起可结算）</t>
   </si>
   <si>
-    <t>第十一条效果类型。它不改卡面上的印刷数字，而是给这名将领记一笔"账"（引擎里那本账叫 state.statModifiers，随存档走、录像能重放）。所以同一张卡在棋盘上会同时存在两个数：卡上印的（永远不变，图鉴与手抄核对用它）和当下算数的（对局里真正用来砍人的）。今天有五个数能被这样改：近战攻击力／远程攻击力／体力上限（v2.8 刀4）＋受到的伤害（v2.8 刀5）＋射程（v2.9.0）。五句实话：①当前体力不走这本账（它本来就是"损失记录"那一本，回血、扣血照旧直接动它）；②护甲、手牌上限这一版还没接（写了会被点名跳过）；③只能改自己的账面数字——"让别人的攻击＋1"那种跨将改数还没有目标选择器，编译时逐条点名跳过；④「受到的伤害」这一格作用在护甲之前：先把伤害这个数摁好，再交给"2 点护甲挡 1 点"那套算术，所以它是"看不见的减伤"，不是第二层护甲，也不改变身上有没有护甲这件事；营地（老家）不吃这一格——规则上营地单次受到的伤害最多 1 点，那一条由攻击那一步钉死，不是账本管的事；⑤官方 95 将与您手上的样本卡今天还没有一条用它（仓库那叠试作样本除外），所以正式对局表现与上一版逐字相同。⑥「射程」这一把有两条自己的规矩（v2.9.0）：(a) 只往外推，不把近处一并放开——加 1 就是从自家营地多够得着对面前线，不会因此够得着自家前线；(b) 近战那一档永远吃不到它，近战只看"挨不挨着"，所以给一员将加射程，它的近战名单一格都不会变多。另外摁成 1 或 0 是合法的＝远程名单直接空掉（"这员将只能近战"），不是回退到默认值。</t>
+    <t>第十一条效果类型。它不改卡面上的印刷数字，而是给这名将领记一笔"账"（引擎里那本账叫 state.statModifiers，随存档走、录像能重放）。所以同一张卡在棋盘上会同时存在两个数：卡上印的（永远不变，图鉴与手抄核对用它）和当下算数的（对局里真正用来砍人的）。今天有六个数能被这样改：近战攻击力／远程攻击力／体力上限（v2.8 刀4）＋受到的伤害（v2.8 刀5）＋射程（v2.9.0）＋造成的伤害（v2.9.4）。五句实话：①当前体力不走这本账（它本来就是"损失记录"那一本，回血、扣血照旧直接动它）；②护甲、手牌上限这一版还没接（写了会被点名跳过）；③只能改自己的账面数字——"让别人的攻击＋1"那种跨将改数还没有目标选择器，编译时逐条点名跳过；④「受到的伤害」与「造成的伤害」这两格都作用在护甲之前，次序是攻击力 → 造成伤害 → 受到伤害 → 护甲抵扣 → 扣血（您 2026-10-14 裁「扣护甲前算」）：先把伤害这个数摁好，再交给"2 点护甲挡 1 点"那套算术，所以它们是"看不见的加减伤"，不是第二层护甲，也不改变身上有没有护甲这件事；营地（老家）这两格都不吃——规则上营地单次受到的伤害最多 1 点，那一条由攻击那一步钉死，不是账本管的事；⑤官方 95 将与您手上的样本卡今天还没有一条用它（仓库那叠试作样本除外），所以正式对局表现与上一版逐字相同。⑥「射程」这一把有两条自己的规矩（v2.9.0）：(a) 只往外推，不把近处一并放开——加 1 就是从自家营地多够得着对面前线，不会因此够得着自家前线；(b) 近战那一档永远吃不到它，近战只看"挨不挨着"，所以给一员将加射程，它的近战名单一格都不会变多。另外摁成 1 或 0 是合法的＝远程名单直接空掉（"这员将只能近战"），不是回退到默认值。⑦「造成的伤害」这一把自己的一条规矩（v2.9.4）：这一格是记在打出去的那一员将身上的，改的是"我这一刀砍出去几"，不是"对面挨几"——两格同时在场时先加后减，再由"固定压过增减"那一条判输赢（受方那一格恒盖造方）。决斗里它是每一轮各算一次（您 2026-10-14 裁），不是整场只算一次。这一格还能再限定"只在某种场合才算数"（近战攻击有护甲的角色／正在打决斗），但那一档界面与 Excel 里都还没有对应的格子，今天只有仓库里写好的技能定义带得进来，您能填的仍是"什么时候都算"。</t>
   </si>
   <si>
     <t>改哪个数 / 怎么改 / 有效周期（Excel 里效果组第 9–11 列）</t>
   </si>
   <si>
-    <t>「修改数值」的三格配套，各占一列（与「我听谁」「门槛」同一族做法，不挤进触发时机那句话）。改哪个数＝上面那五个数之一（v2.9.0 起下拉与 Excel 里多了「射程」）；怎么改＝两档：「增加或减少（可填负数）」＝往上添/往下减，「固定为（覆盖卡面值）」＝不管卡上印几，一律摁成这个数；有效周期＝这笔账管到什么时候（往下数第三行「有效周期（这笔账什么时候结束）」）。只有「效果类型＝修改数值」读这三格，别的类型填了会在导入总结里逐条点名，不会静悄悄收下。数值格是全库唯一允许 0 与负数的地方（往下调就填 −1）。</t>
+    <t>「修改数值」的三格配套，各占一列（与「我听谁」「门槛」同一族做法，不挤进触发时机那句话）。改哪个数＝上面那六个数之一（v2.9.0 起下拉与 Excel 里多了「射程」，v2.9.4 起再多一个「造成的伤害」）；怎么改＝两档：「增加或减少（可填负数）」＝往上添/往下减，「固定为（覆盖卡面值）」＝不管卡上印几，一律摁成这个数；有效周期＝这笔账管到什么时候（往下数第三行「有效周期（这笔账什么时候结束）」）。只有「效果类型＝修改数值」读这三格，别的类型填了会在导入总结里逐条点名，不会静悄悄收下。数值格是全库唯一允许 0 与负数的地方（往下调就填 −1）。</t>
   </si>
   <si>
     <t>获得技能（效果类型，v2.9.3 刀A 起可结算）</t>
@@ -924,13 +924,13 @@
     <t>有效周期（这笔账什么时候结束）</t>
   </si>
   <si>
-    <t>五种写法：到下个己方回合开始前／到下个己方回合结束前／到下个其他玩家回合开始前／到下个其他玩家回合结束前／一次性（用掉就销）（v2.8 刀5 新增，只对「受到的伤害」这把钥匙有意义＝"下一次受到伤害时算，算完当场销掉"；挂到攻击力、体力上限或射程（v2.9.0）上，因为那几样没有"被用掉一次"的那一刻，会被导入报告与编译器逐条点名跳过）。留空＝在场上就一直有效、离场当场结束（表头批注里写了这一句，免得空着被读成"没生效"）。词表里故意没有"直到将领被击杀前"这一档——离场打断一切，它与"直到离开场上前"同义，旧文件真写了这两个词也照样读成留空。周期只跟"发动那一笔"配对：在场即生效的那笔账不许填周期（它本来就没有"开始"以外的时刻，填了编译时点名跳过）。一次性那笔在决斗里只挡一轮（您 2026-10-03 裁："下 1 次受到伤害−1"算一轮、"2 次"算两轮，以此类推），同一次读数里也只销掉最早的那一笔。</t>
+    <t>五种写法：到下个己方回合开始前／到下个己方回合结束前／到下个其他玩家回合开始前／到下个其他玩家回合结束前／一次性（用掉就销）（v2.8 刀5 新增，只对「受到的伤害」「造成的伤害」这两把钥匙有意义＝"下一次读这个数时算进去，算完当场销掉"；挂到攻击力、体力上限或射程（v2.9.0）上，因为那几样没有"被用掉一次"的那一刻，会被导入报告与编译器逐条点名跳过）。留空＝在场上就一直有效、离场当场结束（表头批注里写了这一句，免得空着被读成"没生效"）。词表里故意没有"直到将领被击杀前"这一档——离场打断一切，它与"直到离开场上前"同义，旧文件真写了这两个词也照样读成留空。周期只跟"发动那一笔"配对：在场即生效的那笔账不许填周期（它本来就没有"开始"以外的时刻，填了编译时点名跳过）。一次性那笔在决斗里只挡一轮（您 2026-10-03 裁："下 1 次受到伤害−1"算一轮、"2 次"算两轮，以此类推），同一次读数里也只销掉最早的那一笔。</t>
   </si>
   <si>
     <t>几笔账同时算一个数时谁说了算</t>
   </si>
   <si>
-    <t>规矩是「固定」压过「增减」：只要有一笔"固定为"在场，同一种伤害上所有"增减"都不参与（先按您定的规则走完"固定"这一段，增减没有可作用的中间值）；同一形态有多笔，按发动的先后排，后落的那笔接着前一笔的结果算——同格两笔"固定"⇒后发的那笔盖掉先发的那笔（v2.8 刀5 钉死）。"固定"那笔一旦失效（用掉、离场、周期到点），此前被压住的增减立刻恢复参与，不用重新发动（被压住的那笔一次性增减不算被用掉，它还留着等下一刀）。跨侧（一个技能改自己受到的伤害、另一个改自己造成的伤害）谁赢＝已裁＝受方那一格恒盖过造方那一格，实现方式不是弹窗口问先后，而是入算次序：造方先入算、受方后入算，后读的覆写先读的（v2.8 刀5 只接了受方这一把钥匙，造方那一把您裁了本轮不接，规矩先立着等接线那把刀）。账本上标了「锁定技」的那一笔，别的技能移不走——这是"锁定技不能被改变"这枚徽章第一次真的由结算来管；但请注意它的边界：它管的是"这笔账不许被撤销"，不管"这条技能不许被无效"（后一半今天仍然没有任何结算代码读它）。</t>
+    <t>规矩是「固定」压过「增减」：只要有一笔"固定为"在场，同一种伤害上所有"增减"都不参与（先按您定的规则走完"固定"这一段，增减没有可作用的中间值）；同一形态有多笔，按发动的先后排，后落的那笔接着前一笔的结果算——同格两笔"固定"⇒后发的那笔盖掉先发的那笔（v2.8 刀5 钉死）。"固定"那笔一旦失效（用掉、离场、周期到点），此前被压住的增减立刻恢复参与，不用重新发动（被压住的那笔一次性增减不算被用掉，它还留着等下一刀）。跨侧（一个技能改自己受到的伤害、另一个改自己造成的伤害）谁赢＝已裁＝受方那一格恒盖过造方那一格，实现方式不是弹窗口问先后，而是入算次序：造方先入算、受方后入算，后读的覆写先读的（v2.8 刀5 只接了受方这一把钥匙，造方那一把当时裁了本轮不接、规矩先立着等接线那把刀；v2.9.4 造方这一把也接上了＝这条"受方恒盖造方"自此不是纸面规矩，而是入算次序真兑出来的结果。两本账都为空时这两个函数逐字返回原数⇒上一版所有对局一字未变）。账本上标了「锁定技」的那一笔，别的技能移不走——这是"锁定技不能被改变"这枚徽章第一次真的由结算来管；但请注意它的边界：它管的是"这笔账不许被撤销"，不管"这条技能不许被无效"（后一半今天仍然没有任何结算代码读它）。</t>
   </si>
   <si>
     <t>击破 / 出局 / 阵亡 / 获得胜利</t>

--- a/词汇表.xlsx
+++ b/词汇表.xlsx
@@ -762,13 +762,13 @@
     <t>觉醒技</t>
   </si>
   <si>
-    <t>分类徽章（您 2026-10-04 给的口径原文存档："一般是满足一定条件后可以自选发动，从而获得新技能或者改变已有技能的效果，非强制发动"）。v2.9.3 起这一格真的管事了，翻译成对局里该发生的事＝条件满足了在达成那一刻当场问您一次（您 2026-10-08 裁的：不当场问、拖到回合结束不算），问的是"觉醒／不觉醒"；点头才结算这枚技能写的那一句（拿到新技能，或者让账面数字变），摇头不扣额度、以后还有机会。一局只觉醒一次，这一笔账跟限定技走同一本（您 2026-10-08 裁："觉醒技和限定技同理，在同一局中发动过一次就不能再发动"），用尽后不再问。边界四句实话：①它不是到点自己响、也不是被动一直算数；②勾了「强制发动」的觉醒技例外——到点自己结算、不停下来问，但额度那一半照扣；③觉醒技挂不得"在场即生效"和"多选一"这两种形状，硬挂会在导入总结里点名退回，不会静悄悄当没事；④问句挂着的时候全场冻结，只有被问的那一席能答（答或者跳过），跟响应链那一格同一套规矩。今天的官方 95 将与您手上的样本卡还没有一条挂这一枚（有测试钉着这个数），所以正式对局里的表现与上一版逐字相同。裁决原文与判据＝PROJECT_HANDOFF.md §12。</t>
+    <t>分类徽章（您 2026-10-04 给的口径原文存档："一般是满足一定条件后可以自选发动，从而获得新技能或者改变已有技能的效果，非强制发动"）。v2.9.3 起这一格真的管事了，翻译成对局里该发生的事＝条件满足了在达成那一刻当场问您一次（您 2026-10-08 裁的：不当场问、拖到回合结束不算），问的是"觉醒／不觉醒"；点头才结算这枚技能写的那一句（拿到新技能，或者让账面数字变），摇头不扣额度、以后还有机会。一局只觉醒一次，这一笔账跟限定技走同一本（您 2026-10-08 裁："觉醒技和限定技同理，在同一局中发动过一次就不能再发动"），用尽后不再问。边界四句实话：①它不是到点自己响、也不是被动一直算数；②勾了「强制发动」的觉醒技例外——到点自己结算、不停下来问，但额度那一半照扣；③觉醒技挂不得"在场即生效"和"多选一"这两种形状，硬挂会在导入总结里点名退回，不会静悄悄当没事；④问句挂着的时候全场冻结，只有被问的那一席能答（答或者跳过），跟响应链那一格同一套规矩。v2.9.6 起这一枚第一次挂上了官方将＝魏关羽的「单骑」（名册 96 将里当场量过，用这一枚的只有这一条，有测试钉着这个数）。裁决原文与判据＝PROJECT_HANDOFF.md §12。</t>
   </si>
   <si>
     <t>强制发动</t>
   </si>
   <si>
-    <t>编辑器里的开关（Excel 也有这一列）：满足触发条件与代价后直接响／直接适用效果，不用玩家点头。它跟锁定技不是一件事，跟"数值变化／持续生效"也不绑定，三者可以任意组合。v2.8.25 起这一格真的管事了：勾上之后，凡是本来会停下来问您"要不要发动"的那一刻（＝成为目标时／受到伤害后这两型），这条技能不再问、自己就响了；不勾就照旧问。四句实话边界：①它只决定"问不问人"，不会让一条技能多响一次，也不绕过发动门槛与代价；②本来就到点自动响的时机（登场／回合开始／击杀／失去手牌……）勾不勾都一样（v2.9.3 起唯一一条例外：同一条技能挂了「觉醒技」徽章时，这些时机改成停下来问您一次，勾了才自己响）；③「回合结束时」那一型永远要您点头（一条技能不许响两次的常设规矩），勾了也不自响；④决斗那一套的"开局被点名"与"收官掉血"两刻同样吃这一格——勾了就自己响、没勾就问；⑤v2.8.31 起它与"不勾"完全同一条时机判据（您 2026-10-04 定稿：强制发动和手动发动的处理必须一致，区别只在"需不需要玩家自行响应"）——被这一刀砍死时，勾了的「成为目标时」照样响、勾了的「受到伤害后」照样不响，与没勾时问您那一型逐字同形（只有「自身被击杀时」那一型放行）。今天的官方 95 将与您手上的样本卡还没有一条勾了这个开关，所以对局里的表现与上一版逐字相同。</t>
+    <t>编辑器里的开关（Excel 也有这一列）：满足触发条件与代价后直接响／直接适用效果，不用玩家点头。它跟锁定技不是一件事，跟"数值变化／持续生效"也不绑定，三者可以任意组合。v2.8.25 起这一格真的管事了：勾上之后，凡是本来会停下来问您"要不要发动"的那一刻（＝成为目标时／受到伤害后这两型），这条技能不再问、自己就响了；不勾就照旧问。四句实话边界：①它只决定"问不问人"，不会让一条技能多响一次，也不绕过发动门槛与代价；②本来就到点自动响的时机（登场／回合开始／击杀／失去手牌……）勾不勾都一样（v2.9.3 起唯一一条例外：同一条技能挂了「觉醒技」徽章时，这些时机改成停下来问您一次，勾了才自己响）；③「回合结束时」那一型永远要您点头（一条技能不许响两次的常设规矩），勾了也不自响；④决斗那一套的"开局被点名"与"收官掉血"两刻同样吃这一格——勾了就自己响、没勾就问；⑤v2.8.31 起它与"不勾"完全同一条时机判据（您 2026-10-04 定稿：强制发动和手动发动的处理必须一致，区别只在"需不需要玩家自行响应"）——被这一刀砍死时，勾了的「成为目标时」照样响、勾了的「受到伤害后」照样不响，与没勾时问您那一型逐字同形（只有「自身被击杀时」那一型放行）。今天的官方 96 将与您手上的样本卡还没有一条勾了这个开关（v2.9.6 新上的「单骑」也没勾——它停下来问您靠的是上面「觉醒技」那一枚，不是这一格），所以对局里的表现与上一版逐字相同。</t>
   </si>
   <si>
     <t>触发时机</t>
@@ -786,7 +786,7 @@
     <t>在场即生效（不用发动，人在就算）（v2.8 刀4 起可结算）</t>
   </si>
   <si>
-    <t>第十一种选择，但它根本不是"哪一刻响"——它是"没有哪一刻需要它响"。这一型编译出来不监听任何事件、不进问答窗、不吃「强制发动」那一格：将领登场那一刻落一笔账（配合下面的「修改数值」用），离场当场销账，人在的整段时间都算数。三句实话：①旧名字「全局生效（在场时持续）」容易读成"影响全场所有人"，v2.8 刀4 起改叫这个名，旧 Excel 里那一格照样读得懂、再导出会写新名；②这一型不许配门槛、不许配有效周期、不许配「选择其一」（门槛要"情况一变就改口"、周期要"发动笔"那一档、择一要有人点头——三样都没有落点），填了会在编译时逐条点名跳过，不会悄悄变成"全都要"；③官方 95 将与您手上的样本卡今天还没有一条用这一型，所以对局里的表现与上一版逐字相同。</t>
+    <t>第十一种选择，但它根本不是"哪一刻响"——它是"没有哪一刻需要它响"。这一型编译出来不监听任何事件、不进问答窗、不吃「强制发动」那一格：将领登场那一刻落一笔账（配合下面的「修改数值」用），离场当场销账，人在的整段时间都算数。三句实话：①旧名字「全局生效（在场时持续）」容易读成"影响全场所有人"，v2.8 刀4 起改叫这个名，旧 Excel 里那一格照样读得懂、再导出会写新名；②这一型不许配门槛、不许配有效周期、不许配「选择其一」（门槛要"情况一变就改口"、周期要"发动笔"那一档、择一要有人点头——三样都没有落点），填了会在编译时逐条点名跳过，不会悄悄变成"全都要"；③v2.9.6 起这一型第一次挂上了官方将＝魏、蜀两张关羽卡上共用的「武圣」（出牌时把远程攻击力往上顶 1，人在就算、离场当场销账）；同一轮立起来的独立技能表里「怒斩」也是这一型。名册 96 将里用这一型的就这一条（当场量过，有测试钉着）。</t>
   </si>
   <si>
     <t>攻击伤害 / 技能伤害</t>
@@ -885,10 +885,10 @@
     <t>自己的将领和目标的将领轮流各出手三次（最多六次）互砍：每一轮用当下出手那一方的攻击力，护甲之前那两格（造成伤害 → 受到伤害）也是每一轮各算一次（v2.9.4＝您裁"决斗的每一轮都算"；一次性那笔仍旧一轮只销一次），护甲照旧"2 点挡 1 点"；伤害算技能伤害、不消耗手牌；谁先体力归零就当场停，剩下的轮次不补。决斗中阵亡同样算"被击破"，由失去这名将领的一方补抽 1 张。只能由技能发起——棋盘上没有"决斗"按钮。问答节奏（2.8.24 起）：开场先停下来问一遍"成为技能目标"（被决斗点名的那一方、以及监听范围填了"己方／场上"的这一类被动都有表态权；答复里回复的体力算进决斗起点；2.8.25 起这一层还吃「强制发动」那一格——打了勾的技能不问、自己响完，且这一层全部响完才开始互砍）；这一层全部问完才开始互砍，互砍的每一"打"中间不唤任何监听；全部打完再按"受到伤害后"问一遍——判定值＝该将领这一场实际掉掉的体力总额（军备减免不算），只算一笔、只问一次、绝不再扣第二次血；问的次序＝受邀者那笔先问完（本人先答→旁人按座次绕圈），发起者那笔后问。决斗中阵亡的那一位那一笔整笔跳过（本人和旁人均不问），但他的遗言技（自身被击杀时）与击破补偿抽照旧。</t>
   </si>
   <si>
-    <t>效果模式：全部生效 / 选择其一</t>
-  </si>
-  <si>
-    <t>一个技能里多条效果是"全都要"还是"只能挑一条"。对局里挑那条时会弹"抉择"窗。</t>
+    <t>效果模式：全部生效 / 选择其一 / 链式若-则</t>
+  </si>
+  <si>
+    <t>一个技能里多条效果是"全都要"还是"只能挑一条"。对局里挑那条时会弹"抉择"窗。第三档「链式若-则」（v2.8.34 起能结算，词汇表这一格当时漏写了，v2.9.6 补上）＝一条条按顺序走，前一条真的结算成了才走到下一条；中途哪一条没成，后面整段都不补。Excel 那一格就认这三个词，别的写法按没填处理（＝全部生效）。v2.9.6 修掉的一处真缺陷：这一格挂「链式若-则」的技能导出时被写成"无"、再导回来就变成"全部生效"＝来回一趟档位丢了；现在导出/导入都走同一份词表。名册 96 将里用这一档的只有魏关羽的「单骑」。</t>
   </si>
   <si>
     <t>技能门槛 / 效果N门槛</t>
@@ -900,7 +900,7 @@
     <t>修改数值（效果类型，v2.8 刀4 起可结算）</t>
   </si>
   <si>
-    <t>第十一条效果类型。它不改卡面上的印刷数字，而是给这名将领记一笔"账"（引擎里那本账叫 state.statModifiers，随存档走、录像能重放）。所以同一张卡在棋盘上会同时存在两个数：卡上印的（永远不变，图鉴与手抄核对用它）和当下算数的（对局里真正用来砍人的）。今天有六个数能被这样改：近战攻击力／远程攻击力／体力上限（v2.8 刀4）＋受到的伤害（v2.8 刀5）＋射程（v2.9.0）＋造成的伤害（v2.9.4）。五句实话：①当前体力不走这本账（它本来就是"损失记录"那一本，回血、扣血照旧直接动它）；②护甲、手牌上限这一版还没接（写了会被点名跳过）；③只能改自己的账面数字——"让别人的攻击＋1"那种跨将改数还没有目标选择器，编译时逐条点名跳过；④「受到的伤害」与「造成的伤害」这两格都作用在护甲之前，次序是攻击力 → 造成伤害 → 受到伤害 → 护甲抵扣 → 扣血（您 2026-10-14 裁「扣护甲前算」）：先把伤害这个数摁好，再交给"2 点护甲挡 1 点"那套算术，所以它们是"看不见的加减伤"，不是第二层护甲，也不改变身上有没有护甲这件事；营地（老家）这两格都不吃——规则上营地单次受到的伤害最多 1 点，那一条由攻击那一步钉死，不是账本管的事；⑤官方 95 将与您手上的样本卡今天还没有一条用它（仓库那叠试作样本除外），所以正式对局表现与上一版逐字相同。⑥「射程」这一把有两条自己的规矩（v2.9.0）：(a) 只往外推，不把近处一并放开——加 1 就是从自家营地多够得着对面前线，不会因此够得着自家前线；(b) 近战那一档永远吃不到它，近战只看"挨不挨着"，所以给一员将加射程，它的近战名单一格都不会变多。另外摁成 1 或 0 是合法的＝远程名单直接空掉（"这员将只能近战"），不是回退到默认值。⑦「造成的伤害」这一把自己的一条规矩（v2.9.4）：这一格是记在打出去的那一员将身上的，改的是"我这一刀砍出去几"，不是"对面挨几"——两格同时在场时先加后减，再由"固定压过增减"那一条判输赢（受方那一格恒盖造方）。决斗里它是每一轮各算一次（您 2026-10-14 裁），不是整场只算一次。这一格还能再限定"只在某种场合才算数"（近战攻击有护甲的角色／正在打决斗），但那一档界面与 Excel 里都还没有对应的格子，今天只有仓库里写好的技能定义带得进来，您能填的仍是"什么时候都算"。</t>
+    <t>第十一条效果类型。它不改卡面上的印刷数字，而是给这名将领记一笔"账"（引擎里那本账叫 state.statModifiers，随存档走、录像能重放）。所以同一张卡在棋盘上会同时存在两个数：卡上印的（永远不变，图鉴与手抄核对用它）和当下算数的（对局里真正用来砍人的）。今天有六个数能被这样改：近战攻击力／远程攻击力／体力上限（v2.8 刀4）＋受到的伤害（v2.8 刀5）＋射程（v2.9.0）＋造成的伤害（v2.9.4）。五句实话：①当前体力不走这本账（它本来就是"损失记录"那一本，回血、扣血照旧直接动它）；②护甲、手牌上限这一版还没接（写了会被点名跳过）；③只能改自己的账面数字——"让别人的攻击＋1"那种跨将改数还没有目标选择器，编译时逐条点名跳过；④「受到的伤害」与「造成的伤害」这两格都作用在护甲之前，次序是攻击力 → 造成伤害 → 受到伤害 → 护甲抵扣 → 扣血（您 2026-10-14 裁「扣护甲前算」）：先把伤害这个数摁好，再交给"2 点护甲挡 1 点"那套算术，所以它们是"看不见的加减伤"，不是第二层护甲，也不改变身上有没有护甲这件事；营地（老家）这两格都不吃——规则上营地单次受到的伤害最多 1 点，那一条由攻击那一步钉死，不是账本管的事；⑤v2.9.6 起这一档第一次挂上了官方将：「武圣」用它加射程那一格（上面 ⑥ 那把钥匙）、「单骑」用它把体力上限摁低 1（上面 ① 说的"上限另有一本账"就是走这一格）；独立技能表里的「怒斩」用它的造成的伤害那一格（还带了"只在决斗里算／只在近战砍有护甲的人时算"那两种限定）。名册 96 将里用到这一档的就这两条（当场量过，有测试钉着）。⑥「射程」这一把有两条自己的规矩（v2.9.0）：(a) 只往外推，不把近处一并放开——加 1 就是从自家营地多够得着对面前线，不会因此够得着自家前线；(b) 近战那一档永远吃不到它，近战只看"挨不挨着"，所以给一员将加射程，它的近战名单一格都不会变多。另外摁成 1 或 0 是合法的＝远程名单直接空掉（"这员将只能近战"），不是回退到默认值。⑦「造成的伤害」这一把自己的一条规矩（v2.9.4）：这一格是记在打出去的那一员将身上的，改的是"我这一刀砍出去几"，不是"对面挨几"——两格同时在场时先加后减，再由"固定压过增减"那一条判输赢（受方那一格恒盖造方）。决斗里它是每一轮各算一次（您 2026-10-14 裁），不是整场只算一次。这一格还能再限定"只在某种场合才算数"（近战攻击有护甲的角色／正在打决斗），但那一档界面与 Excel 里都还没有对应的格子，今天只有仓库里写好的技能定义带得进来，您能填的仍是"什么时候都算"。</t>
   </si>
   <si>
     <t>改哪个数 / 怎么改 / 有效周期（Excel 里效果组第 9–11 列）</t>
@@ -912,7 +912,7 @@
     <t>获得技能（效果类型，v2.9.3 刀A 起可结算）</t>
   </si>
   <si>
-    <t>第十二条效果类型，和「修改数值」正好是一正一反：那一档只动账本、卡面一字不改；这一档只动卡面——往这一员将的技能表上添一枚技能，不改任何数字、不掉血、不搬牌。四句实话：①认的是名字，您在那一格里写什么，引擎就拿什么去查名册（＝官方将领卡上印着的那些技能名）；查不到、或者同名却有两份不同内容，都会被导入报告与编译器逐条点名跳过，绝不猜一个"最像的"（自己新编的 DIY 技能名这一版还查不到，已另立待办）；②只能添在自己身上——"给别的将领技能"要等目标选择器那把刀；③添进来之后从下一次发动起这一员将就听得见这枚新技能（本项目没有"技能表缓存"，每次发动前都从对局现场重算一遍），同一枚拿第二次也只留一份；④如果拿到的是一枚在场即生效的技能，那笔账在获得这一刻补落进账本（同一枚不落第二笔），不是等下一次登场。另外官方 95 将与您手上的样本卡今天还没有一条用它，所以正式对局表现与上一版逐字相同。</t>
+    <t>第十二条效果类型，和「修改数值」正好是一正一反：那一档只动账本、卡面一字不改；这一档只动卡面——往这一员将的技能表上添一枚技能，不改任何数字、不掉血、不搬牌。四句实话：①认的是名字，您在那一格里写什么，引擎就拿什么去查名册（＝官方将领卡上印着的那些技能名）；查不到、或者同名却有两份不同内容，都会被导入报告与编译器逐条点名跳过，绝不猜一个"最像的"（自己新编的 DIY 技能名这一版还查不到，已另立待办）；②只能添在自己身上——"给别的将领技能"要等目标选择器那把刀；③添进来之后从下一次发动起这一员将就听得见这枚新技能（本项目没有"技能表缓存"，每次发动前都从对局现场重算一遍），同一枚拿第二次也只留一份；④如果拿到的是一枚在场即生效的技能，那笔账在获得这一刻补落进账本（同一枚不落第二笔），不是等下一次登场。另外v2.9.6 起这一档第一次挂上了官方将＝魏关羽的「单骑」：觉醒那一刻它照这一格去查名册，把「怒斩」添进这名将的技能表——查的正是那张新立的独立技能表（src/data/standaloneSkills.ts，v2.9.4 只有一张空架子、里面一条真内容都没有，所以当时谁也查不到）。名册 96 将里用到这一档的只有这一条（当场量过，有测试钉着）。</t>
   </si>
   <si>
     <t>获得哪个技能（Excel 里效果组第 12 列）</t>

--- a/词汇表.xlsx
+++ b/词汇表.xlsx
@@ -900,7 +900,7 @@
     <t>修改数值（效果类型，v2.8 刀4 起可结算）</t>
   </si>
   <si>
-    <t>第十一条效果类型。它不改卡面上的印刷数字，而是给这名将领记一笔"账"（引擎里那本账叫 state.statModifiers，随存档走、录像能重放）。所以同一张卡在棋盘上会同时存在两个数：卡上印的（永远不变，图鉴与手抄核对用它）和当下算数的（对局里真正用来砍人的）。今天有六个数能被这样改：近战攻击力／远程攻击力／体力上限（v2.8 刀4）＋受到的伤害（v2.8 刀5）＋射程（v2.9.0）＋造成的伤害（v2.9.4）。五句实话：①当前体力不走这本账（它本来就是"损失记录"那一本，回血、扣血照旧直接动它）；②护甲、手牌上限这一版还没接（写了会被点名跳过）；③只能改自己的账面数字——"让别人的攻击＋1"那种跨将改数还没有目标选择器，编译时逐条点名跳过；④「受到的伤害」与「造成的伤害」这两格都作用在护甲之前，次序是攻击力 → 造成伤害 → 受到伤害 → 护甲抵扣 → 扣血（您 2026-10-14 裁「扣护甲前算」）：先把伤害这个数摁好，再交给"2 点护甲挡 1 点"那套算术，所以它们是"看不见的加减伤"，不是第二层护甲，也不改变身上有没有护甲这件事；营地（老家）这两格都不吃——规则上营地单次受到的伤害最多 1 点，那一条由攻击那一步钉死，不是账本管的事；⑤v2.9.6 起这一档第一次挂上了官方将：「武圣」用它加射程那一格（上面 ⑥ 那把钥匙）、「单骑」用它把体力上限摁低 1（上面 ① 说的"上限另有一本账"就是走这一格）；独立技能表里的「怒斩」用它的造成的伤害那一格（还带了"只在决斗里算／只在近战砍有护甲的人时算"那两种限定）。名册 96 将里用到这一档的就这两条（当场量过，有测试钉着）。⑥「射程」这一把有两条自己的规矩（v2.9.0）：(a) 只往外推，不把近处一并放开——加 1 就是从自家营地多够得着对面前线，不会因此够得着自家前线；(b) 近战那一档永远吃不到它，近战只看"挨不挨着"，所以给一员将加射程，它的近战名单一格都不会变多。另外摁成 1 或 0 是合法的＝远程名单直接空掉（"这员将只能近战"），不是回退到默认值。⑦「造成的伤害」这一把自己的一条规矩（v2.9.4）：这一格是记在打出去的那一员将身上的，改的是"我这一刀砍出去几"，不是"对面挨几"——两格同时在场时先加后减，再由"固定压过增减"那一条判输赢（受方那一格恒盖造方）。决斗里它是每一轮各算一次（您 2026-10-14 裁），不是整场只算一次。这一格还能再限定"只在某种场合才算数"（近战攻击有护甲的角色／正在打决斗），但那一档界面与 Excel 里都还没有对应的格子，今天只有仓库里写好的技能定义带得进来，您能填的仍是"什么时候都算"。</t>
+    <t>第十一条效果类型。它不改卡面上的印刷数字，而是给这名将领记一笔"账"（引擎里那本账叫 state.statModifiers，随存档走、录像能重放）。所以同一张卡在棋盘上会同时存在两个数：卡上印的（永远不变，图鉴与手抄核对用它）和当下算数的（对局里真正用来砍人的）。今天有六个数能被这样改：近战攻击力／远程攻击力／体力上限（v2.8 刀4）＋受到的伤害（v2.8 刀5）＋射程（v2.9.0）＋造成的伤害（v2.9.4）。五句实话：①当前体力不走这本账（它本来就是"损失记录"那一本，回血、扣血照旧直接动它）；②护甲、手牌上限这一版还没接（写了会被点名跳过）；③只能改自己的账面数字——"让别人的攻击＋1"那种跨将改数还没有目标选择器，编译时逐条点名跳过；④「受到的伤害」与「造成的伤害」这两格都作用在护甲之前，次序是攻击力 → 造成伤害 → 受到伤害 → 护甲抵扣 → 扣血（您 2026-10-14 裁「扣护甲前算」）：先把伤害这个数摁好，再交给"2 点护甲挡 1 点"那套算术，所以它们是"看不见的加减伤"，不是第二层护甲，也不改变身上有没有护甲这件事；营地（老家）这两格都不吃——规则上营地单次受到的伤害最多 1 点，那一条由攻击那一步钉死，不是账本管的事；⑤v2.9.6 起这一档第一次挂上了官方将：「武圣」用它把远程攻击力往上顶 1（就是六把钥匙里第一号那类"攻击力"，不是下面 ⑥ 那把射程）、「单骑」用它把体力上限摁低 1（上面 ① 说的"上限另有一本账"就是走这一格）；独立技能表里的「怒斩」用它的造成的伤害那一格（还带了"只在决斗里算／只在近战砍有护甲的人时算"那两种限定）。名册 96 将里用到这一档的就这两条（当场量过，有测试钉着）。⑥「射程」这一把有两条自己的规矩（v2.9.0）：(a) 只往外推，不把近处一并放开——加 1 就是从自家营地多够得着对面前线，不会因此够得着自家前线；(b) 近战那一档永远吃不到它，近战只看"挨不挨着"，所以给一员将加射程，它的近战名单一格都不会变多。另外摁成 1 或 0 是合法的＝远程名单直接空掉（"这员将只能近战"），不是回退到默认值。⑦「造成的伤害」这一把自己的一条规矩（v2.9.4）：这一格是记在打出去的那一员将身上的，改的是"我这一刀砍出去几"，不是"对面挨几"——两格同时在场时先加后减，再由"固定压过增减"那一条判输赢（受方那一格恒盖造方）。决斗里它是每一轮各算一次（您 2026-10-14 裁），不是整场只算一次。这一格还能再限定"只在某种场合才算数"（近战攻击有护甲的角色／正在打决斗），但那一档界面与 Excel 里都还没有对应的格子，今天只有仓库里写好的技能定义带得进来，您能填的仍是"什么时候都算"。</t>
   </si>
   <si>
     <t>改哪个数 / 怎么改 / 有效周期（Excel 里效果组第 9–11 列）</t>

--- a/词汇表.xlsx
+++ b/词汇表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="442">
   <si>
     <t>玩家词汇 · 大白话对照表（v2.8.18 界面口径）</t>
   </si>
@@ -46,7 +46,7 @@
     <t>工作表一览：</t>
   </si>
   <si>
-    <t>一 棋盘与数字：30 条</t>
+    <t>一 棋盘与数字：31 条</t>
   </si>
   <si>
     <t>二 行动按钮与提示：38 条</t>
@@ -204,6 +204,12 @@
     <t>将领外面的缓冲层。关键：攒够 2 点护甲才抵消 1 点伤害，只有 1 点时它不挡刀、原样留着。定规则：core/armorDamage.ts:15。v2.8.18 起这句话也印在卡面那一格上（图鉴与操作条的"🛡️护甲"悬停提示），规则页也写明了。</t>
   </si>
   <si>
+    <t>打谁一目了然（鼠标指上去的预览）</t>
+  </si>
+  <si>
+    <t>选攻击目标时，鼠标停在哪个目标上，棋盘上方就浮出三个数：伤害（红）｜护甲掉几点（蓝，一点没掉就写"护甲不变"）｜打完还剩几体力/上限（黄）。这三个数不是另算一套——用的就是引擎那一刀的同一份算术（core/attackPreview.ts），所以"看着是 2 点、点下去变 3 点"这种分叉不允许出现。打营地那一格只写「营地 −N」（它没有护甲、也没有体力上限）。您的原话：「指向哪个目标就提前显示对方的体力/护甲变化（体力变化用黄色，护甲变化用蓝色）」；v2.9.7 起配色与措辞照这一句对齐（旧写法是"HP:"与"N甲／无甲"，颜色是红／绿／橙）。</t>
+  </si>
+  <si>
     <t>🛡️基础</t>
   </si>
   <si>
@@ -786,7 +792,7 @@
     <t>在场即生效（不用发动，人在就算）（v2.8 刀4 起可结算）</t>
   </si>
   <si>
-    <t>第十一种选择，但它根本不是"哪一刻响"——它是"没有哪一刻需要它响"。这一型编译出来不监听任何事件、不进问答窗、不吃「强制发动」那一格：将领登场那一刻落一笔账（配合下面的「修改数值」用），离场当场销账，人在的整段时间都算数。三句实话：①旧名字「全局生效（在场时持续）」容易读成"影响全场所有人"，v2.8 刀4 起改叫这个名，旧 Excel 里那一格照样读得懂、再导出会写新名；②这一型不许配门槛、不许配有效周期、不许配「选择其一」（门槛要"情况一变就改口"、周期要"发动笔"那一档、择一要有人点头——三样都没有落点），填了会在编译时逐条点名跳过，不会悄悄变成"全都要"；③v2.9.6 起这一型第一次挂上了官方将＝魏、蜀两张关羽卡上共用的「武圣」（出牌时把远程攻击力往上顶 1，人在就算、离场当场销账）；同一轮立起来的独立技能表里「怒斩」也是这一型。名册 96 将里用这一型的就这一条（当场量过，有测试钉着）。</t>
+    <t>第十一种选择，但它根本不是"哪一刻响"——它是"没有哪一刻需要它响"。这一型编译出来不监听任何事件、不进问答窗、不吃「强制发动」那一格：将领登场那一刻落一笔账（配合下面的「修改数值」用），离场当场销账，人在的整段时间都算数。三句实话：①旧名字「全局生效（在场时持续）」容易读成"影响全场所有人"，v2.8 刀4 起改叫这个名，旧 Excel 里那一格照样读得懂、再导出会写新名；②这一型不许配门槛、不许配有效周期、不许配「选择其一」（门槛要"情况一变就改口"、周期要"发动笔"那一档、择一要有人点头——三样都没有落点），填了会在编译时逐条点名跳过，不会悄悄变成"全都要"；③v2.9.6 起这一型第一次挂上了官方将＝魏、蜀两张关羽卡上共用的「武圣」（出牌时把远程攻击力往上顶 1，人在就算、离场当场销账）；技能表上那一枚「怒斩」也是这一型（它不印在任何将卡上）。96 将里用这一型的就这一条（当场量过，有测试钉着）。</t>
   </si>
   <si>
     <t>攻击伤害 / 技能伤害</t>
@@ -900,7 +906,7 @@
     <t>修改数值（效果类型，v2.8 刀4 起可结算）</t>
   </si>
   <si>
-    <t>第十一条效果类型。它不改卡面上的印刷数字，而是给这名将领记一笔"账"（引擎里那本账叫 state.statModifiers，随存档走、录像能重放）。所以同一张卡在棋盘上会同时存在两个数：卡上印的（永远不变，图鉴与手抄核对用它）和当下算数的（对局里真正用来砍人的）。今天有六个数能被这样改：近战攻击力／远程攻击力／体力上限（v2.8 刀4）＋受到的伤害（v2.8 刀5）＋射程（v2.9.0）＋造成的伤害（v2.9.4）。五句实话：①当前体力不走这本账（它本来就是"损失记录"那一本，回血、扣血照旧直接动它）；②护甲、手牌上限这一版还没接（写了会被点名跳过）；③只能改自己的账面数字——"让别人的攻击＋1"那种跨将改数还没有目标选择器，编译时逐条点名跳过；④「受到的伤害」与「造成的伤害」这两格都作用在护甲之前，次序是攻击力 → 造成伤害 → 受到伤害 → 护甲抵扣 → 扣血（您 2026-10-14 裁「扣护甲前算」）：先把伤害这个数摁好，再交给"2 点护甲挡 1 点"那套算术，所以它们是"看不见的加减伤"，不是第二层护甲，也不改变身上有没有护甲这件事；营地（老家）这两格都不吃——规则上营地单次受到的伤害最多 1 点，那一条由攻击那一步钉死，不是账本管的事；⑤v2.9.6 起这一档第一次挂上了官方将：「武圣」用它把远程攻击力往上顶 1（就是六把钥匙里第一号那类"攻击力"，不是下面 ⑥ 那把射程）、「单骑」用它把体力上限摁低 1（上面 ① 说的"上限另有一本账"就是走这一格）；独立技能表里的「怒斩」用它的造成的伤害那一格（还带了"只在决斗里算／只在近战砍有护甲的人时算"那两种限定）。名册 96 将里用到这一档的就这两条（当场量过，有测试钉着）。⑥「射程」这一把有两条自己的规矩（v2.9.0）：(a) 只往外推，不把近处一并放开——加 1 就是从自家营地多够得着对面前线，不会因此够得着自家前线；(b) 近战那一档永远吃不到它，近战只看"挨不挨着"，所以给一员将加射程，它的近战名单一格都不会变多。另外摁成 1 或 0 是合法的＝远程名单直接空掉（"这员将只能近战"），不是回退到默认值。⑦「造成的伤害」这一把自己的一条规矩（v2.9.4）：这一格是记在打出去的那一员将身上的，改的是"我这一刀砍出去几"，不是"对面挨几"——两格同时在场时先加后减，再由"固定压过增减"那一条判输赢（受方那一格恒盖造方）。决斗里它是每一轮各算一次（您 2026-10-14 裁），不是整场只算一次。这一格还能再限定"只在某种场合才算数"（近战攻击有护甲的角色／正在打决斗），但那一档界面与 Excel 里都还没有对应的格子，今天只有仓库里写好的技能定义带得进来，您能填的仍是"什么时候都算"。</t>
+    <t>第十一条效果类型。它不改卡面上的印刷数字，而是给这名将领记一笔"账"（引擎里那本账叫 state.statModifiers，随存档走、录像能重放）。所以同一张卡在棋盘上会同时存在两个数：卡上印的（永远不变，图鉴与手抄核对用它）和当下算数的（对局里真正用来砍人的）。今天有六个数能被这样改：近战攻击力／远程攻击力／体力上限（v2.8 刀4）＋受到的伤害（v2.8 刀5）＋射程（v2.9.0）＋造成的伤害（v2.9.4）。五句实话：①当前体力不走这本账（它本来就是"损失记录"那一本，回血、扣血照旧直接动它）；②护甲、手牌上限这一版还没接（写了会被点名跳过）；③只能改自己的账面数字——"让别人的攻击＋1"那种跨将改数还没有目标选择器，编译时逐条点名跳过；④「受到的伤害」与「造成的伤害」这两格都作用在护甲之前，次序是攻击力 → 造成伤害 → 受到伤害 → 护甲抵扣 → 扣血（您 2026-10-14 裁「扣护甲前算」）：先把伤害这个数摁好，再交给"2 点护甲挡 1 点"那套算术，所以它们是"看不见的加减伤"，不是第二层护甲，也不改变身上有没有护甲这件事；营地（老家）这两格都不吃——规则上营地单次受到的伤害最多 1 点，那一条由攻击那一步钉死，不是账本管的事；⑤v2.9.6 起这一档第一次挂上了官方将：「武圣」用它把远程攻击力往上顶 1（就是六把钥匙里第一号那类"攻击力"，不是下面 ⑥ 那把射程）、「单骑」用它把体力上限摁低 1（上面 ① 说的"上限另有一本账"就是走这一格）；技能表里的「怒斩」用它的造成的伤害那一格（还带了"只在决斗里算／只在近战砍有护甲的人时算"那两种限定）。名册 96 将里用到这一档的就这两条（当场量过，有测试钉着）。⑥「射程」这一把有两条自己的规矩（v2.9.0）：(a) 只往外推，不把近处一并放开——加 1 就是从自家营地多够得着对面前线，不会因此够得着自家前线；(b) 近战那一档永远吃不到它，近战只看"挨不挨着"，所以给一员将加射程，它的近战名单一格都不会变多。另外摁成 1 或 0 是合法的＝远程名单直接空掉（"这员将只能近战"），不是回退到默认值。⑦「造成的伤害」这一把自己的一条规矩（v2.9.4）：这一格是记在打出去的那一员将身上的，改的是"我这一刀砍出去几"，不是"对面挨几"——两格同时在场时先加后减，再由"固定压过增减"那一条判输赢（受方那一格恒盖造方）。决斗里它是每一轮各算一次（您 2026-10-14 裁），不是整场只算一次。这一格还能再限定"只在某种场合才算数"（近战攻击有护甲的角色／正在打决斗），但那一档界面与 Excel 里都还没有对应的格子，今天只有仓库里写好的技能定义带得进来，您能填的仍是"什么时候都算"。</t>
   </si>
   <si>
     <t>改哪个数 / 怎么改 / 有效周期（Excel 里效果组第 9–11 列）</t>
@@ -912,13 +918,13 @@
     <t>获得技能（效果类型，v2.9.3 刀A 起可结算）</t>
   </si>
   <si>
-    <t>第十二条效果类型，和「修改数值」正好是一正一反：那一档只动账本、卡面一字不改；这一档只动卡面——往这一员将的技能表上添一枚技能，不改任何数字、不掉血、不搬牌。四句实话：①认的是名字，您在那一格里写什么，引擎就拿什么去查名册（＝官方将领卡上印着的那些技能名）；查不到、或者同名却有两份不同内容，都会被导入报告与编译器逐条点名跳过，绝不猜一个"最像的"（自己新编的 DIY 技能名这一版还查不到，已另立待办）；②只能添在自己身上——"给别的将领技能"要等目标选择器那把刀；③添进来之后从下一次发动起这一员将就听得见这枚新技能（本项目没有"技能表缓存"，每次发动前都从对局现场重算一遍），同一枚拿第二次也只留一份；④如果拿到的是一枚在场即生效的技能，那笔账在获得这一刻补落进账本（同一枚不落第二笔），不是等下一次登场。另外v2.9.6 起这一档第一次挂上了官方将＝魏关羽的「单骑」：觉醒那一刻它照这一格去查名册，把「怒斩」添进这名将的技能表——查的正是那张新立的独立技能表（src/data/standaloneSkills.ts，v2.9.4 只有一张空架子、里面一条真内容都没有，所以当时谁也查不到）。名册 96 将里用到这一档的只有这一条（当场量过，有测试钉着）。</t>
+    <t>第十二条效果类型，和「修改数值」正好是一正一反：那一档只动账本、卡面一字不改；这一档只动卡面——往这一员将身上添一枚技能（添进他卡面上那份技能清单），不改任何数字、不掉血、不搬牌。五句实话：①认的是名字，您在那一格里写什么，引擎就拿什么去查技能表（v2.9.7 起这一档只认这一本名单＝卡上有真结算内容的技能自动在册＋不印在任何将卡上、写在表里的那几枚；今天表上 41 个名字，当场量过、有测试钉着）；②只在卡上印了个名字、还没挂上可结算内容的那一类不在表上（您 2026-10-16 裁「技能表只做有真内容的」）——填了会被点名跳过，而不是让您拿到一枚空的；卡上那枚哪天挂上内容，它自己就进表，这一条跟着生效，不用另改任何名单；③查不到、或者同名却有两份不同内容，都会被导入报告与编译器逐条点名跳过，绝不猜一个"最像的"（自己新编的 DIY 技能名这一版还查不到，已另立待办）；④只能添在自己身上——"给别的将领添技能"要等目标选择器那把刀；而且从下一次发动起这一员将才听得见这枚新技能（本项目没有卡面技能清单的缓存，每次发动前都从对局现场重算一遍），同一枚拿第二次也只留一份；⑤如果拿到的是一枚在场即生效的技能，那笔账在获得这一刻补落进账本（同一枚不落第二笔），不是等下一次登场。另外v2.9.6 起这一档第一次挂上了官方将＝魏关羽的「单骑」：觉醒那一刻它照这一格去查技能表，把「怒斩」添进这名将身上——「怒斩」不印在任何将卡上，住在表里（src/data/skillTable.ts；v2.9.4 那一版这张表还是空架子，一条真内容都没有，所以当时谁也查不到）。将领名册 96 将里用到这一档的只有这一条（当场量过，有测试钉着）。</t>
   </si>
   <si>
     <t>获得哪个技能（Excel 里效果组第 12 列）</t>
   </si>
   <si>
-    <t>「获得技能」那一枚的名字格，只服务这一个效果类型（与「改哪个数」「我听谁」同一族做法：一个正交维度占一列）。这一格故意不做死下拉：可选的名字是一百多个技能名、而且随内容增长，做成封闭下拉会把"先写技能、那枚技能还没进池"这条路堵死——所以名字是原样收字，认不认由引擎那一处唯一的查名册说了算（界面里给的是可自由输入的候选清单，不是强制选项）。只有「效果类型＝获得技能」读这一格，别的类型填了会在导入总结里点名、按没填处理；这一格留空同样点名（那是一条半截效果，不会被静悄悄收下）。旧的 11 列导出文件照样能导入，只是那种文件里没有这一格——凡是「获得技能」的效果会报"缺名字"。</t>
+    <t>「获得技能」那一枚的名字格，只服务这一个效果类型（与「改哪个数」「我听谁」同一族做法：一个正交维度占一列）。这一格故意不做死下拉：可选的名字＝技能表上那 41 个（数随内容增长），做成封闭下拉会把"先写技能、那枚技能还没进表"这条路堵死——所以名字是原样收字，认不认由引擎那一处唯一的解析点（＝查技能表）说了算（界面里给的是可自由输入的候选清单，不是强制选项）。只有「效果类型＝获得技能」读这一格，别的类型填了会在导入总结里点名、按没填处理；这一格留空同样点名（那是一条半截效果，不会被静悄悄收下）。旧的 11 列导出文件照样能导入，只是那种文件里没有这一格——凡是「获得技能」的效果会报"缺名字"。</t>
   </si>
   <si>
     <t>有效周期（这笔账什么时候结束）</t>
@@ -1858,7 +1864,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -2083,40 +2089,40 @@
         <v>61</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>62</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="C22" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2171,18 +2177,18 @@
         <v>80</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>81</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="C29" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2204,6 +2210,17 @@
         <v>87</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2236,10 +2253,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -2247,10 +2264,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -2258,10 +2275,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -2269,10 +2286,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -2280,10 +2297,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -2291,10 +2308,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -2302,10 +2319,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -2313,10 +2330,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -2324,10 +2341,10 @@
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -2335,10 +2352,10 @@
     </row>
     <row r="11" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>1</v>
@@ -2346,10 +2363,10 @@
     </row>
     <row r="12" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>1</v>
@@ -2357,10 +2374,10 @@
     </row>
     <row r="13" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>1</v>
@@ -2368,21 +2385,21 @@
     </row>
     <row r="14" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>1</v>
@@ -2390,10 +2407,10 @@
     </row>
     <row r="16" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>1</v>
@@ -2401,10 +2418,10 @@
     </row>
     <row r="17" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>1</v>
@@ -2412,10 +2429,10 @@
     </row>
     <row r="18" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>1</v>
@@ -2423,10 +2440,10 @@
     </row>
     <row r="19" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>1</v>
@@ -2434,10 +2451,10 @@
     </row>
     <row r="20" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>1</v>
@@ -2445,10 +2462,10 @@
     </row>
     <row r="21" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>1</v>
@@ -2456,10 +2473,10 @@
     </row>
     <row r="22" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>1</v>
@@ -2467,10 +2484,10 @@
     </row>
     <row r="23" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>1</v>
@@ -2478,10 +2495,10 @@
     </row>
     <row r="24" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>1</v>
@@ -2489,10 +2506,10 @@
     </row>
     <row r="25" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>1</v>
@@ -2500,10 +2517,10 @@
     </row>
     <row r="26" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>1</v>
@@ -2511,10 +2528,10 @@
     </row>
     <row r="27" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>1</v>
@@ -2522,10 +2539,10 @@
     </row>
     <row r="28" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>1</v>
@@ -2533,10 +2550,10 @@
     </row>
     <row r="29" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>1</v>
@@ -2544,10 +2561,10 @@
     </row>
     <row r="30" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>1</v>
@@ -2555,10 +2572,10 @@
     </row>
     <row r="31" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>1</v>
@@ -2566,10 +2583,10 @@
     </row>
     <row r="32" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>1</v>
@@ -2577,10 +2594,10 @@
     </row>
     <row r="33" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>1</v>
@@ -2588,10 +2605,10 @@
     </row>
     <row r="34" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>1</v>
@@ -2599,10 +2616,10 @@
     </row>
     <row r="35" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>1</v>
@@ -2610,10 +2627,10 @@
     </row>
     <row r="36" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>1</v>
@@ -2621,10 +2638,10 @@
     </row>
     <row r="37" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>1</v>
@@ -2632,10 +2649,10 @@
     </row>
     <row r="38" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>1</v>
@@ -2643,10 +2660,10 @@
     </row>
     <row r="39" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>1</v>
@@ -2681,10 +2698,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -2692,10 +2709,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -2703,21 +2720,21 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -2725,10 +2742,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -2736,10 +2753,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -2747,10 +2764,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -2758,10 +2775,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -2769,21 +2786,21 @@
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>1</v>
@@ -2791,10 +2808,10 @@
     </row>
     <row r="12" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>1</v>
@@ -2802,10 +2819,10 @@
     </row>
     <row r="13" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>1</v>
@@ -2813,10 +2830,10 @@
     </row>
     <row r="14" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>1</v>
@@ -2824,10 +2841,10 @@
     </row>
     <row r="15" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>1</v>
@@ -2835,10 +2852,10 @@
     </row>
     <row r="16" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>1</v>
@@ -2846,10 +2863,10 @@
     </row>
     <row r="17" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>1</v>
@@ -2857,10 +2874,10 @@
     </row>
     <row r="18" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>1</v>
@@ -2868,10 +2885,10 @@
     </row>
     <row r="19" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>1</v>
@@ -2879,10 +2896,10 @@
     </row>
     <row r="20" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>1</v>
@@ -2890,10 +2907,10 @@
     </row>
     <row r="21" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>1</v>
@@ -2901,10 +2918,10 @@
     </row>
     <row r="22" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>1</v>
@@ -2912,10 +2929,10 @@
     </row>
     <row r="23" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>1</v>
@@ -2923,10 +2940,10 @@
     </row>
     <row r="24" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>1</v>
@@ -2934,10 +2951,10 @@
     </row>
     <row r="25" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>1</v>
@@ -2945,10 +2962,10 @@
     </row>
     <row r="26" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>1</v>
@@ -2956,10 +2973,10 @@
     </row>
     <row r="27" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>1</v>
@@ -2967,10 +2984,10 @@
     </row>
     <row r="28" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>1</v>
@@ -2978,10 +2995,10 @@
     </row>
     <row r="29" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>1</v>
@@ -2989,10 +3006,10 @@
     </row>
     <row r="30" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>1</v>
@@ -3000,10 +3017,10 @@
     </row>
     <row r="31" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>1</v>
@@ -3011,10 +3028,10 @@
     </row>
     <row r="32" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>1</v>
@@ -3022,10 +3039,10 @@
     </row>
     <row r="33" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>1</v>
@@ -3033,10 +3050,10 @@
     </row>
     <row r="34" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>1</v>
@@ -3044,10 +3061,10 @@
     </row>
     <row r="35" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>1</v>
@@ -3082,10 +3099,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3093,10 +3110,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3104,10 +3121,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3115,10 +3132,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3126,10 +3143,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3137,10 +3154,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3148,10 +3165,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3159,10 +3176,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3170,10 +3187,10 @@
     </row>
     <row r="10" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -3184,10 +3201,10 @@
     </row>
     <row r="11" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>1</v>
@@ -3195,10 +3212,10 @@
     </row>
     <row r="12" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>1</v>
@@ -3206,10 +3223,10 @@
     </row>
     <row r="13" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>1</v>
@@ -3217,10 +3234,10 @@
     </row>
     <row r="14" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>1</v>
@@ -3228,10 +3245,10 @@
     </row>
     <row r="15" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>1</v>
@@ -3239,10 +3256,10 @@
     </row>
     <row r="16" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>1</v>
@@ -3250,10 +3267,10 @@
     </row>
     <row r="17" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>1</v>
@@ -3261,10 +3278,10 @@
     </row>
     <row r="18" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>1</v>
@@ -3272,10 +3289,10 @@
     </row>
     <row r="19" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>1</v>
@@ -3283,10 +3300,10 @@
     </row>
     <row r="20" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>1</v>
@@ -3294,10 +3311,10 @@
     </row>
     <row r="21" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>1</v>
@@ -3305,10 +3322,10 @@
     </row>
     <row r="22" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>1</v>
@@ -3316,10 +3333,10 @@
     </row>
     <row r="23" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>1</v>
@@ -3327,10 +3344,10 @@
     </row>
     <row r="24" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>1</v>
@@ -3338,10 +3355,10 @@
     </row>
     <row r="25" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>1</v>
@@ -3349,10 +3366,10 @@
     </row>
     <row r="26" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>1</v>
@@ -3360,10 +3377,10 @@
     </row>
     <row r="27" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>1</v>
@@ -3371,10 +3388,10 @@
     </row>
     <row r="28" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>1</v>
@@ -3382,10 +3399,10 @@
     </row>
     <row r="29" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>1</v>
@@ -3393,10 +3410,10 @@
     </row>
     <row r="30" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>1</v>
@@ -3404,10 +3421,10 @@
     </row>
     <row r="31" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>1</v>
@@ -3415,10 +3432,10 @@
     </row>
     <row r="32" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>1</v>
@@ -3426,10 +3443,10 @@
     </row>
     <row r="33" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>1</v>
@@ -3437,10 +3454,10 @@
     </row>
     <row r="34" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>1</v>
@@ -3448,10 +3465,10 @@
     </row>
     <row r="35" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>1</v>
@@ -3459,10 +3476,10 @@
     </row>
     <row r="36" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>1</v>
@@ -3470,10 +3487,10 @@
     </row>
     <row r="37" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>1</v>
@@ -3481,7 +3498,7 @@
     </row>
     <row r="39" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -3518,10 +3535,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3529,10 +3546,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3540,10 +3557,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3551,10 +3568,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3562,10 +3579,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3573,10 +3590,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3584,10 +3601,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3595,10 +3612,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3606,10 +3623,10 @@
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -3644,10 +3661,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3655,10 +3672,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3666,10 +3683,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3677,10 +3694,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3688,10 +3705,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3699,10 +3716,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3710,10 +3727,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3721,10 +3738,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3732,10 +3749,10 @@
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -3743,10 +3760,10 @@
     </row>
     <row r="11" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>1</v>
@@ -3754,10 +3771,10 @@
     </row>
     <row r="12" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>1</v>
@@ -3765,10 +3782,10 @@
     </row>
     <row r="13" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>1</v>
@@ -3776,10 +3793,10 @@
     </row>
     <row r="14" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>1</v>
@@ -3787,10 +3804,10 @@
     </row>
     <row r="15" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>1</v>
@@ -3798,10 +3815,10 @@
     </row>
     <row r="16" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>1</v>
@@ -3809,10 +3826,10 @@
     </row>
     <row r="17" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>1</v>
@@ -3820,10 +3837,10 @@
     </row>
     <row r="18" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>1</v>
@@ -3831,10 +3848,10 @@
     </row>
     <row r="19" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>1</v>
@@ -3858,10 +3875,10 @@
   <sheetData>
     <row r="1" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>18</v>
@@ -3869,10 +3886,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3880,10 +3897,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3891,10 +3908,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3902,10 +3919,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3913,10 +3930,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3924,10 +3941,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3935,10 +3952,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3946,10 +3963,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3974,206 +3991,206 @@
   <sheetData>
     <row r="1" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>

--- a/词汇表.xlsx
+++ b/词汇表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="444">
   <si>
     <t>玩家词汇 · 大白话对照表（v2.8.18 界面口径）</t>
   </si>
@@ -55,7 +55,7 @@
     <t>三 抽卡与开局：34 条</t>
   </si>
   <si>
-    <t>四 技能相关词：36 条</t>
+    <t>四 技能相关词：37 条</t>
   </si>
   <si>
     <t>五 结算录像日志：9 条</t>
@@ -925,6 +925,12 @@
   </si>
   <si>
     <t>「获得技能」那一枚的名字格，只服务这一个效果类型（与「改哪个数」「我听谁」同一族做法：一个正交维度占一列）。这一格故意不做死下拉：可选的名字＝技能表上那 41 个（数随内容增长），做成封闭下拉会把"先写技能、那枚技能还没进表"这条路堵死——所以名字是原样收字，认不认由引擎那一处唯一的解析点（＝查技能表）说了算（界面里给的是可自由输入的候选清单，不是强制选项）。只有「效果类型＝获得技能」读这一格，别的类型填了会在导入总结里点名、按没填处理；这一格留空同样点名（那是一条半截效果，不会被静悄悄收下）。旧的 11 列导出文件照样能导入，只是那种文件里没有这一格——凡是「获得技能」的效果会报"缺名字"。</t>
+  </si>
+  <si>
+    <t>拼积木生成卡面话（v2.9.8 起）</t>
+  </si>
+  <si>
+    <t>编辑器里把「触发时机＋发动门槛＋结构化效果」这三格积木挑齐，下面那句卡面话就由系统替您写出来（例：回合开始时，摸 3 张牌。；整条技能的总述另拼一句，多行用「；」连、「选择其一」那句以 以下择一 打头）。这句您随时能改成自己的说法——改过一次之后，上面积木再怎么动也不会覆盖您写的字，框旁边会出现「↺ 用积木重写这句」，点它就重新听积木的。积木没齐（没填可结算的效果）时系统不替您编半句，那句得您自己写；「单效果」那一档压根没有积木格，界面会当场写明"这一档只有文字、保存后不参与对局结算"。⚠️ 两处不会替引擎撒谎的口径：「对谁」只在引擎真读"对象"那一格的六档上写（伤害／回复／护甲／弃牌／拆解军备／发放；摸牌／看牌堆顶／放回牌堆恒归发动者那一席，所以那三档绝不写"对目标"），默认档（目标）不标字，句子少一层噪音。唯一词源＝src/skills/skillSentence.ts（:97 一条效果一句、:118 整条技能总述、:134／:143 接线规则＝"空着或跟上一次生成的一句逐字相同 ⇒ 还跟积木走"）；效果行右侧那格预览与卡面那句共用同一份词（src/components/skillEditor/RuntimeEditor.tsx）。</t>
   </si>
   <si>
     <t>有效周期（这笔账什么时候结束）</t>
@@ -3078,7 +3084,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -3496,16 +3502,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="6" t="s">
+    <row r="38" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
+      <c r="B38" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A40:C40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3535,10 +3552,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3546,10 +3563,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3557,10 +3574,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3568,10 +3585,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3579,10 +3596,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3590,10 +3607,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3601,10 +3618,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3612,10 +3629,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3623,10 +3640,10 @@
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -3661,10 +3678,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3672,10 +3689,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3683,10 +3700,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3694,10 +3711,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3705,10 +3722,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3716,10 +3733,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3727,10 +3744,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3738,10 +3755,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3749,10 +3766,10 @@
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -3760,10 +3777,10 @@
     </row>
     <row r="11" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>1</v>
@@ -3771,10 +3788,10 @@
     </row>
     <row r="12" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>1</v>
@@ -3782,10 +3799,10 @@
     </row>
     <row r="13" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>1</v>
@@ -3793,10 +3810,10 @@
     </row>
     <row r="14" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>1</v>
@@ -3804,10 +3821,10 @@
     </row>
     <row r="15" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>1</v>
@@ -3815,10 +3832,10 @@
     </row>
     <row r="16" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>1</v>
@@ -3826,10 +3843,10 @@
     </row>
     <row r="17" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>1</v>
@@ -3837,10 +3854,10 @@
     </row>
     <row r="18" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>1</v>
@@ -3848,10 +3865,10 @@
     </row>
     <row r="19" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>1</v>
@@ -3875,10 +3892,10 @@
   <sheetData>
     <row r="1" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>18</v>
@@ -3886,10 +3903,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3897,10 +3914,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3908,10 +3925,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3919,10 +3936,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3930,10 +3947,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3941,10 +3958,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3952,10 +3969,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3963,10 +3980,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3991,206 +4008,206 @@
   <sheetData>
     <row r="1" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
   </sheetData>

--- a/词汇表.xlsx
+++ b/词汇表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="446">
   <si>
     <t>玩家词汇 · 大白话对照表（v2.8.18 界面口径）</t>
   </si>
@@ -55,7 +55,7 @@
     <t>三 抽卡与开局：34 条</t>
   </si>
   <si>
-    <t>四 技能相关词：37 条</t>
+    <t>四 技能相关词：38 条</t>
   </si>
   <si>
     <t>五 结算录像日志：9 条</t>
@@ -930,7 +930,13 @@
     <t>拼积木生成卡面话（v2.9.8 起）</t>
   </si>
   <si>
-    <t>编辑器里把「触发时机＋发动门槛＋结构化效果」这三格积木挑齐，下面那句卡面话就由系统替您写出来（例：回合开始时，摸 3 张牌。；整条技能的总述另拼一句，多行用「；」连、「选择其一」那句以 以下择一 打头）。这句您随时能改成自己的说法——改过一次之后，上面积木再怎么动也不会覆盖您写的字，框旁边会出现「↺ 用积木重写这句」，点它就重新听积木的。积木没齐（没填可结算的效果）时系统不替您编半句，那句得您自己写；「单效果」那一档压根没有积木格，界面会当场写明"这一档只有文字、保存后不参与对局结算"。⚠️ 两处不会替引擎撒谎的口径：「对谁」只在引擎真读"对象"那一格的六档上写（伤害／回复／护甲／弃牌／拆解军备／发放；摸牌／看牌堆顶／放回牌堆恒归发动者那一席，所以那三档绝不写"对目标"），默认档（目标）不标字，句子少一层噪音。唯一词源＝src/skills/skillSentence.ts（:97 一条效果一句、:118 整条技能总述、:134／:143 接线规则＝"空着或跟上一次生成的一句逐字相同 ⇒ 还跟积木走"）；效果行右侧那格预览与卡面那句共用同一份词（src/components/skillEditor/RuntimeEditor.tsx）。</t>
+    <t>编辑器里把「触发时机＋发动门槛＋结构化效果」这三格积木挑齐，下面那句卡面话就由系统替您写出来（例：回合开始时，摸 3 张牌。；整条技能的总述另拼一句，多行用「；」连、「选择其一」那句以 以下择一 打头）。这句您随时能改成自己的说法——改过一次之后，上面积木再怎么动也不会覆盖您写的字，框旁边会出现「↺ 用积木重写这句」，点它就重新听积木的。积木没齐（没填可结算的效果）时系统不替您编半句，那句得您自己写；「单效果」那一档压根没有积木格，界面会当场写明"这一档只有文字、保存后不参与对局结算"。⚠️ 两处不会替引擎撒谎的口径：「对谁」只在引擎真读"对象"那一格的六档上写（伤害／回复／护甲／弃牌／拆解军备／发放；摸牌／看牌堆顶／放回牌堆恒归发动者那一席，所以那三档绝不写"对目标"），默认档（目标）不标字，句子少一层噪音。唯一词源＝src/skills/skillSentence.ts（:146 一条效果一句、:167 整条技能总述、:195／:204 接线规则＝"空着或跟上一次生成的一句逐字相同 ⇒ 还跟积木走"）；效果行右侧那格预览与卡面那句共用同一份词（src/components/skillEditor/RuntimeEditor.tsx）。</t>
+  </si>
+  <si>
+    <t>自己写效果（v2.9.9 起）</t>
+  </si>
+  <si>
+    <t>技能卡片上「✍️ 自己写效果（一句话生成积木）」那一格：您用大白话写，系统替您反推成上面那三格积木，先给您看它打算怎么说，您点头才进格子（不点头什么都不会变），点「✔ 采用」后就是原来的拼积木界面，逐条改即可。写的是一行一段、句号分开；以下择一／以下依次生效 两句当头一句写，就按"选择其一"／"链式"登记；要满足手牌≤2 写在最前面＝整组门槛、写在某条时机后面＝那一条自己的门槛。认得的说法＝词表里那十二档动作与三档对象，中文数字（两、十二）与阿拉伯数字同解，「全部」＝整只手，观顶3张「拆掉 1 张装备卡」这类旧行话也照旧读得懂（只进不出）。读不懂的绝不猜、也没有一段是悄悄丢掉的：哪一段不支持就原文点出来＋一句照着改得动的理由（例："这一句要作用在'别人'身上……想让别的玩家执行的那类内容还没做出来"、"若…则…请改写「以下依次生效」"、"限定技是徽章，去徽章那一格勾"）。⚠️ 退回看这一段写在动作的哪一边，因为两句话的意思不一样：写在动作前面＝它正在给这个动作补"对谁／在什么前提下做"⇒这一条整条退回（只收动作那半＝做成另一件事）；写在动作后面＝像是第二件事⇒前面那件读懂的照做、后面这段单独点名并教您另起一句（一段只认一件事，第二件不顶掉第一件）。⚠️ 两种"不支持"也分开了：① 形状写错了 ⇒ 那一条不生成；② 格子有、引擎还没接线（例如下拉里那些还没上事件面的时机） ⇒ 照样生成、也能采用，但界面当场说一句"这条今天不会响"。这一格没有大模型、不联网，纯离线词表；能不能编出结算问的是编译器那一支自己（skillCompiler.judgeSkillEffect，反解侧与真编译路共用同一判据，不可能两边各说一套）。反解侧＝src/skills/skillTextParse.ts，界面＝src/components/skillEditor/SkillTextPanel.tsx；两侧由 skillTextParse.test.ts 的往返钉钉住（生成的那句再解回去、再生成 ⇒ 逐字同一句）。</t>
   </si>
   <si>
     <t>有效周期（这笔账什么时候结束）</t>
@@ -3084,7 +3090,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -3513,16 +3519,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="6" t="s">
+    <row r="39" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
+      <c r="B39" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A41:C41"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3552,10 +3569,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3563,10 +3580,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3574,10 +3591,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3585,10 +3602,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3596,10 +3613,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3607,10 +3624,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3618,10 +3635,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3629,10 +3646,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3640,10 +3657,10 @@
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -3678,10 +3695,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3689,10 +3706,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3700,10 +3717,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3711,10 +3728,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3722,10 +3739,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3733,10 +3750,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3744,10 +3761,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3755,10 +3772,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3766,10 +3783,10 @@
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -3777,10 +3794,10 @@
     </row>
     <row r="11" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>1</v>
@@ -3788,10 +3805,10 @@
     </row>
     <row r="12" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>1</v>
@@ -3799,10 +3816,10 @@
     </row>
     <row r="13" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>1</v>
@@ -3810,10 +3827,10 @@
     </row>
     <row r="14" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>1</v>
@@ -3821,10 +3838,10 @@
     </row>
     <row r="15" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>1</v>
@@ -3832,10 +3849,10 @@
     </row>
     <row r="16" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>1</v>
@@ -3843,10 +3860,10 @@
     </row>
     <row r="17" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>1</v>
@@ -3854,10 +3871,10 @@
     </row>
     <row r="18" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>1</v>
@@ -3865,10 +3882,10 @@
     </row>
     <row r="19" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>1</v>
@@ -3892,10 +3909,10 @@
   <sheetData>
     <row r="1" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>18</v>
@@ -3903,10 +3920,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3914,10 +3931,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3925,10 +3942,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3936,10 +3953,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3947,10 +3964,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3958,10 +3975,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3969,10 +3986,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3980,10 +3997,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -4008,206 +4025,206 @@
   <sheetData>
     <row r="1" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
   </sheetData>

--- a/词汇表.xlsx
+++ b/词汇表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="456">
   <si>
     <t>玩家词汇 · 大白话对照表（v2.8.18 界面口径）</t>
   </si>
@@ -52,7 +52,7 @@
     <t>二 行动按钮与提示：38 条</t>
   </si>
   <si>
-    <t>三 抽卡与开局：34 条</t>
+    <t>三 抽卡与开局：39 条</t>
   </si>
   <si>
     <t>四 技能相关词：38 条</t>
@@ -687,13 +687,13 @@
     <t>临时填一个显示名（最多 12 个字）。</t>
   </si>
   <si>
-    <t>还没做的：左上角 ping 表与掉线判定（J3）、客人动手与座位绑定（J4）。客人这一格仍然只是"看见同一局"，动不了牌</t>
-  </si>
-  <si>
-    <t>这两句写在大厅页脚（还没连的时候就在，连上之后也一直在）。第二刀做到"客人能看见房主那一局的牌桌"，但客人这边一个能按的牌钮都没有——真要让客人动手＝J4。</t>
-  </si>
-  <si>
-    <t>牌由房主那台机器算，传话程序只转发。现在做到"连得上、版本对得上、看得见谁在场，客人还能看见房主那一局的牌桌"</t>
+    <t>还没做的：掉线之后那两选一（保存并退出／交给 AI 继续）＝J5、客人动手与座位绑定＝J4</t>
+  </si>
+  <si>
+    <t>写在大厅页脚（还没连的时候就在，连上之后也一直在）。第三刀做到"全桌共用一张公开连线表、谁能看出谁掉线"，但掉线以后这一局怎么继续还没做；客人那边一个能按的牌钮也没有——真要让客人动手＝J4。</t>
+  </si>
+  <si>
+    <t>牌由房主那台机器算，传话程序只转发。现在做到"连得上、版本对得上、看得见谁在场，客人能看见房主那一局的牌桌，全桌还共用一张公开连线表"。</t>
   </si>
   <si>
     <t>大厅第一屏的边界句（还没连的时候就能读到）。它写明这一格做到哪一步，不让人以为连上了就开了联机局。</t>
@@ -723,10 +723,40 @@
     <t>观战牌桌底下的说明，同时也是这一刀的规矩：私有的东西只发数量，线上根本不会出现别人的手牌、将池名单、牌堆顺序。</t>
   </si>
   <si>
-    <t>先关掉这个窗不会退房——连线还在，房主那边继续发局面。真要断线请点「离开房间」</t>
-  </si>
-  <si>
-    <t>大厅页脚第一句。关掉弹窗≠退出房间：房主关了大厅去开局，客人照样看得见；想真断开只有「离开房间」那一个钮。</t>
+    <t>先关掉这个窗不会退房——连线还在，房主那边继续发局面，左上角那张连线表也会继续刷新。真要断线请点「离开房间」</t>
+  </si>
+  <si>
+    <t>大厅页脚第一句。关掉弹窗≠退出房间：房主关了大厅去开局，客人照样看得见、连线表照样在刷；想真断开只有「离开房间」那一个钮。</t>
+  </si>
+  <si>
+    <t>谁掉线由房主那台机器判（15 秒收不到某人任何一条消息才算），客人这边只照抄房主发来的表；探测约 2 秒一次，所以判定最多比真正断线晚约两秒显示出来</t>
+  </si>
+  <si>
+    <t>大厅页脚第二句＝这一刀的判据写在界面上。三件事：① 只有房主那台机器做判断，客人自己绝不猜；② 计时看的是"任何一条消息"，不是只看探路那一条；③ 屏幕上那条掉线会比真的断开晚大约两秒，不是秒判。</t>
+  </si>
+  <si>
+    <t>📶 连线情况（N 人·全桌公开）</t>
+  </si>
+  <si>
+    <t>房间左上角那张表的名字（不在大厅弹窗里，关了大厅也在）。N＝表里几个人，每人一行，全桌看到同一张。</t>
+  </si>
+  <si>
+    <t>还没回话 / N 毫秒</t>
+  </si>
+  <si>
+    <t>连线表里"连线"那一列的两种读数。还没回话＝这条刚上线、房主还没来得及问他一次；N 毫秒＝房主问他一次、他把问题上的时间戳原样抄回来、房主用自己那只钟算出的往返时间。</t>
+  </si>
+  <si>
+    <t>●（红点）/ ○（绿点）／掉线</t>
+  </si>
+  <si>
+    <t>连线表里每行的状态点：绿点＝在线，红点＝房主判他掉线（15 秒没收到他任何一条消息）。掉线那行还会在表下面点名：「⚠️ 某某 掉线了（15 秒没收到他任何一条消息）」，并写明"接下来那两选一还没做"。</t>
+  </si>
+  <si>
+    <t>这里的数字是各人与「房主那台机器」之间的往返时间，不是两人之间的真实延时，也不是卡顿指标</t>
+  </si>
+  <si>
+    <t>连线表底下的如实边界三句话（它跟表一起挂在左上角）。第一句：这张表量的是"每人到房主那台机器"，两个人各自 60 毫秒不代表他俩之间 60 毫秒。第二句：房主机器忙的时候这个数字也会变大，它不是卡不卡的分数。</t>
   </si>
   <si>
     <t>现在有 N 位客人正在看这一局</t>
@@ -1353,13 +1383,13 @@
     <t>「联网对战」四个字说大了</t>
   </si>
   <si>
-    <t>主菜单按钮与大厅标题写 🌐 联网对战，第一刀（v2.9.1）只做到"连得上、版本对得上、看得见谁在场"；第二刀（v2.9.2）客人这一格能看见房主那一局的牌桌（谁在场面、剩多少体力、轮到谁、营地与牌堆剩多少），但动不了牌——ping 表与掉线判定＝J3、客人动手＝J4 还没做。大厅页脚始终写着这两格没做。</t>
-  </si>
-  <si>
-    <t>传话程序只转发、不算牌；牌由房主那台机器算。观战那块牌桌是房主发来的读数，不是客人自己在打。</t>
-  </si>
-  <si>
-    <t>⏳ 待您裁：按钮名与标题仍一字未动（沿用您 2026-10-08 的「1.不用改」）。现在"连上了"多了"看得见同一局牌桌"，仍然不等于开了一局两人联机对局；要不要再改口，等 J4 客人能动手那天您再定</t>
+    <t>主菜单按钮与大厅标题写 🌐 联网对战，第一刀（v2.9.1）只做到"连得上、版本对得上、看得见谁在场"；第二刀（v2.9.2）客人这一格能看见房主那一局的牌桌（谁在场面、剩多少体力、轮到谁、营地与牌堆剩多少），但动不了牌；第三刀（v2.9.10）全桌共用一张公开连线表（房主每约 2 秒问一次、15 秒收不到某人任何一条消息才算掉线、只有房主判）。客人动手＝J4、掉线之后那两选一＝J5 还没做，大厅页脚始终写着这两格没做。</t>
+  </si>
+  <si>
+    <t>传话程序只转发、不算牌；牌由房主那台机器算。观战那块牌桌是房主发来的读数，不是客人自己在打。连线表那个数字也只是"每人到房主那台机器"的往返时间，不是两人之间的真实延时。</t>
+  </si>
+  <si>
+    <t>⏳ 待您裁：按钮名与标题仍一字未动（沿用您 2026-10-08 的「1.不用改」）。现在"连上了"多了"看得见同一局牌桌"和"看得见谁掉线"，仍然不等于开了一局两人联机对局；要不要再改口，等 J4 客人能动手那天您再定</t>
   </si>
 </sst>
 </file>
@@ -2689,7 +2719,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -3079,6 +3109,61 @@
         <v>236</v>
       </c>
       <c r="C35" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3111,10 +3196,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3122,10 +3207,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3133,10 +3218,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3144,10 +3229,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3155,10 +3240,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3166,10 +3251,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3177,10 +3262,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3188,10 +3273,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3199,10 +3284,10 @@
     </row>
     <row r="10" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -3213,10 +3298,10 @@
     </row>
     <row r="11" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>1</v>
@@ -3224,10 +3309,10 @@
     </row>
     <row r="12" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>1</v>
@@ -3235,10 +3320,10 @@
     </row>
     <row r="13" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>1</v>
@@ -3246,10 +3331,10 @@
     </row>
     <row r="14" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>1</v>
@@ -3257,10 +3342,10 @@
     </row>
     <row r="15" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>1</v>
@@ -3268,10 +3353,10 @@
     </row>
     <row r="16" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>1</v>
@@ -3279,10 +3364,10 @@
     </row>
     <row r="17" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>1</v>
@@ -3290,10 +3375,10 @@
     </row>
     <row r="18" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>1</v>
@@ -3301,10 +3386,10 @@
     </row>
     <row r="19" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>1</v>
@@ -3312,10 +3397,10 @@
     </row>
     <row r="20" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>1</v>
@@ -3323,10 +3408,10 @@
     </row>
     <row r="21" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>1</v>
@@ -3334,10 +3419,10 @@
     </row>
     <row r="22" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>1</v>
@@ -3345,10 +3430,10 @@
     </row>
     <row r="23" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>1</v>
@@ -3356,10 +3441,10 @@
     </row>
     <row r="24" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>1</v>
@@ -3367,10 +3452,10 @@
     </row>
     <row r="25" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>1</v>
@@ -3378,10 +3463,10 @@
     </row>
     <row r="26" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>1</v>
@@ -3389,10 +3474,10 @@
     </row>
     <row r="27" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>1</v>
@@ -3400,10 +3485,10 @@
     </row>
     <row r="28" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>1</v>
@@ -3411,10 +3496,10 @@
     </row>
     <row r="29" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>1</v>
@@ -3422,10 +3507,10 @@
     </row>
     <row r="30" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>1</v>
@@ -3433,10 +3518,10 @@
     </row>
     <row r="31" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>1</v>
@@ -3444,10 +3529,10 @@
     </row>
     <row r="32" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>1</v>
@@ -3455,10 +3540,10 @@
     </row>
     <row r="33" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>1</v>
@@ -3466,10 +3551,10 @@
     </row>
     <row r="34" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>1</v>
@@ -3477,10 +3562,10 @@
     </row>
     <row r="35" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>1</v>
@@ -3488,10 +3573,10 @@
     </row>
     <row r="36" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>1</v>
@@ -3499,10 +3584,10 @@
     </row>
     <row r="37" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>1</v>
@@ -3510,10 +3595,10 @@
     </row>
     <row r="38" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>1</v>
@@ -3521,10 +3606,10 @@
     </row>
     <row r="39" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>1</v>
@@ -3532,7 +3617,7 @@
     </row>
     <row r="41" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -3569,10 +3654,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3580,10 +3665,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3591,10 +3676,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3602,10 +3687,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3613,10 +3698,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3624,10 +3709,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3635,10 +3720,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3646,10 +3731,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3657,10 +3742,10 @@
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -3695,10 +3780,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3706,10 +3791,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3717,10 +3802,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3728,10 +3813,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3739,10 +3824,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3750,10 +3835,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3761,10 +3846,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3772,10 +3857,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3783,10 +3868,10 @@
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -3794,10 +3879,10 @@
     </row>
     <row r="11" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>1</v>
@@ -3805,10 +3890,10 @@
     </row>
     <row r="12" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>1</v>
@@ -3816,10 +3901,10 @@
     </row>
     <row r="13" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>1</v>
@@ -3827,10 +3912,10 @@
     </row>
     <row r="14" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>1</v>
@@ -3838,10 +3923,10 @@
     </row>
     <row r="15" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>1</v>
@@ -3849,10 +3934,10 @@
     </row>
     <row r="16" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>1</v>
@@ -3860,10 +3945,10 @@
     </row>
     <row r="17" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>1</v>
@@ -3871,10 +3956,10 @@
     </row>
     <row r="18" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>1</v>
@@ -3882,10 +3967,10 @@
     </row>
     <row r="19" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>1</v>
@@ -3909,10 +3994,10 @@
   <sheetData>
     <row r="1" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>18</v>
@@ -3920,10 +4005,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3931,10 +4016,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3942,10 +4027,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3953,10 +4038,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3964,10 +4049,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3975,10 +4060,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3986,10 +4071,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3997,10 +4082,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -4025,206 +4110,206 @@
   <sheetData>
     <row r="1" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
     </row>
   </sheetData>

--- a/词汇表.xlsx
+++ b/词汇表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="476">
   <si>
     <t>玩家词汇 · 大白话对照表（v2.8.18 界面口径）</t>
   </si>
@@ -52,7 +52,7 @@
     <t>二 行动按钮与提示：38 条</t>
   </si>
   <si>
-    <t>三 抽卡与开局：39 条</t>
+    <t>三 抽卡与开局：49 条</t>
   </si>
   <si>
     <t>四 技能相关词：38 条</t>
@@ -687,22 +687,34 @@
     <t>临时填一个显示名（最多 12 个字）。</t>
   </si>
   <si>
-    <t>还没做的：掉线之后那两选一（保存并退出／交给 AI 继续）＝J5、客人动手与座位绑定＝J4</t>
-  </si>
-  <si>
-    <t>写在大厅页脚（还没连的时候就在，连上之后也一直在）。第三刀做到"全桌共用一张公开连线表、谁能看出谁掉线"，但掉线以后这一局怎么继续还没做；客人那边一个能按的牌钮也没有——真要让客人动手＝J4。</t>
-  </si>
-  <si>
-    <t>牌由房主那台机器算，传话程序只转发。现在做到"连得上、版本对得上、看得见谁在场，客人能看见房主那一局的牌桌，全桌还共用一张公开连线表"。</t>
+    <t>还没做的：掉线之后那两选一（保存并退出／交给 AI 继续）＝J5、局外开新局投票＝J6</t>
+  </si>
+  <si>
+    <t>写在大厅页脚（还没连的时候就在，连上之后也一直在）。第四刀（v2.9.11）把"客人动手＝J4"做完了，页脚于是只剩这两格；它跟着实现走，绝不让人以为连上就开了完整联机。</t>
+  </si>
+  <si>
+    <t>客人动手（J4）现在做到：椅子由房主按进房顺序排…客人点出去只交回「第几席＋编号」…清单一次最多列 32 步</t>
+  </si>
+  <si>
+    <t>大厅页脚第三句（v2.9.11 新增）＝把这一刀到底做了什么说全：房主排座、房主算按钮、客人只交回席位号与编号、房主重算对得上才走、对不上退回并说明、清单封顶 32 步且没列出的条数会写在下面。</t>
+  </si>
+  <si>
+    <t>这一版不防作弊：清单虽然只指名发给那一席，传话程序只认房间不认人，同桌理论上看得见别人那几行的文字</t>
+  </si>
+  <si>
+    <t>页脚里的如实边界（v2.9.11 新增）。传话程序只按房间转发、不认人，所以同一屋的人理论上嗅得到别人那一行的文字。牌面内容本来就不上线，能嗅到的只是"那几行给人看的短语"。</t>
+  </si>
+  <si>
+    <t>牌由房主那台机器算，传话程序只转发。现在做到"连得上、版本对得上、看得见谁在场，客人能看见房主那一局的牌桌、还能点自己那一席（按钮由房主算好发过来），全桌共用一张公开连线表"。</t>
   </si>
   <si>
     <t>大厅第一屏的边界句（还没连的时候就能读到）。它写明这一格做到哪一步，不让人以为连上了就开了联机局。</t>
   </si>
   <si>
-    <t>👀 观战 · 这一局由房主算牌，你这边只看不动</t>
-  </si>
-  <si>
-    <t>客人连上后大厅里那块牌桌的名字。观战＝跟着看、动不了：谁在场面上、谁剩多少体力、轮到谁、营地还剩多少，都跟着房主那边变。</t>
+    <t>👀 牌桌 · 这一局由房主算牌，这里只画局面，要动手看下面席位表</t>
+  </si>
+  <si>
+    <t>客人连上后大厅里那块牌桌的名字（v2.9.11 改词：原来叫「观战 · 你这边只看不动」，第四刀之后"动"这一格已经开在下面的席位表里，这句话必须说实话）。谁在场面上、谁剩多少体力、轮到谁、营地还剩多少，都跟着房主那边变；这一块本身仍然一处也不能点。</t>
   </si>
   <si>
     <t>第 N 轮 · 轮到某某 ／ 行动中 ／ 场上没有将领</t>
@@ -765,6 +777,54 @@
     <t>房主那侧才会出现这句（有客人才显示），提醒他：现在每次局面变化都会往出发一份遮蔽过的局面。</t>
   </si>
   <si>
+    <t>💺 席位表（房主那边绑的，客人这边照抄）</t>
+  </si>
+  <si>
+    <t>v2.9.11（第四刀 J4）那张"谁坐哪一把椅子"的表名。它挂在客人那边的大厅里，同时房主屏幕右上角也有一张（关了大厅也在，只给人看、一个也不能点）。座次只在房主那台机器上算：房主占第一把，客人按进房顺序坐后面的；桌上全是电脑＝这张表根本没有席位。</t>
+  </si>
+  <si>
+    <t>第 N 席 · 本机在点 · 客人 · 别人 ·（我）</t>
+  </si>
+  <si>
+    <t>席位表每行的读数。「本机在点」＝这把椅子还没交给任何人，仍由房主那台机器自己按；「客人」是房主看别人、「别人」是客人看别人、「（我）」标自己。客人这边绝不自己排一遍座次——两边各排一次就会出现"他以为坐第三把、我给他算的是第四把"。</t>
+  </si>
+  <si>
+    <t>你坐第 N 席。现在能走：</t>
+  </si>
+  <si>
+    <t>客人那一格的动作清单标题（v2.9.11）。下面每一行就是一个能按的按钮，文字由房主算好发来，与热座界面同一批词（⏭️结束回合／🚶前进／💊补给／🛡️叠甲／⚔️登场将领／🚫 跳过／结算失去体力／✓ 确认／选项N：…）。</t>
+  </si>
+  <si>
+    <t>椅子还没排到你（房主重排后会发新的一份过来）——你这边先只看</t>
+  </si>
+  <si>
+    <t>客人连上了但席位表里还没有他那一格时的说法（开局前桌上没有席位，所以这一步也还没得点）。</t>
+  </si>
+  <si>
+    <t>这一席此刻一步也走不了（等牌走到要你动手的那一步）</t>
+  </si>
+  <si>
+    <t>清单是空的——不是出故障，是房主那台机器算出来"这一席现在确实没有合法动作"。</t>
+  </si>
+  <si>
+    <t>⚠️ 这里只列出前 N 步，还有 M 步没列出来——房主本机那边看得见全部，要走没列出的那一步得请房主点</t>
+  </si>
+  <si>
+    <t>清单封顶 32 步时的那句缺分母补上的话。它明说这不是全部，并说清怎么走到没列出的那一步。</t>
+  </si>
+  <si>
+    <t>↩️ 房主那边没让走：〈一句话〉</t>
+  </si>
+  <si>
+    <t>客人点了、但房主不认这一步时的回话（信封上的名字叫 actno）。括号里那句是房主给的原因，比如「这一步已经不成立——清单是按房主当下的局面重算的，牌一动就换一批」「这一席绑的是别人，我不能让你点他的座」「这一席是电脑在打，交不出去」。认不出的内部码也照原样带上，不编一句好听的话糊弄。</t>
+  </si>
+  <si>
+    <t>点出去的那一步只是把「第几席＋这个编号」交给房主，你的手牌与牌面内容一个都不上线。牌动了这份清单会自己换一批；没走成时会在这里说明为什么</t>
+  </si>
+  <si>
+    <t>客人那一格底下的规矩句（v2.9.11）。线上跑的只有席位号与编号，动作本体不上线；清单会随局面自己换一批，换的时候上一句退回说明也跟着消失。</t>
+  </si>
+  <si>
     <t>锁定技</t>
   </si>
   <si>
@@ -1383,7 +1443,7 @@
     <t>「联网对战」四个字说大了</t>
   </si>
   <si>
-    <t>主菜单按钮与大厅标题写 🌐 联网对战，第一刀（v2.9.1）只做到"连得上、版本对得上、看得见谁在场"；第二刀（v2.9.2）客人这一格能看见房主那一局的牌桌（谁在场面、剩多少体力、轮到谁、营地与牌堆剩多少），但动不了牌；第三刀（v2.9.10）全桌共用一张公开连线表（房主每约 2 秒问一次、15 秒收不到某人任何一条消息才算掉线、只有房主判）。客人动手＝J4、掉线之后那两选一＝J5 还没做，大厅页脚始终写着这两格没做。</t>
+    <t>主菜单按钮与大厅标题写 🌐 联网对战，第一刀（v2.9.1）只做到"连得上、版本对得上、看得见谁在场"；第二刀（v2.9.2）客人这一格能看见房主那一局的牌桌（谁在场面、剩多少体力、轮到谁、营地与牌堆剩多少），但动不了牌；第三刀（v2.9.10）全桌共用一张公开连线表（房主每约 2 秒问一次、15 秒收不到某人任何一条消息才算掉线、只有房主判）。客人动手＝J4、掉线之后那两选一＝J5 还没做，大厅页脚始终写着这两格没做。〔v2.9.11 就地更新：J4 已落地＝椅子由房主绑、按钮由房主算给那一席、客人只交回「第几席＋编号」、房主重算对得上才走；页脚现在只剩 J5（掉线二选一）与 J6（局外开新局投票） 两格没做。那一格「👀 观战 · 你这边只看不动」也随这刀改了口＝牌桌 · 这里只画局面，要动手看下面席位表，因为"只看不动"已经不是实话。〕</t>
   </si>
   <si>
     <t>传话程序只转发、不算牌；牌由房主那台机器算。观战那块牌桌是房主发来的读数，不是客人自己在打。连线表那个数字也只是"每人到房主那台机器"的往返时间，不是两人之间的真实延时。</t>
@@ -2719,7 +2779,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -3164,6 +3224,116 @@
         <v>246</v>
       </c>
       <c r="C40" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3196,10 +3366,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3207,10 +3377,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3218,10 +3388,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3229,10 +3399,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3240,10 +3410,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3251,10 +3421,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3262,10 +3432,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3273,10 +3443,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3284,10 +3454,10 @@
     </row>
     <row r="10" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>263</v>
+        <v>283</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>264</v>
+        <v>284</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -3298,10 +3468,10 @@
     </row>
     <row r="11" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>265</v>
+        <v>285</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>266</v>
+        <v>286</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>1</v>
@@ -3309,10 +3479,10 @@
     </row>
     <row r="12" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>1</v>
@@ -3320,10 +3490,10 @@
     </row>
     <row r="13" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>1</v>
@@ -3331,10 +3501,10 @@
     </row>
     <row r="14" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>1</v>
@@ -3342,10 +3512,10 @@
     </row>
     <row r="15" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>274</v>
+        <v>294</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>1</v>
@@ -3353,10 +3523,10 @@
     </row>
     <row r="16" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>275</v>
+        <v>295</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>276</v>
+        <v>296</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>1</v>
@@ -3364,10 +3534,10 @@
     </row>
     <row r="17" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>277</v>
+        <v>297</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>278</v>
+        <v>298</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>1</v>
@@ -3375,10 +3545,10 @@
     </row>
     <row r="18" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>279</v>
+        <v>299</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>1</v>
@@ -3386,10 +3556,10 @@
     </row>
     <row r="19" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>281</v>
+        <v>301</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>282</v>
+        <v>302</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>1</v>
@@ -3397,10 +3567,10 @@
     </row>
     <row r="20" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>283</v>
+        <v>303</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>284</v>
+        <v>304</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>1</v>
@@ -3408,10 +3578,10 @@
     </row>
     <row r="21" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>286</v>
+        <v>306</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>1</v>
@@ -3419,10 +3589,10 @@
     </row>
     <row r="22" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>288</v>
+        <v>308</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>1</v>
@@ -3430,10 +3600,10 @@
     </row>
     <row r="23" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>289</v>
+        <v>309</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>1</v>
@@ -3441,10 +3611,10 @@
     </row>
     <row r="24" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>292</v>
+        <v>312</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>1</v>
@@ -3452,10 +3622,10 @@
     </row>
     <row r="25" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>293</v>
+        <v>313</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>1</v>
@@ -3463,10 +3633,10 @@
     </row>
     <row r="26" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>296</v>
+        <v>316</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>1</v>
@@ -3474,10 +3644,10 @@
     </row>
     <row r="27" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>297</v>
+        <v>317</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>1</v>
@@ -3485,10 +3655,10 @@
     </row>
     <row r="28" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>299</v>
+        <v>319</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>1</v>
@@ -3496,10 +3666,10 @@
     </row>
     <row r="29" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>301</v>
+        <v>321</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>302</v>
+        <v>322</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>1</v>
@@ -3507,10 +3677,10 @@
     </row>
     <row r="30" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>303</v>
+        <v>323</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>304</v>
+        <v>324</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>1</v>
@@ -3518,10 +3688,10 @@
     </row>
     <row r="31" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>305</v>
+        <v>325</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>306</v>
+        <v>326</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>1</v>
@@ -3529,10 +3699,10 @@
     </row>
     <row r="32" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>307</v>
+        <v>327</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>308</v>
+        <v>328</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>1</v>
@@ -3540,10 +3710,10 @@
     </row>
     <row r="33" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>309</v>
+        <v>329</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>1</v>
@@ -3551,10 +3721,10 @@
     </row>
     <row r="34" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>312</v>
+        <v>332</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>1</v>
@@ -3562,10 +3732,10 @@
     </row>
     <row r="35" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>313</v>
+        <v>333</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>314</v>
+        <v>334</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>1</v>
@@ -3573,10 +3743,10 @@
     </row>
     <row r="36" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>315</v>
+        <v>335</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>316</v>
+        <v>336</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>1</v>
@@ -3584,10 +3754,10 @@
     </row>
     <row r="37" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>317</v>
+        <v>337</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>1</v>
@@ -3595,10 +3765,10 @@
     </row>
     <row r="38" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>319</v>
+        <v>339</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>1</v>
@@ -3606,10 +3776,10 @@
     </row>
     <row r="39" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>321</v>
+        <v>341</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>322</v>
+        <v>342</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>1</v>
@@ -3617,7 +3787,7 @@
     </row>
     <row r="41" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>323</v>
+        <v>343</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -3654,10 +3824,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>325</v>
+        <v>345</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3665,10 +3835,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>326</v>
+        <v>346</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>327</v>
+        <v>347</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3676,10 +3846,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>328</v>
+        <v>348</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>329</v>
+        <v>349</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3687,10 +3857,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>331</v>
+        <v>351</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3698,10 +3868,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>332</v>
+        <v>352</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>333</v>
+        <v>353</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3709,10 +3879,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>334</v>
+        <v>354</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3720,10 +3890,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>336</v>
+        <v>356</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3731,10 +3901,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>338</v>
+        <v>358</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>339</v>
+        <v>359</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3742,10 +3912,10 @@
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>341</v>
+        <v>361</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -3780,10 +3950,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>342</v>
+        <v>362</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3791,10 +3961,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>344</v>
+        <v>364</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>345</v>
+        <v>365</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3802,10 +3972,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>346</v>
+        <v>366</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>347</v>
+        <v>367</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3813,10 +3983,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>348</v>
+        <v>368</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>349</v>
+        <v>369</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3824,10 +3994,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>351</v>
+        <v>371</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3835,10 +4005,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>352</v>
+        <v>372</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>353</v>
+        <v>373</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3846,10 +4016,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>354</v>
+        <v>374</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>355</v>
+        <v>375</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3857,10 +4027,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>356</v>
+        <v>376</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>357</v>
+        <v>377</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3868,10 +4038,10 @@
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>358</v>
+        <v>378</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -3879,10 +4049,10 @@
     </row>
     <row r="11" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>361</v>
+        <v>381</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>1</v>
@@ -3890,10 +4060,10 @@
     </row>
     <row r="12" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>362</v>
+        <v>382</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>1</v>
@@ -3901,10 +4071,10 @@
     </row>
     <row r="13" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>365</v>
+        <v>385</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>1</v>
@@ -3912,10 +4082,10 @@
     </row>
     <row r="14" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>366</v>
+        <v>386</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>1</v>
@@ -3923,10 +4093,10 @@
     </row>
     <row r="15" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>368</v>
+        <v>388</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>369</v>
+        <v>389</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>1</v>
@@ -3934,10 +4104,10 @@
     </row>
     <row r="16" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>370</v>
+        <v>390</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>371</v>
+        <v>391</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>1</v>
@@ -3945,10 +4115,10 @@
     </row>
     <row r="17" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>372</v>
+        <v>392</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>373</v>
+        <v>393</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>1</v>
@@ -3956,10 +4126,10 @@
     </row>
     <row r="18" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>375</v>
+        <v>395</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>1</v>
@@ -3967,10 +4137,10 @@
     </row>
     <row r="19" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>377</v>
+        <v>397</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>1</v>
@@ -3994,10 +4164,10 @@
   <sheetData>
     <row r="1" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>378</v>
+        <v>398</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>379</v>
+        <v>399</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>18</v>
@@ -4005,10 +4175,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>381</v>
+        <v>401</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -4016,10 +4186,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>383</v>
+        <v>403</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -4027,10 +4197,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>384</v>
+        <v>404</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>385</v>
+        <v>405</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -4038,10 +4208,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>386</v>
+        <v>406</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>387</v>
+        <v>407</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -4049,10 +4219,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>388</v>
+        <v>408</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>389</v>
+        <v>409</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -4060,10 +4230,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>391</v>
+        <v>411</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -4071,10 +4241,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -4082,10 +4252,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -4110,206 +4280,206 @@
   <sheetData>
     <row r="1" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>397</v>
+        <v>417</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>400</v>
+        <v>420</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>402</v>
+        <v>422</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>404</v>
+        <v>424</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>408</v>
+        <v>428</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>409</v>
+        <v>429</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>410</v>
+        <v>430</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>411</v>
+        <v>431</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>412</v>
+        <v>432</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>413</v>
+        <v>433</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>414</v>
+        <v>434</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>415</v>
+        <v>435</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>416</v>
+        <v>436</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>417</v>
+        <v>437</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>418</v>
+        <v>438</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>419</v>
+        <v>439</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>421</v>
+        <v>441</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>422</v>
+        <v>442</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>423</v>
+        <v>443</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>424</v>
+        <v>444</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>425</v>
+        <v>445</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>426</v>
+        <v>446</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>427</v>
+        <v>447</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>428</v>
+        <v>448</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>429</v>
+        <v>449</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>430</v>
+        <v>450</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>431</v>
+        <v>451</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>432</v>
+        <v>452</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>433</v>
+        <v>453</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>434</v>
+        <v>454</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>435</v>
+        <v>455</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>437</v>
+        <v>457</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>438</v>
+        <v>458</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>439</v>
+        <v>459</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>440</v>
+        <v>460</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>441</v>
+        <v>461</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>442</v>
+        <v>462</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>443</v>
+        <v>463</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>444</v>
+        <v>464</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>445</v>
+        <v>465</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>446</v>
+        <v>466</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>447</v>
+        <v>467</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>448</v>
+        <v>468</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>449</v>
+        <v>469</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>450</v>
+        <v>470</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>451</v>
+        <v>471</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>452</v>
+        <v>472</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>453</v>
+        <v>473</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>454</v>
+        <v>474</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>455</v>
+        <v>475</v>
       </c>
     </row>
   </sheetData>

--- a/词汇表.xlsx
+++ b/词汇表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="486">
   <si>
     <t>玩家词汇 · 大白话对照表（v2.8.18 界面口径）</t>
   </si>
@@ -61,7 +61,7 @@
     <t>五 结算录像日志：9 条</t>
   </si>
   <si>
-    <t>六 图鉴设置开发者：18 条</t>
+    <t>六 图鉴设置开发者：23 条</t>
   </si>
   <si>
     <t>七 界面里没有的词：8 条</t>
@@ -1216,6 +1216,36 @@
   </si>
   <si>
     <t>回合收尾时要不要停下来问你的档位。智能（默认）＝确实有能发动的才问，不能发动的不列；完整＝只要场上有"回合结束时"技能就问，暂时不能发动的也列出来并写明原因。两档都不改变技能本身能不能发动，也不影响录像。</t>
+  </si>
+  <si>
+    <t>📦 导出内容包 / 📥 导入内容包（将领编辑器 → 内容包，2.9.12 起）</t>
+  </si>
+  <si>
+    <t>把你这台机器上"玩家自制"的将打成一个文件发给别人，或者把别人发来的文件装进你的将池。包里只有自制的将；你对官方卡的修改、锁定、禁用不在包里。不需要开发者口令，也不用开房。</t>
+  </si>
+  <si>
+    <t>内容包的"指纹"</t>
+  </si>
+  <si>
+    <t>文件里的一串校验码，只证明一件事：这个文件发出去之后没被人动过一个字、也没传坏。字序、空格变了照样认（比的是内容不是字节）。它不证明"这张卡是谁写的"，也不防人故意伪造——这一版不防作弊。</t>
+  </si>
+  <si>
+    <t>只导出合格的 N 张</t>
+  </si>
+  <si>
+    <t>你自制的将里有几张带着"装包那一侧不认"的毛病（比如技能没名字）时，导出会先拦住、逐条点名。这个按钮＝跳过它们，只把合格的那几张写进文件。</t>
+  </si>
+  <si>
+    <t>「这个包没有装上（一张也没有）」</t>
+  </si>
+  <si>
+    <t>装包最怕装到一半，所以只要有一条不合格，好的一张也不装，并把每条的原因逐行列出来。改好了再导一次即可，你现有的卡不会被动。</t>
+  </si>
+  <si>
+    <t>「已经有了，不用重复装」</t>
+  </si>
+  <si>
+    <t>同一个包导入第二遍会出现这句。意思是这台机器上已有一模一样的这张，不会长出两张同名卡，也不算失败。</t>
   </si>
   <si>
     <t>你以为有的词</t>
@@ -3929,7 +3959,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -4143,6 +4173,61 @@
         <v>397</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4164,10 +4249,10 @@
   <sheetData>
     <row r="1" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>18</v>
@@ -4175,10 +4260,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -4186,10 +4271,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -4197,10 +4282,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -4208,10 +4293,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -4219,10 +4304,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -4230,10 +4315,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -4241,10 +4326,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -4252,10 +4337,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -4280,206 +4365,206 @@
   <sheetData>
     <row r="1" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>463</v>
+        <v>473</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>465</v>
+        <v>475</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>472</v>
+        <v>482</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>473</v>
+        <v>483</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>475</v>
+        <v>485</v>
       </c>
     </row>
   </sheetData>

--- a/词汇表.xlsx
+++ b/词汇表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="488">
   <si>
     <t>玩家词汇 · 大白话对照表（v2.8.18 界面口径）</t>
   </si>
@@ -46,7 +46,7 @@
     <t>工作表一览：</t>
   </si>
   <si>
-    <t>一 棋盘与数字：31 条</t>
+    <t>一 棋盘与数字：32 条</t>
   </si>
   <si>
     <t>二 行动按钮与提示：38 条</t>
@@ -116,6 +116,12 @@
   </si>
   <si>
     <t>你手里攥着的牌。本作里它既是"钱"也是"血包"：几乎所有行动都要烧掉手牌当费用。</t>
+  </si>
+  <si>
+    <t>角色 / 玩家（这两个词不是一回事）</t>
+  </si>
+  <si>
+    <t>「角色」＝棋盘上那一员将（一名将领）；「玩家」＝坐在席位上的那一家。手牌、体力池、回合、抽牌这些记在"玩家"名下，将领头上没有"手牌"这个东西。所以卡面话里没有"角色摸牌"这种说法，只有"玩家摸牌"＝"某某摸 2 张牌"落到那一家的手上（您 2026-10-18 原话：「我的游戏里没有「角色摸牌」，只有「玩家摸牌」，摸牌摸上来的是手牌，角色是没有手牌这个概念的」）。编辑器里「自己写效果」那一格现在就按这条判：您写「其他角色摸两张牌」会被当作用词写错点出来（不是"这条做不了"），并给您一句能改对的写法「其他玩家摸两张牌」；换成那句走的就是"要作用在别人身上、那一类内容还没做出来"这一条（真正的对象选择器还没施工）。反过来，"角色"当登场／受伤／被杀这类事的主语是成立的，卡面上那三档定语「其他角色／己方角色／敌方角色」也照您的写法认（见「我听谁」那一行）。</t>
   </si>
   <si>
     <t>将领池</t>
@@ -897,10 +903,10 @@
     <t>"被点名"这一刻分三种来路：成为攻击目标＝被人拿兵刃指上；成为技能目标＝被一条技能点上火；成为目标（两种都算）＝两条来路都算。不选＝只算攻击，与今天对局一致。你手上的旧 Excel 里那格"成为攻击目标时"照样读得懂，只是再导出会写成"成为目标时→成为攻击目标"。要紧的实话（2.8.24 更新）："成为技能目标"这一声如今有一个发射器＝决斗开局（哪个技能拿「决斗」点了敌将的名，决斗开打前必发这一声）；其余"技能指名目标"的路还没接上（仍要等内容刀）。"成为攻击目标"那一声照常由每次普攻发出。</t>
   </si>
   <si>
-    <t>我听谁（只听自己／听己方（同一席位）／听场上（所有玩家））</t>
-  </si>
-  <si>
-    <t>与"哪一刻响"无关的第二把尺子：那一声响起时，这条技能听多宽。只听自己＝只算这名将自己身上发生的事；听己方（同一席位）＝同一个玩家席位下的全部将领都算己方（跟"座位"走，不跟"势力"走）；听场上（所有玩家）＝谁的席位出事都算听到。Excel 里它是自己的一列（技能级「我听谁」＋每个效果的「效果N我听谁」），不写在触发时机那句话里，跟"技能门槛／效果N门槛"那两列一个摆法。不填＝只听自己，与今天对局逐字一致。两个实话：①手牌、回合这类事本来就记在玩家身上，所以这类时机里"只听自己"与"听己方（同一席位）"是同一回事；②"回合结束时、其他玩家登场时、技能失效时"这几类不认这一栏——填了会按没填处理并在导入总结里点名，不会静悄悄收下。</t>
+    <t>我听谁（只听自己／听己方（同一席位）／听除自身以外／听敌方（其他席位）／听场上（所有玩家））</t>
+  </si>
+  <si>
+    <t>与"哪一刻响"无关的第二把尺子：那一声响起时，这条技能听多宽。只听自己＝只算这名将自己身上发生的事；听己方（同一席位）＝同一个玩家席位下的全部将领都算己方（跟"座位"走，不跟"势力"走）；听除自身以外（v2.9.13 新增）＝除"我这一员"以外都算——同一个席位上的别的将也算，不只算别人席位的；听敌方（其他席位）（v2.9.13 新增）＝别的玩家席位出事才算，自家席位的别的将不算；听场上（所有玩家）＝谁的席位出事都算听到。Excel 里它是自己的一列（技能级「我听谁」＋每个效果「效果N我听谁」），不写在触发时机那句话里，跟"技能门槛／效果N门槛"那两列一个摆法。不填＝只听自己，与今天对局逐字一致。两个实话：①手牌、回合这类事本来就记在玩家身上，所以这类时机里"只听自己"与"听己方（同一席位）"是同一回事；②"回合结束时、其他玩家登场时、技能失效时"这几类不认这一栏——填了会按没填处理并在导入总结里点名，不会静悄悄收下。卡面上您那套说法也认得（v2.9.13 起，只有"登场"这一格）：您写的「其他角色＝自身以外、己方角色＝包括自身的己方玩家的角色、敌方角色＝己方玩家外的所有玩家的角色」就是上面这三档，自己写效果时那句定语照您的写法打进来即可（拼法全库只有一处，界面里那句提示是现拼的，不是另抄一份）。注意"敌方"这里按席位算，不按魏蜀吴群那种势力算（您 2026-10-18 那两句原话就是这么划的：「敌方角色＝己方玩家外的所有玩家的角色」）。</t>
   </si>
   <si>
     <t>细分（伤害类型／被谁指名／击杀对象／卡牌时机／失效条件）</t>
@@ -1026,7 +1032,7 @@
     <t>自己写效果（v2.9.9 起）</t>
   </si>
   <si>
-    <t>技能卡片上「✍️ 自己写效果（一句话生成积木）」那一格：您用大白话写，系统替您反推成上面那三格积木，先给您看它打算怎么说，您点头才进格子（不点头什么都不会变），点「✔ 采用」后就是原来的拼积木界面，逐条改即可。写的是一行一段、句号分开；以下择一／以下依次生效 两句当头一句写，就按"选择其一"／"链式"登记；要满足手牌≤2 写在最前面＝整组门槛、写在某条时机后面＝那一条自己的门槛。认得的说法＝词表里那十二档动作与三档对象，中文数字（两、十二）与阿拉伯数字同解，「全部」＝整只手，观顶3张「拆掉 1 张装备卡」这类旧行话也照旧读得懂（只进不出）。读不懂的绝不猜、也没有一段是悄悄丢掉的：哪一段不支持就原文点出来＋一句照着改得动的理由（例："这一句要作用在'别人'身上……想让别的玩家执行的那类内容还没做出来"、"若…则…请改写「以下依次生效」"、"限定技是徽章，去徽章那一格勾"）。⚠️ 退回看这一段写在动作的哪一边，因为两句话的意思不一样：写在动作前面＝它正在给这个动作补"对谁／在什么前提下做"⇒这一条整条退回（只收动作那半＝做成另一件事）；写在动作后面＝像是第二件事⇒前面那件读懂的照做、后面这段单独点名并教您另起一句（一段只认一件事，第二件不顶掉第一件）。⚠️ 两种"不支持"也分开了：① 形状写错了 ⇒ 那一条不生成；② 格子有、引擎还没接线（例如下拉里那些还没上事件面的时机） ⇒ 照样生成、也能采用，但界面当场说一句"这条今天不会响"。这一格没有大模型、不联网，纯离线词表；能不能编出结算问的是编译器那一支自己（skillCompiler.judgeSkillEffect，反解侧与真编译路共用同一判据，不可能两边各说一套）。反解侧＝src/skills/skillTextParse.ts，界面＝src/components/skillEditor/SkillTextPanel.tsx；两侧由 skillTextParse.test.ts 的往返钉钉住（生成的那句再解回去、再生成 ⇒ 逐字同一句）。</t>
+    <t>技能卡片上「✍️ 自己写效果（一句话生成积木）」那一格：您用大白话写，系统替您反推成上面那三格积木，先给您看它打算怎么说，您点头才进格子（不点头什么都不会变），点「✔ 采用」后就是原来的拼积木界面，逐条改即可。写的是一行一段、句号分开；以下择一／以下依次生效 两句当头一句写，就按"选择其一"／"链式"登记；要满足手牌≤2 写在最前面＝整组门槛、写在某条时机后面＝那一条自己的门槛。认得的说法＝词表里那十二档动作与三档对象，中文数字（两、十二）与阿拉伯数字同解，「全部」＝整只手，观顶3张「拆掉 1 张装备卡」这类旧行话也照旧读得懂（只进不出）。读不懂的绝不猜、也没有一段是悄悄丢掉的：哪一段不支持就原文点出来＋一句照着改得动的理由（例："这一句要作用在'别人'身上……想让别的玩家执行的那类内容还没做出来"、"若…则…请改写「以下依次生效」"、"限定技是徽章，去徽章那一格勾"）。⚠️ 退回看这一段写在动作的哪一边，因为两句话的意思不一样：写在动作前面＝它正在给这个动作补"对谁／在什么前提下做"⇒这一条整条退回（只收动作那半＝做成另一件事）；写在动作后面＝像是第二件事⇒前面那件读懂的照做、后面这段单独点名并教您另起一句（一段只认一件事，第二件不顶掉第一件）。⚠️ 两种"不支持"也分开了：① 形状写错了 ⇒ 那一条不生成；② 格子有、引擎还没接线（例如下拉里那些还没上事件面的时机） ⇒ 照样生成、也能采用，但界面当场说一句"这条今天不会响"。这一格没有大模型、不联网，纯离线词表；能不能编出结算问的是编译器那一支自己（skillCompiler.judgeSkillEffect，反解侧与真编译路共用同一判据，不可能两边各说一套）。反解侧＝src/skills/skillTextParse.ts，界面＝src/components/skillEditor/SkillTextPanel.tsx；两侧由 skillTextParse.test.ts 的往返钉钉住（生成的那句再解回去、再生成 ⇒ 逐字同一句）。v2.9.13 这一格新认得的两样：①「将领登场时」这一档多了您那三句定语——其他角色登场时／己方角色登场时／敌方角色登场时（加上自身登场时与场上所有角色登场时一共五种写法），拼出来的都是上面「我听谁」那五档里的同一档，拼法全库只有一处（data/generals.ts 那张对照表），界面提示与这句反解都从它现取，不会各写一份；②其他角色摸两张牌这类用词写错的句子，现在走的是"这一句的说法本作不成立"那一档理由，并给您一句改得动的写法（详见上面「角色 / 玩家」那一行）——它跟"内容还没做出来"是两回事，分开点名。</t>
   </si>
   <si>
     <t>有效周期（这笔账什么时候结束）</t>
@@ -1053,7 +1059,7 @@
     <t>（旧说法，已作废）击破横幅上方那行残留的英文小字，v2.8.18 已翻成中文，v2.8.39 起那里写的是「营地击破」。</t>
   </si>
   <si>
-    <t>本节末尾必须说清的一件事：五个"××技"徽章和"强制发动"这一列，v2.8.19 起读得到、写得出、显示得出、还能核对（一枚技能可挂几枚；徽章与触发时机对不上会在编辑器与导入总结里点名）。这两样如今落地程度不同：「强制发动」v2.8.25 起接进对局了——全库只有一个地方读它（skills/SkillTriggerBridge.ts 的 defersToReactionQueue：受击／受伤这两型里没打勾的定义才交给问答队列问人，打了勾的直接走自动发动那条路；v2.9.3 起这一处还多认一枚徽章——挂了「觉醒技」的技能没打勾时同样停下来问您，打了勾就照旧自己响），所以它管的事恰恰只有一件＝"这一刻问不问您"；徽章里「锁定技」v2.8 刀4 起有了第一个结算侧的消费者，但只管一寸地方：编译器认出这枚徽章 → 这条技能往数值账本落的那笔账打上"移不走"的记号（statModifiers.revokeModifier 是全库唯一"移走别人那笔账"的入口，它见到这个记号就拒绝）。徽章的其余部分（"不能被无效""不能被改变"在伤害、护甲、被弃牌这些环节到底管不管）今天仍然没有任何结算代码读它；四枚徽章里限定技自 v2.8.32 起有了第二个结算侧消费者（编译器认出它 ⇒ 这枚技能每发动一次就在同一本账上落一笔，账上有这一笔就不再让它发动；"一局一次"的判据与记账形状全库只有一份＝skills/skillQuota.ts，三条发动路——回合结束、停下问您、到点自己响——都从这里过），登场／遗计还是纯分类，而「觉醒技」自 v2.9.3 起也有了结算侧消费者：编译器认出这枚徽章后同时发生两件事——这枚技能听的那一声从"到点自己响"搬进"停下来问您一次"的队列，并且它与限定技共用同一本一局一次的账（摇头不算发动、不扣这笔账）。所以现在决定一条技能"什么时候响、响不响、响几次"的是：触发时机（含细分）＋「我听谁」与「被谁指名」这两档监听范围（v2.8.21 起触发桥逐条读；两档的缺省＝只听自己／只算攻击，⇒ 与今天对局逐字一致。"成为技能目标"这一声 v2.8.24 起已有发射器＝决斗开局（其余技能指名目标的路仍未发这一声，等内容刀））＋ 发动门槛 ＋ 那条"每回合限一次"的账 ＋ 限定技与觉醒技"一局一次"的同一本账（v2.8.32 起／v2.9.3 起）＋「强制发动」这一格（v2.8.25 起，只管问不问人；v2.9.3 起它对觉醒技同样管用——勾了就不问、到点自己结算）。「在场即生效」那一型不看上面这些，它只在登场／离场两刻动账本。徽章的读写口径全库只有一份，在 domain/skillTags.ts。</t>
+    <t>本节末尾必须说清的一件事：五个"××技"徽章和"强制发动"这一列，v2.8.19 起读得到、写得出、显示得出、还能核对（一枚技能可挂几枚；徽章与触发时机对不上会在编辑器与导入总结里点名）。这两样如今落地程度不同：「强制发动」v2.8.25 起接进对局了——全库只有一个地方读它（skills/SkillTriggerBridge.ts 的 defersToReactionQueue：受击／受伤这两型里没打勾的定义才交给问答队列问人，打了勾的直接走自动发动那条路；v2.9.3 起这一处还多认一枚徽章——挂了「觉醒技」的技能没打勾时同样停下来问您，打了勾就照旧自己响），所以它管的事恰恰只有一件＝"这一刻问不问您"；徽章里「锁定技」v2.8 刀4 起有了第一个结算侧的消费者，但只管一寸地方：编译器认出这枚徽章 → 这条技能往数值账本落的那笔账打上"移不走"的记号（statModifiers.revokeModifier 是全库唯一"移走别人那笔账"的入口，它见到这个记号就拒绝）。徽章的其余部分（"不能被无效""不能被改变"在伤害、护甲、被弃牌这些环节到底管不管）今天仍然没有任何结算代码读它；四枚徽章里限定技自 v2.8.32 起有了第二个结算侧消费者（编译器认出它 ⇒ 这枚技能每发动一次就在同一本账上落一笔，账上有这一笔就不再让它发动；"一局一次"的判据与记账形状全库只有一份＝skills/skillQuota.ts，三条发动路——回合结束、停下问您、到点自己响——都从这里过），登场／遗计还是纯分类，而「觉醒技」自 v2.9.3 起也有了结算侧消费者：编译器认出这枚徽章后同时发生两件事——这枚技能听的那一声从"到点自己响"搬进"停下来问您一次"的队列，并且它与限定技共用同一本一局一次的账（摇头不算发动、不扣这笔账）。所以现在决定一条技能"什么时候响、响不响、响几次"的是：触发时机（含细分）＋「我听谁」这一档监听范围（五档，v2.8.21 起三档、v2.9.13 起五档；触发桥逐条读；缺省＝只听自己，⇒ 与今天对局逐字一致。「被谁指名」那一档＝成为目标时的细分，另算一维（"成为技能目标"这一声 v2.8.24 起已有发射器＝决斗开局，其余技能指名目标的路仍未发这一声，等内容刀））＋ 发动门槛 ＋ 那条"每回合限一次"的账 ＋ 限定技与觉醒技"一局一次"的同一本账（v2.8.32 起／v2.9.3 起）＋「强制发动」这一格（v2.8.25 起，只管问不问人；v2.9.3 起它对觉醒技同样管用——勾了就不问、到点自己结算）。「在场即生效」那一型不看上面这些，它只在登场／离场两刻动账本。徽章的读写口径全库只有一份，在 domain/skillTags.ts。</t>
   </si>
   <si>
     <t>游戏结束 / 对局结束</t>
@@ -1996,7 +2002,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -2078,18 +2084,18 @@
         <v>33</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2100,7 +2106,7 @@
         <v>38</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2144,18 +2150,18 @@
         <v>46</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>47</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2232,40 +2238,40 @@
         <v>63</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>64</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="C22" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2320,18 +2326,18 @@
         <v>82</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>83</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="C30" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2353,6 +2359,17 @@
         <v>89</v>
       </c>
       <c r="C32" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2385,10 +2402,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -2396,10 +2413,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -2407,10 +2424,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -2418,10 +2435,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -2429,10 +2446,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -2440,10 +2457,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -2451,10 +2468,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -2462,10 +2479,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -2473,10 +2490,10 @@
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -2484,10 +2501,10 @@
     </row>
     <row r="11" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>1</v>
@@ -2495,10 +2512,10 @@
     </row>
     <row r="12" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>1</v>
@@ -2506,10 +2523,10 @@
     </row>
     <row r="13" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>1</v>
@@ -2517,21 +2534,21 @@
     </row>
     <row r="14" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>1</v>
@@ -2539,10 +2556,10 @@
     </row>
     <row r="16" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>1</v>
@@ -2550,10 +2567,10 @@
     </row>
     <row r="17" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>1</v>
@@ -2561,10 +2578,10 @@
     </row>
     <row r="18" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>1</v>
@@ -2572,10 +2589,10 @@
     </row>
     <row r="19" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>1</v>
@@ -2583,10 +2600,10 @@
     </row>
     <row r="20" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>1</v>
@@ -2594,10 +2611,10 @@
     </row>
     <row r="21" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>1</v>
@@ -2605,10 +2622,10 @@
     </row>
     <row r="22" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>1</v>
@@ -2616,10 +2633,10 @@
     </row>
     <row r="23" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>1</v>
@@ -2627,10 +2644,10 @@
     </row>
     <row r="24" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>1</v>
@@ -2638,10 +2655,10 @@
     </row>
     <row r="25" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>1</v>
@@ -2649,10 +2666,10 @@
     </row>
     <row r="26" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>1</v>
@@ -2660,10 +2677,10 @@
     </row>
     <row r="27" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>1</v>
@@ -2671,10 +2688,10 @@
     </row>
     <row r="28" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>1</v>
@@ -2682,10 +2699,10 @@
     </row>
     <row r="29" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>1</v>
@@ -2693,10 +2710,10 @@
     </row>
     <row r="30" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>1</v>
@@ -2704,10 +2721,10 @@
     </row>
     <row r="31" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>1</v>
@@ -2715,10 +2732,10 @@
     </row>
     <row r="32" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>1</v>
@@ -2726,10 +2743,10 @@
     </row>
     <row r="33" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>1</v>
@@ -2737,10 +2754,10 @@
     </row>
     <row r="34" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>1</v>
@@ -2748,10 +2765,10 @@
     </row>
     <row r="35" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>1</v>
@@ -2759,10 +2776,10 @@
     </row>
     <row r="36" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>1</v>
@@ -2770,10 +2787,10 @@
     </row>
     <row r="37" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>1</v>
@@ -2781,10 +2798,10 @@
     </row>
     <row r="38" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>1</v>
@@ -2792,10 +2809,10 @@
     </row>
     <row r="39" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>1</v>
@@ -2830,10 +2847,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -2841,10 +2858,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -2852,21 +2869,21 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -2874,10 +2891,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -2885,10 +2902,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -2896,10 +2913,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -2907,10 +2924,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -2918,21 +2935,21 @@
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>1</v>
@@ -2940,10 +2957,10 @@
     </row>
     <row r="12" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>1</v>
@@ -2951,10 +2968,10 @@
     </row>
     <row r="13" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>1</v>
@@ -2962,10 +2979,10 @@
     </row>
     <row r="14" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>1</v>
@@ -2973,10 +2990,10 @@
     </row>
     <row r="15" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>1</v>
@@ -2984,10 +3001,10 @@
     </row>
     <row r="16" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>1</v>
@@ -2995,10 +3012,10 @@
     </row>
     <row r="17" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>1</v>
@@ -3006,10 +3023,10 @@
     </row>
     <row r="18" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>1</v>
@@ -3017,10 +3034,10 @@
     </row>
     <row r="19" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>1</v>
@@ -3028,10 +3045,10 @@
     </row>
     <row r="20" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>1</v>
@@ -3039,10 +3056,10 @@
     </row>
     <row r="21" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>1</v>
@@ -3050,10 +3067,10 @@
     </row>
     <row r="22" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>1</v>
@@ -3061,10 +3078,10 @@
     </row>
     <row r="23" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>1</v>
@@ -3072,10 +3089,10 @@
     </row>
     <row r="24" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>1</v>
@@ -3083,10 +3100,10 @@
     </row>
     <row r="25" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>1</v>
@@ -3094,10 +3111,10 @@
     </row>
     <row r="26" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>1</v>
@@ -3105,10 +3122,10 @@
     </row>
     <row r="27" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>1</v>
@@ -3116,10 +3133,10 @@
     </row>
     <row r="28" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>1</v>
@@ -3127,10 +3144,10 @@
     </row>
     <row r="29" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>1</v>
@@ -3138,10 +3155,10 @@
     </row>
     <row r="30" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>1</v>
@@ -3149,10 +3166,10 @@
     </row>
     <row r="31" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>1</v>
@@ -3160,10 +3177,10 @@
     </row>
     <row r="32" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>1</v>
@@ -3171,10 +3188,10 @@
     </row>
     <row r="33" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>1</v>
@@ -3182,10 +3199,10 @@
     </row>
     <row r="34" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>1</v>
@@ -3193,10 +3210,10 @@
     </row>
     <row r="35" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>1</v>
@@ -3204,10 +3221,10 @@
     </row>
     <row r="36" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>1</v>
@@ -3215,10 +3232,10 @@
     </row>
     <row r="37" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>1</v>
@@ -3226,10 +3243,10 @@
     </row>
     <row r="38" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>1</v>
@@ -3237,10 +3254,10 @@
     </row>
     <row r="39" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>1</v>
@@ -3248,10 +3265,10 @@
     </row>
     <row r="40" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>1</v>
@@ -3259,10 +3276,10 @@
     </row>
     <row r="41" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>1</v>
@@ -3270,10 +3287,10 @@
     </row>
     <row r="42" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>1</v>
@@ -3281,10 +3298,10 @@
     </row>
     <row r="43" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>1</v>
@@ -3292,10 +3309,10 @@
     </row>
     <row r="44" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>1</v>
@@ -3303,10 +3320,10 @@
     </row>
     <row r="45" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>1</v>
@@ -3314,10 +3331,10 @@
     </row>
     <row r="46" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>1</v>
@@ -3325,10 +3342,10 @@
     </row>
     <row r="47" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>1</v>
@@ -3336,10 +3353,10 @@
     </row>
     <row r="48" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>1</v>
@@ -3347,10 +3364,10 @@
     </row>
     <row r="49" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>1</v>
@@ -3358,10 +3375,10 @@
     </row>
     <row r="50" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>1</v>
@@ -3396,10 +3413,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3407,10 +3424,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3418,10 +3435,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3429,10 +3446,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3440,10 +3457,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3451,10 +3468,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3462,10 +3479,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3473,10 +3490,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3484,10 +3501,10 @@
     </row>
     <row r="10" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -3498,10 +3515,10 @@
     </row>
     <row r="11" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>1</v>
@@ -3509,10 +3526,10 @@
     </row>
     <row r="12" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>1</v>
@@ -3520,10 +3537,10 @@
     </row>
     <row r="13" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>1</v>
@@ -3531,10 +3548,10 @@
     </row>
     <row r="14" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>1</v>
@@ -3542,10 +3559,10 @@
     </row>
     <row r="15" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>1</v>
@@ -3553,10 +3570,10 @@
     </row>
     <row r="16" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>1</v>
@@ -3564,10 +3581,10 @@
     </row>
     <row r="17" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>1</v>
@@ -3575,10 +3592,10 @@
     </row>
     <row r="18" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>1</v>
@@ -3586,10 +3603,10 @@
     </row>
     <row r="19" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>1</v>
@@ -3597,10 +3614,10 @@
     </row>
     <row r="20" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>1</v>
@@ -3608,10 +3625,10 @@
     </row>
     <row r="21" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>1</v>
@@ -3619,10 +3636,10 @@
     </row>
     <row r="22" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>1</v>
@@ -3630,10 +3647,10 @@
     </row>
     <row r="23" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>1</v>
@@ -3641,10 +3658,10 @@
     </row>
     <row r="24" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>1</v>
@@ -3652,10 +3669,10 @@
     </row>
     <row r="25" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>1</v>
@@ -3663,10 +3680,10 @@
     </row>
     <row r="26" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>1</v>
@@ -3674,10 +3691,10 @@
     </row>
     <row r="27" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>1</v>
@@ -3685,10 +3702,10 @@
     </row>
     <row r="28" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>1</v>
@@ -3696,10 +3713,10 @@
     </row>
     <row r="29" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>1</v>
@@ -3707,10 +3724,10 @@
     </row>
     <row r="30" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>1</v>
@@ -3718,10 +3735,10 @@
     </row>
     <row r="31" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>1</v>
@@ -3729,10 +3746,10 @@
     </row>
     <row r="32" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>1</v>
@@ -3740,10 +3757,10 @@
     </row>
     <row r="33" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>1</v>
@@ -3751,10 +3768,10 @@
     </row>
     <row r="34" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>1</v>
@@ -3762,10 +3779,10 @@
     </row>
     <row r="35" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>1</v>
@@ -3773,10 +3790,10 @@
     </row>
     <row r="36" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>1</v>
@@ -3784,10 +3801,10 @@
     </row>
     <row r="37" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>1</v>
@@ -3795,10 +3812,10 @@
     </row>
     <row r="38" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>1</v>
@@ -3806,10 +3823,10 @@
     </row>
     <row r="39" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>1</v>
@@ -3817,7 +3834,7 @@
     </row>
     <row r="41" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -3854,10 +3871,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3865,10 +3882,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3876,10 +3893,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3887,10 +3904,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3898,10 +3915,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3909,10 +3926,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3920,10 +3937,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3931,10 +3948,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3942,10 +3959,10 @@
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -3980,10 +3997,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3991,10 +4008,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -4002,10 +4019,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -4013,10 +4030,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -4024,10 +4041,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -4035,10 +4052,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -4046,10 +4063,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -4057,10 +4074,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -4068,10 +4085,10 @@
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -4079,10 +4096,10 @@
     </row>
     <row r="11" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>1</v>
@@ -4090,10 +4107,10 @@
     </row>
     <row r="12" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>1</v>
@@ -4101,10 +4118,10 @@
     </row>
     <row r="13" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>1</v>
@@ -4112,10 +4129,10 @@
     </row>
     <row r="14" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>1</v>
@@ -4123,10 +4140,10 @@
     </row>
     <row r="15" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>1</v>
@@ -4134,10 +4151,10 @@
     </row>
     <row r="16" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>1</v>
@@ -4145,10 +4162,10 @@
     </row>
     <row r="17" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>1</v>
@@ -4156,10 +4173,10 @@
     </row>
     <row r="18" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>1</v>
@@ -4167,10 +4184,10 @@
     </row>
     <row r="19" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>1</v>
@@ -4178,10 +4195,10 @@
     </row>
     <row r="20" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>1</v>
@@ -4189,10 +4206,10 @@
     </row>
     <row r="21" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>1</v>
@@ -4200,10 +4217,10 @@
     </row>
     <row r="22" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>1</v>
@@ -4211,10 +4228,10 @@
     </row>
     <row r="23" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>1</v>
@@ -4222,10 +4239,10 @@
     </row>
     <row r="24" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>1</v>
@@ -4249,10 +4266,10 @@
   <sheetData>
     <row r="1" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>18</v>
@@ -4260,10 +4277,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -4271,10 +4288,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -4282,10 +4299,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -4293,10 +4310,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -4304,10 +4321,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -4315,10 +4332,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -4326,10 +4343,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -4337,10 +4354,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -4365,206 +4382,206 @@
   <sheetData>
     <row r="1" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
   </sheetData>

--- a/词汇表.xlsx
+++ b/词汇表.xlsx
@@ -879,16 +879,16 @@
     <t>"这技能在哪一刻响"的下拉。玩家在对局里只会看到结果，看不到这个词本身。</t>
   </si>
   <si>
-    <t>回合开始时 / 回合结束时 / 将领登场时 / 受到伤害后 / 造成伤害后 / 成为目标时 / 击杀将领时 / 自身被击杀时 / 失去手牌时 / 获得手牌时</t>
-  </si>
-  <si>
-    <t>十种"哪一刻响"的说法，字面就是那件事发生的时刻。（"成为攻击目标时"这个旧名字 v2.8.21 起改成了泛指的"成为目标时"，具体被谁指名交给下面那一格说。）「受到伤害后」的判据（v2.8 刀5 起，您 2026-10-03 重新裁定）＝只有真的掉了体力才算受到了伤害：这一刀被护甲全挡住、一点血没掉 ⇒ 不算受到，技能不问也不响；伤害算出来是 0 或负数 ⇒ 也不算。掉多少算多少：普攻／技能伤害每一刀各算一声；决斗那一整场只在打完时按"这个将一共掉了多少体力"算一笔（见上面「决斗」那一格）。被这一刀打死的那一位，两类里只有「受到伤害后」不算（v2.8.31 定稿＝您 2026-10-04 把两类的定义封死：「成为目标时」＝受击，它在伤害算出来之前就发动完了，所以和这一刀实际打多少、主人会不会被这一刀砍死无关——被砍死的那一刀里它照样问、照样响；「受到伤害后」＝受伤，必须真的掉了血才成立，所以它在伤害之后才问，主人死在这一刀里就不问也不响）。两条路的判据一模一样，区别只在"需不需要您自己点头"。追加的那一条（甲）也在这里生效：反伤先把出手的那位扎死了⇒那一刀跟着取消，挨打的那位自救成功，粮草也没被吃掉。唯一的豁口＝「自身被击杀时」那一型（遗言／遗计）：它按定义就是在主人离场这一声上发动，所以两边都放行，牌照旧摸进手。判据与取证＝PROJECT_HANDOFF.md §12-100／§12-101／§12-102。</t>
+    <t>回合开始时 / 回合结束时 / 将领登场时 / 受到伤害后 / 造成伤害后 / 成为目标时 / 击杀将领时 / 自身被击杀时 / 失去手牌时 / 获得手牌时 / 营地受到伤害时</t>
+  </si>
+  <si>
+    <t>十一种"哪一刻响"的说法，字面就是那件事发生的时刻。（"成为攻击目标时"这个旧名字 v2.8.21 起改成了泛指的"成为目标时"，具体被谁指名交给下面那一格说。）「受到伤害后」的判据（v2.8 刀5 起，您 2026-10-03 重新裁定）＝只有真的掉了体力才算受到了伤害：这一刀被护甲全挡住、一点血没掉 ⇒ 不算受到，技能不问也不响；伤害算出来是 0 或负数 ⇒ 也不算。掉多少算多少：普攻／技能伤害每一刀各算一声；决斗那一整场只在打完时按"这个将一共掉了多少体力"算一笔（见上面「决斗」那一格）。被这一刀打死的那一位，两类里只有「受到伤害后」不算（v2.8.31 定稿＝您 2026-10-04 把两类的定义封死：「成为目标时」＝受击，它在伤害算出来之前就发动完了，所以和这一刀实际打多少、主人会不会被这一刀砍死无关——被砍死的那一刀里它照样问、照样响；「受到伤害后」＝受伤，必须真的掉了血才成立，所以它在伤害之后才问，主人死在这一刀里就不问也不响）。两条路的判据一模一样，区别只在"需不需要您自己点头"。追加的那一条（甲）也在这里生效：反伤先把出手的那位扎死了⇒那一刀跟着取消，挨打的那位自救成功，粮草也没被吃掉。唯一的豁口＝「自身被击杀时」那一型（遗言／遗计）：它按定义就是在主人离场这一声上发动，所以两边都放行，牌照旧摸进手。最后那一格（营地受到伤害时）是 v2.9.14 才接上电的（您 2026-10-18 定"先做「营地受到伤害时」"）：它听的是营地那一格掉了血这一声，判据跟上面同一句——只有真的掉了体力才算受到伤害，那一刀被挡光、一点没掉⇒不算、不响。三句实话：①它只认自家那一席的营地，别人家营地掉血不算（营地不是任何一员将，所以"我听谁的营地"这一维今天没有做，界面上那一格下拉对这一型直接不出现，从旧 Excel 硬塞一格进来会被点名跳过、不静悄悄当成"只听自家"）；②它到点自己响，不停下来问您（跟登场／回合开始同一类，跟「受到伤害后」要点头那一类不同），勾不勾「强制发动」都一样；③另两格营地系的说法「营地成为攻击目标时」「营地成为技能目标时」还是没接线（那两声身上没带"这是哪一席的营地"这个记号，接了就是瞎响），下拉里点得到、界面照旧会当场写明它今天不会响。顺带修掉一条老毛病：v2.8.21 给「受到伤害后」加上"听别人"那几档之后，自家营地掉血也曾被它当成"受到了伤害"（那几档不比是哪一员将，营地那一身就顺着席位混进来了）⇒ 本轮起「受到伤害后」只管人、营地交给这一格。判据与取证＝PROJECT_HANDOFF.md §12-100／§12-101／§12-102／§12-130。</t>
   </si>
   <si>
     <t>在场即生效（不用发动，人在就算）（v2.8 刀4 起可结算）</t>
   </si>
   <si>
-    <t>第十一种选择，但它根本不是"哪一刻响"——它是"没有哪一刻需要它响"。这一型编译出来不监听任何事件、不进问答窗、不吃「强制发动」那一格：将领登场那一刻落一笔账（配合下面的「修改数值」用），离场当场销账，人在的整段时间都算数。三句实话：①旧名字「全局生效（在场时持续）」容易读成"影响全场所有人"，v2.8 刀4 起改叫这个名，旧 Excel 里那一格照样读得懂、再导出会写新名；②这一型不许配门槛、不许配有效周期、不许配「选择其一」（门槛要"情况一变就改口"、周期要"发动笔"那一档、择一要有人点头——三样都没有落点），填了会在编译时逐条点名跳过，不会悄悄变成"全都要"；③v2.9.6 起这一型第一次挂上了官方将＝魏、蜀两张关羽卡上共用的「武圣」（出牌时把远程攻击力往上顶 1，人在就算、离场当场销账）；技能表上那一枚「怒斩」也是这一型（它不印在任何将卡上）。96 将里用这一型的就这一条（当场量过，有测试钉着）。</t>
+    <t>跟上面那一串并列的另一格，但它根本不是"哪一刻响"——它是"没有哪一刻需要它响"。这一型编译出来不监听任何事件、不进问答窗、不吃「强制发动」那一格：将领登场那一刻落一笔账（配合下面的「修改数值」用），离场当场销账，人在的整段时间都算数。三句实话：①旧名字「全局生效（在场时持续）」容易读成"影响全场所有人"，v2.8 刀4 起改叫这个名，旧 Excel 里那一格照样读得懂、再导出会写新名；②这一型不许配门槛、不许配有效周期、不许配「选择其一」（门槛要"情况一变就改口"、周期要"发动笔"那一档、择一要有人点头——三样都没有落点），填了会在编译时逐条点名跳过，不会悄悄变成"全都要"；③v2.9.6 起这一型第一次挂上了官方将＝魏、蜀两张关羽卡上共用的「武圣」（出牌时把远程攻击力往上顶 1，人在就算、离场当场销账）；技能表上那一枚「怒斩」也是这一型（它不印在任何将卡上）。96 将里用这一型的就这一条（当场量过，有测试钉着）。</t>
   </si>
   <si>
     <t>攻击伤害 / 技能伤害</t>
@@ -906,7 +906,7 @@
     <t>我听谁（只听自己／听己方（同一席位）／听除自身以外／听敌方（其他席位）／听场上（所有玩家））</t>
   </si>
   <si>
-    <t>与"哪一刻响"无关的第二把尺子：那一声响起时，这条技能听多宽。只听自己＝只算这名将自己身上发生的事；听己方（同一席位）＝同一个玩家席位下的全部将领都算己方（跟"座位"走，不跟"势力"走）；听除自身以外（v2.9.13 新增）＝除"我这一员"以外都算——同一个席位上的别的将也算，不只算别人席位的；听敌方（其他席位）（v2.9.13 新增）＝别的玩家席位出事才算，自家席位的别的将不算；听场上（所有玩家）＝谁的席位出事都算听到。Excel 里它是自己的一列（技能级「我听谁」＋每个效果「效果N我听谁」），不写在触发时机那句话里，跟"技能门槛／效果N门槛"那两列一个摆法。不填＝只听自己，与今天对局逐字一致。两个实话：①手牌、回合这类事本来就记在玩家身上，所以这类时机里"只听自己"与"听己方（同一席位）"是同一回事；②"回合结束时、其他玩家登场时、技能失效时"这几类不认这一栏——填了会按没填处理并在导入总结里点名，不会静悄悄收下。卡面上您那套说法也认得（v2.9.13 起，只有"登场"这一格）：您写的「其他角色＝自身以外、己方角色＝包括自身的己方玩家的角色、敌方角色＝己方玩家外的所有玩家的角色」就是上面这三档，自己写效果时那句定语照您的写法打进来即可（拼法全库只有一处，界面里那句提示是现拼的，不是另抄一份）。注意"敌方"这里按席位算，不按魏蜀吴群那种势力算（您 2026-10-18 那两句原话就是这么划的：「敌方角色＝己方玩家外的所有玩家的角色」）。</t>
+    <t>与"哪一刻响"无关的第二把尺子：那一声响起时，这条技能听多宽。只听自己＝只算这名将自己身上发生的事；听己方（同一席位）＝同一个玩家席位下的全部将领都算己方（跟"座位"走，不跟"势力"走）；听除自身以外（v2.9.13 新增）＝除"我这一员"以外都算——同一个席位上的别的将也算，不只算别人席位的；听敌方（其他席位）（v2.9.13 新增）＝别的玩家席位出事才算，自家席位的别的将不算；听场上（所有玩家）＝谁的席位出事都算听到。Excel 里它是自己的一列（技能级「我听谁」＋每个效果「效果N我听谁」），不写在触发时机那句话里，跟"技能门槛／效果N门槛"那两列一个摆法。不填＝只听自己，与今天对局逐字一致。两个实话：①手牌、回合这类事本来就记在玩家身上，所以这类时机里"只听自己"与"听己方（同一席位）"是同一回事；②"回合结束时、其他玩家登场时、技能失效时、营地受到伤害时"这几类不认这一栏——填了会按没填处理并在导入总结里点名，不会静悄悄收下。营地那一格更彻底：因为营地不是任何一员将，"我听谁的营地"这一维压根没有，所以选了"营地受到伤害时"之后，界面上「我听谁」那一行直接消失（不是灰着，也不是留着让您填）。卡面上您那套说法也认得（v2.9.13 起，只有"登场"这一格）：您写的「其他角色＝自身以外、己方角色＝包括自身的己方玩家的角色、敌方角色＝己方玩家外的所有玩家的角色」就是上面这三档，自己写效果时那句定语照您的写法打进来即可（拼法全库只有一处，界面里那句提示是现拼的，不是另抄一份）。注意"敌方"这里按席位算，不按魏蜀吴群那种势力算（您 2026-10-18 那两句原话就是这么划的：「敌方角色＝己方玩家外的所有玩家的角色」）。</t>
   </si>
   <si>
     <t>细分（伤害类型／被谁指名／击杀对象／卡牌时机／失效条件）</t>

--- a/词汇表.xlsx
+++ b/词汇表.xlsx
@@ -879,10 +879,10 @@
     <t>"这技能在哪一刻响"的下拉。玩家在对局里只会看到结果，看不到这个词本身。</t>
   </si>
   <si>
-    <t>回合开始时 / 回合结束时 / 将领登场时 / 受到伤害后 / 造成伤害后 / 成为目标时 / 击杀将领时 / 自身被击杀时 / 失去手牌时 / 获得手牌时 / 营地受到伤害时</t>
-  </si>
-  <si>
-    <t>十一种"哪一刻响"的说法，字面就是那件事发生的时刻。（"成为攻击目标时"这个旧名字 v2.8.21 起改成了泛指的"成为目标时"，具体被谁指名交给下面那一格说。）「受到伤害后」的判据（v2.8 刀5 起，您 2026-10-03 重新裁定）＝只有真的掉了体力才算受到了伤害：这一刀被护甲全挡住、一点血没掉 ⇒ 不算受到，技能不问也不响；伤害算出来是 0 或负数 ⇒ 也不算。掉多少算多少：普攻／技能伤害每一刀各算一声；决斗那一整场只在打完时按"这个将一共掉了多少体力"算一笔（见上面「决斗」那一格）。被这一刀打死的那一位，两类里只有「受到伤害后」不算（v2.8.31 定稿＝您 2026-10-04 把两类的定义封死：「成为目标时」＝受击，它在伤害算出来之前就发动完了，所以和这一刀实际打多少、主人会不会被这一刀砍死无关——被砍死的那一刀里它照样问、照样响；「受到伤害后」＝受伤，必须真的掉了血才成立，所以它在伤害之后才问，主人死在这一刀里就不问也不响）。两条路的判据一模一样，区别只在"需不需要您自己点头"。追加的那一条（甲）也在这里生效：反伤先把出手的那位扎死了⇒那一刀跟着取消，挨打的那位自救成功，粮草也没被吃掉。唯一的豁口＝「自身被击杀时」那一型（遗言／遗计）：它按定义就是在主人离场这一声上发动，所以两边都放行，牌照旧摸进手。最后那一格（营地受到伤害时）是 v2.9.14 才接上电的（您 2026-10-18 定"先做「营地受到伤害时」"）：它听的是营地那一格掉了血这一声，判据跟上面同一句——只有真的掉了体力才算受到伤害，那一刀被挡光、一点没掉⇒不算、不响。三句实话：①它只认自家那一席的营地，别人家营地掉血不算（营地不是任何一员将，所以"我听谁的营地"这一维今天没有做，界面上那一格下拉对这一型直接不出现，从旧 Excel 硬塞一格进来会被点名跳过、不静悄悄当成"只听自家"）；②它到点自己响，不停下来问您（跟登场／回合开始同一类，跟「受到伤害后」要点头那一类不同），勾不勾「强制发动」都一样；③另两格营地系的说法「营地成为攻击目标时」「营地成为技能目标时」还是没接线（那两声身上没带"这是哪一席的营地"这个记号，接了就是瞎响），下拉里点得到、界面照旧会当场写明它今天不会响。顺带修掉一条老毛病：v2.8.21 给「受到伤害后」加上"听别人"那几档之后，自家营地掉血也曾被它当成"受到了伤害"（那几档不比是哪一员将，营地那一身就顺着席位混进来了）⇒ 本轮起「受到伤害后」只管人、营地交给这一格。判据与取证＝PROJECT_HANDOFF.md §12-100／§12-101／§12-102／§12-130。</t>
+    <t>回合开始时 / 回合结束时 / 将领登场时 / 受到伤害后 / 造成伤害后 / 成为目标时 / 击杀将领时 / 自身被击杀时 / 失去手牌时 / 获得手牌时 / 营地受到伤害时 / 其他将领技能发动时</t>
+  </si>
+  <si>
+    <t>十二种"哪一刻响"的说法，字面就是那件事发生的时刻。（"成为攻击目标时"这个旧名字 v2.8.21 起改成了泛指的"成为目标时"，具体被谁指名交给下面那一格说。）「受到伤害后」的判据（v2.8 刀5 起，您 2026-10-03 重新裁定）＝只有真的掉了体力才算受到了伤害：这一刀被护甲全挡住、一点血没掉 ⇒ 不算受到，技能不问也不响；伤害算出来是 0 或负数 ⇒ 也不算。掉多少算多少：普攻／技能伤害每一刀各算一声；决斗那一整场只在打完时按"这个将一共掉了多少体力"算一笔（见上面「决斗」那一格）。被这一刀打死的那一位，两类里只有「受到伤害后」不算（v2.8.31 定稿＝您 2026-10-04 把两类的定义封死：「成为目标时」＝受击，它在伤害算出来之前就发动完了，所以和这一刀实际打多少、主人会不会被这一刀砍死无关——被砍死的那一刀里它照样问、照样响；「受到伤害后」＝受伤，必须真的掉了血才成立，所以它在伤害之后才问，主人死在这一刀里就不问也不响）。两条路的判据一模一样，区别只在"需不需要您自己点头"。追加的那一条（甲）也在这里生效：反伤先把出手的那位扎死了⇒那一刀跟着取消，挨打的那位自救成功，粮草也没被吃掉。唯一的豁口＝「自身被击杀时」那一型（遗言／遗计）：它按定义就是在主人离场这一声上发动，所以两边都放行，牌照旧摸进手。最后那一格（营地受到伤害时）是 v2.9.14 才接上电的（您 2026-10-18 定"先做「营地受到伤害时」"）：它听的是营地那一格掉了血这一声，判据跟上面同一句——只有真的掉了体力才算受到伤害，那一刀被挡光、一点没掉⇒不算、不响。三句实话：①它只认自家那一席的营地，别人家营地掉血不算（营地不是任何一员将，所以"我听谁的营地"这一维今天没有做，界面上那一格下拉对这一型直接不出现，从旧 Excel 硬塞一格进来会被点名跳过、不静悄悄当成"只听自家"）；②它到点自己响，不停下来问您（跟登场／回合开始同一类，跟「受到伤害后」要点头那一类不同），勾不勾「强制发动」都一样；③另两格营地系的说法「营地成为攻击目标时」「营地成为技能目标时」还是没接线（那两声身上没带"这是哪一席的营地"这个记号，接了就是瞎响），下拉里点得到、界面照旧会当场写明它今天不会响。顺带修掉一条老毛病：v2.8.21 给「受到伤害后」加上"听别人"那几档之后，自家营地掉血也曾被它当成"受到了伤害"（那几档不比是哪一员将，营地那一身就顺着席位混进来了）⇒ 本轮起「受到伤害后」只管人、营地交给这一格。最后这一格（其他将领技能发动时）是 v2.9.15 才接上电的（您 2026-10-18 那句"做完「营地受到伤害时」就做「别人使用技能时」"）：它听的是某一枚技能真的发动了一次那一声。四句实话：①这一声过去只有"一局一次"那种带额度的技能才会留下记录，而且只记在台账里、不外传⇒本轮把"发动公告"改成每次真发动都出声，普通技能那一身不带台账键＝牌桌状态一个字都不动（所以对局里多出来的只是声音，两锚因此逐字没挪）；②"什么算别人"用的是上一刀那同一根轴（席位＋将领两维一起看，同一个席位上的别的将也算），没有另抄一份判据；③套娃只传一层＝由这一声引起的发动，自己再公告时身上带一个"我是被这一声叫起来的"记号，这一格听见这个记号就闭嘴——不然两员"别人发动我就摸牌"的能把彼此的牌堆摸穿；④空发不出声（那一条什么都没做成的发动不算发动，跟"没发动成功不消耗额度"是同一句诚实），而且它到点自己响、绝不停下来问您，跟营地那一格、登场／回合开始同一类。判据与取证＝PROJECT_HANDOFF.md §12-100／§12-101／§12-102／§12-130／§12-131。</t>
   </si>
   <si>
     <t>在场即生效（不用发动，人在就算）（v2.8 刀4 起可结算）</t>
@@ -906,7 +906,7 @@
     <t>我听谁（只听自己／听己方（同一席位）／听除自身以外／听敌方（其他席位）／听场上（所有玩家））</t>
   </si>
   <si>
-    <t>与"哪一刻响"无关的第二把尺子：那一声响起时，这条技能听多宽。只听自己＝只算这名将自己身上发生的事；听己方（同一席位）＝同一个玩家席位下的全部将领都算己方（跟"座位"走，不跟"势力"走）；听除自身以外（v2.9.13 新增）＝除"我这一员"以外都算——同一个席位上的别的将也算，不只算别人席位的；听敌方（其他席位）（v2.9.13 新增）＝别的玩家席位出事才算，自家席位的别的将不算；听场上（所有玩家）＝谁的席位出事都算听到。Excel 里它是自己的一列（技能级「我听谁」＋每个效果「效果N我听谁」），不写在触发时机那句话里，跟"技能门槛／效果N门槛"那两列一个摆法。不填＝只听自己，与今天对局逐字一致。两个实话：①手牌、回合这类事本来就记在玩家身上，所以这类时机里"只听自己"与"听己方（同一席位）"是同一回事；②"回合结束时、其他玩家登场时、技能失效时、营地受到伤害时"这几类不认这一栏——填了会按没填处理并在导入总结里点名，不会静悄悄收下。营地那一格更彻底：因为营地不是任何一员将，"我听谁的营地"这一维压根没有，所以选了"营地受到伤害时"之后，界面上「我听谁」那一行直接消失（不是灰着，也不是留着让您填）。卡面上您那套说法也认得（v2.9.13 起，只有"登场"这一格）：您写的「其他角色＝自身以外、己方角色＝包括自身的己方玩家的角色、敌方角色＝己方玩家外的所有玩家的角色」就是上面这三档，自己写效果时那句定语照您的写法打进来即可（拼法全库只有一处，界面里那句提示是现拼的，不是另抄一份）。注意"敌方"这里按席位算，不按魏蜀吴群那种势力算（您 2026-10-18 那两句原话就是这么划的：「敌方角色＝己方玩家外的所有玩家的角色」）。</t>
+    <t>与"哪一刻响"无关的第二把尺子：那一声响起时，这条技能听多宽。只听自己＝只算这名将自己身上发生的事；听己方（同一席位）＝同一个玩家席位下的全部将领都算己方（跟"座位"走，不跟"势力"走）；听除自身以外（v2.9.13 新增）＝除"我这一员"以外都算——同一个席位上的别的将也算，不只算别人席位的；听敌方（其他席位）（v2.9.13 新增）＝别的玩家席位出事才算，自家席位的别的将不算；听场上（所有玩家）＝谁的席位出事都算听到。Excel 里它是自己的一列（技能级「我听谁」＋每个效果「效果N我听谁」），不写在触发时机那句话里，跟"技能门槛／效果N门槛"那两列一个摆法。不填＝只听自己，与今天对局逐字一致。两个实话：①手牌、回合这类事本来就记在玩家身上，所以这类时机里"只听自己"与"听己方（同一席位）"是同一回事；②"回合结束时、其他玩家登场时、技能失效时、营地受到伤害时、其他将领技能发动时"这几类不认这一栏——填了会按没填处理并在导入总结里点名，不会静悄悄收下。营地那一格与"其他将领技能发动时"这两格更彻底：前者因为营地不是任何一员将、"我听谁的营地"这一维压根没有；后者因为它的名号已经替您说清了听谁＝除自己以外的将（同一个席位上的别的将也算），所以再让您挑一遍只会挑出矛盾。这两类被选中后，界面上「我听谁」那一行直接消失（不是灰着，也不是留着让您填）。卡面上您那套说法也认得（v2.9.13 起，只有"登场"这一格）：您写的「其他角色＝自身以外、己方角色＝包括自身的己方玩家的角色、敌方角色＝己方玩家外的所有玩家的角色」就是上面这三档，自己写效果时那句定语照您的写法打进来即可（拼法全库只有一处，界面里那句提示是现拼的，不是另抄一份）。注意"敌方"这里按席位算，不按魏蜀吴群那种势力算（您 2026-10-18 那两句原话就是这么划的：「敌方角色＝己方玩家外的所有玩家的角色」）。</t>
   </si>
   <si>
     <t>细分（伤害类型／被谁指名／击杀对象／卡牌时机／失效条件）</t>
@@ -1032,7 +1032,7 @@
     <t>自己写效果（v2.9.9 起）</t>
   </si>
   <si>
-    <t>技能卡片上「✍️ 自己写效果（一句话生成积木）」那一格：您用大白话写，系统替您反推成上面那三格积木，先给您看它打算怎么说，您点头才进格子（不点头什么都不会变），点「✔ 采用」后就是原来的拼积木界面，逐条改即可。写的是一行一段、句号分开；以下择一／以下依次生效 两句当头一句写，就按"选择其一"／"链式"登记；要满足手牌≤2 写在最前面＝整组门槛、写在某条时机后面＝那一条自己的门槛。认得的说法＝词表里那十二档动作与三档对象，中文数字（两、十二）与阿拉伯数字同解，「全部」＝整只手，观顶3张「拆掉 1 张装备卡」这类旧行话也照旧读得懂（只进不出）。读不懂的绝不猜、也没有一段是悄悄丢掉的：哪一段不支持就原文点出来＋一句照着改得动的理由（例："这一句要作用在'别人'身上……想让别的玩家执行的那类内容还没做出来"、"若…则…请改写「以下依次生效」"、"限定技是徽章，去徽章那一格勾"）。⚠️ 退回看这一段写在动作的哪一边，因为两句话的意思不一样：写在动作前面＝它正在给这个动作补"对谁／在什么前提下做"⇒这一条整条退回（只收动作那半＝做成另一件事）；写在动作后面＝像是第二件事⇒前面那件读懂的照做、后面这段单独点名并教您另起一句（一段只认一件事，第二件不顶掉第一件）。⚠️ 两种"不支持"也分开了：① 形状写错了 ⇒ 那一条不生成；② 格子有、引擎还没接线（例如下拉里那些还没上事件面的时机） ⇒ 照样生成、也能采用，但界面当场说一句"这条今天不会响"。这一格没有大模型、不联网，纯离线词表；能不能编出结算问的是编译器那一支自己（skillCompiler.judgeSkillEffect，反解侧与真编译路共用同一判据，不可能两边各说一套）。反解侧＝src/skills/skillTextParse.ts，界面＝src/components/skillEditor/SkillTextPanel.tsx；两侧由 skillTextParse.test.ts 的往返钉钉住（生成的那句再解回去、再生成 ⇒ 逐字同一句）。v2.9.13 这一格新认得的两样：①「将领登场时」这一档多了您那三句定语——其他角色登场时／己方角色登场时／敌方角色登场时（加上自身登场时与场上所有角色登场时一共五种写法），拼出来的都是上面「我听谁」那五档里的同一档，拼法全库只有一处（data/generals.ts 那张对照表），界面提示与这句反解都从它现取，不会各写一份；②其他角色摸两张牌这类用词写错的句子，现在走的是"这一句的说法本作不成立"那一档理由，并给您一句改得动的写法（详见上面「角色 / 玩家」那一行）——它跟"内容还没做出来"是两回事，分开点名。</t>
+    <t>技能卡片上「✍️ 自己写效果（一句话生成积木）」那一格：您用大白话写，系统替您反推成上面那三格积木，先给您看它打算怎么说，您点头才进格子（不点头什么都不会变），点「✔ 采用」后就是原来的拼积木界面，逐条改即可。写的是一行一段、句号分开；以下择一／以下依次生效 两句当头一句写，就按"选择其一"／"链式"登记；要满足手牌≤2 写在最前面＝整组门槛、写在某条时机后面＝那一条自己的门槛。认得的说法＝词表里那十二档动作与三档对象，中文数字（两、十二）与阿拉伯数字同解，「全部」＝整只手，观顶3张「拆掉 1 张装备卡」这类旧行话也照旧读得懂（只进不出）。读不懂的绝不猜、也没有一段是悄悄丢掉的：哪一段不支持就原文点出来＋一句照着改得动的理由（例："这一句要作用在'别人'身上……想让别的玩家执行的那类内容还没做出来"、"若…则…请改写「以下依次生效」"、"限定技是徽章，去徽章那一格勾"）。⚠️ 退回看这一段写在动作的哪一边，因为两句话的意思不一样：写在动作前面＝它正在给这个动作补"对谁／在什么前提下做"⇒这一条整条退回（只收动作那半＝做成另一件事）；写在动作后面＝像是第二件事⇒前面那件读懂的照做、后面这段单独点名并教您另起一句（一段只认一件事，第二件不顶掉第一件）。⚠️ 两种"不支持"也分开了：① 形状写错了 ⇒ 那一条不生成；② 格子有、引擎还没接线（例如下拉里那些还没上事件面的时机） ⇒ 照样生成、也能采用，但界面当场说一句"这条今天不会响"。这一格没有大模型、不联网，纯离线词表；能不能编出结算问的是编译器那一支自己（skillCompiler.judgeSkillEffect，反解侧与真编译路共用同一判据，不可能两边各说一套）。反解侧＝src/skills/skillTextParse.ts，界面＝src/components/skillEditor/SkillTextPanel.tsx；两侧由 skillTextParse.test.ts 的往返钉钉住（生成的那句再解回去、再生成 ⇒ 逐字同一句）。v2.9.13 这一格新认得的两样：①「将领登场时」这一档多了您那三句定语——其他角色登场时／己方角色登场时／敌方角色登场时（加上自身登场时与场上所有角色登场时一共五种写法），拼出来的都是上面「我听谁」那五档里的同一档，拼法全库只有一处（data/generals.ts 那张对照表），界面提示与这句反解都从它现取，不会各写一份；②其他角色摸两张牌这类用词写错的句子，现在走的是"这一句的说法本作不成立"那一档理由，并给您一句改得动的写法（详见上面「角色 / 玩家」那一行）——它跟"内容还没做出来"是两回事，分开点名。v2.9.15 这一格又多认一句：其他将领技能发动时，摸一张牌。（时机名与上面下拉那一格逐字同一份词表）现在照生成、照能采用，上一版挂在它那句"这条今天不会响"的提示随接线自行消失——这句提示不是写死在界面上的，它是问编译器"这一条到底编不编得出来"，所以哪天接上电它就自己没了。</t>
   </si>
   <si>
     <t>有效周期（这笔账什么时候结束）</t>

--- a/词汇表.xlsx
+++ b/词汇表.xlsx
@@ -870,7 +870,7 @@
     <t>强制发动</t>
   </si>
   <si>
-    <t>编辑器里的开关（Excel 也有这一列）：满足触发条件与代价后直接响／直接适用效果，不用玩家点头。它跟锁定技不是一件事，跟"数值变化／持续生效"也不绑定，三者可以任意组合。v2.8.25 起这一格真的管事了：勾上之后，凡是本来会停下来问您"要不要发动"的那一刻（＝成为目标时／受到伤害后这两型），这条技能不再问、自己就响了；不勾就照旧问。四句实话边界：①它只决定"问不问人"，不会让一条技能多响一次，也不绕过发动门槛与代价；②本来就到点自动响的时机（登场／回合开始／击杀／失去手牌……）勾不勾都一样（v2.9.3 起唯一一条例外：同一条技能挂了「觉醒技」徽章时，这些时机改成停下来问您一次，勾了才自己响）；③「回合结束时」那一型永远要您点头（一条技能不许响两次的常设规矩），勾了也不自响；④决斗那一套的"开局被点名"与"收官掉血"两刻同样吃这一格——勾了就自己响、没勾就问；⑤v2.8.31 起它与"不勾"完全同一条时机判据（您 2026-10-04 定稿：强制发动和手动发动的处理必须一致，区别只在"需不需要玩家自行响应"）——被这一刀砍死时，勾了的「成为目标时」照样响、勾了的「受到伤害后」照样不响，与没勾时问您那一型逐字同形（只有「自身被击杀时」那一型放行）。今天的官方 96 将与您手上的样本卡还没有一条勾了这个开关（v2.9.6 新上的「单骑」也没勾——它停下来问您靠的是上面「觉醒技」那一枚，不是这一格），所以对局里的表现与上一版逐字相同。</t>
+    <t>编辑器里的开关（Excel 也有这一列）：满足触发条件与代价后直接响／直接适用效果，不用玩家点头。它跟锁定技不是一件事，跟"数值变化／持续生效"也不绑定，三者可以任意组合。v2.8.25 起这一格真的管事了，v2.9.16 起它管的是全部时机（您 2026-10-20 裁："在场即生效和强制发动不问"）：勾上之后，凡是本来会停下来问您"要不要发动"的那一刻，这条技能不再问、自己就响了；不勾就照旧问——而且今天每一型都会问。五句实话边界：①它只决定"问不问人"，不会让一条技能多响一次，也不绕过发动门槛与代价；②本来就到点自动响的时机（登场／回合开始／击杀／失去手牌……）勾不勾都一样（旧说法，已作废）（这句自 v2.9.16 作废：这些时机今天照样停下来问您，勾了才自己响；「在场即生效」那一型是唯一一个根本不存在"响"这一刻的，它不吃这一格，也不会有人来问）；③「回合结束时」那一型走的是它自己那个窗（一条技能不许响两次的常设规矩），所以它勾了也照样问——这一条跟您"强制发动不问"那句正面相撞，本轮没有擅自改，已立案等您裁（裁决与判据＝PROJECT_HANDOFF.md §12）；④决斗那一套的"开局被点名"与"收官掉血"两刻同样吃这一格——勾了就自己响、没勾就问；⑤v2.8.31 起它与"不勾"完全同一条时机判据（您 2026-10-04 定稿：强制发动和手动发动的处理必须一致，区别只在"需不需要玩家自行响应"）——被这一刀砍死时，勾了的「成为目标时」照样响、勾了的「受到伤害后」照样不响，与没勾时问您那一型逐字同形（只有「自身被击杀时」那一型放行）。这一刀改了您对局里看到的东西：今天的官方 96 将与您手上的样本卡还没有一条勾了这个开关（v2.9.6 新上的「单骑」也没勾——它停下来问您靠的是上面「觉醒技」那一枚，不是这一格），所以从这一版起，只要桌上有人挂着会响的技能，那一刻就会停下来问他；哪一枚您想让它到点自己响，就去把那一枚的这格勾上。</t>
   </si>
   <si>
     <t>触发时机</t>
@@ -882,7 +882,7 @@
     <t>回合开始时 / 回合结束时 / 将领登场时 / 受到伤害后 / 造成伤害后 / 成为目标时 / 击杀将领时 / 自身被击杀时 / 失去手牌时 / 获得手牌时 / 营地受到伤害时 / 其他将领技能发动时</t>
   </si>
   <si>
-    <t>十二种"哪一刻响"的说法，字面就是那件事发生的时刻。（"成为攻击目标时"这个旧名字 v2.8.21 起改成了泛指的"成为目标时"，具体被谁指名交给下面那一格说。）「受到伤害后」的判据（v2.8 刀5 起，您 2026-10-03 重新裁定）＝只有真的掉了体力才算受到了伤害：这一刀被护甲全挡住、一点血没掉 ⇒ 不算受到，技能不问也不响；伤害算出来是 0 或负数 ⇒ 也不算。掉多少算多少：普攻／技能伤害每一刀各算一声；决斗那一整场只在打完时按"这个将一共掉了多少体力"算一笔（见上面「决斗」那一格）。被这一刀打死的那一位，两类里只有「受到伤害后」不算（v2.8.31 定稿＝您 2026-10-04 把两类的定义封死：「成为目标时」＝受击，它在伤害算出来之前就发动完了，所以和这一刀实际打多少、主人会不会被这一刀砍死无关——被砍死的那一刀里它照样问、照样响；「受到伤害后」＝受伤，必须真的掉了血才成立，所以它在伤害之后才问，主人死在这一刀里就不问也不响）。两条路的判据一模一样，区别只在"需不需要您自己点头"。追加的那一条（甲）也在这里生效：反伤先把出手的那位扎死了⇒那一刀跟着取消，挨打的那位自救成功，粮草也没被吃掉。唯一的豁口＝「自身被击杀时」那一型（遗言／遗计）：它按定义就是在主人离场这一声上发动，所以两边都放行，牌照旧摸进手。最后那一格（营地受到伤害时）是 v2.9.14 才接上电的（您 2026-10-18 定"先做「营地受到伤害时」"）：它听的是营地那一格掉了血这一声，判据跟上面同一句——只有真的掉了体力才算受到伤害，那一刀被挡光、一点没掉⇒不算、不响。三句实话：①它只认自家那一席的营地，别人家营地掉血不算（营地不是任何一员将，所以"我听谁的营地"这一维今天没有做，界面上那一格下拉对这一型直接不出现，从旧 Excel 硬塞一格进来会被点名跳过、不静悄悄当成"只听自家"）；②它到点自己响，不停下来问您（跟登场／回合开始同一类，跟「受到伤害后」要点头那一类不同），勾不勾「强制发动」都一样；③另两格营地系的说法「营地成为攻击目标时」「营地成为技能目标时」还是没接线（那两声身上没带"这是哪一席的营地"这个记号，接了就是瞎响），下拉里点得到、界面照旧会当场写明它今天不会响。顺带修掉一条老毛病：v2.8.21 给「受到伤害后」加上"听别人"那几档之后，自家营地掉血也曾被它当成"受到了伤害"（那几档不比是哪一员将，营地那一身就顺着席位混进来了）⇒ 本轮起「受到伤害后」只管人、营地交给这一格。最后这一格（其他将领技能发动时）是 v2.9.15 才接上电的（您 2026-10-18 那句"做完「营地受到伤害时」就做「别人使用技能时」"）：它听的是某一枚技能真的发动了一次那一声。四句实话：①这一声过去只有"一局一次"那种带额度的技能才会留下记录，而且只记在台账里、不外传⇒本轮把"发动公告"改成每次真发动都出声，普通技能那一身不带台账键＝牌桌状态一个字都不动（所以对局里多出来的只是声音，两锚因此逐字没挪）；②"什么算别人"用的是上一刀那同一根轴（席位＋将领两维一起看，同一个席位上的别的将也算），没有另抄一份判据；③套娃只传一层＝由这一声引起的发动，自己再公告时身上带一个"我是被这一声叫起来的"记号，这一格听见这个记号就闭嘴——不然两员"别人发动我就摸牌"的能把彼此的牌堆摸穿；④空发不出声（那一条什么都没做成的发动不算发动，跟"没发动成功不消耗额度"是同一句诚实），而且它到点自己响、绝不停下来问您，跟营地那一格、登场／回合开始同一类。判据与取证＝PROJECT_HANDOFF.md §12-100／§12-101／§12-102／§12-130／§12-131。</t>
+    <t>十二种"哪一刻响"的说法，字面就是那件事发生的时刻。（"成为攻击目标时"这个旧名字 v2.8.21 起改成了泛指的"成为目标时"，具体被谁指名交给下面那一格说。）「受到伤害后」的判据（v2.8 刀5 起，您 2026-10-03 重新裁定）＝只有真的掉了体力才算受到了伤害：这一刀被护甲全挡住、一点血没掉 ⇒ 不算受到，技能不问也不响；伤害算出来是 0 或负数 ⇒ 也不算。掉多少算多少：普攻／技能伤害每一刀各算一声；决斗那一整场只在打完时按"这个将一共掉了多少体力"算一笔（见上面「决斗」那一格）。被这一刀打死的那一位，两类里只有「受到伤害后」不算（v2.8.31 定稿＝您 2026-10-04 把两类的定义封死：「成为目标时」＝受击，它在伤害算出来之前就发动完了，所以和这一刀实际打多少、主人会不会被这一刀砍死无关——被砍死的那一刀里它照样问、照样响；「受到伤害后」＝受伤，必须真的掉了血才成立，所以它在伤害之后才问，主人死在这一刀里就不问也不响）。两条路的判据一模一样，区别只在"需不需要您自己点头"。追加的那一条（甲）也在这里生效：反伤先把出手的那位扎死了⇒那一刀跟着取消，挨打的那位自救成功，粮草也没被吃掉。唯一的豁口＝「自身被击杀时」那一型（遗言／遗计）：它按定义就是在主人离场这一声上发动，所以两边都放行，牌照旧摸进手。最后那一格（营地受到伤害时）是 v2.9.14 才接上电的（您 2026-10-18 定"先做「营地受到伤害时」"）：它听的是营地那一格掉了血这一声，判据跟上面同一句——只有真的掉了体力才算受到伤害，那一刀被挡光、一点没掉⇒不算、不响。三句实话：①它只认自家那一席的营地，别人家营地掉血不算（营地不是任何一员将，所以"我听谁的营地"这一维今天没有做，界面上那一格下拉对这一型直接不出现，从旧 Excel 硬塞一格进来会被点名跳过、不静悄悄当成"只听自家"）；②它到点自己响，不停下来问您（跟登场／回合开始同一类，跟「受到伤害后」要点头那一类不同），勾不勾「强制发动」都一样（旧说法，已作废）（这句自 v2.9.16 作废：跟「受到伤害后」同一类＝停下来问您，勾了「强制发动」才自己响）；③另两格营地系的说法「营地成为攻击目标时」「营地成为技能目标时」还是没接线（那两声身上没带"这是哪一席的营地"这个记号，接了就是瞎响），下拉里点得到、界面照旧会当场写明它今天不会响。顺带修掉一条老毛病：v2.8.21 给「受到伤害后」加上"听别人"那几档之后，自家营地掉血也曾被它当成"受到了伤害"（那几档不比是哪一员将，营地那一身就顺着席位混进来了）⇒ 本轮起「受到伤害后」只管人、营地交给这一格。最后这一格（其他将领技能发动时）是 v2.9.15 才接上电的（您 2026-10-18 那句"做完「营地受到伤害时」就做「别人使用技能时」"）：它听的是某一枚技能真的发动了一次那一声。四句实话：①这一声过去只有"一局一次"那种带额度的技能才会留下记录，而且只记在台账里、不外传⇒本轮把"发动公告"改成每次真发动都出声，普通技能那一身不带台账键＝牌桌状态一个字都不动（所以对局里多出来的只是声音，两锚因此逐字没挪）；②"什么算别人"用的是上一刀那同一根轴（席位＋将领两维一起看，同一个席位上的别的将也算），没有另抄一份判据；③套娃只传一层＝由这一声引起的发动，自己再公告时身上带一个"我是被这一声叫起来的"记号，这一格听见这个记号就闭嘴——不然两员"别人发动我就摸牌"的能把彼此的牌堆摸穿；④空发不出声（那一条什么都没做成的发动不算发动，跟"没发动成功不消耗额度"是同一句诚实），而且它到点自己响、绝不停下来问您，跟营地那一格、登场／回合开始同一类（旧说法，已作废）（这句自 v2.9.16 作废：跟营地那一格、登场／回合开始同一类＝没勾就问、勾了才自己响）。判据与取证＝PROJECT_HANDOFF.md §12-100／§12-101／§12-102／§12-130／§12-131。</t>
   </si>
   <si>
     <t>在场即生效（不用发动，人在就算）（v2.8 刀4 起可结算）</t>
@@ -1059,7 +1059,7 @@
     <t>（旧说法，已作废）击破横幅上方那行残留的英文小字，v2.8.18 已翻成中文，v2.8.39 起那里写的是「营地击破」。</t>
   </si>
   <si>
-    <t>本节末尾必须说清的一件事：五个"××技"徽章和"强制发动"这一列，v2.8.19 起读得到、写得出、显示得出、还能核对（一枚技能可挂几枚；徽章与触发时机对不上会在编辑器与导入总结里点名）。这两样如今落地程度不同：「强制发动」v2.8.25 起接进对局了——全库只有一个地方读它（skills/SkillTriggerBridge.ts 的 defersToReactionQueue：受击／受伤这两型里没打勾的定义才交给问答队列问人，打了勾的直接走自动发动那条路；v2.9.3 起这一处还多认一枚徽章——挂了「觉醒技」的技能没打勾时同样停下来问您，打了勾就照旧自己响），所以它管的事恰恰只有一件＝"这一刻问不问您"；徽章里「锁定技」v2.8 刀4 起有了第一个结算侧的消费者，但只管一寸地方：编译器认出这枚徽章 → 这条技能往数值账本落的那笔账打上"移不走"的记号（statModifiers.revokeModifier 是全库唯一"移走别人那笔账"的入口，它见到这个记号就拒绝）。徽章的其余部分（"不能被无效""不能被改变"在伤害、护甲、被弃牌这些环节到底管不管）今天仍然没有任何结算代码读它；四枚徽章里限定技自 v2.8.32 起有了第二个结算侧消费者（编译器认出它 ⇒ 这枚技能每发动一次就在同一本账上落一笔，账上有这一笔就不再让它发动；"一局一次"的判据与记账形状全库只有一份＝skills/skillQuota.ts，三条发动路——回合结束、停下问您、到点自己响——都从这里过），登场／遗计还是纯分类，而「觉醒技」自 v2.9.3 起也有了结算侧消费者：编译器认出这枚徽章后同时发生两件事——这枚技能听的那一声从"到点自己响"搬进"停下来问您一次"的队列，并且它与限定技共用同一本一局一次的账（摇头不算发动、不扣这笔账）。所以现在决定一条技能"什么时候响、响不响、响几次"的是：触发时机（含细分）＋「我听谁」这一档监听范围（五档，v2.8.21 起三档、v2.9.13 起五档；触发桥逐条读；缺省＝只听自己，⇒ 与今天对局逐字一致。「被谁指名」那一档＝成为目标时的细分，另算一维（"成为技能目标"这一声 v2.8.24 起已有发射器＝决斗开局，其余技能指名目标的路仍未发这一声，等内容刀））＋ 发动门槛 ＋ 那条"每回合限一次"的账 ＋ 限定技与觉醒技"一局一次"的同一本账（v2.8.32 起／v2.9.3 起）＋「强制发动」这一格（v2.8.25 起，只管问不问人；v2.9.3 起它对觉醒技同样管用——勾了就不问、到点自己结算）。「在场即生效」那一型不看上面这些，它只在登场／离场两刻动账本。徽章的读写口径全库只有一份，在 domain/skillTags.ts。</t>
+    <t>本节末尾必须说清的一件事：五个"××技"徽章和"强制发动"这一列，v2.8.19 起读得到、写得出、显示得出、还能核对（一枚技能可挂几枚；徽章与触发时机对不上会在编辑器与导入总结里点名）。这两样如今落地程度不同：「强制发动」v2.8.25 起接进对局了——全库只有一个地方读它（skills/SkillTriggerBridge.ts 的 defersToReactionQueue：v2.9.16 起是"每一型"——凡是听得懂至少一声的时机里没打勾的定义都交给问答队列问人，打了勾的直接走自动发动那条路；「在场即生效」压根不监听任何一声，所以它既不会被问也不会自己响；v2.9.3 起这一处还多认一枚徽章——挂了「觉醒技」的技能没打勾时同样停下来问您，打了勾就照旧自己响），所以它管的事恰恰只有一件＝"这一刻问不问您"；徽章里「锁定技」v2.8 刀4 起有了第一个结算侧的消费者，但只管一寸地方：编译器认出这枚徽章 → 这条技能往数值账本落的那笔账打上"移不走"的记号（statModifiers.revokeModifier 是全库唯一"移走别人那笔账"的入口，它见到这个记号就拒绝）。徽章的其余部分（"不能被无效""不能被改变"在伤害、护甲、被弃牌这些环节到底管不管）今天仍然没有任何结算代码读它；四枚徽章里限定技自 v2.8.32 起有了第二个结算侧消费者（编译器认出它 ⇒ 这枚技能每发动一次就在同一本账上落一笔，账上有这一笔就不再让它发动；"一局一次"的判据与记账形状全库只有一份＝skills/skillQuota.ts，三条发动路——回合结束、停下问您、到点自己响——都从这里过），登场／遗计还是纯分类，而「觉醒技」自 v2.9.3 起也有了结算侧消费者：编译器认出这枚徽章后同时发生两件事——这枚技能听的那一声从"到点自己响"搬进"停下来问您一次"的队列，并且它与限定技共用同一本一局一次的账（摇头不算发动、不扣这笔账）。所以现在决定一条技能"什么时候响、响不响、响几次"的是：触发时机（含细分）＋「我听谁」这一档监听范围（五档，v2.8.21 起三档、v2.9.13 起五档；触发桥逐条读；缺省＝只听自己，⇒ 与今天对局逐字一致。「被谁指名」那一档＝成为目标时的细分，另算一维（"成为技能目标"这一声 v2.8.24 起已有发射器＝决斗开局，其余技能指名目标的路仍未发这一声，等内容刀））＋ 发动门槛 ＋ 那条"每回合限一次"的账 ＋ 限定技与觉醒技"一局一次"的同一本账（v2.8.32 起／v2.9.3 起）＋「强制发动」这一格（v2.8.25 起，只管问不问人；v2.9.3 起它对觉醒技同样管用——勾了就不问、到点自己结算）。「在场即生效」那一型不看上面这些，它只在登场／离场两刻动账本。徽章的读写口径全库只有一份，在 domain/skillTags.ts。</t>
   </si>
   <si>
     <t>游戏结束 / 对局结束</t>

--- a/词汇表.xlsx
+++ b/词汇表.xlsx
@@ -37,7 +37,7 @@
     <t>· 出处：所有词条都对应到 文件:行号（仓库根＝Qoder/2.0）。规则类翻译另标了"定规则的代码在哪"，方便日后核对。</t>
   </si>
   <si>
-    <t>· 已知坑：第八节那十条"界面这么说、代码这么算"的冲突，第 1～8 条与第 10 条已经对齐（v2.8.14／v2.8.18）；第 9 条自 v2.8.25 起拆成两半——「强制发动」那一半已经进引擎（勾了就不问玩家、到点自己响），徽章那一半：限定技的"一局一次"自 v2.8.32 起已经进引擎（见第四节「限定技」那一格），锁定技的"不能被无效"仍只是分类（引擎里压根没有"无效技能"这套机制，没有可以 enforcement 的对象）；已作废的旧写法在表里用 ~~删除线~~ 标出，投影进 Excel 时会渲染成"（旧说法，已作废）"。</t>
+    <t>· 已知坑：第八节那十条"界面这么说、代码这么算"的冲突，第 1～8 条与第 10 条已经对齐（v2.8.14／v2.8.18）；第 9 条自 v2.8.25 起拆成两半——「强制发动」那一半已经进引擎（勾了就不问玩家、到点自己响；v2.9.16 起管到每一型，v2.9.17 起连「回合结束时」那扇窗也不问），徽章那一半：限定技的"一局一次"自 v2.8.32 起已经进引擎（见第四节「限定技」那一格），锁定技的"不能被无效"仍只是分类（引擎里压根没有"无效技能"这套机制，没有可以 enforcement 的对象）；已作废的旧写法在表里用 ~~删除线~~ 标出，投影进 Excel 时会渲染成"（旧说法，已作废）"。</t>
   </si>
   <si>
     <t>· 本轮之后如果界面改词，这张表要跟着改；它随 Git 走，别在别处另抄一份。</t>
@@ -444,7 +444,7 @@
     <t>🌙 回合结束询问 · 是否发动将领技能？</t>
   </si>
   <si>
-    <t>回合收尾时问你一句：这些"回合结束时"技能要不要现在用。问不问、列不列不能发动的，由对局设置里的「技能提示」两档决定（见 §六）。</t>
+    <t>回合收尾时问你一句：这些"回合结束时"技能要不要现在用。问不问、列不列不能发动的，由对局设置里的「技能提示」两档决定（见 §六）。v2.9.17 起勾了「强制发动」的那几枚不进这扇窗（您 2026-10-21 裁："强制发动永远是强制发动，无论什么节点"）：点「⏭️结束回合」的那一刻，系统先在同一条规范动作里替您把它们发动完（照样飘 ⚡ 小广播、照样记"这回合已用过"那笔账），窗里只剩没勾的那些；一员都没勾就压根不开这扇窗，回合直接结束。</t>
   </si>
   <si>
     <t>🚫 都不发动</t>
@@ -498,7 +498,7 @@
     <t>⚡ {将名}【{技能名}】</t>
   </si>
   <si>
-    <t>技能响了一下的小广播，下面那行是它干了什么。</t>
+    <t>技能响了一下的小广播，下面那行是它干了什么。v2.9.17 起这一条是一条硬义务（您 2026-10-21 裁："强制发动永远是强制发动，无论什么节点，但是一定要通知玩家有什么技能发动了"）：三条发动路——您点头发动的、到点自己响的、回合结束那一刻系统替您发动的——每一次真的发动都要飘出这一条；勾了「强制发动」的不问您，但照样飘。约 3 秒后自己散，它只是给您看的，不进牌桌、不进录像。</t>
   </si>
   <si>
     <t>⚔️ 开始行动</t>
@@ -870,7 +870,7 @@
     <t>强制发动</t>
   </si>
   <si>
-    <t>编辑器里的开关（Excel 也有这一列）：满足触发条件与代价后直接响／直接适用效果，不用玩家点头。它跟锁定技不是一件事，跟"数值变化／持续生效"也不绑定，三者可以任意组合。v2.8.25 起这一格真的管事了，v2.9.16 起它管的是全部时机（您 2026-10-20 裁："在场即生效和强制发动不问"）：勾上之后，凡是本来会停下来问您"要不要发动"的那一刻，这条技能不再问、自己就响了；不勾就照旧问——而且今天每一型都会问。五句实话边界：①它只决定"问不问人"，不会让一条技能多响一次，也不绕过发动门槛与代价；②本来就到点自动响的时机（登场／回合开始／击杀／失去手牌……）勾不勾都一样（旧说法，已作废）（这句自 v2.9.16 作废：这些时机今天照样停下来问您，勾了才自己响；「在场即生效」那一型是唯一一个根本不存在"响"这一刻的，它不吃这一格，也不会有人来问）；③「回合结束时」那一型走的是它自己那个窗（一条技能不许响两次的常设规矩），所以它勾了也照样问——这一条跟您"强制发动不问"那句正面相撞，本轮没有擅自改，已立案等您裁（裁决与判据＝PROJECT_HANDOFF.md §12）；④决斗那一套的"开局被点名"与"收官掉血"两刻同样吃这一格——勾了就自己响、没勾就问；⑤v2.8.31 起它与"不勾"完全同一条时机判据（您 2026-10-04 定稿：强制发动和手动发动的处理必须一致，区别只在"需不需要玩家自行响应"）——被这一刀砍死时，勾了的「成为目标时」照样响、勾了的「受到伤害后」照样不响，与没勾时问您那一型逐字同形（只有「自身被击杀时」那一型放行）。这一刀改了您对局里看到的东西：今天的官方 96 将与您手上的样本卡还没有一条勾了这个开关（v2.9.6 新上的「单骑」也没勾——它停下来问您靠的是上面「觉醒技」那一枚，不是这一格），所以从这一版起，只要桌上有人挂着会响的技能，那一刻就会停下来问他；哪一枚您想让它到点自己响，就去把那一枚的这格勾上。</t>
+    <t>编辑器里的开关（Excel 也有这一列）：满足触发条件与代价后直接响／直接适用效果，不用玩家点头。它跟锁定技不是一件事，跟"数值变化／持续生效"也不绑定，三者可以任意组合。v2.8.25 起这一格真的管事了，v2.9.16 起它管的是全部时机（您 2026-10-20 裁："在场即生效和强制发动不问"）：勾上之后，凡是本来会停下来问您"要不要发动"的那一刻，这条技能不再问、自己就响了；不勾就照旧问——而且今天每一型都会问。五句实话边界：①它只决定"问不问人"，不会让一条技能多响一次，也不绕过发动门槛与代价；②本来就到点自动响的时机（登场／回合开始／击杀／失去手牌……）勾不勾都一样（旧说法，已作废）（这句自 v2.9.16 作废：这些时机今天照样停下来问您，勾了才自己响；「在场即生效」那一型是唯一一个根本不存在"响"这一刻的，它不吃这一格，也不会有人来问）；③「回合结束时」那一型自 v2.9.17 起也吃这一格（您 2026-10-21 裁："强制发动永远是强制发动，无论什么节点，但是一定要通知玩家有什么技能发动了"）：勾了的不进那扇问话窗——点「⏭️结束回合」那一刻由系统在同一条规范动作里替这一席发动完，再开窗问剩下的；一员都没勾就压根不开窗。旧的"勾了也照样问"（v2.3.1 起那一版逢人就问）自本版作废，因为它跟您那句正面相撞；这条裁决有真机对照＝同一张牌桌、同一个位置，两员只差这一格勾没勾，勾了的没开窗、没勾的照旧开窗；④决斗那一套的"开局被点名"与"收官掉血"两刻同样吃这一格——勾了就自己响、没勾就问；⑤v2.8.31 起它与"不勾"完全同一条时机判据（您 2026-10-04 定稿：强制发动和手动发动的处理必须一致，区别只在"需不需要玩家自行响应"）——被这一刀砍死时，勾了的「成为目标时」照样响、勾了的「受到伤害后」照样不响，与没勾时问您那一型逐字同形（只有「自身被击杀时」那一型放行）。这一刀改了您对局里看到的东西：今天的官方 96 将与您手上的样本卡还没有一条勾了这个开关（v2.9.6 新上的「单骑」也没勾——它停下来问您靠的是上面「觉醒技」那一枚，不是这一格），所以从这一版起，只要桌上有人挂着会响的技能，那一刻就会停下来问他；哪一枚您想让它到点自己响，就去把那一枚的这格勾上。v2.9.17 两条配套硬义务（您同日的两句）：①这一格由您自己勾＝"哪些官方卡是强制发动，这部分由我自己来填写"⇒官方 96 将与您手上的样本卡到今天仍然一枚都没勾，我不往任何卡面上加这一格；②不问可以、看不见不行＝凡是真发动了（包括系统替您发动那一路），界面左上角当场飘一条 ⚡ 小广播，写清是谁的哪一枚、干了什么。</t>
   </si>
   <si>
     <t>触发时机</t>
@@ -1059,7 +1059,7 @@
     <t>（旧说法，已作废）击破横幅上方那行残留的英文小字，v2.8.18 已翻成中文，v2.8.39 起那里写的是「营地击破」。</t>
   </si>
   <si>
-    <t>本节末尾必须说清的一件事：五个"××技"徽章和"强制发动"这一列，v2.8.19 起读得到、写得出、显示得出、还能核对（一枚技能可挂几枚；徽章与触发时机对不上会在编辑器与导入总结里点名）。这两样如今落地程度不同：「强制发动」v2.8.25 起接进对局了——全库只有一个地方读它（skills/SkillTriggerBridge.ts 的 defersToReactionQueue：v2.9.16 起是"每一型"——凡是听得懂至少一声的时机里没打勾的定义都交给问答队列问人，打了勾的直接走自动发动那条路；「在场即生效」压根不监听任何一声，所以它既不会被问也不会自己响；v2.9.3 起这一处还多认一枚徽章——挂了「觉醒技」的技能没打勾时同样停下来问您，打了勾就照旧自己响），所以它管的事恰恰只有一件＝"这一刻问不问您"；徽章里「锁定技」v2.8 刀4 起有了第一个结算侧的消费者，但只管一寸地方：编译器认出这枚徽章 → 这条技能往数值账本落的那笔账打上"移不走"的记号（statModifiers.revokeModifier 是全库唯一"移走别人那笔账"的入口，它见到这个记号就拒绝）。徽章的其余部分（"不能被无效""不能被改变"在伤害、护甲、被弃牌这些环节到底管不管）今天仍然没有任何结算代码读它；四枚徽章里限定技自 v2.8.32 起有了第二个结算侧消费者（编译器认出它 ⇒ 这枚技能每发动一次就在同一本账上落一笔，账上有这一笔就不再让它发动；"一局一次"的判据与记账形状全库只有一份＝skills/skillQuota.ts，三条发动路——回合结束、停下问您、到点自己响——都从这里过），登场／遗计还是纯分类，而「觉醒技」自 v2.9.3 起也有了结算侧消费者：编译器认出这枚徽章后同时发生两件事——这枚技能听的那一声从"到点自己响"搬进"停下来问您一次"的队列，并且它与限定技共用同一本一局一次的账（摇头不算发动、不扣这笔账）。所以现在决定一条技能"什么时候响、响不响、响几次"的是：触发时机（含细分）＋「我听谁」这一档监听范围（五档，v2.8.21 起三档、v2.9.13 起五档；触发桥逐条读；缺省＝只听自己，⇒ 与今天对局逐字一致。「被谁指名」那一档＝成为目标时的细分，另算一维（"成为技能目标"这一声 v2.8.24 起已有发射器＝决斗开局，其余技能指名目标的路仍未发这一声，等内容刀））＋ 发动门槛 ＋ 那条"每回合限一次"的账 ＋ 限定技与觉醒技"一局一次"的同一本账（v2.8.32 起／v2.9.3 起）＋「强制发动」这一格（v2.8.25 起，只管问不问人；v2.9.3 起它对觉醒技同样管用——勾了就不问、到点自己结算）。「在场即生效」那一型不看上面这些，它只在登场／离场两刻动账本。徽章的读写口径全库只有一份，在 domain/skillTags.ts。</t>
+    <t>本节末尾必须说清的一件事：五个"××技"徽章和"强制发动"这一列，v2.8.19 起读得到、写得出、显示得出、还能核对（一枚技能可挂几枚；徽章与触发时机对不上会在编辑器与导入总结里点名）。这两样如今落地程度不同：「强制发动」v2.8.25 起接进对局了——全库只有两处读它（①skills/SkillTriggerBridge.ts 的 defersToReactionQueue：v2.9.16 起是"每一型"——凡是听得懂至少一声的时机里没打勾的定义都交给问答队列问人，打了勾的直接走自动发动那条路；「在场即生效」压根不监听任何一声，所以它既不会被问也不会自己响；v2.9.3 起这一处还多认一枚徽章——挂了「觉醒技」的技能没打勾时同样停下来问您，打了勾就照旧自己响；②v2.9.17 起新增skills/turnEndSkills.ts 的 listForcedTurnEndActivations，它不是第二套规矩＝同一份"这席位上此刻还能不能发动"的合法清单的过滤视图，只把打了勾的那几枚挑出来交给系统替玩家发动），所以它管的事恰恰只有一件＝"这一刻问不问您"；徽章里「锁定技」v2.8 刀4 起有了第一个结算侧的消费者，但只管一寸地方：编译器认出这枚徽章 → 这条技能往数值账本落的那笔账打上"移不走"的记号（statModifiers.revokeModifier 是全库唯一"移走别人那笔账"的入口，它见到这个记号就拒绝）。徽章的其余部分（"不能被无效""不能被改变"在伤害、护甲、被弃牌这些环节到底管不管）今天仍然没有任何结算代码读它；四枚徽章里限定技自 v2.8.32 起有了第二个结算侧消费者（编译器认出它 ⇒ 这枚技能每发动一次就在同一本账上落一笔，账上有这一笔就不再让它发动；"一局一次"的判据与记账形状全库只有一份＝skills/skillQuota.ts，三条发动路——回合结束、停下问您、到点自己响——都从这里过），登场／遗计还是纯分类，而「觉醒技」自 v2.9.3 起也有了结算侧消费者：编译器认出这枚徽章后同时发生两件事——这枚技能听的那一声从"到点自己响"搬进"停下来问您一次"的队列，并且它与限定技共用同一本一局一次的账（摇头不算发动、不扣这笔账）。所以现在决定一条技能"什么时候响、响不响、响几次"的是：触发时机（含细分）＋「我听谁」这一档监听范围（五档，v2.8.21 起三档、v2.9.13 起五档；触发桥逐条读；缺省＝只听自己，⇒ 与今天对局逐字一致。「被谁指名」那一档＝成为目标时的细分，另算一维（"成为技能目标"这一声 v2.8.24 起已有发射器＝决斗开局，其余技能指名目标的路仍未发这一声，等内容刀））＋ 发动门槛 ＋ 那条"每回合限一次"的账 ＋ 限定技与觉醒技"一局一次"的同一本账（v2.8.32 起／v2.9.3 起）＋「强制发动」这一格（v2.8.25 起，只管问不问人；v2.9.3 起它对觉醒技同样管用——勾了就不问、到点自己结算；v2.9.17 起连「回合结束时」那扇窗也吃它——勾了的由系统替玩家发动，不进窗）。「在场即生效」那一型不看上面这些，它只在登场／离场两刻动账本。徽章的读写口径全库只有一份，在 domain/skillTags.ts。</t>
   </si>
   <si>
     <t>游戏结束 / 对局结束</t>
@@ -1452,10 +1452,10 @@
     <t>编辑器只有单枚标签下拉、卡面只印一枚（旧说法，已作废） 已多枚化（v2.8.19：编辑器一排徽章可同时点亮几枚，Excel「技能标签」格用顿号分开写，图鉴／卡面／对局几枚都显示）</t>
   </si>
   <si>
-    <t>三半现在分开了：「强制发动」那半 v2.8.25 已进引擎（SkillTriggerBridge.defersToReactionQueue 读它⇒勾了就不问人、直接走自动发动路；全库只有这一处读，所以它只管"问不问"这一件事）；限定技那半 v2.8.32 已进引擎（编译器读这枚徽章 ⇒ 落额度键；三条发动路的"还能不能发动"与"记这一笔账"全库只有一份＝skills/skillQuota.ts）；剩下锁定技的"不能被无效、不能被改变"结算里仍一处不读——引擎压根没有"无效一枚技能"这套机制，没有可执法的对象（唯一消费者是 v2.8 刀4 那寸"账本移不走"记号）。读写口径全库只有一份（domain/skillTags.ts）</t>
-  </si>
-  <si>
-    <t>✅ 您的更正口径已逐字落进第四节：「锁定技实际上是指无法被无效和改变的技能，而强制发动则是指某些技能在满足触发条件和代价后会强制发动/直接适用其效果，两者和数值变化+永续生效的组合一样，不是强关联」；样本＝闭月同时挂 锁定技＋遗计技。强制发动那一刀已开完（v2.8.25，两锚逐字未动＝今天还没有一条数据勾着它）；限定技那一刀已开完（v2.8.32，同样本池还没有一条数据挂着它⇒两锚读数见 §H10）；锁定技"被无效"那一半不做（没有机制可执法，等引擎长出一套"无效技能"再议）</t>
+    <t>三半现在分开了：「强制发动」那半 v2.8.25 已进引擎（SkillTriggerBridge.defersToReactionQueue 读它⇒勾了就不问人、直接走自动发动路；v2.9.17 起第二处读它的＝skills/turnEndSkills.ts，同一份合法清单的过滤视图，不是第二套规矩，所以它管的事仍然只有"问不问"这一件）；限定技那半 v2.8.32 已进引擎（编译器读这枚徽章 ⇒ 落额度键；三条发动路的"还能不能发动"与"记这一笔账"全库只有一份＝skills/skillQuota.ts）；剩下锁定技的"不能被无效、不能被改变"结算里仍一处不读——引擎压根没有"无效一枚技能"这套机制，没有可执法的对象（唯一消费者是 v2.8 刀4 那寸"账本移不走"记号）。读写口径全库只有一份（domain/skillTags.ts）</t>
+  </si>
+  <si>
+    <t>✅ 您的更正口径已逐字落进第四节：「锁定技实际上是指无法被无效和改变的技能，而强制发动则是指某些技能在满足触发条件和代价后会强制发动/直接适用其效果，两者和数值变化+永续生效的组合一样，不是强关联」；样本＝闭月同时挂 锁定技＋遗计技。强制发动那一刀已开完（v2.8.25，两锚逐字未动＝今天还没有一条数据勾着它）；v2.9.16 起它管到"每一型"（没勾的逢人就问），v2.9.17 起连「回合结束时」那扇窗也吃它＝勾了的那几枚由系统在同一条规范动作里替玩家发动、不进窗，并且每一次真发动（三条路都算）在界面左上角飘一条 ⚡ 小广播。您 2026-10-21 两句原文＝"强制发动永远是强制发动，无论什么节点，但是一定要通知玩家有什么技能发动了"＋"哪些官方卡是强制发动，这部分由我自己来填写"⇒这一格仍由您来勾，官方卡面到今天一枚都没加；限定技那一刀已开完（v2.8.32，同样本池还没有一条数据挂着它⇒两锚读数见 §H10）；锁定技"被无效"那一半不做（没有机制可执法，等引擎长出一套"无效技能"再议）</t>
   </si>
   <si>
     <t>10</t>

--- a/词汇表.xlsx
+++ b/词汇表.xlsx
@@ -1014,13 +1014,13 @@
     <t>获得技能（效果类型，v2.9.3 刀A 起可结算）</t>
   </si>
   <si>
-    <t>第十二条效果类型，和「修改数值」正好是一正一反：那一档只动账本、卡面一字不改；这一档只动卡面——往这一员将身上添一枚技能（添进他卡面上那份技能清单），不改任何数字、不掉血、不搬牌。五句实话：①认的是名字，您在那一格里写什么，引擎就拿什么去查技能表（v2.9.7 起这一档只认这一本名单＝卡上有真结算内容的技能自动在册＋不印在任何将卡上、写在表里的那几枚；今天表上 41 个名字，当场量过、有测试钉着）；②只在卡上印了个名字、还没挂上可结算内容的那一类不在表上（您 2026-10-16 裁「技能表只做有真内容的」）——填了会被点名跳过，而不是让您拿到一枚空的；卡上那枚哪天挂上内容，它自己就进表，这一条跟着生效，不用另改任何名单；③查不到、或者同名却有两份不同内容，都会被导入报告与编译器逐条点名跳过，绝不猜一个"最像的"（自己新编的 DIY 技能名这一版还查不到，已另立待办）；④只能添在自己身上——"给别的将领添技能"要等目标选择器那把刀；而且从下一次发动起这一员将才听得见这枚新技能（本项目没有卡面技能清单的缓存，每次发动前都从对局现场重算一遍），同一枚拿第二次也只留一份；⑤如果拿到的是一枚在场即生效的技能，那笔账在获得这一刻补落进账本（同一枚不落第二笔），不是等下一次登场。另外v2.9.6 起这一档第一次挂上了官方将＝魏关羽的「单骑」：觉醒那一刻它照这一格去查技能表，把「怒斩」添进这名将身上——「怒斩」不印在任何将卡上，住在表里（src/data/skillTable.ts；v2.9.4 那一版这张表还是空架子，一条真内容都没有，所以当时谁也查不到）。将领名册 96 将里用到这一档的只有这一条（当场量过，有测试钉着）。</t>
+    <t>第十二条效果类型，和「修改数值」正好是一正一反：那一档只动账本、卡面一字不改；这一档只动卡面——往这一员将身上添一枚技能（添进他卡面上那份技能清单），不改任何数字、不掉血、不搬牌。五句实话：①认的是名字，您在那一格里写什么，引擎就拿什么去查技能表（v2.9.7 起这一档只认这一本名单＝卡上有真结算内容的技能自动在册＋不印在任何将卡上、写在表里的那几枚；今天这本册子上仓库名册那一份是 41 个名字（当场量过、有测试钉着）；v2.9.18 起这本册子的进料改成"这台机器此刻真在用的那份将领"＝仓库名册＋您的自制卡（都过一遍卡面编辑），所以自制卡上挂上了真内容的技能也照样在册，退出游戏、删掉那张卡它就跟着退册）；②只在卡上印了个名字、还没挂上可结算内容的那一类不在表上（您 2026-10-16 裁「技能表只做有真内容的」）——填了会被点名跳过，而不是让您拿到一枚空的；卡上那枚哪天挂上内容，它自己就进表，这一条跟着生效，不用另改任何名单；③查不到、或者同名却有两份不同内容，都会被导入报告与编译器逐条点名跳过，绝不猜一个"最像的"（v2.9.18 起这一条通了＝您自制卡上那枚挂上了真内容的技能，保存之后下一问就查得到；查得到也照样看得见出处——名字后面那半截写着「官方」还是「玩家自制」，是按这张卡建的时候钉死的那一份来源读的，您 2026-10-21 的口径「开发者模式下新增和改动的就是官方卡」落在这里没有第二套判据）；④只能添在自己身上——"给别的将领添技能"要等目标选择器那把刀；而且从下一次发动起这一员将才听得见这枚新技能（本项目没有卡面技能清单的缓存，每次发动前都从对局现场重算一遍），同一枚拿第二次也只留一份；⑤如果拿到的是一枚在场即生效的技能，那笔账在获得这一刻补落进账本（同一枚不落第二笔），不是等下一次登场。另外v2.9.6 起这一档第一次挂上了官方将＝魏关羽的「单骑」：觉醒那一刻它照这一格去查技能表，把「怒斩」添进这名将身上——「怒斩」不印在任何将卡上，住在表里（src/data/skillTable.ts；v2.9.4 那一版这张表还是空架子，一条真内容都没有，所以当时谁也查不到）。将领名册 96 将里用到这一档的只有这一条（当场量过，有测试钉着）。</t>
   </si>
   <si>
     <t>获得哪个技能（Excel 里效果组第 12 列）</t>
   </si>
   <si>
-    <t>「获得技能」那一枚的名字格，只服务这一个效果类型（与「改哪个数」「我听谁」同一族做法：一个正交维度占一列）。这一格故意不做死下拉：可选的名字＝技能表上那 41 个（数随内容增长），做成封闭下拉会把"先写技能、那枚技能还没进表"这条路堵死——所以名字是原样收字，认不认由引擎那一处唯一的解析点（＝查技能表）说了算（界面里给的是可自由输入的候选清单，不是强制选项）。只有「效果类型＝获得技能」读这一格，别的类型填了会在导入总结里点名、按没填处理；这一格留空同样点名（那是一条半截效果，不会被静悄悄收下）。旧的 11 列导出文件照样能导入，只是那种文件里没有这一格——凡是「获得技能」的效果会报"缺名字"。</t>
+    <t>「获得技能」那一枚的名字格，只服务这一个效果类型（与「改哪个数」「我听谁」同一族做法：一个正交维度占一列）。这一格故意不做死下拉：可选的名字＝技能表上那 41 个（数随内容增长），做成封闭下拉会把"先写技能、那枚技能还没进表"这条路堵死——所以名字是原样收字，认不认由引擎那一处唯一的解析点（＝查技能表）说了算（界面里给的是可自由输入的候选清单，不是强制选项；v2.9.18 起清单里每个名字后面带着它的出处（官方／玩家自制，同一个名字两头都有就两边都列），下面那句小计写着此刻册子里各有多少枚。同一刀还留了一颗今天看不见的按钮「↻ 刷新技能册」：册子今天每问一次就重算一次（您 2026-10-21 裁「现在就按每次重算来做」），所以它不出现；哪天把自动重算关掉，它就跟着那一格出现在界面上，点一下＝当场照这台机器现在的内容重算一遍）。只有「效果类型＝获得技能」读这一格，别的类型填了会在导入总结里点名、按没填处理；这一格留空同样点名（那是一条半截效果，不会被静悄悄收下）。旧的 11 列导出文件照样能导入，只是那种文件里没有这一格——凡是「获得技能」的效果会报"缺名字"。</t>
   </si>
   <si>
     <t>拼积木生成卡面话（v2.9.8 起）</t>

--- a/词汇表.xlsx
+++ b/词汇表.xlsx
@@ -879,10 +879,10 @@
     <t>"这技能在哪一刻响"的下拉。玩家在对局里只会看到结果，看不到这个词本身。</t>
   </si>
   <si>
-    <t>回合开始时 / 回合结束时 / 将领登场时 / 受到伤害后 / 造成伤害后 / 成为目标时 / 击杀将领时 / 自身被击杀时 / 失去手牌时 / 获得手牌时 / 营地受到伤害时 / 其他将领技能发动时</t>
-  </si>
-  <si>
-    <t>十二种"哪一刻响"的说法，字面就是那件事发生的时刻。（"成为攻击目标时"这个旧名字 v2.8.21 起改成了泛指的"成为目标时"，具体被谁指名交给下面那一格说。）「受到伤害后」的判据（v2.8 刀5 起，您 2026-10-03 重新裁定）＝只有真的掉了体力才算受到了伤害：这一刀被护甲全挡住、一点血没掉 ⇒ 不算受到，技能不问也不响；伤害算出来是 0 或负数 ⇒ 也不算。掉多少算多少：普攻／技能伤害每一刀各算一声；决斗那一整场只在打完时按"这个将一共掉了多少体力"算一笔（见上面「决斗」那一格）。被这一刀打死的那一位，两类里只有「受到伤害后」不算（v2.8.31 定稿＝您 2026-10-04 把两类的定义封死：「成为目标时」＝受击，它在伤害算出来之前就发动完了，所以和这一刀实际打多少、主人会不会被这一刀砍死无关——被砍死的那一刀里它照样问、照样响；「受到伤害后」＝受伤，必须真的掉了血才成立，所以它在伤害之后才问，主人死在这一刀里就不问也不响）。两条路的判据一模一样，区别只在"需不需要您自己点头"。追加的那一条（甲）也在这里生效：反伤先把出手的那位扎死了⇒那一刀跟着取消，挨打的那位自救成功，粮草也没被吃掉。唯一的豁口＝「自身被击杀时」那一型（遗言／遗计）：它按定义就是在主人离场这一声上发动，所以两边都放行，牌照旧摸进手。最后那一格（营地受到伤害时）是 v2.9.14 才接上电的（您 2026-10-18 定"先做「营地受到伤害时」"）：它听的是营地那一格掉了血这一声，判据跟上面同一句——只有真的掉了体力才算受到伤害，那一刀被挡光、一点没掉⇒不算、不响。三句实话：①它只认自家那一席的营地，别人家营地掉血不算（营地不是任何一员将，所以"我听谁的营地"这一维今天没有做，界面上那一格下拉对这一型直接不出现，从旧 Excel 硬塞一格进来会被点名跳过、不静悄悄当成"只听自家"）；②它到点自己响，不停下来问您（跟登场／回合开始同一类，跟「受到伤害后」要点头那一类不同），勾不勾「强制发动」都一样（旧说法，已作废）（这句自 v2.9.16 作废：跟「受到伤害后」同一类＝停下来问您，勾了「强制发动」才自己响）；③另两格营地系的说法「营地成为攻击目标时」「营地成为技能目标时」还是没接线（那两声身上没带"这是哪一席的营地"这个记号，接了就是瞎响），下拉里点得到、界面照旧会当场写明它今天不会响。顺带修掉一条老毛病：v2.8.21 给「受到伤害后」加上"听别人"那几档之后，自家营地掉血也曾被它当成"受到了伤害"（那几档不比是哪一员将，营地那一身就顺着席位混进来了）⇒ 本轮起「受到伤害后」只管人、营地交给这一格。最后这一格（其他将领技能发动时）是 v2.9.15 才接上电的（您 2026-10-18 那句"做完「营地受到伤害时」就做「别人使用技能时」"）：它听的是某一枚技能真的发动了一次那一声。四句实话：①这一声过去只有"一局一次"那种带额度的技能才会留下记录，而且只记在台账里、不外传⇒本轮把"发动公告"改成每次真发动都出声，普通技能那一身不带台账键＝牌桌状态一个字都不动（所以对局里多出来的只是声音，两锚因此逐字没挪）；②"什么算别人"用的是上一刀那同一根轴（席位＋将领两维一起看，同一个席位上的别的将也算），没有另抄一份判据；③套娃只传一层＝由这一声引起的发动，自己再公告时身上带一个"我是被这一声叫起来的"记号，这一格听见这个记号就闭嘴——不然两员"别人发动我就摸牌"的能把彼此的牌堆摸穿；④空发不出声（那一条什么都没做成的发动不算发动，跟"没发动成功不消耗额度"是同一句诚实），而且它到点自己响、绝不停下来问您，跟营地那一格、登场／回合开始同一类（旧说法，已作废）（这句自 v2.9.16 作废：跟营地那一格、登场／回合开始同一类＝没勾就问、勾了才自己响）。判据与取证＝PROJECT_HANDOFF.md §12-100／§12-101／§12-102／§12-130／§12-131。</t>
+    <t>回合开始时 / 回合结束时 / 将领登场时 / 受到伤害后 / 造成伤害后 / 成为目标时 / 击杀将领时 / 自身被击杀时 / 失去手牌时 / 获得手牌时 / 营地受到伤害时 / 营地成为攻击目标时 / 营地成为技能目标时 / 其他将领技能发动时</t>
+  </si>
+  <si>
+    <t>十四种"哪一刻响"的说法，字面就是那件事发生的时刻。（"成为攻击目标时"这个旧名字 v2.8.21 起改成了泛指的"成为目标时"，具体被谁指名交给下面那一格说。）「受到伤害后」的判据（v2.8 刀5 起，您 2026-10-03 重新裁定）＝只有真的掉了体力才算受到了伤害：这一刀被护甲全挡住、一点血没掉 ⇒ 不算受到，技能不问也不响；伤害算出来是 0 或负数 ⇒ 也不算。掉多少算多少：普攻／技能伤害每一刀各算一声；决斗那一整场只在打完时按"这个将一共掉了多少体力"算一笔（见上面「决斗」那一格）。被这一刀打死的那一位，两类里只有「受到伤害后」不算（v2.8.31 定稿＝您 2026-10-04 把两类的定义封死：「成为目标时」＝受击，它在伤害算出来之前就发动完了，所以和这一刀实际打多少、主人会不会被这一刀砍死无关——被砍死的那一刀里它照样问、照样响；「受到伤害后」＝受伤，必须真的掉了血才成立，所以它在伤害之后才问，主人死在这一刀里就不问也不响）。两条路的判据一模一样，区别只在"需不需要您自己点头"。追加的那一条（甲）也在这里生效：反伤先把出手的那位扎死了⇒那一刀跟着取消，挨打的那位自救成功，粮草也没被吃掉。唯一的豁口＝「自身被击杀时」那一型（遗言／遗计）：它按定义就是在主人离场这一声上发动，所以两边都放行，牌照旧摸进手。最后那一格（营地受到伤害时）是 v2.9.14 才接上电的（您 2026-10-18 定"先做「营地受到伤害时」"）：它听的是营地那一格掉了血这一声，判据跟上面同一句——只有真的掉了体力才算受到伤害，那一刀被挡光、一点没掉⇒不算、不响。三句实话：①它只认自家那一席的营地，别人家营地掉血不算（营地不是任何一员将，所以"我听谁的营地"这一维今天没有做，界面上那一格下拉对这一型直接不出现，从旧 Excel 硬塞一格进来会被点名跳过、不静悄悄当成"只听自家"）；②它到点自己响，不停下来问您（跟登场／回合开始同一类，跟「受到伤害后」要点头那一类不同），勾不勾「强制发动」都一样（旧说法，已作废）（这句自 v2.9.16 作废：跟「受到伤害后」同一类＝停下来问您，勾了「强制发动」才自己响）；③营地另外两格（「营地成为攻击目标时」「营地成为技能目标时」）自 v2.9.19 也接上电了（您 2026-10-24 那句"选B跟「我听谁」那五档做成同一根轴"）：两格听的都是伤害落下来之前的那一声，跟将领那格「成为目标时」是同一声，分家只靠那一声身上本来就有的两个记号——"这一目标是营地不是将"＋"这一刀是攻击还是技能"，没有为营地另造第二套定语；"打的是哪一席的营地"读的正是您那五档「我听谁」，缺省只听自家，选"听场上"则哪家营地被攻打都响。两格都停下来问您（勾了「强制发动」才自己响），问的那一刻营地一点没掉；摇头不发动，那一刀照样落。一句实话：技能那一格今天只在"某个技能真的把伤害打向营地"的路上出声——界面里"选一个目标"那一类技能的可点名单只有在场的将、没有营地，本刀不扩它（扩＝玩法刀，要走三道闸）。顺带修掉一条老毛病：v2.8.21 给「受到伤害后」加上"听别人"那几档之后，自家营地掉血也曾被它当成"受到了伤害"（那几档不比是哪一员将，营地那一身就顺着席位混进来了）⇒ 本轮起「受到伤害后」只管人、营地交给这一格。最后这一格（其他将领技能发动时）是 v2.9.15 才接上电的（您 2026-10-18 那句"做完「营地受到伤害时」就做「别人使用技能时」"）：它听的是某一枚技能真的发动了一次那一声。四句实话：①这一声过去只有"一局一次"那种带额度的技能才会留下记录，而且只记在台账里、不外传⇒本轮把"发动公告"改成每次真发动都出声，普通技能那一身不带台账键＝牌桌状态一个字都不动（所以对局里多出来的只是声音，两锚因此逐字没挪）；②"什么算别人"用的是上一刀那同一根轴（席位＋将领两维一起看，同一个席位上的别的将也算），没有另抄一份判据；③套娃只传一层＝由这一声引起的发动，自己再公告时身上带一个"我是被这一声叫起来的"记号，这一格听见这个记号就闭嘴——不然两员"别人发动我就摸牌"的能把彼此的牌堆摸穿；④空发不出声（那一条什么都没做成的发动不算发动，跟"没发动成功不消耗额度"是同一句诚实），而且它到点自己响、绝不停下来问您，跟营地那一格、登场／回合开始同一类（旧说法，已作废）（这句自 v2.9.16 作废：跟营地那一格、登场／回合开始同一类＝没勾就问、勾了才自己响）。判据与取证＝PROJECT_HANDOFF.md §12-100／§12-101／§12-102／§12-130／§12-131／§12-136。</t>
   </si>
   <si>
     <t>在场即生效（不用发动，人在就算）（v2.8 刀4 起可结算）</t>

--- a/词汇表.xlsx
+++ b/词汇表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="500">
   <si>
     <t>玩家词汇 · 大白话对照表（v2.8.18 界面口径）</t>
   </si>
@@ -55,13 +55,13 @@
     <t>三 抽卡与开局：49 条</t>
   </si>
   <si>
-    <t>四 技能相关词：38 条</t>
+    <t>四 技能相关词：39 条</t>
   </si>
   <si>
     <t>五 结算录像日志：9 条</t>
   </si>
   <si>
-    <t>六 图鉴设置开发者：23 条</t>
+    <t>六 图鉴设置开发者：28 条</t>
   </si>
   <si>
     <t>七 界面里没有的词：8 条</t>
@@ -843,6 +843,12 @@
     <t>一局只许发动一次，用完就没了（src/skills/skillQuota.ts）。四条细则：① 额度记在每枚技能头上——一个将带两枚限定技就能各用一次；② 用完之后这枚技能在候选里照常列出、但灰掉，写明「本局已用尽」；③ 被人挡掉、无效掉不退额度（用过了就是用过了）；④ 想发动但没当成（代价付不出、被规则拒绝）不消耗额度。⑤ v2.9.3 起「觉醒技」也记在这同一本账上（您 2026-10-08 裁："觉醒技和限定技同理"）：上面①"每枚技能各记一笔"、③"被挡掉不退额度"、④"没当成不消耗"三条一字照搬。唯一的差别在界面——觉醒技用尽之后那一格压根不再问您，因为停下问人这条路没有"照常列出但灰掉、写着本局已用尽"这个形状（那是回合结束那条路的显示）。</t>
   </si>
   <si>
+    <t>每回合限 N 次（编辑器与 Excel 的「每回合限几次」）</t>
+  </si>
+  <si>
+    <t>一条技能在一名玩家的一个回合里最多能发动几次（填正整数：1、2、3…；这一格留空＝不限制，跟以前一模一样）。v2.9.23 起这一格真的管事了，六个问题按您 2026-10-28 的五句裁决逐条落成对局里的行为：① 谁的回合算一个"次"的窗口＝每一名玩家的回合各算一格自己的窗（在别人的回合里能不能发动，从来由「触发时机」＋「我听谁」那两格说了算，这一格不管这件事）；② 什么时候把次数还回来＝这一回合完全结束时——收尾事项全跑完、下一位玩家回合开始那一刻自动归零；旧的那笔账不删，只是换到新格里不再被数到（所以录像与日志翻得回去）；③ N 怎么读＝汉字与阿拉伯数字都认（「一」「两」「三」＝1、2、3），读不出的那一串逐段退回点名问您——系统既不猜数、也不偷偷当成 1、更不偷偷当成没限制；④ 扣在哪一刻＝付了代价、发动了就扣，即使效果后来被改变或者被无效（与限定技同一口径）；而"发动了却一个效果都产不出"这种空发根本不许发动（牌堆空会先洗牌补齐再摸，真处理不了就不让这条技能进候选）；⑤ 用完以后界面怎么说＝这枚技能在候选里照常列出、写明「本回合已用尽」（放行可以、看不见不行）。三句边界实话：它跟限定技是两本账，同一枚技能挂着两个限额时按各自更紧的那一条走，两本同时见底先说「本局已用尽」；同一回合连发几次要占几格由这一格定的数说了算（限 2 就落两笔账），而一次发动只落一笔——这一笔同时给两本账各留一个记号（"一局一次"那本看有没有、"每回合 N 次"那本数几笔），不会一次把两本各扣一遍。卡面上生成出来的那句只有一种写法（「每回合限N次」），读的时候认多种写法（只进不出）。判据全库只有一份＝data/generals.ts::isValidTurnLimit，两本账只有一份＝skills/skillQuota.ts，界面那一格＝components/skillEditor/TurnLimitEditor.tsx，Excel 那一列叫「每回合限几次」。这一格也由您自己填：到今天官方 96 将与您手上的样本卡一条都没填，所以固定种子 300 局的两池回归读数一字未动（成因不是"这一刀没碰结算"，而是没填数时这条新分支一次也不会被走到）。裁决原文与判据＝PROJECT_HANDOFF.md §12。</t>
+  </si>
+  <si>
     <t>登场技</t>
   </si>
   <si>
@@ -1032,7 +1038,7 @@
     <t>自己写效果（v2.9.9 起）</t>
   </si>
   <si>
-    <t>技能卡片上「✍️ 自己写效果（一句话生成积木）」那一格：您用大白话写，系统替您反推成上面那三格积木，先给您看它打算怎么说，您点头才进格子（不点头什么都不会变），点「✔ 采用」后就是原来的拼积木界面，逐条改即可。写的是一行一段、句号分开；以下择一／以下依次生效 两句当头一句写，就按"选择其一"／"链式"登记；要满足手牌≤2 写在最前面＝整组门槛、写在某条时机后面＝那一条自己的门槛。认得的说法＝词表里那十二档动作与三档对象，中文数字（两、十二）与阿拉伯数字同解，「全部」＝整只手，观顶3张「拆掉 1 张装备卡」这类旧行话也照旧读得懂（只进不出）。读不懂的绝不猜、也没有一段是悄悄丢掉的：哪一段不支持就原文点出来＋一句照着改得动的理由（例："这一句要作用在'别人'身上……想让别的玩家执行的那类内容还没做出来"、"若…则…请改写「以下依次生效」"、"限定技是徽章，去徽章那一格勾"）。⚠️ 退回看这一段写在动作的哪一边，因为两句话的意思不一样：写在动作前面＝它正在给这个动作补"对谁／在什么前提下做"⇒这一条整条退回（只收动作那半＝做成另一件事）；写在动作后面＝像是第二件事⇒前面那件读懂的照做、后面这段单独点名并教您另起一句（一段只认一件事，第二件不顶掉第一件）。⚠️ 两种"不支持"也分开了：① 形状写错了 ⇒ 那一条不生成；② 格子有、引擎还没接线（例如下拉里那些还没上事件面的时机） ⇒ 照样生成、也能采用，但界面当场说一句"这条今天不会响"。这一格没有大模型、不联网，纯离线词表；能不能编出结算问的是编译器那一支自己（skillCompiler.judgeSkillEffect，反解侧与真编译路共用同一判据，不可能两边各说一套）。反解侧＝src/skills/skillTextParse.ts，界面＝src/components/skillEditor/SkillTextPanel.tsx；两侧由 skillTextParse.test.ts 的往返钉钉住（生成的那句再解回去、再生成 ⇒ 逐字同一句）。v2.9.13 这一格新认得的两样：①「将领登场时」这一档多了您那三句定语——其他角色登场时／己方角色登场时／敌方角色登场时（加上自身登场时与场上所有角色登场时一共五种写法），拼出来的都是上面「我听谁」那五档里的同一档，拼法全库只有一处（data/generals.ts 那张对照表），界面提示与这句反解都从它现取，不会各写一份；②其他角色摸两张牌这类用词写错的句子，现在走的是"这一句的说法本作不成立"那一档理由，并给您一句改得动的写法（详见上面「角色 / 玩家」那一行）——它跟"内容还没做出来"是两回事，分开点名。v2.9.15 这一格又多认一句：其他将领技能发动时，摸一张牌。（时机名与上面下拉那一格逐字同一份词表）现在照生成、照能采用，上一版挂在它那句"这条今天不会响"的提示随接线自行消失——这句提示不是写死在界面上的，它是问编译器"这一条到底编不编得出来"，所以哪天接上电它就自己没了。</t>
+    <t>技能卡片上「✍️ 自己写效果（一句话生成积木）」那一格：您用大白话写，系统替您反推成上面那三格积木，先给您看它打算怎么说，您点头才进格子（不点头什么都不会变），点「✔ 采用」后就是原来的拼积木界面，逐条改即可。写的是一行一段、句号分开；以下择一／以下依次生效 两句当头一句写，就按"选择其一"／"链式"登记；要满足手牌≤2 写在最前面＝整组门槛、写在某条时机后面＝那一条自己的门槛。认得的说法＝词表里那十二档动作与三档对象，中文数字（两、十二）与阿拉伯数字同解，「全部」＝整只手，观顶3张「拆掉 1 张装备卡」这类旧行话也照旧读得懂（只进不出）。读不懂的绝不猜、也没有一段是悄悄丢掉的：哪一段不支持就原文点出来＋一句照着改得动的理由（例："这一句要作用在'别人'身上……想让别的玩家执行的那类内容还没做出来"、"若…则…请改写「以下依次生效」"、"限定技是徽章，去徽章那一格勾"）。⚠️ 退回看这一段写在动作的哪一边，因为两句话的意思不一样：写在动作前面＝它正在给这个动作补"对谁／在什么前提下做"⇒这一条整条退回（只收动作那半＝做成另一件事）；写在动作后面＝像是第二件事⇒前面那件读懂的照做、后面这段单独点名并教您另起一句（一段只认一件事，第二件不顶掉第一件）。⚠️ 两种"不支持"也分开了：① 形状写错了 ⇒ 那一条不生成；② 格子有、引擎还没接线（例如下拉里那些还没上事件面的时机） ⇒ 照样生成、也能采用，但界面当场说一句"这条今天不会响"。这一格没有大模型、不联网，纯离线词表；能不能编出结算问的是编译器那一支自己（skillCompiler.judgeSkillEffect，反解侧与真编译路共用同一判据，不可能两边各说一套）。反解侧＝src/skills/skillTextParse.ts，界面＝src/components/skillEditor/SkillTextPanel.tsx；两侧由 skillTextParse.test.ts 的往返钉钉住（生成的那句再解回去、再生成 ⇒ 逐字同一句）。v2.9.13 这一格新认得的两样：①「将领登场时」这一档多了您那三句定语——其他角色登场时／己方角色登场时／敌方角色登场时（加上自身登场时与场上所有角色登场时一共五种写法），拼出来的都是上面「我听谁」那五档里的同一档，拼法全库只有一处（data/generals.ts 那张对照表），界面提示与这句反解都从它现取，不会各写一份；②其他角色摸两张牌这类用词写错的句子，现在走的是"这一句的说法本作不成立"那一档理由，并给您一句改得动的写法（详见上面「角色 / 玩家」那一行）——它跟"内容还没做出来"是两回事，分开点名。v2.9.15 这一格又多认一句：其他将领技能发动时，摸一张牌。（时机名与上面下拉那一格逐字同一份词表）现在照生成、照能采用，上一版挂在它那句"这条今天不会响"的提示随接线自行消失——这句提示不是写死在界面上的，它是问编译器"这一条到底编不编得出来"，所以哪天接上电它就自己没了。v2.9.22 这一格认得的写法多了一整批（用户 2026-10-27 拍板「633 条描述走出口①＝补词表/别名」），并且全是只进不出：① 时机的手写说法——死亡时／当你阵亡／每回合结束／受到伤害时候／遭受伤害／被攻击时／成为攻击目标时候／击杀角色时／打死一名敌方武将／放置时／回合开始／造成伤害时候／失去全部手牌／获得所有手牌时／摸到手牌 这类，都归到上面下拉里那一档的同一句话（别名右边给的是档位，串由词表现场生成，没有第二份抄本）；② 紧凑改数式 近战攻击力+1／你的远程攻击力-2＝「让近战攻击力增加 1」那同一块积木，六把钥匙名一律现取；③ 弃置／弃去／弃掉／丢弃 N 张… 与 弃 N 张… 算同一件事；④ 从 Excel 或网页粘进来时开头那种列表编号（1、／2、）当脏片段忽略，并且照样回显给您——跟连接词走同一条路，绝不假装"这句我读过了"。三句实话：卡面上生成出来的那句、导出到 Excel 的那一列，一个字都没变；已经认得的串绝不动——自身登场时 还是 自身登场时，不会被顺手"归一"成缺省那一档（把「我听谁」读没这种事有测试钉着）；语义会动的写法一条都不自动换算，近战伤害+1／受到远程伤害-1／生命上限为3／回复1点生命 仍按原文退回并说清为什么（要么丢掉「近战／远程」这层限定，要么用的是本作没有的那个词）。存量表那一刀的实测数字也摆在这儿，别让"一句话生成"背超出它能力的期待：那 610 句转换表描述，改这批写法之前能点采用的 13 句、之后 38 句（+25），整句一字未退回的从 0 句到 1 句，回归 0 句——剩下那 500 多句卡的不是写法，是引擎根本没有那件事。</t>
   </si>
   <si>
     <t>有效周期（这笔账什么时候结束）</t>
@@ -1059,7 +1065,7 @@
     <t>（旧说法，已作废）击破横幅上方那行残留的英文小字，v2.8.18 已翻成中文，v2.8.39 起那里写的是「营地击破」。</t>
   </si>
   <si>
-    <t>本节末尾必须说清的一件事：五个"××技"徽章和"强制发动"这一列，v2.8.19 起读得到、写得出、显示得出、还能核对（一枚技能可挂几枚；徽章与触发时机对不上会在编辑器与导入总结里点名）。这两样如今落地程度不同：「强制发动」v2.8.25 起接进对局了——全库只有两处读它（①skills/SkillTriggerBridge.ts 的 defersToReactionQueue：v2.9.16 起是"每一型"——凡是听得懂至少一声的时机里没打勾的定义都交给问答队列问人，打了勾的直接走自动发动那条路；「在场即生效」压根不监听任何一声，所以它既不会被问也不会自己响；v2.9.3 起这一处还多认一枚徽章——挂了「觉醒技」的技能没打勾时同样停下来问您，打了勾就照旧自己响；②v2.9.17 起新增skills/turnEndSkills.ts 的 listForcedTurnEndActivations，它不是第二套规矩＝同一份"这席位上此刻还能不能发动"的合法清单的过滤视图，只把打了勾的那几枚挑出来交给系统替玩家发动），所以它管的事恰恰只有一件＝"这一刻问不问您"；徽章里「锁定技」v2.8 刀4 起有了第一个结算侧的消费者，但只管一寸地方：编译器认出这枚徽章 → 这条技能往数值账本落的那笔账打上"移不走"的记号（statModifiers.revokeModifier 是全库唯一"移走别人那笔账"的入口，它见到这个记号就拒绝）。徽章的其余部分（"不能被无效""不能被改变"在伤害、护甲、被弃牌这些环节到底管不管）今天仍然没有任何结算代码读它；四枚徽章里限定技自 v2.8.32 起有了第二个结算侧消费者（编译器认出它 ⇒ 这枚技能每发动一次就在同一本账上落一笔，账上有这一笔就不再让它发动；"一局一次"的判据与记账形状全库只有一份＝skills/skillQuota.ts，三条发动路——回合结束、停下问您、到点自己响——都从这里过），登场／遗计还是纯分类，而「觉醒技」自 v2.9.3 起也有了结算侧消费者：编译器认出这枚徽章后同时发生两件事——这枚技能听的那一声从"到点自己响"搬进"停下来问您一次"的队列，并且它与限定技共用同一本一局一次的账（摇头不算发动、不扣这笔账）。所以现在决定一条技能"什么时候响、响不响、响几次"的是：触发时机（含细分）＋「我听谁」这一档监听范围（五档，v2.8.21 起三档、v2.9.13 起五档；触发桥逐条读；缺省＝只听自己，⇒ 与今天对局逐字一致。「被谁指名」那一档＝成为目标时的细分，另算一维（"成为技能目标"这一声 v2.8.24 起已有发射器＝决斗开局，其余技能指名目标的路仍未发这一声，等内容刀））＋ 发动门槛 ＋ 那条"每回合限一次"的账 ＋ 限定技与觉醒技"一局一次"的同一本账（v2.8.32 起／v2.9.3 起）＋「强制发动」这一格（v2.8.25 起，只管问不问人；v2.9.3 起它对觉醒技同样管用——勾了就不问、到点自己结算；v2.9.17 起连「回合结束时」那扇窗也吃它——勾了的由系统替玩家发动，不进窗）。「在场即生效」那一型不看上面这些，它只在登场／离场两刻动账本。徽章的读写口径全库只有一份，在 domain/skillTags.ts。</t>
+    <t>本节末尾必须说清的一件事：五个"××技"徽章和"强制发动"这一列，v2.8.19 起读得到、写得出、显示得出、还能核对（一枚技能可挂几枚；徽章与触发时机对不上会在编辑器与导入总结里点名）。这两样如今落地程度不同：「强制发动」v2.8.25 起接进对局了——全库只有两处读它（①skills/SkillTriggerBridge.ts 的 defersToReactionQueue：v2.9.16 起是"每一型"——凡是听得懂至少一声的时机里没打勾的定义都交给问答队列问人，打了勾的直接走自动发动那条路；「在场即生效」压根不监听任何一声，所以它既不会被问也不会自己响；v2.9.3 起这一处还多认一枚徽章——挂了「觉醒技」的技能没打勾时同样停下来问您，打了勾就照旧自己响；②v2.9.17 起新增skills/turnEndSkills.ts 的 listForcedTurnEndActivations，它不是第二套规矩＝同一份"这席位上此刻还能不能发动"的合法清单的过滤视图，只把打了勾的那几枚挑出来交给系统替玩家发动），所以它管的事恰恰只有一件＝"这一刻问不问您"；徽章里「锁定技」v2.8 刀4 起有了第一个结算侧的消费者，但只管一寸地方：编译器认出这枚徽章 → 这条技能往数值账本落的那笔账打上"移不走"的记号（statModifiers.revokeModifier 是全库唯一"移走别人那笔账"的入口，它见到这个记号就拒绝）。徽章的其余部分（"不能被无效""不能被改变"在伤害、护甲、被弃牌这些环节到底管不管）今天仍然没有任何结算代码读它；四枚徽章里限定技自 v2.8.32 起有了第二个结算侧消费者（编译器认出它 ⇒ 这枚技能每发动一次就在同一本账上落一笔，账上有这一笔就不再让它发动；"一局一次"的判据与记账形状全库只有一份＝skills/skillQuota.ts，三条发动路——回合结束、停下问您、到点自己响——都从这里过），登场／遗计还是纯分类，而「觉醒技」自 v2.9.3 起也有了结算侧消费者：编译器认出这枚徽章后同时发生两件事——这枚技能听的那一声从"到点自己响"搬进"停下来问您一次"的队列，并且它与限定技共用同一本一局一次的账（摇头不算发动、不扣这笔账）。所以现在决定一条技能"什么时候响、响不响、响几次"的是：触发时机（含细分）＋「我听谁」这一档监听范围（五档，v2.8.21 起三档、v2.9.13 起五档；触发桥逐条读；缺省＝只听自己，⇒ 与今天对局逐字一致。「被谁指名」那一档＝成为目标时的细分，另算一维（"成为技能目标"这一声 v2.8.24 起已有发射器＝决斗开局，其余技能指名目标的路仍未发这一声，等内容刀））＋ 发动门槛 ＋ 那条"每回合只落一笔"的默认账（没填「每回合限几次」的技能照旧＝一格窗里同一枚只结算一次；v2.9.23 起这一条由上面「每回合限 N 次」那一格接手——填了 N 就按 N 次数、不再是"有没有"）＋ 限定技与觉醒技"一局一次"的同一本账（v2.8.32 起／v2.9.3 起）＋「强制发动」这一格（v2.8.25 起，只管问不问人；v2.9.3 起它对觉醒技同样管用——勾了就不问、到点自己结算；v2.9.17 起连「回合结束时」那扇窗也吃它——勾了的由系统替玩家发动，不进窗）。「在场即生效」那一型不看上面这些，它只在登场／离场两刻动账本。徽章的读写口径全库只有一份，在 domain/skillTags.ts。</t>
   </si>
   <si>
     <t>游戏结束 / 对局结束</t>
@@ -1252,6 +1258,36 @@
   </si>
   <si>
     <t>同一个包导入第二遍会出现这句。意思是这台机器上已有一模一样的这张，不会长出两张同名卡，也不算失败。</t>
+  </si>
+  <si>
+    <t>① 将领身份 / ② 技能编辑（将领编辑器，v2.9.21 起）</t>
+  </si>
+  <si>
+    <t>编辑器现在分两步走：第①步只谈这个人（名称／身份／势力／体力／近战／远程六格），第②步才谈他的技能。上面那两个就是步骤条，点哪个看哪一步。</t>
+  </si>
+  <si>
+    <t>✔ 确认将领，进入技能编辑</t>
+  </si>
+  <si>
+    <t>第①步底下那颗蓝色按钮。它不保存——只是把屏幕挪到第②步；你在第①步打的字还没进存档，要落档仍然只有第②步底下那颗「💾 保存修改」。想回头改本人，按「← 回到将领身份」，刚才打的字还在（两步改的是同一份，不是两套）。</t>
+  </si>
+  <si>
+    <t>🪄 一句话生成（下一刀）</t>
+  </si>
+  <si>
+    <t>「说一句话就把这个人建出来」那一格的位置，今天灰着按不动、什么也不会发生。功能在下一刀接。</t>
+  </si>
+  <si>
+    <t>缺少必要数据：没有填势力／势力「X」不认识／没有将领名称</t>
+  </si>
+  <si>
+    <t>Excel 导入时这张卡缺了不能缺的东西就会出现这句（v2.9.20 的口径：同名又同势力才停下来问你，同名不同势力、或者这本名册里根本没有这个名字，就直接新建）。这句出现＝这张没被写进去，等你补齐再来一遍。</t>
+  </si>
+  <si>
+    <t>新建／修改现有／跳过（导入待处理那三档）</t>
+  </si>
+  <si>
+    <t>导入撞上一张"名字和势力都对得上已有卡"的，会弹一块等你决定：新建＝另开一张同名卡（不动原来的）；修改现有＝把改动盖到那张已有卡上；跳过＝这张不要了。三种都不改引擎，也不背着你自动选。</t>
   </si>
   <si>
     <t>你以为有的词</t>
@@ -3392,7 +3428,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -3499,7 +3535,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>285</v>
       </c>
@@ -3509,11 +3545,8 @@
       <c r="C10" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>287</v>
       </c>
@@ -3521,6 +3554,9 @@
         <v>288</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3832,16 +3868,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="6" t="s">
+    <row r="40" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="B41" s="6"/>
-      <c r="C41" s="6"/>
+      <c r="B40" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A42:C42"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3871,10 +3918,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -3882,10 +3929,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -3893,10 +3940,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -3904,10 +3951,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -3915,10 +3962,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -3926,10 +3973,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -3937,10 +3984,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -3948,10 +3995,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -3959,10 +4006,10 @@
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -3976,7 +4023,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -3997,10 +4044,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -4008,10 +4055,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -4019,10 +4066,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -4030,10 +4077,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -4041,10 +4088,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -4052,10 +4099,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -4063,10 +4110,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -4074,10 +4121,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -4085,10 +4132,10 @@
     </row>
     <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>1</v>
@@ -4096,10 +4143,10 @@
     </row>
     <row r="11" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>1</v>
@@ -4107,10 +4154,10 @@
     </row>
     <row r="12" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>1</v>
@@ -4118,10 +4165,10 @@
     </row>
     <row r="13" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>1</v>
@@ -4129,10 +4176,10 @@
     </row>
     <row r="14" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>1</v>
@@ -4140,10 +4187,10 @@
     </row>
     <row r="15" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>1</v>
@@ -4151,10 +4198,10 @@
     </row>
     <row r="16" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>1</v>
@@ -4162,10 +4209,10 @@
     </row>
     <row r="17" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>1</v>
@@ -4173,10 +4220,10 @@
     </row>
     <row r="18" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>1</v>
@@ -4184,10 +4231,10 @@
     </row>
     <row r="19" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>1</v>
@@ -4195,10 +4242,10 @@
     </row>
     <row r="20" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>1</v>
@@ -4206,10 +4253,10 @@
     </row>
     <row r="21" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>1</v>
@@ -4217,10 +4264,10 @@
     </row>
     <row r="22" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>1</v>
@@ -4228,10 +4275,10 @@
     </row>
     <row r="23" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>1</v>
@@ -4239,12 +4286,67 @@
     </row>
     <row r="24" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4266,10 +4368,10 @@
   <sheetData>
     <row r="1" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>18</v>
@@ -4277,10 +4379,10 @@
     </row>
     <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
@@ -4288,10 +4390,10 @@
     </row>
     <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>1</v>
@@ -4299,10 +4401,10 @@
     </row>
     <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -4310,10 +4412,10 @@
     </row>
     <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>1</v>
@@ -4321,10 +4423,10 @@
     </row>
     <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>1</v>
@@ -4332,10 +4434,10 @@
     </row>
     <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -4343,10 +4445,10 @@
     </row>
     <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>1</v>
@@ -4354,10 +4456,10 @@
     </row>
     <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>1</v>
@@ -4382,206 +4484,206 @@
   <sheetData>
     <row r="1" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>457</v>
+        <v>469</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>462</v>
+        <v>474</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>463</v>
+        <v>475</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>474</v>
+        <v>486</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
     </row>
   </sheetData>

--- a/词汇表.xlsx
+++ b/词汇表.xlsx
@@ -1272,10 +1272,10 @@
     <t>第①步底下那颗蓝色按钮。它不保存——只是把屏幕挪到第②步；你在第①步打的字还没进存档，要落档仍然只有第②步底下那颗「💾 保存修改」。想回头改本人，按「← 回到将领身份」，刚才打的字还在（两步改的是同一份，不是两套）。</t>
   </si>
   <si>
-    <t>🪄 一句话生成（下一刀）</t>
-  </si>
-  <si>
-    <t>「说一句话就把这个人建出来」那一格的位置，今天灰着按不动、什么也不会发生。功能在下一刀接。</t>
+    <t>🪄 一句话生成将领（v2.9.24 起；上一版这一格只是灰着的位置，今天接上了）</t>
+  </si>
+  <si>
+    <t>编辑器里有两处这一格——「➕ 新建将领」那一排，以及第①步「将领身份」那一屏。点开是一句大白话，系统替您把将名／势力／体力／近战／远程／技能名这六样读出来，先把"系统准备怎么落"逐条摊给您看，点「✔ 采用」才动格子或建卡；不点头，什么也不会变。切法＝逗号、顿号、分号隔开，一段一件事；张辽，势力魏，体力4，技能：突袭和骁果、名：赵云，蜀，4点体力，远程2 都读得懂，4点体力「体力4」「血量4」「生命值4」同一个意思（只进不出：写出来的那句永远是「体力：N」）。七句实话：①只有体力能兜底——这句没点体力，新建那一张按 4 建，界面当场写明「体力这句没点、按 4 建」；在第①步编辑屏上没点＝那一格一字不动，不会把您手填的数抹回 4；那个 4 与 Excel 导入读的是同一格判据，全库只有一份；②将名与势力缺了不给缺省、也不停下来问您＝「✔ 采用」那颗按不下去，界面写「缺了：将名／势力」，补进这句话或直接用手填都行；③只写「攻击力3」我不替您挑是近战还是远程，原段退回并说清原因；④技能只记名，效果一律留空——名册这一格不收效果，那句效果请去第②步拼积木（您硬写在后面会被点名退回，不会被悄悄当成没写）；⑤身份与归属这句话定不了：身份：…／归属／来源／白锁 一类出现在句子里也不接，要您自己在那一排里选；⑥同一格写了两回＝后一句不落，并点名"近战写了两回，后一句没落进去"这样的原段——解析器绝不自己选一个；⑦读不懂的一段原文点出来＋一句照着改得动的理由，被当成连接词忽略掉的（一位／一个／名将／新将／请／并且……）也照样回显——没有一段是悄悄丢掉的。采用不等于落档：第①步采用之后仍然只有「💾 保存修改」那一条路才写进存档；新建那一排的采用＝走与手动新建同一条建卡路（编号、身份、来源都由那一条唯一的路定，自制卡就是自制卡，一句话不会造出第二种卡）。这一格没有大模型、不联网，纯离线词表；反解侧＝src/components/skillEditor/generalTextParse.ts，界面＝src/components/skillEditor/GeneralTextPanel.tsx，接线＝src/components/SkillEditor.tsx；"能不能采用"与"体力缺省"各只有一份判据（canAdoptGeneral／generalProvenance.hpOrDefault），这一族用词有没有被人抄第二份由全库白名单钉着（src/components/generalTextSingleSource.test.ts）。</t>
   </si>
   <si>
     <t>缺少必要数据：没有填势力／势力「X」不认识／没有将领名称</t>

--- a/词汇表.xlsx
+++ b/词汇表.xlsx
@@ -669,10 +669,10 @@
     <t>主菜单进联机大厅。开房间＝这台机器算牌，去别人房间＝连房主那台机器的地址。（与上面热座的「创建房间」不是一回事：那是同一台电脑大家轮流按。）</t>
   </si>
   <si>
-    <t>传话程序地址 / 房间码（房主那边显示的那六个字符）</t>
-  </si>
-  <si>
-    <t>先在算牌那台机器上双击 启动传话程序.bat，它会印出可填的地址（自己用 127.0.0.1，别人连你填你那台的 IP）。同一屋里两边填同一个地址＋同一个房间码就能见面；异地经虚拟网或服务器时，只换地址那一行。房间码故意不用 I、O、0、1 这几个容易看混的字符。</t>
+    <t>传话程序地址 / 房间码（房主那边显示的那六个字符）／进场字（房主那边显示的那十二个字符）</t>
+  </si>
+  <si>
+    <t>先在算牌那台机器上双击 启动传话程序.bat，它会印出可填的地址（自己用 127.0.0.1，别人连你填你那台的 IP）。同一屋里两边要填同一个地址＋同一个房间码＋同一串进场字才能见面；异地经虚拟网或服务器时，只换地址那一行。房间码与进场字都故意不用 I、O、0、1 这几个容易看混的字符。进场字是房主点「开房间」那一刻生成的，客人手抄时带上短横、空格或打成小写都算同一个（界面自己会归一），但少一个字符就算不对，会在门外被拒。</t>
   </si>
   <si>
     <t>房主·算牌 / 客人 /（我）</t>
@@ -705,10 +705,10 @@
     <t>大厅页脚第三句（v2.9.11 新增）＝把这一刀到底做了什么说全：房主排座、房主算按钮、客人只交回席位号与编号、房主重算对得上才走、对不上退回并说明、清单封顶 32 步且没列出的条数会写在下面。</t>
   </si>
   <si>
-    <t>这一版不防作弊：清单虽然只指名发给那一席，传话程序只认房间不认人，同桌理论上看得见别人那几行的文字</t>
-  </si>
-  <si>
-    <t>页脚里的如实边界（v2.9.11 新增）。传话程序只按房间转发、不认人，所以同一屋的人理论上嗅得到别人那一行的文字。牌面内容本来就不上线，能嗅到的只是"那几行给人看的短语"。</t>
+    <t>这一版不防作弊：进了门以后线上仍是明文，帧里那句"我是谁"仍由发的人自己写，房主那台机器想看谁的手牌就能看</t>
+  </si>
+  <si>
+    <t>页脚里的如实边界（v2.9.11 立，v2.9.25 随⑤改述，v2.9.27 随⑦第一档再改述）。⚠️ 就地更正：这一行原来写的是"传话程序只认房间不认人，同桌理论上看得见别人那几行的文字"——那句从 v2.9.25（切片⑥）起已经不成立，留着＝词汇表在教一件界面早就不做的事。现在的实话是两条：⑥＝写了收件人的帧只交给绑着那个身份号的那条连接、查不到收件人整帧丢掉，没写收件人的照旧全房（观战那条路留着）；⑦第一档＝进门要多一串进场字，只打听到房间码的人连握手都过不了。这两条都不改变"线上明文＋身份号自报＋牌由房主那台机器算"，所以「这一版不防作弊」这句仍然在场，页脚也仍然明写跑传话程序的机器、偷听这条线的人、房主自己那台机器照样看得见别人那一席的字与牌面。</t>
   </si>
   <si>
     <t>牌由房主那台机器算，传话程序只转发。现在做到"连得上、版本对得上、看得见谁在场，客人能看见房主那一局的牌桌、还能点自己那一席（按钮由房主算好发过来），全桌共用一张公开连线表"。</t>

--- a/词汇表.xlsx
+++ b/词汇表.xlsx
@@ -846,7 +846,7 @@
     <t>每回合限 N 次（编辑器与 Excel 的「每回合限几次」）</t>
   </si>
   <si>
-    <t>一条技能在一名玩家的一个回合里最多能发动几次（填正整数：1、2、3…；这一格留空＝不限制，跟以前一模一样）。v2.9.23 起这一格真的管事了，六个问题按您 2026-10-28 的五句裁决逐条落成对局里的行为：① 谁的回合算一个"次"的窗口＝每一名玩家的回合各算一格自己的窗（在别人的回合里能不能发动，从来由「触发时机」＋「我听谁」那两格说了算，这一格不管这件事）；② 什么时候把次数还回来＝这一回合完全结束时——收尾事项全跑完、下一位玩家回合开始那一刻自动归零；旧的那笔账不删，只是换到新格里不再被数到（所以录像与日志翻得回去）；③ N 怎么读＝汉字与阿拉伯数字都认（「一」「两」「三」＝1、2、3），读不出的那一串逐段退回点名问您——系统既不猜数、也不偷偷当成 1、更不偷偷当成没限制；④ 扣在哪一刻＝付了代价、发动了就扣，即使效果后来被改变或者被无效（与限定技同一口径）；而"发动了却一个效果都产不出"这种空发根本不许发动（牌堆空会先洗牌补齐再摸，真处理不了就不让这条技能进候选）；⑤ 用完以后界面怎么说＝这枚技能在候选里照常列出、写明「本回合已用尽」（放行可以、看不见不行）。三句边界实话：它跟限定技是两本账，同一枚技能挂着两个限额时按各自更紧的那一条走，两本同时见底先说「本局已用尽」；同一回合连发几次要占几格由这一格定的数说了算（限 2 就落两笔账），而一次发动只落一笔——这一笔同时给两本账各留一个记号（"一局一次"那本看有没有、"每回合 N 次"那本数几笔），不会一次把两本各扣一遍。卡面上生成出来的那句只有一种写法（「每回合限N次」），读的时候认多种写法（只进不出）。判据全库只有一份＝data/generals.ts::isValidTurnLimit，两本账只有一份＝skills/skillQuota.ts，界面那一格＝components/skillEditor/TurnLimitEditor.tsx，Excel 那一列叫「每回合限几次」。这一格也由您自己填：到今天官方 96 将与您手上的样本卡一条都没填，所以固定种子 300 局的两池回归读数一字未动（成因不是"这一刀没碰结算"，而是没填数时这条新分支一次也不会被走到）。裁决原文与判据＝PROJECT_HANDOFF.md §12。</t>
+    <t>一条技能在一名玩家的一个回合里最多能发动几次（填正整数：1、2、3…；这一格留空＝不限制，跟以前一模一样）。v2.9.23 起这一格真的管事了，六个问题按您 2026-10-28 的五句裁决逐条落成对局里的行为：① 谁的回合算一个"次"的窗口＝每一名玩家的回合各算一格自己的窗（在别人的回合里能不能发动，从来由「触发时机」＋「我听谁」那两格说了算，这一格不管这件事）；② 什么时候把次数还回来＝这一回合完全结束时——收尾事项全跑完、下一位玩家回合开始那一刻自动归零；旧的那笔账不删，只是换到新格里不再被数到（所以录像与日志翻得回去）；③ N 怎么读＝汉字与阿拉伯数字都认（「一」「两」「三」＝1、2、3），读不出的那一串逐段退回点名问您——系统既不猜数、也不偷偷当成 1、更不偷偷当成没限制；④ 扣在哪一刻＝付了代价、发动了就扣，即使效果后来被改变或者被无效（与限定技同一口径）；而"发动了却一个效果都产不出"这种空发根本不许发动（牌堆空会先洗牌补齐再摸，真处理不了就不让这条技能进候选）；⑤ 用完以后界面怎么说＝这枚技能在候选里照常列出、写明「本回合已用尽」（放行可以、看不见不行）。三句边界实话：它跟限定技是两本账，同一枚技能挂着两个限额时按各自更紧的那一条走，两本同时见底先说「本局已用尽」；同一回合连发几次要占几格由这一格定的数说了算（限 2 就落两笔账），而一次发动只落一笔——这一笔同时给两本账各留一个记号（"一局一次"那本看有没有、"每回合 N 次"那本数几笔），不会一次把两本各扣一遍。卡面上生成出来的那句只有一种写法（「每回合限N次」），读的时候认多种写法（只进不出）。判据全库只有一份＝data/generals.ts::isValidTurnLimit，两本账只有一份＝skills/skillQuota.ts，界面那一格＝components/skillEditor/TurnLimitEditor.tsx，Excel 那一列叫「每回合限几次」。这一格也由您自己填：到今天名册全部 335 张（您手写的 96 张＋v2.9.28 从转换表带进来的 239 张）与您手上的样本卡一条都没填，所以固定种子 300 局的两池回归读数一字未动（成因不是"这一刀没碰结算"，而是没填数时这条新分支一次也不会被走到）。裁决原文与判据＝PROJECT_HANDOFF.md §12。</t>
   </si>
   <si>
     <t>登场技</t>
@@ -870,13 +870,13 @@
     <t>觉醒技</t>
   </si>
   <si>
-    <t>分类徽章（您 2026-10-04 给的口径原文存档："一般是满足一定条件后可以自选发动，从而获得新技能或者改变已有技能的效果，非强制发动"）。v2.9.3 起这一格真的管事了，翻译成对局里该发生的事＝条件满足了在达成那一刻当场问您一次（您 2026-10-08 裁的：不当场问、拖到回合结束不算），问的是"觉醒／不觉醒"；点头才结算这枚技能写的那一句（拿到新技能，或者让账面数字变），摇头不扣额度、以后还有机会。一局只觉醒一次，这一笔账跟限定技走同一本（您 2026-10-08 裁："觉醒技和限定技同理，在同一局中发动过一次就不能再发动"），用尽后不再问。边界四句实话：①它不是到点自己响、也不是被动一直算数；②勾了「强制发动」的觉醒技例外——到点自己结算、不停下来问，但额度那一半照扣；③觉醒技挂不得"在场即生效"和"多选一"这两种形状，硬挂会在导入总结里点名退回，不会静悄悄当没事；④问句挂着的时候全场冻结，只有被问的那一席能答（答或者跳过），跟响应链那一格同一套规矩。v2.9.6 起这一枚第一次挂上了官方将＝魏关羽的「单骑」（名册 96 将里当场量过，用这一枚的只有这一条，有测试钉着这个数）。裁决原文与判据＝PROJECT_HANDOFF.md §12。</t>
+    <t>分类徽章（您 2026-10-04 给的口径原文存档："一般是满足一定条件后可以自选发动，从而获得新技能或者改变已有技能的效果，非强制发动"）。v2.9.3 起这一格真的管事了，翻译成对局里该发生的事＝条件满足了在达成那一刻当场问您一次（您 2026-10-08 裁的：不当场问、拖到回合结束不算），问的是"觉醒／不觉醒"；点头才结算这枚技能写的那一句（拿到新技能，或者让账面数字变），摇头不扣额度、以后还有机会。一局只觉醒一次，这一笔账跟限定技走同一本（您 2026-10-08 裁："觉醒技和限定技同理，在同一局中发动过一次就不能再发动"），用尽后不再问。边界四句实话：①它不是到点自己响、也不是被动一直算数；②勾了「强制发动」的觉醒技例外——到点自己结算、不停下来问，但额度那一半照扣；③觉醒技挂不得"在场即生效"和"多选一"这两种形状，硬挂会在导入总结里点名退回，不会静悄悄当没事；④问句挂着的时候全场冻结，只有被问的那一席能答（答或者跳过），跟响应链那一格同一套规矩。v2.9.6 起这一枚第一次挂上了官方将＝魏关羽的「单骑」。（v2.9.28 起名册 335 张里当场量过：挂这枚徽章的一共 3 条＝「单骑」＋转换表带进来的毋丘俭「鸿举」、诸葛诞「举义」；后两条只有卡面文字、没有能结算的内容⇒真会在达成那一刻停下来问您的仍然只有单骑这一条。335／3／1 三个数都有测试钉着。）裁决原文与判据＝PROJECT_HANDOFF.md §12。</t>
   </si>
   <si>
     <t>强制发动</t>
   </si>
   <si>
-    <t>编辑器里的开关（Excel 也有这一列）：满足触发条件与代价后直接响／直接适用效果，不用玩家点头。它跟锁定技不是一件事，跟"数值变化／持续生效"也不绑定，三者可以任意组合。v2.8.25 起这一格真的管事了，v2.9.16 起它管的是全部时机（您 2026-10-20 裁："在场即生效和强制发动不问"）：勾上之后，凡是本来会停下来问您"要不要发动"的那一刻，这条技能不再问、自己就响了；不勾就照旧问——而且今天每一型都会问。五句实话边界：①它只决定"问不问人"，不会让一条技能多响一次，也不绕过发动门槛与代价；②本来就到点自动响的时机（登场／回合开始／击杀／失去手牌……）勾不勾都一样（旧说法，已作废）（这句自 v2.9.16 作废：这些时机今天照样停下来问您，勾了才自己响；「在场即生效」那一型是唯一一个根本不存在"响"这一刻的，它不吃这一格，也不会有人来问）；③「回合结束时」那一型自 v2.9.17 起也吃这一格（您 2026-10-21 裁："强制发动永远是强制发动，无论什么节点，但是一定要通知玩家有什么技能发动了"）：勾了的不进那扇问话窗——点「⏭️结束回合」那一刻由系统在同一条规范动作里替这一席发动完，再开窗问剩下的；一员都没勾就压根不开窗。旧的"勾了也照样问"（v2.3.1 起那一版逢人就问）自本版作废，因为它跟您那句正面相撞；这条裁决有真机对照＝同一张牌桌、同一个位置，两员只差这一格勾没勾，勾了的没开窗、没勾的照旧开窗；④决斗那一套的"开局被点名"与"收官掉血"两刻同样吃这一格——勾了就自己响、没勾就问；⑤v2.8.31 起它与"不勾"完全同一条时机判据（您 2026-10-04 定稿：强制发动和手动发动的处理必须一致，区别只在"需不需要玩家自行响应"）——被这一刀砍死时，勾了的「成为目标时」照样响、勾了的「受到伤害后」照样不响，与没勾时问您那一型逐字同形（只有「自身被击杀时」那一型放行）。这一刀改了您对局里看到的东西：今天的官方 96 将与您手上的样本卡还没有一条勾了这个开关（v2.9.6 新上的「单骑」也没勾——它停下来问您靠的是上面「觉醒技」那一枚，不是这一格），所以从这一版起，只要桌上有人挂着会响的技能，那一刻就会停下来问他；哪一枚您想让它到点自己响，就去把那一枚的这格勾上。v2.9.17 两条配套硬义务（您同日的两句）：①这一格由您自己勾＝"哪些官方卡是强制发动，这部分由我自己来填写"⇒官方 96 将与您手上的样本卡到今天仍然一枚都没勾，我不往任何卡面上加这一格；②不问可以、看不见不行＝凡是真发动了（包括系统替您发动那一路），界面左上角当场飘一条 ⚡ 小广播，写清是谁的哪一枚、干了什么。</t>
+    <t>编辑器里的开关（Excel 也有这一列）：满足触发条件与代价后直接响／直接适用效果，不用玩家点头。它跟锁定技不是一件事，跟"数值变化／持续生效"也不绑定，三者可以任意组合。v2.8.25 起这一格真的管事了，v2.9.16 起它管的是全部时机（您 2026-10-20 裁："在场即生效和强制发动不问"）：勾上之后，凡是本来会停下来问您"要不要发动"的那一刻，这条技能不再问、自己就响了；不勾就照旧问——而且今天每一型都会问。五句实话边界：①它只决定"问不问人"，不会让一条技能多响一次，也不绕过发动门槛与代价；②本来就到点自动响的时机（登场／回合开始／击杀／失去手牌……）勾不勾都一样（旧说法，已作废）（这句自 v2.9.16 作废：这些时机今天照样停下来问您，勾了才自己响；「在场即生效」那一型是唯一一个根本不存在"响"这一刻的，它不吃这一格，也不会有人来问）；③「回合结束时」那一型自 v2.9.17 起也吃这一格（您 2026-10-21 裁："强制发动永远是强制发动，无论什么节点，但是一定要通知玩家有什么技能发动了"）：勾了的不进那扇问话窗——点「⏭️结束回合」那一刻由系统在同一条规范动作里替这一席发动完，再开窗问剩下的；一员都没勾就压根不开窗。旧的"勾了也照样问"（v2.3.1 起那一版逢人就问）自本版作废，因为它跟您那句正面相撞；这条裁决有真机对照＝同一张牌桌、同一个位置，两员只差这一格勾没勾，勾了的没开窗、没勾的照旧开窗；④决斗那一套的"开局被点名"与"收官掉血"两刻同样吃这一格——勾了就自己响、没勾就问；⑤v2.8.31 起它与"不勾"完全同一条时机判据（您 2026-10-04 定稿：强制发动和手动发动的处理必须一致，区别只在"需不需要玩家自行响应"）——被这一刀砍死时，勾了的「成为目标时」照样响、勾了的「受到伤害后」照样不响，与没勾时问您那一型逐字同形（只有「自身被击杀时」那一型放行）。这一刀改了您对局里看到的东西：今天名册全部 335 张与您手上的样本卡还没有一条勾了这个开关（v2.9.6 新上的「单骑」也没勾——它停下来问您靠的是上面「觉醒技」那一枚，不是这一格），所以从这一版起，只要桌上有人挂着会响的技能，那一刻就会停下来问他；哪一枚您想让它到点自己响，就去把那一枚的这格勾上。v2.9.17 两条配套硬义务（您同日的两句）：①这一格由您自己勾＝"哪些官方卡是强制发动，这部分由我自己来填写"⇒名册全部 335 张与您手上的样本卡到今天仍然一枚都没勾，我不往任何卡面上加这一格（v2.9.28 带进来的那 239 张也一样没勾——转换器连表里第 8 列「强制发动」都不读，那一列今天全是「否」）；②不问可以、看不见不行＝凡是真发动了（包括系统替您发动那一路），界面左上角当场飘一条 ⚡ 小广播，写清是谁的哪一枚、干了什么。</t>
   </si>
   <si>
     <t>触发时机</t>
@@ -894,7 +894,7 @@
     <t>在场即生效（不用发动，人在就算）（v2.8 刀4 起可结算）</t>
   </si>
   <si>
-    <t>跟上面那一串并列的另一格，但它根本不是"哪一刻响"——它是"没有哪一刻需要它响"。这一型编译出来不监听任何事件、不进问答窗、不吃「强制发动」那一格：将领登场那一刻落一笔账（配合下面的「修改数值」用），离场当场销账，人在的整段时间都算数。三句实话：①旧名字「全局生效（在场时持续）」容易读成"影响全场所有人"，v2.8 刀4 起改叫这个名，旧 Excel 里那一格照样读得懂、再导出会写新名；②这一型不许配门槛、不许配有效周期、不许配「选择其一」（门槛要"情况一变就改口"、周期要"发动笔"那一档、择一要有人点头——三样都没有落点），填了会在编译时逐条点名跳过，不会悄悄变成"全都要"；③v2.9.6 起这一型第一次挂上了官方将＝魏、蜀两张关羽卡上共用的「武圣」（出牌时把远程攻击力往上顶 1，人在就算、离场当场销账）；技能表上那一枚「怒斩」也是这一型（它不印在任何将卡上）。96 将里用这一型的就这一条（当场量过，有测试钉着）。</t>
+    <t>跟上面那一串并列的另一格，但它根本不是"哪一刻响"——它是"没有哪一刻需要它响"。这一型编译出来不监听任何事件、不进问答窗、不吃「强制发动」那一格：将领登场那一刻落一笔账（配合下面的「修改数值」用），离场当场销账，人在的整段时间都算数。三句实话：①旧名字「全局生效（在场时持续）」容易读成"影响全场所有人"，v2.8 刀4 起改叫这个名，旧 Excel 里那一格照样读得懂、再导出会写新名；②这一型不许配门槛、不许配有效周期、不许配「选择其一」（门槛要"情况一变就改口"、周期要"发动笔"那一档、择一要有人点头——三样都没有落点），填了会在编译时逐条点名跳过，不会悄悄变成"全都要"；③v2.9.6 起这一型第一次挂上了官方将＝魏、蜀两张关羽卡上共用的「武圣」（出牌时把远程攻击力往上顶 1，人在就算、离场当场销账）；技能表上那一枚「怒斩」也是这一型（它不印在任何将卡上）。96 张（您手写的）里用这一型的就这一条；v2.9.28 从转换表带进来的 239 张一条真内容都不带，这个数不会因为它们变大（当场量过，有测试钉着）。</t>
   </si>
   <si>
     <t>攻击伤害 / 技能伤害</t>
@@ -996,7 +996,7 @@
     <t>效果模式：全部生效 / 选择其一 / 链式若-则</t>
   </si>
   <si>
-    <t>一个技能里多条效果是"全都要"还是"只能挑一条"。对局里挑那条时会弹"抉择"窗。第三档「链式若-则」（v2.8.34 起能结算，词汇表这一格当时漏写了，v2.9.6 补上）＝一条条按顺序走，前一条真的结算成了才走到下一条；中途哪一条没成，后面整段都不补。Excel 那一格就认这三个词，别的写法按没填处理（＝全部生效）。v2.9.6 修掉的一处真缺陷：这一格挂「链式若-则」的技能导出时被写成"无"、再导回来就变成"全部生效"＝来回一趟档位丢了；现在导出/导入都走同一份词表。名册 96 将里用这一档的只有魏关羽的「单骑」。</t>
+    <t>一个技能里多条效果是"全都要"还是"只能挑一条"。对局里挑那条时会弹"抉择"窗。第三档「链式若-则」（v2.8.34 起能结算，词汇表这一格当时漏写了，v2.9.6 补上）＝一条条按顺序走，前一条真的结算成了才走到下一条；中途哪一条没成，后面整段都不补。Excel 那一格就认这三个词，别的写法按没填处理（＝全部生效）。v2.9.6 修掉的一处真缺陷：这一格挂「链式若-则」的技能导出时被写成"无"、再导回来就变成"全部生效"＝来回一趟档位丢了；现在导出/导入都走同一份词表。96 张（您手写的）里用这一档的只有魏关羽的「单骑」；v2.9.28 带进来的 239 张一条真内容都不带⇒这个数没挪动。</t>
   </si>
   <si>
     <t>技能门槛 / 效果N门槛</t>
@@ -1008,7 +1008,7 @@
     <t>修改数值（效果类型，v2.8 刀4 起可结算）</t>
   </si>
   <si>
-    <t>第十一条效果类型。它不改卡面上的印刷数字，而是给这名将领记一笔"账"（引擎里那本账叫 state.statModifiers，随存档走、录像能重放）。所以同一张卡在棋盘上会同时存在两个数：卡上印的（永远不变，图鉴与手抄核对用它）和当下算数的（对局里真正用来砍人的）。今天有六个数能被这样改：近战攻击力／远程攻击力／体力上限（v2.8 刀4）＋受到的伤害（v2.8 刀5）＋射程（v2.9.0）＋造成的伤害（v2.9.4）。五句实话：①当前体力不走这本账（它本来就是"损失记录"那一本，回血、扣血照旧直接动它）；②护甲、手牌上限这一版还没接（写了会被点名跳过）；③只能改自己的账面数字——"让别人的攻击＋1"那种跨将改数还没有目标选择器，编译时逐条点名跳过；④「受到的伤害」与「造成的伤害」这两格都作用在护甲之前，次序是攻击力 → 造成伤害 → 受到伤害 → 护甲抵扣 → 扣血（您 2026-10-14 裁「扣护甲前算」）：先把伤害这个数摁好，再交给"2 点护甲挡 1 点"那套算术，所以它们是"看不见的加减伤"，不是第二层护甲，也不改变身上有没有护甲这件事；营地（老家）这两格都不吃——规则上营地单次受到的伤害最多 1 点，那一条由攻击那一步钉死，不是账本管的事；⑤v2.9.6 起这一档第一次挂上了官方将：「武圣」用它把远程攻击力往上顶 1（就是六把钥匙里第一号那类"攻击力"，不是下面 ⑥ 那把射程）、「单骑」用它把体力上限摁低 1（上面 ① 说的"上限另有一本账"就是走这一格）；技能表里的「怒斩」用它的造成的伤害那一格（还带了"只在决斗里算／只在近战砍有护甲的人时算"那两种限定）。名册 96 将里用到这一档的就这两条（当场量过，有测试钉着）。⑥「射程」这一把有两条自己的规矩（v2.9.0）：(a) 只往外推，不把近处一并放开——加 1 就是从自家营地多够得着对面前线，不会因此够得着自家前线；(b) 近战那一档永远吃不到它，近战只看"挨不挨着"，所以给一员将加射程，它的近战名单一格都不会变多。另外摁成 1 或 0 是合法的＝远程名单直接空掉（"这员将只能近战"），不是回退到默认值。⑦「造成的伤害」这一把自己的一条规矩（v2.9.4）：这一格是记在打出去的那一员将身上的，改的是"我这一刀砍出去几"，不是"对面挨几"——两格同时在场时先加后减，再由"固定压过增减"那一条判输赢（受方那一格恒盖造方）。决斗里它是每一轮各算一次（您 2026-10-14 裁），不是整场只算一次。这一格还能再限定"只在某种场合才算数"（近战攻击有护甲的角色／正在打决斗），但那一档界面与 Excel 里都还没有对应的格子，今天只有仓库里写好的技能定义带得进来，您能填的仍是"什么时候都算"。</t>
+    <t>第十一条效果类型。它不改卡面上的印刷数字，而是给这名将领记一笔"账"（引擎里那本账叫 state.statModifiers，随存档走、录像能重放）。所以同一张卡在棋盘上会同时存在两个数：卡上印的（永远不变，图鉴与手抄核对用它）和当下算数的（对局里真正用来砍人的）。今天有六个数能被这样改：近战攻击力／远程攻击力／体力上限（v2.8 刀4）＋受到的伤害（v2.8 刀5）＋射程（v2.9.0）＋造成的伤害（v2.9.4）。五句实话：①当前体力不走这本账（它本来就是"损失记录"那一本，回血、扣血照旧直接动它）；②护甲、手牌上限这一版还没接（写了会被点名跳过）；③只能改自己的账面数字——"让别人的攻击＋1"那种跨将改数还没有目标选择器，编译时逐条点名跳过；④「受到的伤害」与「造成的伤害」这两格都作用在护甲之前，次序是攻击力 → 造成伤害 → 受到伤害 → 护甲抵扣 → 扣血（您 2026-10-14 裁「扣护甲前算」）：先把伤害这个数摁好，再交给"2 点护甲挡 1 点"那套算术，所以它们是"看不见的加减伤"，不是第二层护甲，也不改变身上有没有护甲这件事；营地（老家）这两格都不吃——规则上营地单次受到的伤害最多 1 点，那一条由攻击那一步钉死，不是账本管的事；⑤v2.9.6 起这一档第一次挂上了官方将：「武圣」用它把远程攻击力往上顶 1（就是六把钥匙里第一号那类"攻击力"，不是下面 ⑥ 那把射程）、「单骑」用它把体力上限摁低 1（上面 ① 说的"上限另有一本账"就是走这一格）；技能表里的「怒斩」用它的造成的伤害那一格（还带了"只在决斗里算／只在近战砍有护甲的人时算"那两种限定）。96 张（您手写的）里用到这一档的就这两条；v2.9.28 带进来的 239 张一条真内容都不带⇒这个数没挪动（当场量过，有测试钉着）。⑥「射程」这一把有两条自己的规矩（v2.9.0）：(a) 只往外推，不把近处一并放开——加 1 就是从自家营地多够得着对面前线，不会因此够得着自家前线；(b) 近战那一档永远吃不到它，近战只看"挨不挨着"，所以给一员将加射程，它的近战名单一格都不会变多。另外摁成 1 或 0 是合法的＝远程名单直接空掉（"这员将只能近战"），不是回退到默认值。⑦「造成的伤害」这一把自己的一条规矩（v2.9.4）：这一格是记在打出去的那一员将身上的，改的是"我这一刀砍出去几"，不是"对面挨几"——两格同时在场时先加后减，再由"固定压过增减"那一条判输赢（受方那一格恒盖造方）。决斗里它是每一轮各算一次（您 2026-10-14 裁），不是整场只算一次。这一格还能再限定"只在某种场合才算数"（近战攻击有护甲的角色／正在打决斗），但那一档界面与 Excel 里都还没有对应的格子，今天只有仓库里写好的技能定义带得进来，您能填的仍是"什么时候都算"。</t>
   </si>
   <si>
     <t>改哪个数 / 怎么改 / 有效周期（Excel 里效果组第 9–11 列）</t>
@@ -1020,7 +1020,7 @@
     <t>获得技能（效果类型，v2.9.3 刀A 起可结算）</t>
   </si>
   <si>
-    <t>第十二条效果类型，和「修改数值」正好是一正一反：那一档只动账本、卡面一字不改；这一档只动卡面——往这一员将身上添一枚技能（添进他卡面上那份技能清单），不改任何数字、不掉血、不搬牌。五句实话：①认的是名字，您在那一格里写什么，引擎就拿什么去查技能表（v2.9.7 起这一档只认这一本名单＝卡上有真结算内容的技能自动在册＋不印在任何将卡上、写在表里的那几枚；今天这本册子上仓库名册那一份是 41 个名字（当场量过、有测试钉着）；v2.9.18 起这本册子的进料改成"这台机器此刻真在用的那份将领"＝仓库名册＋您的自制卡（都过一遍卡面编辑），所以自制卡上挂上了真内容的技能也照样在册，退出游戏、删掉那张卡它就跟着退册）；②只在卡上印了个名字、还没挂上可结算内容的那一类不在表上（您 2026-10-16 裁「技能表只做有真内容的」）——填了会被点名跳过，而不是让您拿到一枚空的；卡上那枚哪天挂上内容，它自己就进表，这一条跟着生效，不用另改任何名单；③查不到、或者同名却有两份不同内容，都会被导入报告与编译器逐条点名跳过，绝不猜一个"最像的"（v2.9.18 起这一条通了＝您自制卡上那枚挂上了真内容的技能，保存之后下一问就查得到；查得到也照样看得见出处——名字后面那半截写着「官方」还是「玩家自制」，是按这张卡建的时候钉死的那一份来源读的，您 2026-10-21 的口径「开发者模式下新增和改动的就是官方卡」落在这里没有第二套判据）；④只能添在自己身上——"给别的将领添技能"要等目标选择器那把刀；而且从下一次发动起这一员将才听得见这枚新技能（本项目没有卡面技能清单的缓存，每次发动前都从对局现场重算一遍），同一枚拿第二次也只留一份；⑤如果拿到的是一枚在场即生效的技能，那笔账在获得这一刻补落进账本（同一枚不落第二笔），不是等下一次登场。另外v2.9.6 起这一档第一次挂上了官方将＝魏关羽的「单骑」：觉醒那一刻它照这一格去查技能表，把「怒斩」添进这名将身上——「怒斩」不印在任何将卡上，住在表里（src/data/skillTable.ts；v2.9.4 那一版这张表还是空架子，一条真内容都没有，所以当时谁也查不到）。将领名册 96 将里用到这一档的只有这一条（当场量过，有测试钉着）。</t>
+    <t>第十二条效果类型，和「修改数值」正好是一正一反：那一档只动账本、卡面一字不改；这一档只动卡面——往这一员将身上添一枚技能（添进他卡面上那份技能清单），不改任何数字、不掉血、不搬牌。五句实话：①认的是名字，您在那一格里写什么，引擎就拿什么去查技能表（v2.9.7 起这一档只认这一本名单＝卡上有真结算内容的技能自动在册＋不印在任何将卡上、写在表里的那几枚；今天这本册子上仓库名册那一份是 41 个名字（当场量过、有测试钉着）；v2.9.18 起这本册子的进料改成"这台机器此刻真在用的那份将领"＝仓库名册＋您的自制卡（都过一遍卡面编辑），所以自制卡上挂上了真内容的技能也照样在册，退出游戏、删掉那张卡它就跟着退册）；②只在卡上印了个名字、还没挂上可结算内容的那一类不在表上（您 2026-10-16 裁「技能表只做有真内容的」）——填了会被点名跳过，而不是让您拿到一枚空的；卡上那枚哪天挂上内容，它自己就进表，这一条跟着生效，不用另改任何名单；③查不到、或者同名却有两份不同内容，都会被导入报告与编译器逐条点名跳过，绝不猜一个"最像的"（v2.9.18 起这一条通了＝您自制卡上那枚挂上了真内容的技能，保存之后下一问就查得到；查得到也照样看得见出处——名字后面那半截写着「官方」还是「玩家自制」，是按这张卡建的时候钉死的那一份来源读的，您 2026-10-21 的口径「开发者模式下新增和改动的就是官方卡」落在这里没有第二套判据）；④只能添在自己身上——"给别的将领添技能"要等目标选择器那把刀；而且从下一次发动起这一员将才听得见这枚新技能（本项目没有卡面技能清单的缓存，每次发动前都从对局现场重算一遍），同一枚拿第二次也只留一份；⑤如果拿到的是一枚在场即生效的技能，那笔账在获得这一刻补落进账本（同一枚不落第二笔），不是等下一次登场。另外v2.9.6 起这一档第一次挂上了官方将＝魏关羽的「单骑」：觉醒那一刻它照这一格去查技能表，把「怒斩」添进这名将身上——「怒斩」不印在任何将卡上，住在表里（src/data/skillTable.ts；v2.9.4 那一版这张表还是空架子，一条真内容都没有，所以当时谁也查不到）。96 张（您手写的）里用到这一档的只有这一条；v2.9.28 带进来的 239 张一条真内容都不带⇒这个数没挪动（当场量过，有测试钉着）。</t>
   </si>
   <si>
     <t>获得哪个技能（Excel 里效果组第 12 列）</t>
